--- a/factor_master.xlsx
+++ b/factor_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29911"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrai\Source\risk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C24323-A31A-4C54-B93E-7CDA9B3C5D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEB79B3-8A1F-4750-9F6C-F78A727D4C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="10" xr2:uid="{C31FDC5B-A809-4BFD-99CB-DA02246721F7}"/>
   </bookViews>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2554" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2549" uniqueCount="724">
   <si>
     <t>SPX</t>
   </si>
@@ -2360,111 +2360,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </top>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="39">
     <dxf>
       <border>
         <top style="thin">
@@ -2631,12 +2527,44 @@
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="Table Style 1" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="3" xr9:uid="{26B58CFA-74FB-41FD-AB02-EC6D3EA4F4A1}">
-      <tableStyleElement type="wholeTable" dxfId="5"/>
-      <tableStyleElement type="headerRow" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" size="3" dxfId="3"/>
+      <tableStyleElement type="wholeTable" dxfId="38"/>
+      <tableStyleElement type="headerRow" dxfId="37"/>
+      <tableStyleElement type="firstRowStripe" size="3" dxfId="36"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2735,58 +2663,58 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6DAD1482-C63D-400D-9F51-F22A8E35CAD8}" name="data" displayName="data" ref="A1:T107" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6DAD1482-C63D-400D-9F51-F22A8E35CAD8}" name="data" displayName="data" ref="A1:T106" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{740DC173-AAC9-4239-A44E-C43F8517304D}" name="asset_class" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{A3BC3BB8-0420-458E-AECD-FD567519FA40}" name="region" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{0E50B2E3-0362-41DB-ACC2-478CC6F618A4}" name="factor_name" dataDxfId="42"/>
-    <tableColumn id="11" xr3:uid="{C400A641-F032-4829-A2CD-62831D657B37}" name="source" dataDxfId="41"/>
-    <tableColumn id="12" xr3:uid="{BC682952-ADA8-4869-A16F-B9E7BC86E430}" name="diffusion_type" dataDxfId="40"/>
-    <tableColumn id="16" xr3:uid="{A99CC35E-FB67-451C-BF9C-DA8D933B1B0C}" name="multiplier" dataDxfId="39">
+    <tableColumn id="1" xr3:uid="{740DC173-AAC9-4239-A44E-C43F8517304D}" name="asset_class" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{A3BC3BB8-0420-458E-AECD-FD567519FA40}" name="region" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{0E50B2E3-0362-41DB-ACC2-478CC6F618A4}" name="factor_name" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{C400A641-F032-4829-A2CD-62831D657B37}" name="source" dataDxfId="30"/>
+    <tableColumn id="12" xr3:uid="{BC682952-ADA8-4869-A16F-B9E7BC86E430}" name="diffusion_type" dataDxfId="29"/>
+    <tableColumn id="16" xr3:uid="{A99CC35E-FB67-451C-BF9C-DA8D933B1B0C}" name="multiplier" dataDxfId="28">
       <calculatedColumnFormula array="1">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{02943B27-7FCB-4450-B8E0-CF0DB6CF5CCA}" name="factor_name_new" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{D181BF84-863F-4FD0-B518-14EA5B0FB18E}" name="description_override" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{1C40DF9B-2910-4DE6-A188-563938E39797}" name="Description_GPT" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{1806E074-6CB5-47AB-8FA3-EF0F6E429062}" name="Underlying" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{21539C17-C1CC-4FA9-A0E1-A2F8FF8AB52C}" name="Active" dataDxfId="34"/>
-    <tableColumn id="37" xr3:uid="{DE50B7AE-5F67-471C-BE48-8BFA5076EDB0}" name="hyper_factor" dataDxfId="33"/>
-    <tableColumn id="10" xr3:uid="{494805E4-EBB6-47FD-9BC2-8DAD9FB9D3FA}" name="composite" dataDxfId="32"/>
-    <tableColumn id="14" xr3:uid="{608FE572-4016-436E-8625-08926F3A2371}" name="client" dataDxfId="31"/>
-    <tableColumn id="13" xr3:uid="{64EF0381-B0C5-4226-B34E-0F9752A4A840}" name="ticker" dataDxfId="30">
+    <tableColumn id="8" xr3:uid="{02943B27-7FCB-4450-B8E0-CF0DB6CF5CCA}" name="factor_name_new" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{D181BF84-863F-4FD0-B518-14EA5B0FB18E}" name="description_override" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{1C40DF9B-2910-4DE6-A188-563938E39797}" name="Description_GPT" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{1806E074-6CB5-47AB-8FA3-EF0F6E429062}" name="Underlying" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{21539C17-C1CC-4FA9-A0E1-A2F8FF8AB52C}" name="Active" dataDxfId="23"/>
+    <tableColumn id="37" xr3:uid="{DE50B7AE-5F67-471C-BE48-8BFA5076EDB0}" name="hyper_factor" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{494805E4-EBB6-47FD-9BC2-8DAD9FB9D3FA}" name="composite" dataDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{608FE572-4016-436E-8625-08926F3A2371}" name="client" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{64EF0381-B0C5-4226-B34E-0F9752A4A840}" name="ticker" dataDxfId="19">
       <calculatedColumnFormula>data[[#This Row],[factor_name]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5A601067-D384-419C-A711-AD3034F77E28}" name="description" dataDxfId="29">
+    <tableColumn id="9" xr3:uid="{5A601067-D384-419C-A711-AD3034F77E28}" name="description" dataDxfId="18">
       <calculatedColumnFormula array="1">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{073BDADC-3AC0-4FF9-9654-A316B2345A90}" name="short_name_yf" dataDxfId="28">
+    <tableColumn id="18" xr3:uid="{073BDADC-3AC0-4FF9-9654-A316B2345A90}" name="short_name_yf" dataDxfId="17">
       <calculatedColumnFormula>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{3A563104-B6B0-465C-9D22-154F5FEA1B83}" name="long_name_yf" dataDxfId="27">
+    <tableColumn id="19" xr3:uid="{3A563104-B6B0-465C-9D22-154F5FEA1B83}" name="long_name_yf" dataDxfId="16">
       <calculatedColumnFormula>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{A3F200A1-E769-49BA-8121-88EAA1180E80}" name="summary_yf" dataDxfId="26">
+    <tableColumn id="17" xr3:uid="{A3F200A1-E769-49BA-8121-88EAA1180E80}" name="summary_yf" dataDxfId="15">
       <calculatedColumnFormula>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{D49341AB-DA48-473E-8CCB-3A3D04AED743}" name="note" dataDxfId="25"/>
+    <tableColumn id="15" xr3:uid="{D49341AB-DA48-473E-8CCB-3A3D04AED743}" name="note" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F918301C-859F-40B7-9C3E-90E8F0495E68}" name="data_old" displayName="data_old" ref="A1:I45" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F918301C-859F-40B7-9C3E-90E8F0495E68}" name="data_old" displayName="data_old" ref="A1:I45" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="A1:I45" xr:uid="{6DAD1482-C63D-400D-9F51-F22A8E35CAD8}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{B19D2B17-9AC9-4F1B-B32E-D4F72AAE469F}" name="asset_class" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{2C7CF29D-8E72-4B0C-A212-31F2A25D75C9}" name="region" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{C7E89EEC-2B5D-4C94-9327-1AC8E33DE708}" name="factor_name" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{B3F9004A-8BEB-463E-A746-8189A2AC2B3E}" name="factor_name_new" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{51CD7FB3-58FE-4906-B73C-7726C0A9C471}" name="description_override" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{3CFF990B-3164-4533-821F-08CE7C6D82CA}" name="Description_GPT" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{DD86D53E-A9B4-4387-ABF9-F2625E77982D}" name="Underlying" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{D56FFF9A-72FF-42A4-B3D2-2F27AB16AF7A}" name="Active" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{8476DFDE-B4B1-4FD9-99B4-DF1F2ABBD7D5}" name="description" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{B19D2B17-9AC9-4F1B-B32E-D4F72AAE469F}" name="asset_class" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{2C7CF29D-8E72-4B0C-A212-31F2A25D75C9}" name="region" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{C7E89EEC-2B5D-4C94-9327-1AC8E33DE708}" name="factor_name" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{B3F9004A-8BEB-463E-A746-8189A2AC2B3E}" name="factor_name_new" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{51CD7FB3-58FE-4906-B73C-7726C0A9C471}" name="description_override" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{3CFF990B-3164-4533-821F-08CE7C6D82CA}" name="Description_GPT" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{DD86D53E-A9B4-4387-ABF9-F2625E77982D}" name="Underlying" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{D56FFF9A-72FF-42A4-B3D2-2F27AB16AF7A}" name="Active" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{8476DFDE-B4B1-4FD9-99B4-DF1F2ABBD7D5}" name="description" dataDxfId="3">
       <calculatedColumnFormula>IF(data_old[[#This Row],[description_override]]="",data_old[[#This Row],[Description_GPT]],data_old[[#This Row],[description_override]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5792,11 +5720,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C29859C-7358-4E2F-B5CC-7696F1DAC449}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:Y107"/>
+  <dimension ref="A1:Y106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="44.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="59.140625" bestFit="1" customWidth="1"/>
@@ -12203,60 +12132,57 @@
     </row>
     <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>444</v>
+        <v>527</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>500</v>
+        <v>528</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>445</v>
+        <v>529</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="F104" s="4" cm="1">
-        <f t="array" ref="F104">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
-        <v>1E-4</v>
+        <v>467</v>
+      </c>
+      <c r="F104" s="4">
+        <v>0.01</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
-      <c r="J104" s="4" t="str" cm="1">
-        <f t="array" ref="J104">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$F$2),_xlfn.ANCHORARRAY(composites!$G$2))</f>
-        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
+      <c r="J104" s="4" t="s">
+        <v>530</v>
       </c>
       <c r="K104" s="4">
         <v>1</v>
       </c>
       <c r="L104" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N104" s="4">
         <v>0</v>
       </c>
-      <c r="O104" s="4" t="str">
-        <f>data[[#This Row],[factor_name]]</f>
-        <v>TRADEWAR</v>
+      <c r="O104" s="11" t="s">
+        <v>531</v>
       </c>
       <c r="P104" s="4" t="str" cm="1">
         <f t="array" ref="P104">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
-      </c>
-      <c r="Q104" s="4" t="str">
+        <v>Economic Policy Uncertainty Index for United States</v>
+      </c>
+      <c r="Q104" s="11" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
         <v>-</v>
       </c>
-      <c r="R104" s="4" t="str">
+      <c r="R104" s="11" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
         <v>-</v>
       </c>
-      <c r="S104" s="4" t="str">
+      <c r="S104" s="11" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
         <v>-</v>
       </c>
@@ -12264,29 +12190,28 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>527</v>
+        <v>65</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>528</v>
+        <v>682</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>529</v>
+        <v>686</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="F105" s="4">
-        <v>0.01</v>
+        <v>454</v>
+      </c>
+      <c r="F105" s="4" cm="1">
+        <f t="array" ref="F105">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
+        <v>1E-4</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
-      <c r="J105" s="4" t="s">
-        <v>530</v>
-      </c>
+      <c r="J105" s="4"/>
       <c r="K105" s="4">
         <v>1</v>
       </c>
@@ -12299,22 +12224,22 @@
       <c r="N105" s="4">
         <v>0</v>
       </c>
-      <c r="O105" s="11" t="s">
-        <v>531</v>
+      <c r="O105" s="4" t="s">
+        <v>684</v>
       </c>
       <c r="P105" s="4" t="str" cm="1">
         <f t="array" ref="P105">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Economic Policy Uncertainty Index for United States</v>
-      </c>
-      <c r="Q105" s="11" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q105" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
         <v>-</v>
       </c>
-      <c r="R105" s="11" t="str">
+      <c r="R105" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
         <v>-</v>
       </c>
-      <c r="S105" s="11" t="str">
+      <c r="S105" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
         <v>-</v>
       </c>
@@ -12322,23 +12247,23 @@
     </row>
     <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>65</v>
+        <v>475</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>686</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="F106" s="4" cm="1">
         <f t="array" ref="F106">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
@@ -12357,7 +12282,7 @@
         <v>0</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="P106" s="4" t="str" cm="1">
         <f t="array" ref="P106">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
@@ -12376,63 +12301,6 @@
         <v>-</v>
       </c>
       <c r="T106" s="4"/>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A107" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="F107" s="4" cm="1">
-        <f t="array" ref="F107">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
-        <v>-0.01</v>
-      </c>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
-      <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
-      <c r="K107" s="4">
-        <v>1</v>
-      </c>
-      <c r="L107" s="4">
-        <v>0</v>
-      </c>
-      <c r="M107" s="4">
-        <v>0</v>
-      </c>
-      <c r="N107" s="4">
-        <v>0</v>
-      </c>
-      <c r="O107" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="P107" s="4" t="str" cm="1">
-        <f t="array" ref="P107">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="Q107" s="4" t="str">
-        <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>-</v>
-      </c>
-      <c r="R107" s="4" t="str">
-        <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>-</v>
-      </c>
-      <c r="S107" s="4" t="str">
-        <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>-</v>
-      </c>
-      <c r="T107" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -12612,7 +12480,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5A64DEF-E706-4B9C-B282-71F34F86B3DF}">
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
@@ -12652,11 +12520,11 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A87">_xlfn._xlws.FILTER(data[factor_name],data[Active])</f>
+        <f t="array" ref="A2:A86">_xlfn._xlws.FILTER(data[factor_name],data[Active])</f>
         <v>SPY</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:J87">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
+        <f t="array" ref="B2:J86">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
         <v>Equities</v>
       </c>
       <c r="C2" t="str">
@@ -15278,42 +15146,42 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
-        <v>TRADEWAR</v>
+        <v>UNCERTAINTY</v>
       </c>
       <c r="B84" t="str">
-        <v>Theme</v>
+        <v>Econ</v>
       </c>
       <c r="C84" t="str">
         <v>USD</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" t="str">
-        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
+        <v>Economic Policy Uncertainty Index for United States</v>
       </c>
       <c r="G84" t="str">
-        <v>composite</v>
+        <v>fred</v>
       </c>
       <c r="H84" t="str">
-        <v>TRADEWAR</v>
+        <v>USEPUINDXD</v>
       </c>
       <c r="I84" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J84">
-        <v>1E-4</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
-        <v>UNCERTAINTY</v>
+        <v>BTC</v>
       </c>
       <c r="B85" t="str">
-        <v>Econ</v>
+        <v>Currencies</v>
       </c>
       <c r="C85" t="str">
         <v>USD</v>
@@ -15325,27 +15193,27 @@
         <v>0</v>
       </c>
       <c r="F85" t="str">
-        <v>Economic Policy Uncertainty Index for United States</v>
+        <v>-</v>
       </c>
       <c r="G85" t="str">
-        <v>fred</v>
+        <v>lmxl</v>
       </c>
       <c r="H85" t="str">
-        <v>USEPUINDXD</v>
+        <v>BTC1_price</v>
       </c>
       <c r="I85" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J85">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="str">
-        <v>BTC</v>
+        <v>BTC_vol</v>
       </c>
       <c r="B86" t="str">
-        <v>Currencies</v>
+        <v>Vol</v>
       </c>
       <c r="C86" t="str">
         <v>USD</v>
@@ -15363,44 +15231,12 @@
         <v>lmxl</v>
       </c>
       <c r="H86" t="str">
-        <v>BTC1_price</v>
+        <v>BTC1_atm</v>
       </c>
       <c r="I86" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J86">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" t="str">
-        <v>BTC_vol</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Vol</v>
-      </c>
-      <c r="C87" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D87">
-        <v>0</v>
-      </c>
-      <c r="E87">
-        <v>0</v>
-      </c>
-      <c r="F87" t="str">
-        <v>-</v>
-      </c>
-      <c r="G87" t="str">
-        <v>lmxl</v>
-      </c>
-      <c r="H87" t="str">
-        <v>BTC1_atm</v>
-      </c>
-      <c r="I87" t="str">
-        <v>normal</v>
-      </c>
-      <c r="J87">
         <v>-0.01</v>
       </c>
     </row>
@@ -17795,7 +17631,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2977BD7F-9323-4F6D-98BF-C1B39119DCDE}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
@@ -17835,11 +17671,11 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A87">_xlfn._xlws.FILTER(data[factor_name],data[Active]*(data[client]=0))</f>
+        <f t="array" ref="A2:A86">_xlfn._xlws.FILTER(data[factor_name],data[Active]*(data[client]=0))</f>
         <v>SPY</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:J87">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
+        <f t="array" ref="B2:J86">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
         <v>Equities</v>
       </c>
       <c r="C2" t="str">
@@ -20461,42 +20297,42 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
-        <v>TRADEWAR</v>
+        <v>UNCERTAINTY</v>
       </c>
       <c r="B84" t="str">
-        <v>Theme</v>
+        <v>Econ</v>
       </c>
       <c r="C84" t="str">
         <v>USD</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" t="str">
-        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
+        <v>Economic Policy Uncertainty Index for United States</v>
       </c>
       <c r="G84" t="str">
-        <v>composite</v>
+        <v>fred</v>
       </c>
       <c r="H84" t="str">
-        <v>TRADEWAR</v>
+        <v>USEPUINDXD</v>
       </c>
       <c r="I84" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J84">
-        <v>1E-4</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
-        <v>UNCERTAINTY</v>
+        <v>BTC</v>
       </c>
       <c r="B85" t="str">
-        <v>Econ</v>
+        <v>Currencies</v>
       </c>
       <c r="C85" t="str">
         <v>USD</v>
@@ -20508,27 +20344,27 @@
         <v>0</v>
       </c>
       <c r="F85" t="str">
-        <v>Economic Policy Uncertainty Index for United States</v>
+        <v>-</v>
       </c>
       <c r="G85" t="str">
-        <v>fred</v>
+        <v>lmxl</v>
       </c>
       <c r="H85" t="str">
-        <v>USEPUINDXD</v>
+        <v>BTC1_price</v>
       </c>
       <c r="I85" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J85">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="str">
-        <v>BTC</v>
+        <v>BTC_vol</v>
       </c>
       <c r="B86" t="str">
-        <v>Currencies</v>
+        <v>Vol</v>
       </c>
       <c r="C86" t="str">
         <v>USD</v>
@@ -20546,44 +20382,12 @@
         <v>lmxl</v>
       </c>
       <c r="H86" t="str">
-        <v>BTC1_price</v>
+        <v>BTC1_atm</v>
       </c>
       <c r="I86" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J86">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" t="str">
-        <v>BTC_vol</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Vol</v>
-      </c>
-      <c r="C87" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D87">
-        <v>0</v>
-      </c>
-      <c r="E87">
-        <v>0</v>
-      </c>
-      <c r="F87" t="str">
-        <v>-</v>
-      </c>
-      <c r="G87" t="str">
-        <v>lmxl</v>
-      </c>
-      <c r="H87" t="str">
-        <v>BTC1_atm</v>
-      </c>
-      <c r="I87" t="str">
-        <v>normal</v>
-      </c>
-      <c r="J87">
         <v>-0.01</v>
       </c>
     </row>

--- a/factor_master.xlsx
+++ b/factor_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrai\Source\risk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEB79B3-8A1F-4750-9F6C-F78A727D4C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406E069D-9C47-442C-8EEF-1CEF7710CA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="10" xr2:uid="{C31FDC5B-A809-4BFD-99CB-DA02246721F7}"/>
   </bookViews>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="4">
         <v>0</v>
@@ -11909,7 +11909,7 @@
       <c r="I100" s="4"/>
       <c r="J100" s="4" t="str" cm="1">
         <f t="array" ref="J100">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$F$2),_xlfn.ANCHORARRAY(composites!$G$2))</f>
-        <v>USD 1</v>
+        <v>USO 1</v>
       </c>
       <c r="K100" s="4">
         <v>1</v>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="P100" s="4" t="str" cm="1">
         <f t="array" ref="P100">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>USD 1</v>
+        <v>USO 1</v>
       </c>
       <c r="Q100" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
@@ -12480,7 +12480,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5A64DEF-E706-4B9C-B282-71F34F86B3DF}">
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
@@ -12520,11 +12520,11 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A86">_xlfn._xlws.FILTER(data[factor_name],data[Active])</f>
+        <f t="array" ref="A2:A85">_xlfn._xlws.FILTER(data[factor_name],data[Active])</f>
         <v>SPY</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:J86">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
+        <f t="array" ref="B2:J85">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
         <v>Equities</v>
       </c>
       <c r="C2" t="str">
@@ -13290,7 +13290,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
-        <v>GPZ</v>
+        <v>PFF</v>
       </c>
       <c r="B26" t="str">
         <v>Equities</v>
@@ -13305,13 +13305,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="str">
-        <v>Private Alts</v>
+        <v>Preferred</v>
       </c>
       <c r="G26" t="str">
         <v>yfinance</v>
       </c>
       <c r="H26" t="str">
-        <v>GPZ</v>
+        <v>PFF</v>
       </c>
       <c r="I26" t="str">
         <v>lognormal</v>
@@ -13322,13 +13322,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
-        <v>PFF</v>
+        <v>FEZ</v>
       </c>
       <c r="B27" t="str">
         <v>Equities</v>
       </c>
       <c r="C27" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -13337,13 +13337,13 @@
         <v>0</v>
       </c>
       <c r="F27" t="str">
-        <v>Preferred</v>
+        <v>Eurostoxx 50</v>
       </c>
       <c r="G27" t="str">
         <v>yfinance</v>
       </c>
       <c r="H27" t="str">
-        <v>PFF</v>
+        <v>FEZ</v>
       </c>
       <c r="I27" t="str">
         <v>lognormal</v>
@@ -13354,13 +13354,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <v>FEZ</v>
+        <v>EWU</v>
       </c>
       <c r="B28" t="str">
         <v>Equities</v>
       </c>
       <c r="C28" t="str">
-        <v>EUR</v>
+        <v>GBP</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -13369,13 +13369,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="str">
-        <v>Eurostoxx 50</v>
+        <v>FTSE 100</v>
       </c>
       <c r="G28" t="str">
         <v>yfinance</v>
       </c>
       <c r="H28" t="str">
-        <v>FEZ</v>
+        <v>EWU</v>
       </c>
       <c r="I28" t="str">
         <v>lognormal</v>
@@ -13386,13 +13386,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <v>EWU</v>
+        <v>DAX</v>
       </c>
       <c r="B29" t="str">
         <v>Equities</v>
       </c>
       <c r="C29" t="str">
-        <v>GBP</v>
+        <v>EUR</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -13401,13 +13401,13 @@
         <v>0</v>
       </c>
       <c r="F29" t="str">
-        <v>FTSE 100</v>
+        <v>DAX (Germany)</v>
       </c>
       <c r="G29" t="str">
         <v>yfinance</v>
       </c>
       <c r="H29" t="str">
-        <v>EWU</v>
+        <v>DAX</v>
       </c>
       <c r="I29" t="str">
         <v>lognormal</v>
@@ -13418,13 +13418,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <v>DAX</v>
+        <v>EWC</v>
       </c>
       <c r="B30" t="str">
         <v>Equities</v>
       </c>
       <c r="C30" t="str">
-        <v>EUR</v>
+        <v>CAD</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -13433,13 +13433,13 @@
         <v>0</v>
       </c>
       <c r="F30" t="str">
-        <v>DAX (Germany)</v>
+        <v>MSCI Canada</v>
       </c>
       <c r="G30" t="str">
         <v>yfinance</v>
       </c>
       <c r="H30" t="str">
-        <v>DAX</v>
+        <v>EWC</v>
       </c>
       <c r="I30" t="str">
         <v>lognormal</v>
@@ -13450,13 +13450,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
-        <v>EWC</v>
+        <v>EWI</v>
       </c>
       <c r="B31" t="str">
         <v>Equities</v>
       </c>
       <c r="C31" t="str">
-        <v>CAD</v>
+        <v>EUR</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -13465,13 +13465,13 @@
         <v>0</v>
       </c>
       <c r="F31" t="str">
-        <v>MSCI Canada</v>
+        <v>MSCI Italy</v>
       </c>
       <c r="G31" t="str">
         <v>yfinance</v>
       </c>
       <c r="H31" t="str">
-        <v>EWC</v>
+        <v>EWI</v>
       </c>
       <c r="I31" t="str">
         <v>lognormal</v>
@@ -13482,13 +13482,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
-        <v>EWI</v>
+        <v>^N225</v>
       </c>
       <c r="B32" t="str">
         <v>Equities</v>
       </c>
       <c r="C32" t="str">
-        <v>EUR</v>
+        <v>JPY</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -13497,13 +13497,13 @@
         <v>0</v>
       </c>
       <c r="F32" t="str">
-        <v>MSCI Italy</v>
+        <v>Nikkei 225</v>
       </c>
       <c r="G32" t="str">
         <v>yfinance</v>
       </c>
       <c r="H32" t="str">
-        <v>EWI</v>
+        <v>^N225</v>
       </c>
       <c r="I32" t="str">
         <v>lognormal</v>
@@ -13514,13 +13514,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
-        <v>^N225</v>
+        <v>FXI</v>
       </c>
       <c r="B33" t="str">
         <v>Equities</v>
       </c>
       <c r="C33" t="str">
-        <v>JPY</v>
+        <v>CNH</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -13529,13 +13529,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="str">
-        <v>Nikkei 225</v>
+        <v>China Large-Cap</v>
       </c>
       <c r="G33" t="str">
         <v>yfinance</v>
       </c>
       <c r="H33" t="str">
-        <v>^N225</v>
+        <v>FXI</v>
       </c>
       <c r="I33" t="str">
         <v>lognormal</v>
@@ -13546,7 +13546,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
-        <v>FXI</v>
+        <v>ASHR</v>
       </c>
       <c r="B34" t="str">
         <v>Equities</v>
@@ -13561,13 +13561,13 @@
         <v>0</v>
       </c>
       <c r="F34" t="str">
-        <v>China Large-Cap</v>
+        <v>CSI 300 (China)</v>
       </c>
       <c r="G34" t="str">
         <v>yfinance</v>
       </c>
       <c r="H34" t="str">
-        <v>FXI</v>
+        <v>ASHR</v>
       </c>
       <c r="I34" t="str">
         <v>lognormal</v>
@@ -13578,7 +13578,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
-        <v>ASHR</v>
+        <v>KWEB</v>
       </c>
       <c r="B35" t="str">
         <v>Equities</v>
@@ -13593,13 +13593,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="str">
-        <v>CSI 300 (China)</v>
+        <v>CSI China Internet</v>
       </c>
       <c r="G35" t="str">
         <v>yfinance</v>
       </c>
       <c r="H35" t="str">
-        <v>ASHR</v>
+        <v>KWEB</v>
       </c>
       <c r="I35" t="str">
         <v>lognormal</v>
@@ -13610,13 +13610,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
-        <v>KWEB</v>
+        <v>EEM</v>
       </c>
       <c r="B36" t="str">
         <v>Equities</v>
       </c>
       <c r="C36" t="str">
-        <v>CNH</v>
+        <v>EM</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -13625,13 +13625,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="str">
-        <v>CSI China Internet</v>
+        <v>MSCI EM</v>
       </c>
       <c r="G36" t="str">
         <v>yfinance</v>
       </c>
       <c r="H36" t="str">
-        <v>KWEB</v>
+        <v>EEM</v>
       </c>
       <c r="I36" t="str">
         <v>lognormal</v>
@@ -13642,13 +13642,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
-        <v>EEM</v>
+        <v>LQD</v>
       </c>
       <c r="B37" t="str">
-        <v>Equities</v>
+        <v>Credit</v>
       </c>
       <c r="C37" t="str">
-        <v>EM</v>
+        <v>USD</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -13657,13 +13657,13 @@
         <v>0</v>
       </c>
       <c r="F37" t="str">
-        <v>MSCI EM</v>
+        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
       </c>
       <c r="G37" t="str">
         <v>yfinance</v>
       </c>
       <c r="H37" t="str">
-        <v>EEM</v>
+        <v>LQD</v>
       </c>
       <c r="I37" t="str">
         <v>lognormal</v>
@@ -13674,7 +13674,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
-        <v>LQD</v>
+        <v>BSV</v>
       </c>
       <c r="B38" t="str">
         <v>Credit</v>
@@ -13689,13 +13689,13 @@
         <v>0</v>
       </c>
       <c r="F38" t="str">
-        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
+        <v>Vanguard Short-Term Bond Index Fund ETF</v>
       </c>
       <c r="G38" t="str">
         <v>yfinance</v>
       </c>
       <c r="H38" t="str">
-        <v>LQD</v>
+        <v>BSV</v>
       </c>
       <c r="I38" t="str">
         <v>lognormal</v>
@@ -13706,7 +13706,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
-        <v>BSV</v>
+        <v>HYG</v>
       </c>
       <c r="B39" t="str">
         <v>Credit</v>
@@ -13721,13 +13721,13 @@
         <v>0</v>
       </c>
       <c r="F39" t="str">
-        <v>Vanguard Short-Term Bond Index Fund ETF</v>
+        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
       </c>
       <c r="G39" t="str">
         <v>yfinance</v>
       </c>
       <c r="H39" t="str">
-        <v>BSV</v>
+        <v>HYG</v>
       </c>
       <c r="I39" t="str">
         <v>lognormal</v>
@@ -13738,7 +13738,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
-        <v>HYG</v>
+        <v>LQDH</v>
       </c>
       <c r="B40" t="str">
         <v>Credit</v>
@@ -13747,19 +13747,19 @@
         <v>USD</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40" t="str">
-        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
+        <v>Hedged LQD</v>
       </c>
       <c r="G40" t="str">
         <v>yfinance</v>
       </c>
       <c r="H40" t="str">
-        <v>HYG</v>
+        <v>LQDH</v>
       </c>
       <c r="I40" t="str">
         <v>lognormal</v>
@@ -13770,7 +13770,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
-        <v>LQDH</v>
+        <v>HYGH</v>
       </c>
       <c r="B41" t="str">
         <v>Credit</v>
@@ -13779,19 +13779,19 @@
         <v>USD</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41" t="str">
-        <v>Hedged LQD</v>
+        <v>Hedged HYG</v>
       </c>
       <c r="G41" t="str">
         <v>yfinance</v>
       </c>
       <c r="H41" t="str">
-        <v>LQDH</v>
+        <v>HYGH</v>
       </c>
       <c r="I41" t="str">
         <v>lognormal</v>
@@ -13802,7 +13802,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
-        <v>HYGH</v>
+        <v>BKLN</v>
       </c>
       <c r="B42" t="str">
         <v>Credit</v>
@@ -13817,13 +13817,13 @@
         <v>0</v>
       </c>
       <c r="F42" t="str">
-        <v>Hedged HYG</v>
+        <v>Bank Loans</v>
       </c>
       <c r="G42" t="str">
         <v>yfinance</v>
       </c>
       <c r="H42" t="str">
-        <v>HYGH</v>
+        <v>BKLN</v>
       </c>
       <c r="I42" t="str">
         <v>lognormal</v>
@@ -13834,7 +13834,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
-        <v>BKLN</v>
+        <v>AGG</v>
       </c>
       <c r="B43" t="str">
         <v>Credit</v>
@@ -13849,13 +13849,13 @@
         <v>0</v>
       </c>
       <c r="F43" t="str">
-        <v>Bank Loans</v>
+        <v>US Agg</v>
       </c>
       <c r="G43" t="str">
         <v>yfinance</v>
       </c>
       <c r="H43" t="str">
-        <v>BKLN</v>
+        <v>AGG</v>
       </c>
       <c r="I43" t="str">
         <v>lognormal</v>
@@ -13866,10 +13866,10 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
-        <v>AGG</v>
+        <v>^TNX</v>
       </c>
       <c r="B44" t="str">
-        <v>Credit</v>
+        <v>Rates</v>
       </c>
       <c r="C44" t="str">
         <v>USD</v>
@@ -13881,24 +13881,24 @@
         <v>0</v>
       </c>
       <c r="F44" t="str">
-        <v>US Agg</v>
+        <v>CBOE Interest Rate 10 Year</v>
       </c>
       <c r="G44" t="str">
         <v>yfinance</v>
       </c>
       <c r="H44" t="str">
-        <v>AGG</v>
+        <v>^TNX</v>
       </c>
       <c r="I44" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J44">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
-        <v>^TNX</v>
+        <v>SHY</v>
       </c>
       <c r="B45" t="str">
         <v>Rates</v>
@@ -13913,24 +13913,24 @@
         <v>0</v>
       </c>
       <c r="F45" t="str">
-        <v>CBOE Interest Rate 10 Year</v>
+        <v>1-3 Year Treasury</v>
       </c>
       <c r="G45" t="str">
         <v>yfinance</v>
       </c>
       <c r="H45" t="str">
-        <v>^TNX</v>
+        <v>SHY</v>
       </c>
       <c r="I45" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J45">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
-        <v>SHY</v>
+        <v>IEI</v>
       </c>
       <c r="B46" t="str">
         <v>Rates</v>
@@ -13945,13 +13945,13 @@
         <v>0</v>
       </c>
       <c r="F46" t="str">
-        <v>1-3 Year Treasury</v>
+        <v>3-7 Year Treasury</v>
       </c>
       <c r="G46" t="str">
         <v>yfinance</v>
       </c>
       <c r="H46" t="str">
-        <v>SHY</v>
+        <v>IEI</v>
       </c>
       <c r="I46" t="str">
         <v>lognormal</v>
@@ -13962,7 +13962,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
-        <v>IEI</v>
+        <v>IEF</v>
       </c>
       <c r="B47" t="str">
         <v>Rates</v>
@@ -13971,19 +13971,19 @@
         <v>USD</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47" t="str">
-        <v>3-7 Year Treasury</v>
+        <v>7-10 Year Treasury</v>
       </c>
       <c r="G47" t="str">
         <v>yfinance</v>
       </c>
       <c r="H47" t="str">
-        <v>IEI</v>
+        <v>IEF</v>
       </c>
       <c r="I47" t="str">
         <v>lognormal</v>
@@ -13994,7 +13994,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
-        <v>IEF</v>
+        <v>TLT</v>
       </c>
       <c r="B48" t="str">
         <v>Rates</v>
@@ -14003,19 +14003,19 @@
         <v>USD</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="str">
-        <v>7-10 Year Treasury</v>
+        <v>20+ Year Treasury</v>
       </c>
       <c r="G48" t="str">
         <v>yfinance</v>
       </c>
       <c r="H48" t="str">
-        <v>IEF</v>
+        <v>TLT</v>
       </c>
       <c r="I48" t="str">
         <v>lognormal</v>
@@ -14026,7 +14026,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
-        <v>TLT</v>
+        <v>TIP</v>
       </c>
       <c r="B49" t="str">
         <v>Rates</v>
@@ -14041,13 +14041,13 @@
         <v>0</v>
       </c>
       <c r="F49" t="str">
-        <v>20+ Year Treasury</v>
+        <v>iShares TIPS Bond ETF</v>
       </c>
       <c r="G49" t="str">
         <v>yfinance</v>
       </c>
       <c r="H49" t="str">
-        <v>TLT</v>
+        <v>TIP</v>
       </c>
       <c r="I49" t="str">
         <v>lognormal</v>
@@ -14058,7 +14058,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
-        <v>TIP</v>
+        <v>VTIP</v>
       </c>
       <c r="B50" t="str">
         <v>Rates</v>
@@ -14073,13 +14073,13 @@
         <v>0</v>
       </c>
       <c r="F50" t="str">
-        <v>iShares TIPS Bond ETF</v>
+        <v>Short-Term Inflation-Protected Securities ETF</v>
       </c>
       <c r="G50" t="str">
         <v>yfinance</v>
       </c>
       <c r="H50" t="str">
-        <v>TIP</v>
+        <v>VTIP</v>
       </c>
       <c r="I50" t="str">
         <v>lognormal</v>
@@ -14090,7 +14090,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
-        <v>VTIP</v>
+        <v>AGNC</v>
       </c>
       <c r="B51" t="str">
         <v>Rates</v>
@@ -14105,13 +14105,13 @@
         <v>0</v>
       </c>
       <c r="F51" t="str">
-        <v>Short-Term Inflation-Protected Securities ETF</v>
+        <v>AGNC Investment Corp.</v>
       </c>
       <c r="G51" t="str">
         <v>yfinance</v>
       </c>
       <c r="H51" t="str">
-        <v>VTIP</v>
+        <v>AGNC</v>
       </c>
       <c r="I51" t="str">
         <v>lognormal</v>
@@ -14122,7 +14122,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
-        <v>AGNC</v>
+        <v>VMBS</v>
       </c>
       <c r="B52" t="str">
         <v>Rates</v>
@@ -14137,13 +14137,13 @@
         <v>0</v>
       </c>
       <c r="F52" t="str">
-        <v>AGNC Investment Corp.</v>
+        <v>Mortgage-Backed Securities ETF</v>
       </c>
       <c r="G52" t="str">
         <v>yfinance</v>
       </c>
       <c r="H52" t="str">
-        <v>AGNC</v>
+        <v>VMBS</v>
       </c>
       <c r="I52" t="str">
         <v>lognormal</v>
@@ -14154,7 +14154,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
-        <v>VMBS</v>
+        <v>CMBS</v>
       </c>
       <c r="B53" t="str">
         <v>Rates</v>
@@ -14169,13 +14169,13 @@
         <v>0</v>
       </c>
       <c r="F53" t="str">
-        <v>Mortgage-Backed Securities ETF</v>
+        <v>iShares CMBS ETF</v>
       </c>
       <c r="G53" t="str">
         <v>yfinance</v>
       </c>
       <c r="H53" t="str">
-        <v>VMBS</v>
+        <v>CMBS</v>
       </c>
       <c r="I53" t="str">
         <v>lognormal</v>
@@ -14186,13 +14186,13 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
-        <v>CMBS</v>
+        <v>EMB</v>
       </c>
       <c r="B54" t="str">
         <v>Rates</v>
       </c>
       <c r="C54" t="str">
-        <v>USD</v>
+        <v>EM</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -14201,13 +14201,13 @@
         <v>0</v>
       </c>
       <c r="F54" t="str">
-        <v>iShares CMBS ETF</v>
+        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
       </c>
       <c r="G54" t="str">
         <v>yfinance</v>
       </c>
       <c r="H54" t="str">
-        <v>CMBS</v>
+        <v>EMB</v>
       </c>
       <c r="I54" t="str">
         <v>lognormal</v>
@@ -14218,13 +14218,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
-        <v>EMB</v>
+        <v>GLD</v>
       </c>
       <c r="B55" t="str">
-        <v>Rates</v>
+        <v>Commodities</v>
       </c>
       <c r="C55" t="str">
-        <v>EM</v>
+        <v>USD</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -14233,13 +14233,13 @@
         <v>0</v>
       </c>
       <c r="F55" t="str">
-        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
+        <v>SPDR Gold Shares</v>
       </c>
       <c r="G55" t="str">
         <v>yfinance</v>
       </c>
       <c r="H55" t="str">
-        <v>EMB</v>
+        <v>GLD</v>
       </c>
       <c r="I55" t="str">
         <v>lognormal</v>
@@ -14250,7 +14250,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
-        <v>GLD</v>
+        <v>SLV</v>
       </c>
       <c r="B56" t="str">
         <v>Commodities</v>
@@ -14265,13 +14265,13 @@
         <v>0</v>
       </c>
       <c r="F56" t="str">
-        <v>SPDR Gold Shares</v>
+        <v>iShares Silver Trust</v>
       </c>
       <c r="G56" t="str">
         <v>yfinance</v>
       </c>
       <c r="H56" t="str">
-        <v>GLD</v>
+        <v>SLV</v>
       </c>
       <c r="I56" t="str">
         <v>lognormal</v>
@@ -14282,7 +14282,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
-        <v>SLV</v>
+        <v>USO</v>
       </c>
       <c r="B57" t="str">
         <v>Commodities</v>
@@ -14297,13 +14297,13 @@
         <v>0</v>
       </c>
       <c r="F57" t="str">
-        <v>iShares Silver Trust</v>
+        <v>United States Oil Fund</v>
       </c>
       <c r="G57" t="str">
         <v>yfinance</v>
       </c>
       <c r="H57" t="str">
-        <v>SLV</v>
+        <v>USO</v>
       </c>
       <c r="I57" t="str">
         <v>lognormal</v>
@@ -14314,10 +14314,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
-        <v>USO</v>
+        <v>UUP</v>
       </c>
       <c r="B58" t="str">
-        <v>Commodities</v>
+        <v>Currencies</v>
       </c>
       <c r="C58" t="str">
         <v>USD</v>
@@ -14329,13 +14329,13 @@
         <v>0</v>
       </c>
       <c r="F58" t="str">
-        <v>United States Oil Fund</v>
+        <v>Invesco DB US Dollar Index Bullish Fund</v>
       </c>
       <c r="G58" t="str">
         <v>yfinance</v>
       </c>
       <c r="H58" t="str">
-        <v>USO</v>
+        <v>UUP</v>
       </c>
       <c r="I58" t="str">
         <v>lognormal</v>
@@ -14346,7 +14346,7 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
-        <v>UUP</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="B59" t="str">
         <v>Currencies</v>
@@ -14361,13 +14361,13 @@
         <v>0</v>
       </c>
       <c r="F59" t="str">
-        <v>Invesco DB US Dollar Index Bullish Fund</v>
+        <v>U.S. Dollar Index</v>
       </c>
       <c r="G59" t="str">
         <v>yfinance</v>
       </c>
       <c r="H59" t="str">
-        <v>UUP</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="I59" t="str">
         <v>lognormal</v>
@@ -14378,13 +14378,13 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
-        <v>DX-Y.NYB</v>
+        <v>FXE</v>
       </c>
       <c r="B60" t="str">
         <v>Currencies</v>
       </c>
       <c r="C60" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -14393,13 +14393,13 @@
         <v>0</v>
       </c>
       <c r="F60" t="str">
-        <v>U.S. Dollar Index</v>
+        <v>Invesco CurrencyShares Euro Trust</v>
       </c>
       <c r="G60" t="str">
         <v>yfinance</v>
       </c>
       <c r="H60" t="str">
-        <v>DX-Y.NYB</v>
+        <v>FXE</v>
       </c>
       <c r="I60" t="str">
         <v>lognormal</v>
@@ -14410,7 +14410,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
-        <v>FXE</v>
+        <v>FXF</v>
       </c>
       <c r="B61" t="str">
         <v>Currencies</v>
@@ -14425,13 +14425,13 @@
         <v>0</v>
       </c>
       <c r="F61" t="str">
-        <v>Invesco CurrencyShares Euro Trust</v>
+        <v>Invesco CurrencyShares Swiss Franc Trust</v>
       </c>
       <c r="G61" t="str">
         <v>yfinance</v>
       </c>
       <c r="H61" t="str">
-        <v>FXE</v>
+        <v>FXF</v>
       </c>
       <c r="I61" t="str">
         <v>lognormal</v>
@@ -14442,13 +14442,13 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
-        <v>FXF</v>
+        <v>FXA</v>
       </c>
       <c r="B62" t="str">
         <v>Currencies</v>
       </c>
       <c r="C62" t="str">
-        <v>EUR</v>
+        <v>Commod</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -14457,13 +14457,13 @@
         <v>0</v>
       </c>
       <c r="F62" t="str">
-        <v>Invesco CurrencyShares Swiss Franc Trust</v>
+        <v>Invesco CurrencyShares Australian Dollar Trust</v>
       </c>
       <c r="G62" t="str">
         <v>yfinance</v>
       </c>
       <c r="H62" t="str">
-        <v>FXF</v>
+        <v>FXA</v>
       </c>
       <c r="I62" t="str">
         <v>lognormal</v>
@@ -14474,13 +14474,13 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
-        <v>FXA</v>
+        <v>FXB</v>
       </c>
       <c r="B63" t="str">
         <v>Currencies</v>
       </c>
       <c r="C63" t="str">
-        <v>Commod</v>
+        <v>GBP</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -14489,13 +14489,13 @@
         <v>0</v>
       </c>
       <c r="F63" t="str">
-        <v>Invesco CurrencyShares Australian Dollar Trust</v>
+        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
       </c>
       <c r="G63" t="str">
         <v>yfinance</v>
       </c>
       <c r="H63" t="str">
-        <v>FXA</v>
+        <v>FXB</v>
       </c>
       <c r="I63" t="str">
         <v>lognormal</v>
@@ -14506,13 +14506,13 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
-        <v>FXB</v>
+        <v>FXC</v>
       </c>
       <c r="B64" t="str">
         <v>Currencies</v>
       </c>
       <c r="C64" t="str">
-        <v>GBP</v>
+        <v>USD</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -14521,13 +14521,13 @@
         <v>0</v>
       </c>
       <c r="F64" t="str">
-        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
+        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
       </c>
       <c r="G64" t="str">
         <v>yfinance</v>
       </c>
       <c r="H64" t="str">
-        <v>FXB</v>
+        <v>FXC</v>
       </c>
       <c r="I64" t="str">
         <v>lognormal</v>
@@ -14538,13 +14538,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
-        <v>FXC</v>
+        <v>FXY</v>
       </c>
       <c r="B65" t="str">
         <v>Currencies</v>
       </c>
       <c r="C65" t="str">
-        <v>USD</v>
+        <v>JPY</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -14553,13 +14553,13 @@
         <v>0</v>
       </c>
       <c r="F65" t="str">
-        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
+        <v>Invesco CurrencyShares Japanese Yen Trust</v>
       </c>
       <c r="G65" t="str">
         <v>yfinance</v>
       </c>
       <c r="H65" t="str">
-        <v>FXC</v>
+        <v>FXY</v>
       </c>
       <c r="I65" t="str">
         <v>lognormal</v>
@@ -14570,13 +14570,13 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
-        <v>FXY</v>
+        <v>^VIX</v>
       </c>
       <c r="B66" t="str">
-        <v>Currencies</v>
+        <v>Vol</v>
       </c>
       <c r="C66" t="str">
-        <v>JPY</v>
+        <v>USD</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -14585,24 +14585,24 @@
         <v>0</v>
       </c>
       <c r="F66" t="str">
-        <v>Invesco CurrencyShares Japanese Yen Trust</v>
+        <v>CBOE Volatility Index</v>
       </c>
       <c r="G66" t="str">
         <v>yfinance</v>
       </c>
       <c r="H66" t="str">
-        <v>FXY</v>
+        <v>^VIX</v>
       </c>
       <c r="I66" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J66">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
-        <v>^VIX</v>
+        <v>VXX</v>
       </c>
       <c r="B67" t="str">
         <v>Vol</v>
@@ -14617,13 +14617,13 @@
         <v>0</v>
       </c>
       <c r="F67" t="str">
-        <v>CBOE Volatility Index</v>
+        <v>VIX Short-Term Futures ETN</v>
       </c>
       <c r="G67" t="str">
         <v>yfinance</v>
       </c>
       <c r="H67" t="str">
-        <v>^VIX</v>
+        <v>VXX</v>
       </c>
       <c r="I67" t="str">
         <v>normal</v>
@@ -14634,7 +14634,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
-        <v>VXX</v>
+        <v>^VIX3M</v>
       </c>
       <c r="B68" t="str">
         <v>Vol</v>
@@ -14649,13 +14649,13 @@
         <v>0</v>
       </c>
       <c r="F68" t="str">
-        <v>VIX Short-Term Futures ETN</v>
+        <v>CBOE S&amp;P 500 3-Month Volatility</v>
       </c>
       <c r="G68" t="str">
         <v>yfinance</v>
       </c>
       <c r="H68" t="str">
-        <v>VXX</v>
+        <v>^VIX3M</v>
       </c>
       <c r="I68" t="str">
         <v>normal</v>
@@ -14666,7 +14666,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
-        <v>^VIX3M</v>
+        <v>^MOVE</v>
       </c>
       <c r="B69" t="str">
         <v>Vol</v>
@@ -14681,13 +14681,13 @@
         <v>0</v>
       </c>
       <c r="F69" t="str">
-        <v>CBOE S&amp;P 500 3-Month Volatility</v>
+        <v>ICE BofAML MOVE Index</v>
       </c>
       <c r="G69" t="str">
         <v>yfinance</v>
       </c>
       <c r="H69" t="str">
-        <v>^VIX3M</v>
+        <v>^MOVE</v>
       </c>
       <c r="I69" t="str">
         <v>normal</v>
@@ -14698,7 +14698,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
-        <v>^MOVE</v>
+        <v>^OVX</v>
       </c>
       <c r="B70" t="str">
         <v>Vol</v>
@@ -14713,13 +14713,13 @@
         <v>0</v>
       </c>
       <c r="F70" t="str">
-        <v>ICE BofAML MOVE Index</v>
+        <v>CBOE Crude Oil Volatility Index</v>
       </c>
       <c r="G70" t="str">
         <v>yfinance</v>
       </c>
       <c r="H70" t="str">
-        <v>^MOVE</v>
+        <v>^OVX</v>
       </c>
       <c r="I70" t="str">
         <v>normal</v>
@@ -14730,7 +14730,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
-        <v>^OVX</v>
+        <v>^GVZ</v>
       </c>
       <c r="B71" t="str">
         <v>Vol</v>
@@ -14745,13 +14745,13 @@
         <v>0</v>
       </c>
       <c r="F71" t="str">
-        <v>CBOE Crude Oil Volatility Index</v>
+        <v>CBOE Gold Volatility Index</v>
       </c>
       <c r="G71" t="str">
         <v>yfinance</v>
       </c>
       <c r="H71" t="str">
-        <v>^OVX</v>
+        <v>^GVZ</v>
       </c>
       <c r="I71" t="str">
         <v>normal</v>
@@ -14762,39 +14762,39 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
-        <v>^GVZ</v>
+        <v>MWTIX</v>
       </c>
       <c r="B72" t="str">
-        <v>Vol</v>
+        <v>Portfolio</v>
       </c>
       <c r="C72" t="str">
         <v>USD</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72" t="str">
-        <v>CBOE Gold Volatility Index</v>
+        <v>TCW MetWest Total Return Bd I</v>
       </c>
       <c r="G72" t="str">
         <v>yfinance</v>
       </c>
       <c r="H72" t="str">
-        <v>^GVZ</v>
+        <v>MWTIX</v>
       </c>
       <c r="I72" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J72">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
-        <v>MWTIX</v>
+        <v>FCNTX</v>
       </c>
       <c r="B73" t="str">
         <v>Portfolio</v>
@@ -14803,19 +14803,19 @@
         <v>USD</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73" t="str">
-        <v>TCW MetWest Total Return Bd I</v>
+        <v>Fidelity Contrafund</v>
       </c>
       <c r="G73" t="str">
         <v>yfinance</v>
       </c>
       <c r="H73" t="str">
-        <v>MWTIX</v>
+        <v>FCNTX</v>
       </c>
       <c r="I73" t="str">
         <v>lognormal</v>
@@ -14826,28 +14826,28 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
-        <v>FCNTX</v>
+        <v>ELECTION</v>
       </c>
       <c r="B74" t="str">
-        <v>Portfolio</v>
+        <v>Theme</v>
       </c>
       <c r="C74" t="str">
         <v>USD</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="str">
-        <v>Fidelity Contrafund</v>
+        <v>XLF 1.5, ICLN -1, IWM 1.5, FEZ -1</v>
       </c>
       <c r="G74" t="str">
-        <v>yfinance</v>
+        <v>composite</v>
       </c>
       <c r="H74" t="str">
-        <v>FCNTX</v>
+        <v>ELECTION</v>
       </c>
       <c r="I74" t="str">
         <v>lognormal</v>
@@ -14858,7 +14858,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
-        <v>ELECTION</v>
+        <v>FED</v>
       </c>
       <c r="B75" t="str">
         <v>Theme</v>
@@ -14873,13 +14873,13 @@
         <v>1</v>
       </c>
       <c r="F75" t="str">
-        <v>XLF 1.5, ICLN -1, IWM 1.5, FEZ -1</v>
+        <v>SHY 1, BSV 1</v>
       </c>
       <c r="G75" t="str">
         <v>composite</v>
       </c>
       <c r="H75" t="str">
-        <v>ELECTION</v>
+        <v>FED</v>
       </c>
       <c r="I75" t="str">
         <v>lognormal</v>
@@ -14890,7 +14890,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
-        <v>FED</v>
+        <v>AI</v>
       </c>
       <c r="B76" t="str">
         <v>Theme</v>
@@ -14905,13 +14905,13 @@
         <v>1</v>
       </c>
       <c r="F76" t="str">
-        <v>SHY 1, BSV 1</v>
+        <v>AIQ 1, QQQ 0.25, IWM -0.25</v>
       </c>
       <c r="G76" t="str">
         <v>composite</v>
       </c>
       <c r="H76" t="str">
-        <v>FED</v>
+        <v>AI</v>
       </c>
       <c r="I76" t="str">
         <v>lognormal</v>
@@ -14922,7 +14922,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
-        <v>AI</v>
+        <v>GEOPOLITICS</v>
       </c>
       <c r="B77" t="str">
         <v>Theme</v>
@@ -14937,13 +14937,13 @@
         <v>1</v>
       </c>
       <c r="F77" t="str">
-        <v>AIQ 1, QQQ 0.25, IWM -0.25</v>
+        <v>GLD 0.65, USO 0.3, ^VIX3M -0.15, FEZ -0.05</v>
       </c>
       <c r="G77" t="str">
         <v>composite</v>
       </c>
       <c r="H77" t="str">
-        <v>AI</v>
+        <v>GEOPOLITICS</v>
       </c>
       <c r="I77" t="str">
         <v>lognormal</v>
@@ -14954,7 +14954,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
-        <v>GEOPOLITICS</v>
+        <v>TRADEWAR</v>
       </c>
       <c r="B78" t="str">
         <v>Theme</v>
@@ -14969,13 +14969,13 @@
         <v>1</v>
       </c>
       <c r="F78" t="str">
-        <v>GLD 0.65, USO 0.3, ^VIX3M -0.15, FEZ -0.05</v>
+        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
       </c>
       <c r="G78" t="str">
         <v>composite</v>
       </c>
       <c r="H78" t="str">
-        <v>GEOPOLITICS</v>
+        <v>TRADEWAR</v>
       </c>
       <c r="I78" t="str">
         <v>lognormal</v>
@@ -14986,7 +14986,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
-        <v>TRADEWAR</v>
+        <v>IRAN</v>
       </c>
       <c r="B79" t="str">
         <v>Theme</v>
@@ -15001,13 +15001,13 @@
         <v>1</v>
       </c>
       <c r="F79" t="str">
-        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
+        <v>USO 1</v>
       </c>
       <c r="G79" t="str">
         <v>composite</v>
       </c>
       <c r="H79" t="str">
-        <v>TRADEWAR</v>
+        <v>IRAN</v>
       </c>
       <c r="I79" t="str">
         <v>lognormal</v>
@@ -15018,7 +15018,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
-        <v>IRAN</v>
+        <v>SEMI-SOFT</v>
       </c>
       <c r="B80" t="str">
         <v>Theme</v>
@@ -15033,13 +15033,13 @@
         <v>1</v>
       </c>
       <c r="F80" t="str">
-        <v>USD 1</v>
+        <v>SMH 1, IGV -1</v>
       </c>
       <c r="G80" t="str">
         <v>composite</v>
       </c>
       <c r="H80" t="str">
-        <v>IRAN</v>
+        <v>SEMI-SOFT</v>
       </c>
       <c r="I80" t="str">
         <v>lognormal</v>
@@ -15050,10 +15050,10 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
-        <v>SEMI-SOFT</v>
+        <v>2s10s</v>
       </c>
       <c r="B81" t="str">
-        <v>Theme</v>
+        <v>Rates</v>
       </c>
       <c r="C81" t="str">
         <v>USD</v>
@@ -15065,13 +15065,13 @@
         <v>1</v>
       </c>
       <c r="F81" t="str">
-        <v>SMH 1, IGV -1</v>
+        <v>SHY -3.86, IEF 1</v>
       </c>
       <c r="G81" t="str">
         <v>composite</v>
       </c>
       <c r="H81" t="str">
-        <v>SEMI-SOFT</v>
+        <v>2s10s</v>
       </c>
       <c r="I81" t="str">
         <v>lognormal</v>
@@ -15082,10 +15082,10 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
-        <v>2s10s</v>
+        <v>XLPXLY</v>
       </c>
       <c r="B82" t="str">
-        <v>Rates</v>
+        <v>Equities</v>
       </c>
       <c r="C82" t="str">
         <v>USD</v>
@@ -15097,13 +15097,13 @@
         <v>1</v>
       </c>
       <c r="F82" t="str">
-        <v>SHY -3.86, IEF 1</v>
+        <v>Staples/Discretionary</v>
       </c>
       <c r="G82" t="str">
         <v>composite</v>
       </c>
       <c r="H82" t="str">
-        <v>2s10s</v>
+        <v>XLPXLY</v>
       </c>
       <c r="I82" t="str">
         <v>lognormal</v>
@@ -15114,42 +15114,42 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="str">
-        <v>XLPXLY</v>
+        <v>UNCERTAINTY</v>
       </c>
       <c r="B83" t="str">
-        <v>Equities</v>
+        <v>Econ</v>
       </c>
       <c r="C83" t="str">
         <v>USD</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="str">
-        <v>Staples/Discretionary</v>
+        <v>Economic Policy Uncertainty Index for United States</v>
       </c>
       <c r="G83" t="str">
-        <v>composite</v>
+        <v>fred</v>
       </c>
       <c r="H83" t="str">
-        <v>XLPXLY</v>
+        <v>USEPUINDXD</v>
       </c>
       <c r="I83" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J83">
-        <v>1E-4</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
-        <v>UNCERTAINTY</v>
+        <v>BTC</v>
       </c>
       <c r="B84" t="str">
-        <v>Econ</v>
+        <v>Currencies</v>
       </c>
       <c r="C84" t="str">
         <v>USD</v>
@@ -15161,27 +15161,27 @@
         <v>0</v>
       </c>
       <c r="F84" t="str">
-        <v>Economic Policy Uncertainty Index for United States</v>
+        <v>-</v>
       </c>
       <c r="G84" t="str">
-        <v>fred</v>
+        <v>lmxl</v>
       </c>
       <c r="H84" t="str">
-        <v>USEPUINDXD</v>
+        <v>BTC1_price</v>
       </c>
       <c r="I84" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J84">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
-        <v>BTC</v>
+        <v>BTC_vol</v>
       </c>
       <c r="B85" t="str">
-        <v>Currencies</v>
+        <v>Vol</v>
       </c>
       <c r="C85" t="str">
         <v>USD</v>
@@ -15199,44 +15199,12 @@
         <v>lmxl</v>
       </c>
       <c r="H85" t="str">
-        <v>BTC1_price</v>
+        <v>BTC1_atm</v>
       </c>
       <c r="I85" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J85">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" t="str">
-        <v>BTC_vol</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Vol</v>
-      </c>
-      <c r="C86" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D86">
-        <v>0</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86" t="str">
-        <v>-</v>
-      </c>
-      <c r="G86" t="str">
-        <v>lmxl</v>
-      </c>
-      <c r="H86" t="str">
-        <v>BTC1_atm</v>
-      </c>
-      <c r="I86" t="str">
-        <v>normal</v>
-      </c>
-      <c r="J86">
         <v>-0.01</v>
       </c>
     </row>
@@ -15247,7 +15215,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9123E77-EA56-403E-A728-B01259D22573}">
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
@@ -15287,11 +15255,11 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A74">_xlfn._xlws.FILTER(data[factor_name],(data[Active])*(data[source]="yfinance"))</f>
+        <f t="array" ref="A2:A73">_xlfn._xlws.FILTER(data[factor_name],(data[Active])*(data[source]="yfinance"))</f>
         <v>SPY</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:J74">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
+        <f t="array" ref="B2:J73">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
         <v>Equities</v>
       </c>
       <c r="C2" t="str">
@@ -16057,7 +16025,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
-        <v>GPZ</v>
+        <v>PFF</v>
       </c>
       <c r="B26" t="str">
         <v>Equities</v>
@@ -16072,13 +16040,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="str">
-        <v>Private Alts</v>
+        <v>Preferred</v>
       </c>
       <c r="G26" t="str">
         <v>yfinance</v>
       </c>
       <c r="H26" t="str">
-        <v>GPZ</v>
+        <v>PFF</v>
       </c>
       <c r="I26" t="str">
         <v>lognormal</v>
@@ -16089,13 +16057,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
-        <v>PFF</v>
+        <v>FEZ</v>
       </c>
       <c r="B27" t="str">
         <v>Equities</v>
       </c>
       <c r="C27" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -16104,13 +16072,13 @@
         <v>0</v>
       </c>
       <c r="F27" t="str">
-        <v>Preferred</v>
+        <v>Eurostoxx 50</v>
       </c>
       <c r="G27" t="str">
         <v>yfinance</v>
       </c>
       <c r="H27" t="str">
-        <v>PFF</v>
+        <v>FEZ</v>
       </c>
       <c r="I27" t="str">
         <v>lognormal</v>
@@ -16121,13 +16089,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <v>FEZ</v>
+        <v>EWU</v>
       </c>
       <c r="B28" t="str">
         <v>Equities</v>
       </c>
       <c r="C28" t="str">
-        <v>EUR</v>
+        <v>GBP</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -16136,13 +16104,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="str">
-        <v>Eurostoxx 50</v>
+        <v>FTSE 100</v>
       </c>
       <c r="G28" t="str">
         <v>yfinance</v>
       </c>
       <c r="H28" t="str">
-        <v>FEZ</v>
+        <v>EWU</v>
       </c>
       <c r="I28" t="str">
         <v>lognormal</v>
@@ -16153,13 +16121,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <v>EWU</v>
+        <v>DAX</v>
       </c>
       <c r="B29" t="str">
         <v>Equities</v>
       </c>
       <c r="C29" t="str">
-        <v>GBP</v>
+        <v>EUR</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -16168,13 +16136,13 @@
         <v>0</v>
       </c>
       <c r="F29" t="str">
-        <v>FTSE 100</v>
+        <v>DAX (Germany)</v>
       </c>
       <c r="G29" t="str">
         <v>yfinance</v>
       </c>
       <c r="H29" t="str">
-        <v>EWU</v>
+        <v>DAX</v>
       </c>
       <c r="I29" t="str">
         <v>lognormal</v>
@@ -16185,13 +16153,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <v>DAX</v>
+        <v>EWC</v>
       </c>
       <c r="B30" t="str">
         <v>Equities</v>
       </c>
       <c r="C30" t="str">
-        <v>EUR</v>
+        <v>CAD</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -16200,13 +16168,13 @@
         <v>0</v>
       </c>
       <c r="F30" t="str">
-        <v>DAX (Germany)</v>
+        <v>MSCI Canada</v>
       </c>
       <c r="G30" t="str">
         <v>yfinance</v>
       </c>
       <c r="H30" t="str">
-        <v>DAX</v>
+        <v>EWC</v>
       </c>
       <c r="I30" t="str">
         <v>lognormal</v>
@@ -16217,13 +16185,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
-        <v>EWC</v>
+        <v>EWI</v>
       </c>
       <c r="B31" t="str">
         <v>Equities</v>
       </c>
       <c r="C31" t="str">
-        <v>CAD</v>
+        <v>EUR</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -16232,13 +16200,13 @@
         <v>0</v>
       </c>
       <c r="F31" t="str">
-        <v>MSCI Canada</v>
+        <v>MSCI Italy</v>
       </c>
       <c r="G31" t="str">
         <v>yfinance</v>
       </c>
       <c r="H31" t="str">
-        <v>EWC</v>
+        <v>EWI</v>
       </c>
       <c r="I31" t="str">
         <v>lognormal</v>
@@ -16249,13 +16217,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
-        <v>EWI</v>
+        <v>^N225</v>
       </c>
       <c r="B32" t="str">
         <v>Equities</v>
       </c>
       <c r="C32" t="str">
-        <v>EUR</v>
+        <v>JPY</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -16264,13 +16232,13 @@
         <v>0</v>
       </c>
       <c r="F32" t="str">
-        <v>MSCI Italy</v>
+        <v>Nikkei 225</v>
       </c>
       <c r="G32" t="str">
         <v>yfinance</v>
       </c>
       <c r="H32" t="str">
-        <v>EWI</v>
+        <v>^N225</v>
       </c>
       <c r="I32" t="str">
         <v>lognormal</v>
@@ -16281,13 +16249,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
-        <v>^N225</v>
+        <v>FXI</v>
       </c>
       <c r="B33" t="str">
         <v>Equities</v>
       </c>
       <c r="C33" t="str">
-        <v>JPY</v>
+        <v>CNH</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -16296,13 +16264,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="str">
-        <v>Nikkei 225</v>
+        <v>China Large-Cap</v>
       </c>
       <c r="G33" t="str">
         <v>yfinance</v>
       </c>
       <c r="H33" t="str">
-        <v>^N225</v>
+        <v>FXI</v>
       </c>
       <c r="I33" t="str">
         <v>lognormal</v>
@@ -16313,7 +16281,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
-        <v>FXI</v>
+        <v>ASHR</v>
       </c>
       <c r="B34" t="str">
         <v>Equities</v>
@@ -16328,13 +16296,13 @@
         <v>0</v>
       </c>
       <c r="F34" t="str">
-        <v>China Large-Cap</v>
+        <v>CSI 300 (China)</v>
       </c>
       <c r="G34" t="str">
         <v>yfinance</v>
       </c>
       <c r="H34" t="str">
-        <v>FXI</v>
+        <v>ASHR</v>
       </c>
       <c r="I34" t="str">
         <v>lognormal</v>
@@ -16345,7 +16313,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
-        <v>ASHR</v>
+        <v>KWEB</v>
       </c>
       <c r="B35" t="str">
         <v>Equities</v>
@@ -16360,13 +16328,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="str">
-        <v>CSI 300 (China)</v>
+        <v>CSI China Internet</v>
       </c>
       <c r="G35" t="str">
         <v>yfinance</v>
       </c>
       <c r="H35" t="str">
-        <v>ASHR</v>
+        <v>KWEB</v>
       </c>
       <c r="I35" t="str">
         <v>lognormal</v>
@@ -16377,13 +16345,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
-        <v>KWEB</v>
+        <v>EEM</v>
       </c>
       <c r="B36" t="str">
         <v>Equities</v>
       </c>
       <c r="C36" t="str">
-        <v>CNH</v>
+        <v>EM</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -16392,13 +16360,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="str">
-        <v>CSI China Internet</v>
+        <v>MSCI EM</v>
       </c>
       <c r="G36" t="str">
         <v>yfinance</v>
       </c>
       <c r="H36" t="str">
-        <v>KWEB</v>
+        <v>EEM</v>
       </c>
       <c r="I36" t="str">
         <v>lognormal</v>
@@ -16409,13 +16377,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
-        <v>EEM</v>
+        <v>LQD</v>
       </c>
       <c r="B37" t="str">
-        <v>Equities</v>
+        <v>Credit</v>
       </c>
       <c r="C37" t="str">
-        <v>EM</v>
+        <v>USD</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -16424,13 +16392,13 @@
         <v>0</v>
       </c>
       <c r="F37" t="str">
-        <v>MSCI EM</v>
+        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
       </c>
       <c r="G37" t="str">
         <v>yfinance</v>
       </c>
       <c r="H37" t="str">
-        <v>EEM</v>
+        <v>LQD</v>
       </c>
       <c r="I37" t="str">
         <v>lognormal</v>
@@ -16441,7 +16409,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
-        <v>LQD</v>
+        <v>BSV</v>
       </c>
       <c r="B38" t="str">
         <v>Credit</v>
@@ -16456,13 +16424,13 @@
         <v>0</v>
       </c>
       <c r="F38" t="str">
-        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
+        <v>Vanguard Short-Term Bond Index Fund ETF</v>
       </c>
       <c r="G38" t="str">
         <v>yfinance</v>
       </c>
       <c r="H38" t="str">
-        <v>LQD</v>
+        <v>BSV</v>
       </c>
       <c r="I38" t="str">
         <v>lognormal</v>
@@ -16473,7 +16441,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
-        <v>BSV</v>
+        <v>HYG</v>
       </c>
       <c r="B39" t="str">
         <v>Credit</v>
@@ -16488,13 +16456,13 @@
         <v>0</v>
       </c>
       <c r="F39" t="str">
-        <v>Vanguard Short-Term Bond Index Fund ETF</v>
+        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
       </c>
       <c r="G39" t="str">
         <v>yfinance</v>
       </c>
       <c r="H39" t="str">
-        <v>BSV</v>
+        <v>HYG</v>
       </c>
       <c r="I39" t="str">
         <v>lognormal</v>
@@ -16505,7 +16473,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
-        <v>HYG</v>
+        <v>LQDH</v>
       </c>
       <c r="B40" t="str">
         <v>Credit</v>
@@ -16514,19 +16482,19 @@
         <v>USD</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40" t="str">
-        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
+        <v>Hedged LQD</v>
       </c>
       <c r="G40" t="str">
         <v>yfinance</v>
       </c>
       <c r="H40" t="str">
-        <v>HYG</v>
+        <v>LQDH</v>
       </c>
       <c r="I40" t="str">
         <v>lognormal</v>
@@ -16537,7 +16505,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
-        <v>LQDH</v>
+        <v>HYGH</v>
       </c>
       <c r="B41" t="str">
         <v>Credit</v>
@@ -16546,19 +16514,19 @@
         <v>USD</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41" t="str">
-        <v>Hedged LQD</v>
+        <v>Hedged HYG</v>
       </c>
       <c r="G41" t="str">
         <v>yfinance</v>
       </c>
       <c r="H41" t="str">
-        <v>LQDH</v>
+        <v>HYGH</v>
       </c>
       <c r="I41" t="str">
         <v>lognormal</v>
@@ -16569,7 +16537,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
-        <v>HYGH</v>
+        <v>BKLN</v>
       </c>
       <c r="B42" t="str">
         <v>Credit</v>
@@ -16584,13 +16552,13 @@
         <v>0</v>
       </c>
       <c r="F42" t="str">
-        <v>Hedged HYG</v>
+        <v>Bank Loans</v>
       </c>
       <c r="G42" t="str">
         <v>yfinance</v>
       </c>
       <c r="H42" t="str">
-        <v>HYGH</v>
+        <v>BKLN</v>
       </c>
       <c r="I42" t="str">
         <v>lognormal</v>
@@ -16601,7 +16569,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
-        <v>BKLN</v>
+        <v>AGG</v>
       </c>
       <c r="B43" t="str">
         <v>Credit</v>
@@ -16616,13 +16584,13 @@
         <v>0</v>
       </c>
       <c r="F43" t="str">
-        <v>Bank Loans</v>
+        <v>US Agg</v>
       </c>
       <c r="G43" t="str">
         <v>yfinance</v>
       </c>
       <c r="H43" t="str">
-        <v>BKLN</v>
+        <v>AGG</v>
       </c>
       <c r="I43" t="str">
         <v>lognormal</v>
@@ -16633,10 +16601,10 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
-        <v>AGG</v>
+        <v>^TNX</v>
       </c>
       <c r="B44" t="str">
-        <v>Credit</v>
+        <v>Rates</v>
       </c>
       <c r="C44" t="str">
         <v>USD</v>
@@ -16648,24 +16616,24 @@
         <v>0</v>
       </c>
       <c r="F44" t="str">
-        <v>US Agg</v>
+        <v>CBOE Interest Rate 10 Year</v>
       </c>
       <c r="G44" t="str">
         <v>yfinance</v>
       </c>
       <c r="H44" t="str">
-        <v>AGG</v>
+        <v>^TNX</v>
       </c>
       <c r="I44" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J44">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
-        <v>^TNX</v>
+        <v>SHY</v>
       </c>
       <c r="B45" t="str">
         <v>Rates</v>
@@ -16680,24 +16648,24 @@
         <v>0</v>
       </c>
       <c r="F45" t="str">
-        <v>CBOE Interest Rate 10 Year</v>
+        <v>1-3 Year Treasury</v>
       </c>
       <c r="G45" t="str">
         <v>yfinance</v>
       </c>
       <c r="H45" t="str">
-        <v>^TNX</v>
+        <v>SHY</v>
       </c>
       <c r="I45" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J45">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
-        <v>SHY</v>
+        <v>IEI</v>
       </c>
       <c r="B46" t="str">
         <v>Rates</v>
@@ -16712,13 +16680,13 @@
         <v>0</v>
       </c>
       <c r="F46" t="str">
-        <v>1-3 Year Treasury</v>
+        <v>3-7 Year Treasury</v>
       </c>
       <c r="G46" t="str">
         <v>yfinance</v>
       </c>
       <c r="H46" t="str">
-        <v>SHY</v>
+        <v>IEI</v>
       </c>
       <c r="I46" t="str">
         <v>lognormal</v>
@@ -16729,7 +16697,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
-        <v>IEI</v>
+        <v>IEF</v>
       </c>
       <c r="B47" t="str">
         <v>Rates</v>
@@ -16738,19 +16706,19 @@
         <v>USD</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47" t="str">
-        <v>3-7 Year Treasury</v>
+        <v>7-10 Year Treasury</v>
       </c>
       <c r="G47" t="str">
         <v>yfinance</v>
       </c>
       <c r="H47" t="str">
-        <v>IEI</v>
+        <v>IEF</v>
       </c>
       <c r="I47" t="str">
         <v>lognormal</v>
@@ -16761,7 +16729,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
-        <v>IEF</v>
+        <v>TLT</v>
       </c>
       <c r="B48" t="str">
         <v>Rates</v>
@@ -16770,19 +16738,19 @@
         <v>USD</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="str">
-        <v>7-10 Year Treasury</v>
+        <v>20+ Year Treasury</v>
       </c>
       <c r="G48" t="str">
         <v>yfinance</v>
       </c>
       <c r="H48" t="str">
-        <v>IEF</v>
+        <v>TLT</v>
       </c>
       <c r="I48" t="str">
         <v>lognormal</v>
@@ -16793,7 +16761,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
-        <v>TLT</v>
+        <v>TIP</v>
       </c>
       <c r="B49" t="str">
         <v>Rates</v>
@@ -16808,13 +16776,13 @@
         <v>0</v>
       </c>
       <c r="F49" t="str">
-        <v>20+ Year Treasury</v>
+        <v>iShares TIPS Bond ETF</v>
       </c>
       <c r="G49" t="str">
         <v>yfinance</v>
       </c>
       <c r="H49" t="str">
-        <v>TLT</v>
+        <v>TIP</v>
       </c>
       <c r="I49" t="str">
         <v>lognormal</v>
@@ -16825,7 +16793,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
-        <v>TIP</v>
+        <v>VTIP</v>
       </c>
       <c r="B50" t="str">
         <v>Rates</v>
@@ -16840,13 +16808,13 @@
         <v>0</v>
       </c>
       <c r="F50" t="str">
-        <v>iShares TIPS Bond ETF</v>
+        <v>Short-Term Inflation-Protected Securities ETF</v>
       </c>
       <c r="G50" t="str">
         <v>yfinance</v>
       </c>
       <c r="H50" t="str">
-        <v>TIP</v>
+        <v>VTIP</v>
       </c>
       <c r="I50" t="str">
         <v>lognormal</v>
@@ -16857,7 +16825,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
-        <v>VTIP</v>
+        <v>AGNC</v>
       </c>
       <c r="B51" t="str">
         <v>Rates</v>
@@ -16872,13 +16840,13 @@
         <v>0</v>
       </c>
       <c r="F51" t="str">
-        <v>Short-Term Inflation-Protected Securities ETF</v>
+        <v>AGNC Investment Corp.</v>
       </c>
       <c r="G51" t="str">
         <v>yfinance</v>
       </c>
       <c r="H51" t="str">
-        <v>VTIP</v>
+        <v>AGNC</v>
       </c>
       <c r="I51" t="str">
         <v>lognormal</v>
@@ -16889,7 +16857,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
-        <v>AGNC</v>
+        <v>VMBS</v>
       </c>
       <c r="B52" t="str">
         <v>Rates</v>
@@ -16904,13 +16872,13 @@
         <v>0</v>
       </c>
       <c r="F52" t="str">
-        <v>AGNC Investment Corp.</v>
+        <v>Mortgage-Backed Securities ETF</v>
       </c>
       <c r="G52" t="str">
         <v>yfinance</v>
       </c>
       <c r="H52" t="str">
-        <v>AGNC</v>
+        <v>VMBS</v>
       </c>
       <c r="I52" t="str">
         <v>lognormal</v>
@@ -16921,7 +16889,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
-        <v>VMBS</v>
+        <v>CMBS</v>
       </c>
       <c r="B53" t="str">
         <v>Rates</v>
@@ -16936,13 +16904,13 @@
         <v>0</v>
       </c>
       <c r="F53" t="str">
-        <v>Mortgage-Backed Securities ETF</v>
+        <v>iShares CMBS ETF</v>
       </c>
       <c r="G53" t="str">
         <v>yfinance</v>
       </c>
       <c r="H53" t="str">
-        <v>VMBS</v>
+        <v>CMBS</v>
       </c>
       <c r="I53" t="str">
         <v>lognormal</v>
@@ -16953,13 +16921,13 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
-        <v>CMBS</v>
+        <v>EMB</v>
       </c>
       <c r="B54" t="str">
         <v>Rates</v>
       </c>
       <c r="C54" t="str">
-        <v>USD</v>
+        <v>EM</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -16968,13 +16936,13 @@
         <v>0</v>
       </c>
       <c r="F54" t="str">
-        <v>iShares CMBS ETF</v>
+        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
       </c>
       <c r="G54" t="str">
         <v>yfinance</v>
       </c>
       <c r="H54" t="str">
-        <v>CMBS</v>
+        <v>EMB</v>
       </c>
       <c r="I54" t="str">
         <v>lognormal</v>
@@ -16985,13 +16953,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
-        <v>EMB</v>
+        <v>GLD</v>
       </c>
       <c r="B55" t="str">
-        <v>Rates</v>
+        <v>Commodities</v>
       </c>
       <c r="C55" t="str">
-        <v>EM</v>
+        <v>USD</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -17000,13 +16968,13 @@
         <v>0</v>
       </c>
       <c r="F55" t="str">
-        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
+        <v>SPDR Gold Shares</v>
       </c>
       <c r="G55" t="str">
         <v>yfinance</v>
       </c>
       <c r="H55" t="str">
-        <v>EMB</v>
+        <v>GLD</v>
       </c>
       <c r="I55" t="str">
         <v>lognormal</v>
@@ -17017,7 +16985,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
-        <v>GLD</v>
+        <v>SLV</v>
       </c>
       <c r="B56" t="str">
         <v>Commodities</v>
@@ -17032,13 +17000,13 @@
         <v>0</v>
       </c>
       <c r="F56" t="str">
-        <v>SPDR Gold Shares</v>
+        <v>iShares Silver Trust</v>
       </c>
       <c r="G56" t="str">
         <v>yfinance</v>
       </c>
       <c r="H56" t="str">
-        <v>GLD</v>
+        <v>SLV</v>
       </c>
       <c r="I56" t="str">
         <v>lognormal</v>
@@ -17049,7 +17017,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
-        <v>SLV</v>
+        <v>USO</v>
       </c>
       <c r="B57" t="str">
         <v>Commodities</v>
@@ -17064,13 +17032,13 @@
         <v>0</v>
       </c>
       <c r="F57" t="str">
-        <v>iShares Silver Trust</v>
+        <v>United States Oil Fund</v>
       </c>
       <c r="G57" t="str">
         <v>yfinance</v>
       </c>
       <c r="H57" t="str">
-        <v>SLV</v>
+        <v>USO</v>
       </c>
       <c r="I57" t="str">
         <v>lognormal</v>
@@ -17081,10 +17049,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
-        <v>USO</v>
+        <v>UUP</v>
       </c>
       <c r="B58" t="str">
-        <v>Commodities</v>
+        <v>Currencies</v>
       </c>
       <c r="C58" t="str">
         <v>USD</v>
@@ -17096,13 +17064,13 @@
         <v>0</v>
       </c>
       <c r="F58" t="str">
-        <v>United States Oil Fund</v>
+        <v>Invesco DB US Dollar Index Bullish Fund</v>
       </c>
       <c r="G58" t="str">
         <v>yfinance</v>
       </c>
       <c r="H58" t="str">
-        <v>USO</v>
+        <v>UUP</v>
       </c>
       <c r="I58" t="str">
         <v>lognormal</v>
@@ -17113,7 +17081,7 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
-        <v>UUP</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="B59" t="str">
         <v>Currencies</v>
@@ -17128,13 +17096,13 @@
         <v>0</v>
       </c>
       <c r="F59" t="str">
-        <v>Invesco DB US Dollar Index Bullish Fund</v>
+        <v>U.S. Dollar Index</v>
       </c>
       <c r="G59" t="str">
         <v>yfinance</v>
       </c>
       <c r="H59" t="str">
-        <v>UUP</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="I59" t="str">
         <v>lognormal</v>
@@ -17145,13 +17113,13 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
-        <v>DX-Y.NYB</v>
+        <v>FXE</v>
       </c>
       <c r="B60" t="str">
         <v>Currencies</v>
       </c>
       <c r="C60" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -17160,13 +17128,13 @@
         <v>0</v>
       </c>
       <c r="F60" t="str">
-        <v>U.S. Dollar Index</v>
+        <v>Invesco CurrencyShares Euro Trust</v>
       </c>
       <c r="G60" t="str">
         <v>yfinance</v>
       </c>
       <c r="H60" t="str">
-        <v>DX-Y.NYB</v>
+        <v>FXE</v>
       </c>
       <c r="I60" t="str">
         <v>lognormal</v>
@@ -17177,7 +17145,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
-        <v>FXE</v>
+        <v>FXF</v>
       </c>
       <c r="B61" t="str">
         <v>Currencies</v>
@@ -17192,13 +17160,13 @@
         <v>0</v>
       </c>
       <c r="F61" t="str">
-        <v>Invesco CurrencyShares Euro Trust</v>
+        <v>Invesco CurrencyShares Swiss Franc Trust</v>
       </c>
       <c r="G61" t="str">
         <v>yfinance</v>
       </c>
       <c r="H61" t="str">
-        <v>FXE</v>
+        <v>FXF</v>
       </c>
       <c r="I61" t="str">
         <v>lognormal</v>
@@ -17209,13 +17177,13 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
-        <v>FXF</v>
+        <v>FXA</v>
       </c>
       <c r="B62" t="str">
         <v>Currencies</v>
       </c>
       <c r="C62" t="str">
-        <v>EUR</v>
+        <v>Commod</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -17224,13 +17192,13 @@
         <v>0</v>
       </c>
       <c r="F62" t="str">
-        <v>Invesco CurrencyShares Swiss Franc Trust</v>
+        <v>Invesco CurrencyShares Australian Dollar Trust</v>
       </c>
       <c r="G62" t="str">
         <v>yfinance</v>
       </c>
       <c r="H62" t="str">
-        <v>FXF</v>
+        <v>FXA</v>
       </c>
       <c r="I62" t="str">
         <v>lognormal</v>
@@ -17241,13 +17209,13 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
-        <v>FXA</v>
+        <v>FXB</v>
       </c>
       <c r="B63" t="str">
         <v>Currencies</v>
       </c>
       <c r="C63" t="str">
-        <v>Commod</v>
+        <v>GBP</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -17256,13 +17224,13 @@
         <v>0</v>
       </c>
       <c r="F63" t="str">
-        <v>Invesco CurrencyShares Australian Dollar Trust</v>
+        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
       </c>
       <c r="G63" t="str">
         <v>yfinance</v>
       </c>
       <c r="H63" t="str">
-        <v>FXA</v>
+        <v>FXB</v>
       </c>
       <c r="I63" t="str">
         <v>lognormal</v>
@@ -17273,13 +17241,13 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
-        <v>FXB</v>
+        <v>FXC</v>
       </c>
       <c r="B64" t="str">
         <v>Currencies</v>
       </c>
       <c r="C64" t="str">
-        <v>GBP</v>
+        <v>USD</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -17288,13 +17256,13 @@
         <v>0</v>
       </c>
       <c r="F64" t="str">
-        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
+        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
       </c>
       <c r="G64" t="str">
         <v>yfinance</v>
       </c>
       <c r="H64" t="str">
-        <v>FXB</v>
+        <v>FXC</v>
       </c>
       <c r="I64" t="str">
         <v>lognormal</v>
@@ -17305,13 +17273,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
-        <v>FXC</v>
+        <v>FXY</v>
       </c>
       <c r="B65" t="str">
         <v>Currencies</v>
       </c>
       <c r="C65" t="str">
-        <v>USD</v>
+        <v>JPY</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -17320,13 +17288,13 @@
         <v>0</v>
       </c>
       <c r="F65" t="str">
-        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
+        <v>Invesco CurrencyShares Japanese Yen Trust</v>
       </c>
       <c r="G65" t="str">
         <v>yfinance</v>
       </c>
       <c r="H65" t="str">
-        <v>FXC</v>
+        <v>FXY</v>
       </c>
       <c r="I65" t="str">
         <v>lognormal</v>
@@ -17337,13 +17305,13 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
-        <v>FXY</v>
+        <v>^VIX</v>
       </c>
       <c r="B66" t="str">
-        <v>Currencies</v>
+        <v>Vol</v>
       </c>
       <c r="C66" t="str">
-        <v>JPY</v>
+        <v>USD</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -17352,24 +17320,24 @@
         <v>0</v>
       </c>
       <c r="F66" t="str">
-        <v>Invesco CurrencyShares Japanese Yen Trust</v>
+        <v>CBOE Volatility Index</v>
       </c>
       <c r="G66" t="str">
         <v>yfinance</v>
       </c>
       <c r="H66" t="str">
-        <v>FXY</v>
+        <v>^VIX</v>
       </c>
       <c r="I66" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J66">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
-        <v>^VIX</v>
+        <v>VXX</v>
       </c>
       <c r="B67" t="str">
         <v>Vol</v>
@@ -17384,13 +17352,13 @@
         <v>0</v>
       </c>
       <c r="F67" t="str">
-        <v>CBOE Volatility Index</v>
+        <v>VIX Short-Term Futures ETN</v>
       </c>
       <c r="G67" t="str">
         <v>yfinance</v>
       </c>
       <c r="H67" t="str">
-        <v>^VIX</v>
+        <v>VXX</v>
       </c>
       <c r="I67" t="str">
         <v>normal</v>
@@ -17401,7 +17369,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
-        <v>VXX</v>
+        <v>^VIX3M</v>
       </c>
       <c r="B68" t="str">
         <v>Vol</v>
@@ -17416,13 +17384,13 @@
         <v>0</v>
       </c>
       <c r="F68" t="str">
-        <v>VIX Short-Term Futures ETN</v>
+        <v>CBOE S&amp;P 500 3-Month Volatility</v>
       </c>
       <c r="G68" t="str">
         <v>yfinance</v>
       </c>
       <c r="H68" t="str">
-        <v>VXX</v>
+        <v>^VIX3M</v>
       </c>
       <c r="I68" t="str">
         <v>normal</v>
@@ -17433,7 +17401,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
-        <v>^VIX3M</v>
+        <v>^MOVE</v>
       </c>
       <c r="B69" t="str">
         <v>Vol</v>
@@ -17448,13 +17416,13 @@
         <v>0</v>
       </c>
       <c r="F69" t="str">
-        <v>CBOE S&amp;P 500 3-Month Volatility</v>
+        <v>ICE BofAML MOVE Index</v>
       </c>
       <c r="G69" t="str">
         <v>yfinance</v>
       </c>
       <c r="H69" t="str">
-        <v>^VIX3M</v>
+        <v>^MOVE</v>
       </c>
       <c r="I69" t="str">
         <v>normal</v>
@@ -17465,7 +17433,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
-        <v>^MOVE</v>
+        <v>^OVX</v>
       </c>
       <c r="B70" t="str">
         <v>Vol</v>
@@ -17480,13 +17448,13 @@
         <v>0</v>
       </c>
       <c r="F70" t="str">
-        <v>ICE BofAML MOVE Index</v>
+        <v>CBOE Crude Oil Volatility Index</v>
       </c>
       <c r="G70" t="str">
         <v>yfinance</v>
       </c>
       <c r="H70" t="str">
-        <v>^MOVE</v>
+        <v>^OVX</v>
       </c>
       <c r="I70" t="str">
         <v>normal</v>
@@ -17497,7 +17465,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
-        <v>^OVX</v>
+        <v>^GVZ</v>
       </c>
       <c r="B71" t="str">
         <v>Vol</v>
@@ -17512,13 +17480,13 @@
         <v>0</v>
       </c>
       <c r="F71" t="str">
-        <v>CBOE Crude Oil Volatility Index</v>
+        <v>CBOE Gold Volatility Index</v>
       </c>
       <c r="G71" t="str">
         <v>yfinance</v>
       </c>
       <c r="H71" t="str">
-        <v>^OVX</v>
+        <v>^GVZ</v>
       </c>
       <c r="I71" t="str">
         <v>normal</v>
@@ -17529,39 +17497,39 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
-        <v>^GVZ</v>
+        <v>MWTIX</v>
       </c>
       <c r="B72" t="str">
-        <v>Vol</v>
+        <v>Portfolio</v>
       </c>
       <c r="C72" t="str">
         <v>USD</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72" t="str">
-        <v>CBOE Gold Volatility Index</v>
+        <v>TCW MetWest Total Return Bd I</v>
       </c>
       <c r="G72" t="str">
         <v>yfinance</v>
       </c>
       <c r="H72" t="str">
-        <v>^GVZ</v>
+        <v>MWTIX</v>
       </c>
       <c r="I72" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J72">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
-        <v>MWTIX</v>
+        <v>FCNTX</v>
       </c>
       <c r="B73" t="str">
         <v>Portfolio</v>
@@ -17570,56 +17538,24 @@
         <v>USD</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73" t="str">
-        <v>TCW MetWest Total Return Bd I</v>
+        <v>Fidelity Contrafund</v>
       </c>
       <c r="G73" t="str">
         <v>yfinance</v>
       </c>
       <c r="H73" t="str">
-        <v>MWTIX</v>
+        <v>FCNTX</v>
       </c>
       <c r="I73" t="str">
         <v>lognormal</v>
       </c>
       <c r="J73">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" t="str">
-        <v>FCNTX</v>
-      </c>
-      <c r="B74" t="str">
-        <v>Portfolio</v>
-      </c>
-      <c r="C74" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D74">
-        <v>0</v>
-      </c>
-      <c r="E74">
-        <v>0</v>
-      </c>
-      <c r="F74" t="str">
-        <v>Fidelity Contrafund</v>
-      </c>
-      <c r="G74" t="str">
-        <v>yfinance</v>
-      </c>
-      <c r="H74" t="str">
-        <v>FCNTX</v>
-      </c>
-      <c r="I74" t="str">
-        <v>lognormal</v>
-      </c>
-      <c r="J74">
         <v>1E-4</v>
       </c>
     </row>
@@ -17631,7 +17567,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2977BD7F-9323-4F6D-98BF-C1B39119DCDE}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
@@ -17671,11 +17607,11 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A86">_xlfn._xlws.FILTER(data[factor_name],data[Active]*(data[client]=0))</f>
+        <f t="array" ref="A2:A85">_xlfn._xlws.FILTER(data[factor_name],data[Active]*(data[client]=0))</f>
         <v>SPY</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:J86">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
+        <f t="array" ref="B2:J85">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
         <v>Equities</v>
       </c>
       <c r="C2" t="str">
@@ -18441,7 +18377,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
-        <v>GPZ</v>
+        <v>PFF</v>
       </c>
       <c r="B26" t="str">
         <v>Equities</v>
@@ -18456,13 +18392,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="str">
-        <v>Private Alts</v>
+        <v>Preferred</v>
       </c>
       <c r="G26" t="str">
         <v>yfinance</v>
       </c>
       <c r="H26" t="str">
-        <v>GPZ</v>
+        <v>PFF</v>
       </c>
       <c r="I26" t="str">
         <v>lognormal</v>
@@ -18473,13 +18409,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
-        <v>PFF</v>
+        <v>FEZ</v>
       </c>
       <c r="B27" t="str">
         <v>Equities</v>
       </c>
       <c r="C27" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -18488,13 +18424,13 @@
         <v>0</v>
       </c>
       <c r="F27" t="str">
-        <v>Preferred</v>
+        <v>Eurostoxx 50</v>
       </c>
       <c r="G27" t="str">
         <v>yfinance</v>
       </c>
       <c r="H27" t="str">
-        <v>PFF</v>
+        <v>FEZ</v>
       </c>
       <c r="I27" t="str">
         <v>lognormal</v>
@@ -18505,13 +18441,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <v>FEZ</v>
+        <v>EWU</v>
       </c>
       <c r="B28" t="str">
         <v>Equities</v>
       </c>
       <c r="C28" t="str">
-        <v>EUR</v>
+        <v>GBP</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -18520,13 +18456,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="str">
-        <v>Eurostoxx 50</v>
+        <v>FTSE 100</v>
       </c>
       <c r="G28" t="str">
         <v>yfinance</v>
       </c>
       <c r="H28" t="str">
-        <v>FEZ</v>
+        <v>EWU</v>
       </c>
       <c r="I28" t="str">
         <v>lognormal</v>
@@ -18537,13 +18473,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <v>EWU</v>
+        <v>DAX</v>
       </c>
       <c r="B29" t="str">
         <v>Equities</v>
       </c>
       <c r="C29" t="str">
-        <v>GBP</v>
+        <v>EUR</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -18552,13 +18488,13 @@
         <v>0</v>
       </c>
       <c r="F29" t="str">
-        <v>FTSE 100</v>
+        <v>DAX (Germany)</v>
       </c>
       <c r="G29" t="str">
         <v>yfinance</v>
       </c>
       <c r="H29" t="str">
-        <v>EWU</v>
+        <v>DAX</v>
       </c>
       <c r="I29" t="str">
         <v>lognormal</v>
@@ -18569,13 +18505,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <v>DAX</v>
+        <v>EWC</v>
       </c>
       <c r="B30" t="str">
         <v>Equities</v>
       </c>
       <c r="C30" t="str">
-        <v>EUR</v>
+        <v>CAD</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -18584,13 +18520,13 @@
         <v>0</v>
       </c>
       <c r="F30" t="str">
-        <v>DAX (Germany)</v>
+        <v>MSCI Canada</v>
       </c>
       <c r="G30" t="str">
         <v>yfinance</v>
       </c>
       <c r="H30" t="str">
-        <v>DAX</v>
+        <v>EWC</v>
       </c>
       <c r="I30" t="str">
         <v>lognormal</v>
@@ -18601,13 +18537,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
-        <v>EWC</v>
+        <v>EWI</v>
       </c>
       <c r="B31" t="str">
         <v>Equities</v>
       </c>
       <c r="C31" t="str">
-        <v>CAD</v>
+        <v>EUR</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -18616,13 +18552,13 @@
         <v>0</v>
       </c>
       <c r="F31" t="str">
-        <v>MSCI Canada</v>
+        <v>MSCI Italy</v>
       </c>
       <c r="G31" t="str">
         <v>yfinance</v>
       </c>
       <c r="H31" t="str">
-        <v>EWC</v>
+        <v>EWI</v>
       </c>
       <c r="I31" t="str">
         <v>lognormal</v>
@@ -18633,13 +18569,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
-        <v>EWI</v>
+        <v>^N225</v>
       </c>
       <c r="B32" t="str">
         <v>Equities</v>
       </c>
       <c r="C32" t="str">
-        <v>EUR</v>
+        <v>JPY</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -18648,13 +18584,13 @@
         <v>0</v>
       </c>
       <c r="F32" t="str">
-        <v>MSCI Italy</v>
+        <v>Nikkei 225</v>
       </c>
       <c r="G32" t="str">
         <v>yfinance</v>
       </c>
       <c r="H32" t="str">
-        <v>EWI</v>
+        <v>^N225</v>
       </c>
       <c r="I32" t="str">
         <v>lognormal</v>
@@ -18665,13 +18601,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
-        <v>^N225</v>
+        <v>FXI</v>
       </c>
       <c r="B33" t="str">
         <v>Equities</v>
       </c>
       <c r="C33" t="str">
-        <v>JPY</v>
+        <v>CNH</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -18680,13 +18616,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="str">
-        <v>Nikkei 225</v>
+        <v>China Large-Cap</v>
       </c>
       <c r="G33" t="str">
         <v>yfinance</v>
       </c>
       <c r="H33" t="str">
-        <v>^N225</v>
+        <v>FXI</v>
       </c>
       <c r="I33" t="str">
         <v>lognormal</v>
@@ -18697,7 +18633,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
-        <v>FXI</v>
+        <v>ASHR</v>
       </c>
       <c r="B34" t="str">
         <v>Equities</v>
@@ -18712,13 +18648,13 @@
         <v>0</v>
       </c>
       <c r="F34" t="str">
-        <v>China Large-Cap</v>
+        <v>CSI 300 (China)</v>
       </c>
       <c r="G34" t="str">
         <v>yfinance</v>
       </c>
       <c r="H34" t="str">
-        <v>FXI</v>
+        <v>ASHR</v>
       </c>
       <c r="I34" t="str">
         <v>lognormal</v>
@@ -18729,7 +18665,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
-        <v>ASHR</v>
+        <v>KWEB</v>
       </c>
       <c r="B35" t="str">
         <v>Equities</v>
@@ -18744,13 +18680,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="str">
-        <v>CSI 300 (China)</v>
+        <v>CSI China Internet</v>
       </c>
       <c r="G35" t="str">
         <v>yfinance</v>
       </c>
       <c r="H35" t="str">
-        <v>ASHR</v>
+        <v>KWEB</v>
       </c>
       <c r="I35" t="str">
         <v>lognormal</v>
@@ -18761,13 +18697,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
-        <v>KWEB</v>
+        <v>EEM</v>
       </c>
       <c r="B36" t="str">
         <v>Equities</v>
       </c>
       <c r="C36" t="str">
-        <v>CNH</v>
+        <v>EM</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -18776,13 +18712,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="str">
-        <v>CSI China Internet</v>
+        <v>MSCI EM</v>
       </c>
       <c r="G36" t="str">
         <v>yfinance</v>
       </c>
       <c r="H36" t="str">
-        <v>KWEB</v>
+        <v>EEM</v>
       </c>
       <c r="I36" t="str">
         <v>lognormal</v>
@@ -18793,13 +18729,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
-        <v>EEM</v>
+        <v>LQD</v>
       </c>
       <c r="B37" t="str">
-        <v>Equities</v>
+        <v>Credit</v>
       </c>
       <c r="C37" t="str">
-        <v>EM</v>
+        <v>USD</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -18808,13 +18744,13 @@
         <v>0</v>
       </c>
       <c r="F37" t="str">
-        <v>MSCI EM</v>
+        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
       </c>
       <c r="G37" t="str">
         <v>yfinance</v>
       </c>
       <c r="H37" t="str">
-        <v>EEM</v>
+        <v>LQD</v>
       </c>
       <c r="I37" t="str">
         <v>lognormal</v>
@@ -18825,7 +18761,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
-        <v>LQD</v>
+        <v>BSV</v>
       </c>
       <c r="B38" t="str">
         <v>Credit</v>
@@ -18840,13 +18776,13 @@
         <v>0</v>
       </c>
       <c r="F38" t="str">
-        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
+        <v>Vanguard Short-Term Bond Index Fund ETF</v>
       </c>
       <c r="G38" t="str">
         <v>yfinance</v>
       </c>
       <c r="H38" t="str">
-        <v>LQD</v>
+        <v>BSV</v>
       </c>
       <c r="I38" t="str">
         <v>lognormal</v>
@@ -18857,7 +18793,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
-        <v>BSV</v>
+        <v>HYG</v>
       </c>
       <c r="B39" t="str">
         <v>Credit</v>
@@ -18872,13 +18808,13 @@
         <v>0</v>
       </c>
       <c r="F39" t="str">
-        <v>Vanguard Short-Term Bond Index Fund ETF</v>
+        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
       </c>
       <c r="G39" t="str">
         <v>yfinance</v>
       </c>
       <c r="H39" t="str">
-        <v>BSV</v>
+        <v>HYG</v>
       </c>
       <c r="I39" t="str">
         <v>lognormal</v>
@@ -18889,7 +18825,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
-        <v>HYG</v>
+        <v>LQDH</v>
       </c>
       <c r="B40" t="str">
         <v>Credit</v>
@@ -18898,19 +18834,19 @@
         <v>USD</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40" t="str">
-        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
+        <v>Hedged LQD</v>
       </c>
       <c r="G40" t="str">
         <v>yfinance</v>
       </c>
       <c r="H40" t="str">
-        <v>HYG</v>
+        <v>LQDH</v>
       </c>
       <c r="I40" t="str">
         <v>lognormal</v>
@@ -18921,7 +18857,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
-        <v>LQDH</v>
+        <v>HYGH</v>
       </c>
       <c r="B41" t="str">
         <v>Credit</v>
@@ -18930,19 +18866,19 @@
         <v>USD</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41" t="str">
-        <v>Hedged LQD</v>
+        <v>Hedged HYG</v>
       </c>
       <c r="G41" t="str">
         <v>yfinance</v>
       </c>
       <c r="H41" t="str">
-        <v>LQDH</v>
+        <v>HYGH</v>
       </c>
       <c r="I41" t="str">
         <v>lognormal</v>
@@ -18953,7 +18889,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
-        <v>HYGH</v>
+        <v>BKLN</v>
       </c>
       <c r="B42" t="str">
         <v>Credit</v>
@@ -18968,13 +18904,13 @@
         <v>0</v>
       </c>
       <c r="F42" t="str">
-        <v>Hedged HYG</v>
+        <v>Bank Loans</v>
       </c>
       <c r="G42" t="str">
         <v>yfinance</v>
       </c>
       <c r="H42" t="str">
-        <v>HYGH</v>
+        <v>BKLN</v>
       </c>
       <c r="I42" t="str">
         <v>lognormal</v>
@@ -18985,7 +18921,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
-        <v>BKLN</v>
+        <v>AGG</v>
       </c>
       <c r="B43" t="str">
         <v>Credit</v>
@@ -19000,13 +18936,13 @@
         <v>0</v>
       </c>
       <c r="F43" t="str">
-        <v>Bank Loans</v>
+        <v>US Agg</v>
       </c>
       <c r="G43" t="str">
         <v>yfinance</v>
       </c>
       <c r="H43" t="str">
-        <v>BKLN</v>
+        <v>AGG</v>
       </c>
       <c r="I43" t="str">
         <v>lognormal</v>
@@ -19017,10 +18953,10 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
-        <v>AGG</v>
+        <v>^TNX</v>
       </c>
       <c r="B44" t="str">
-        <v>Credit</v>
+        <v>Rates</v>
       </c>
       <c r="C44" t="str">
         <v>USD</v>
@@ -19032,24 +18968,24 @@
         <v>0</v>
       </c>
       <c r="F44" t="str">
-        <v>US Agg</v>
+        <v>CBOE Interest Rate 10 Year</v>
       </c>
       <c r="G44" t="str">
         <v>yfinance</v>
       </c>
       <c r="H44" t="str">
-        <v>AGG</v>
+        <v>^TNX</v>
       </c>
       <c r="I44" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J44">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
-        <v>^TNX</v>
+        <v>SHY</v>
       </c>
       <c r="B45" t="str">
         <v>Rates</v>
@@ -19064,24 +19000,24 @@
         <v>0</v>
       </c>
       <c r="F45" t="str">
-        <v>CBOE Interest Rate 10 Year</v>
+        <v>1-3 Year Treasury</v>
       </c>
       <c r="G45" t="str">
         <v>yfinance</v>
       </c>
       <c r="H45" t="str">
-        <v>^TNX</v>
+        <v>SHY</v>
       </c>
       <c r="I45" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J45">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
-        <v>SHY</v>
+        <v>IEI</v>
       </c>
       <c r="B46" t="str">
         <v>Rates</v>
@@ -19096,13 +19032,13 @@
         <v>0</v>
       </c>
       <c r="F46" t="str">
-        <v>1-3 Year Treasury</v>
+        <v>3-7 Year Treasury</v>
       </c>
       <c r="G46" t="str">
         <v>yfinance</v>
       </c>
       <c r="H46" t="str">
-        <v>SHY</v>
+        <v>IEI</v>
       </c>
       <c r="I46" t="str">
         <v>lognormal</v>
@@ -19113,7 +19049,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
-        <v>IEI</v>
+        <v>IEF</v>
       </c>
       <c r="B47" t="str">
         <v>Rates</v>
@@ -19122,19 +19058,19 @@
         <v>USD</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47" t="str">
-        <v>3-7 Year Treasury</v>
+        <v>7-10 Year Treasury</v>
       </c>
       <c r="G47" t="str">
         <v>yfinance</v>
       </c>
       <c r="H47" t="str">
-        <v>IEI</v>
+        <v>IEF</v>
       </c>
       <c r="I47" t="str">
         <v>lognormal</v>
@@ -19145,7 +19081,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
-        <v>IEF</v>
+        <v>TLT</v>
       </c>
       <c r="B48" t="str">
         <v>Rates</v>
@@ -19154,19 +19090,19 @@
         <v>USD</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="str">
-        <v>7-10 Year Treasury</v>
+        <v>20+ Year Treasury</v>
       </c>
       <c r="G48" t="str">
         <v>yfinance</v>
       </c>
       <c r="H48" t="str">
-        <v>IEF</v>
+        <v>TLT</v>
       </c>
       <c r="I48" t="str">
         <v>lognormal</v>
@@ -19177,7 +19113,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
-        <v>TLT</v>
+        <v>TIP</v>
       </c>
       <c r="B49" t="str">
         <v>Rates</v>
@@ -19192,13 +19128,13 @@
         <v>0</v>
       </c>
       <c r="F49" t="str">
-        <v>20+ Year Treasury</v>
+        <v>iShares TIPS Bond ETF</v>
       </c>
       <c r="G49" t="str">
         <v>yfinance</v>
       </c>
       <c r="H49" t="str">
-        <v>TLT</v>
+        <v>TIP</v>
       </c>
       <c r="I49" t="str">
         <v>lognormal</v>
@@ -19209,7 +19145,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
-        <v>TIP</v>
+        <v>VTIP</v>
       </c>
       <c r="B50" t="str">
         <v>Rates</v>
@@ -19224,13 +19160,13 @@
         <v>0</v>
       </c>
       <c r="F50" t="str">
-        <v>iShares TIPS Bond ETF</v>
+        <v>Short-Term Inflation-Protected Securities ETF</v>
       </c>
       <c r="G50" t="str">
         <v>yfinance</v>
       </c>
       <c r="H50" t="str">
-        <v>TIP</v>
+        <v>VTIP</v>
       </c>
       <c r="I50" t="str">
         <v>lognormal</v>
@@ -19241,7 +19177,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
-        <v>VTIP</v>
+        <v>AGNC</v>
       </c>
       <c r="B51" t="str">
         <v>Rates</v>
@@ -19256,13 +19192,13 @@
         <v>0</v>
       </c>
       <c r="F51" t="str">
-        <v>Short-Term Inflation-Protected Securities ETF</v>
+        <v>AGNC Investment Corp.</v>
       </c>
       <c r="G51" t="str">
         <v>yfinance</v>
       </c>
       <c r="H51" t="str">
-        <v>VTIP</v>
+        <v>AGNC</v>
       </c>
       <c r="I51" t="str">
         <v>lognormal</v>
@@ -19273,7 +19209,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
-        <v>AGNC</v>
+        <v>VMBS</v>
       </c>
       <c r="B52" t="str">
         <v>Rates</v>
@@ -19288,13 +19224,13 @@
         <v>0</v>
       </c>
       <c r="F52" t="str">
-        <v>AGNC Investment Corp.</v>
+        <v>Mortgage-Backed Securities ETF</v>
       </c>
       <c r="G52" t="str">
         <v>yfinance</v>
       </c>
       <c r="H52" t="str">
-        <v>AGNC</v>
+        <v>VMBS</v>
       </c>
       <c r="I52" t="str">
         <v>lognormal</v>
@@ -19305,7 +19241,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
-        <v>VMBS</v>
+        <v>CMBS</v>
       </c>
       <c r="B53" t="str">
         <v>Rates</v>
@@ -19320,13 +19256,13 @@
         <v>0</v>
       </c>
       <c r="F53" t="str">
-        <v>Mortgage-Backed Securities ETF</v>
+        <v>iShares CMBS ETF</v>
       </c>
       <c r="G53" t="str">
         <v>yfinance</v>
       </c>
       <c r="H53" t="str">
-        <v>VMBS</v>
+        <v>CMBS</v>
       </c>
       <c r="I53" t="str">
         <v>lognormal</v>
@@ -19337,13 +19273,13 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
-        <v>CMBS</v>
+        <v>EMB</v>
       </c>
       <c r="B54" t="str">
         <v>Rates</v>
       </c>
       <c r="C54" t="str">
-        <v>USD</v>
+        <v>EM</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -19352,13 +19288,13 @@
         <v>0</v>
       </c>
       <c r="F54" t="str">
-        <v>iShares CMBS ETF</v>
+        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
       </c>
       <c r="G54" t="str">
         <v>yfinance</v>
       </c>
       <c r="H54" t="str">
-        <v>CMBS</v>
+        <v>EMB</v>
       </c>
       <c r="I54" t="str">
         <v>lognormal</v>
@@ -19369,13 +19305,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
-        <v>EMB</v>
+        <v>GLD</v>
       </c>
       <c r="B55" t="str">
-        <v>Rates</v>
+        <v>Commodities</v>
       </c>
       <c r="C55" t="str">
-        <v>EM</v>
+        <v>USD</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -19384,13 +19320,13 @@
         <v>0</v>
       </c>
       <c r="F55" t="str">
-        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
+        <v>SPDR Gold Shares</v>
       </c>
       <c r="G55" t="str">
         <v>yfinance</v>
       </c>
       <c r="H55" t="str">
-        <v>EMB</v>
+        <v>GLD</v>
       </c>
       <c r="I55" t="str">
         <v>lognormal</v>
@@ -19401,7 +19337,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
-        <v>GLD</v>
+        <v>SLV</v>
       </c>
       <c r="B56" t="str">
         <v>Commodities</v>
@@ -19416,13 +19352,13 @@
         <v>0</v>
       </c>
       <c r="F56" t="str">
-        <v>SPDR Gold Shares</v>
+        <v>iShares Silver Trust</v>
       </c>
       <c r="G56" t="str">
         <v>yfinance</v>
       </c>
       <c r="H56" t="str">
-        <v>GLD</v>
+        <v>SLV</v>
       </c>
       <c r="I56" t="str">
         <v>lognormal</v>
@@ -19433,7 +19369,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
-        <v>SLV</v>
+        <v>USO</v>
       </c>
       <c r="B57" t="str">
         <v>Commodities</v>
@@ -19448,13 +19384,13 @@
         <v>0</v>
       </c>
       <c r="F57" t="str">
-        <v>iShares Silver Trust</v>
+        <v>United States Oil Fund</v>
       </c>
       <c r="G57" t="str">
         <v>yfinance</v>
       </c>
       <c r="H57" t="str">
-        <v>SLV</v>
+        <v>USO</v>
       </c>
       <c r="I57" t="str">
         <v>lognormal</v>
@@ -19465,10 +19401,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
-        <v>USO</v>
+        <v>UUP</v>
       </c>
       <c r="B58" t="str">
-        <v>Commodities</v>
+        <v>Currencies</v>
       </c>
       <c r="C58" t="str">
         <v>USD</v>
@@ -19480,13 +19416,13 @@
         <v>0</v>
       </c>
       <c r="F58" t="str">
-        <v>United States Oil Fund</v>
+        <v>Invesco DB US Dollar Index Bullish Fund</v>
       </c>
       <c r="G58" t="str">
         <v>yfinance</v>
       </c>
       <c r="H58" t="str">
-        <v>USO</v>
+        <v>UUP</v>
       </c>
       <c r="I58" t="str">
         <v>lognormal</v>
@@ -19497,7 +19433,7 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
-        <v>UUP</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="B59" t="str">
         <v>Currencies</v>
@@ -19512,13 +19448,13 @@
         <v>0</v>
       </c>
       <c r="F59" t="str">
-        <v>Invesco DB US Dollar Index Bullish Fund</v>
+        <v>U.S. Dollar Index</v>
       </c>
       <c r="G59" t="str">
         <v>yfinance</v>
       </c>
       <c r="H59" t="str">
-        <v>UUP</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="I59" t="str">
         <v>lognormal</v>
@@ -19529,13 +19465,13 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
-        <v>DX-Y.NYB</v>
+        <v>FXE</v>
       </c>
       <c r="B60" t="str">
         <v>Currencies</v>
       </c>
       <c r="C60" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -19544,13 +19480,13 @@
         <v>0</v>
       </c>
       <c r="F60" t="str">
-        <v>U.S. Dollar Index</v>
+        <v>Invesco CurrencyShares Euro Trust</v>
       </c>
       <c r="G60" t="str">
         <v>yfinance</v>
       </c>
       <c r="H60" t="str">
-        <v>DX-Y.NYB</v>
+        <v>FXE</v>
       </c>
       <c r="I60" t="str">
         <v>lognormal</v>
@@ -19561,7 +19497,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
-        <v>FXE</v>
+        <v>FXF</v>
       </c>
       <c r="B61" t="str">
         <v>Currencies</v>
@@ -19576,13 +19512,13 @@
         <v>0</v>
       </c>
       <c r="F61" t="str">
-        <v>Invesco CurrencyShares Euro Trust</v>
+        <v>Invesco CurrencyShares Swiss Franc Trust</v>
       </c>
       <c r="G61" t="str">
         <v>yfinance</v>
       </c>
       <c r="H61" t="str">
-        <v>FXE</v>
+        <v>FXF</v>
       </c>
       <c r="I61" t="str">
         <v>lognormal</v>
@@ -19593,13 +19529,13 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
-        <v>FXF</v>
+        <v>FXA</v>
       </c>
       <c r="B62" t="str">
         <v>Currencies</v>
       </c>
       <c r="C62" t="str">
-        <v>EUR</v>
+        <v>Commod</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -19608,13 +19544,13 @@
         <v>0</v>
       </c>
       <c r="F62" t="str">
-        <v>Invesco CurrencyShares Swiss Franc Trust</v>
+        <v>Invesco CurrencyShares Australian Dollar Trust</v>
       </c>
       <c r="G62" t="str">
         <v>yfinance</v>
       </c>
       <c r="H62" t="str">
-        <v>FXF</v>
+        <v>FXA</v>
       </c>
       <c r="I62" t="str">
         <v>lognormal</v>
@@ -19625,13 +19561,13 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
-        <v>FXA</v>
+        <v>FXB</v>
       </c>
       <c r="B63" t="str">
         <v>Currencies</v>
       </c>
       <c r="C63" t="str">
-        <v>Commod</v>
+        <v>GBP</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -19640,13 +19576,13 @@
         <v>0</v>
       </c>
       <c r="F63" t="str">
-        <v>Invesco CurrencyShares Australian Dollar Trust</v>
+        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
       </c>
       <c r="G63" t="str">
         <v>yfinance</v>
       </c>
       <c r="H63" t="str">
-        <v>FXA</v>
+        <v>FXB</v>
       </c>
       <c r="I63" t="str">
         <v>lognormal</v>
@@ -19657,13 +19593,13 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
-        <v>FXB</v>
+        <v>FXC</v>
       </c>
       <c r="B64" t="str">
         <v>Currencies</v>
       </c>
       <c r="C64" t="str">
-        <v>GBP</v>
+        <v>USD</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -19672,13 +19608,13 @@
         <v>0</v>
       </c>
       <c r="F64" t="str">
-        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
+        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
       </c>
       <c r="G64" t="str">
         <v>yfinance</v>
       </c>
       <c r="H64" t="str">
-        <v>FXB</v>
+        <v>FXC</v>
       </c>
       <c r="I64" t="str">
         <v>lognormal</v>
@@ -19689,13 +19625,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
-        <v>FXC</v>
+        <v>FXY</v>
       </c>
       <c r="B65" t="str">
         <v>Currencies</v>
       </c>
       <c r="C65" t="str">
-        <v>USD</v>
+        <v>JPY</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -19704,13 +19640,13 @@
         <v>0</v>
       </c>
       <c r="F65" t="str">
-        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
+        <v>Invesco CurrencyShares Japanese Yen Trust</v>
       </c>
       <c r="G65" t="str">
         <v>yfinance</v>
       </c>
       <c r="H65" t="str">
-        <v>FXC</v>
+        <v>FXY</v>
       </c>
       <c r="I65" t="str">
         <v>lognormal</v>
@@ -19721,13 +19657,13 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
-        <v>FXY</v>
+        <v>^VIX</v>
       </c>
       <c r="B66" t="str">
-        <v>Currencies</v>
+        <v>Vol</v>
       </c>
       <c r="C66" t="str">
-        <v>JPY</v>
+        <v>USD</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -19736,24 +19672,24 @@
         <v>0</v>
       </c>
       <c r="F66" t="str">
-        <v>Invesco CurrencyShares Japanese Yen Trust</v>
+        <v>CBOE Volatility Index</v>
       </c>
       <c r="G66" t="str">
         <v>yfinance</v>
       </c>
       <c r="H66" t="str">
-        <v>FXY</v>
+        <v>^VIX</v>
       </c>
       <c r="I66" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J66">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
-        <v>^VIX</v>
+        <v>VXX</v>
       </c>
       <c r="B67" t="str">
         <v>Vol</v>
@@ -19768,13 +19704,13 @@
         <v>0</v>
       </c>
       <c r="F67" t="str">
-        <v>CBOE Volatility Index</v>
+        <v>VIX Short-Term Futures ETN</v>
       </c>
       <c r="G67" t="str">
         <v>yfinance</v>
       </c>
       <c r="H67" t="str">
-        <v>^VIX</v>
+        <v>VXX</v>
       </c>
       <c r="I67" t="str">
         <v>normal</v>
@@ -19785,7 +19721,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
-        <v>VXX</v>
+        <v>^VIX3M</v>
       </c>
       <c r="B68" t="str">
         <v>Vol</v>
@@ -19800,13 +19736,13 @@
         <v>0</v>
       </c>
       <c r="F68" t="str">
-        <v>VIX Short-Term Futures ETN</v>
+        <v>CBOE S&amp;P 500 3-Month Volatility</v>
       </c>
       <c r="G68" t="str">
         <v>yfinance</v>
       </c>
       <c r="H68" t="str">
-        <v>VXX</v>
+        <v>^VIX3M</v>
       </c>
       <c r="I68" t="str">
         <v>normal</v>
@@ -19817,7 +19753,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
-        <v>^VIX3M</v>
+        <v>^MOVE</v>
       </c>
       <c r="B69" t="str">
         <v>Vol</v>
@@ -19832,13 +19768,13 @@
         <v>0</v>
       </c>
       <c r="F69" t="str">
-        <v>CBOE S&amp;P 500 3-Month Volatility</v>
+        <v>ICE BofAML MOVE Index</v>
       </c>
       <c r="G69" t="str">
         <v>yfinance</v>
       </c>
       <c r="H69" t="str">
-        <v>^VIX3M</v>
+        <v>^MOVE</v>
       </c>
       <c r="I69" t="str">
         <v>normal</v>
@@ -19849,7 +19785,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
-        <v>^MOVE</v>
+        <v>^OVX</v>
       </c>
       <c r="B70" t="str">
         <v>Vol</v>
@@ -19864,13 +19800,13 @@
         <v>0</v>
       </c>
       <c r="F70" t="str">
-        <v>ICE BofAML MOVE Index</v>
+        <v>CBOE Crude Oil Volatility Index</v>
       </c>
       <c r="G70" t="str">
         <v>yfinance</v>
       </c>
       <c r="H70" t="str">
-        <v>^MOVE</v>
+        <v>^OVX</v>
       </c>
       <c r="I70" t="str">
         <v>normal</v>
@@ -19881,7 +19817,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
-        <v>^OVX</v>
+        <v>^GVZ</v>
       </c>
       <c r="B71" t="str">
         <v>Vol</v>
@@ -19896,13 +19832,13 @@
         <v>0</v>
       </c>
       <c r="F71" t="str">
-        <v>CBOE Crude Oil Volatility Index</v>
+        <v>CBOE Gold Volatility Index</v>
       </c>
       <c r="G71" t="str">
         <v>yfinance</v>
       </c>
       <c r="H71" t="str">
-        <v>^OVX</v>
+        <v>^GVZ</v>
       </c>
       <c r="I71" t="str">
         <v>normal</v>
@@ -19913,39 +19849,39 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
-        <v>^GVZ</v>
+        <v>MWTIX</v>
       </c>
       <c r="B72" t="str">
-        <v>Vol</v>
+        <v>Portfolio</v>
       </c>
       <c r="C72" t="str">
         <v>USD</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72" t="str">
-        <v>CBOE Gold Volatility Index</v>
+        <v>TCW MetWest Total Return Bd I</v>
       </c>
       <c r="G72" t="str">
         <v>yfinance</v>
       </c>
       <c r="H72" t="str">
-        <v>^GVZ</v>
+        <v>MWTIX</v>
       </c>
       <c r="I72" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J72">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
-        <v>MWTIX</v>
+        <v>FCNTX</v>
       </c>
       <c r="B73" t="str">
         <v>Portfolio</v>
@@ -19954,19 +19890,19 @@
         <v>USD</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73" t="str">
-        <v>TCW MetWest Total Return Bd I</v>
+        <v>Fidelity Contrafund</v>
       </c>
       <c r="G73" t="str">
         <v>yfinance</v>
       </c>
       <c r="H73" t="str">
-        <v>MWTIX</v>
+        <v>FCNTX</v>
       </c>
       <c r="I73" t="str">
         <v>lognormal</v>
@@ -19977,28 +19913,28 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
-        <v>FCNTX</v>
+        <v>ELECTION</v>
       </c>
       <c r="B74" t="str">
-        <v>Portfolio</v>
+        <v>Theme</v>
       </c>
       <c r="C74" t="str">
         <v>USD</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="str">
-        <v>Fidelity Contrafund</v>
+        <v>XLF 1.5, ICLN -1, IWM 1.5, FEZ -1</v>
       </c>
       <c r="G74" t="str">
-        <v>yfinance</v>
+        <v>composite</v>
       </c>
       <c r="H74" t="str">
-        <v>FCNTX</v>
+        <v>ELECTION</v>
       </c>
       <c r="I74" t="str">
         <v>lognormal</v>
@@ -20009,7 +19945,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
-        <v>ELECTION</v>
+        <v>FED</v>
       </c>
       <c r="B75" t="str">
         <v>Theme</v>
@@ -20024,13 +19960,13 @@
         <v>1</v>
       </c>
       <c r="F75" t="str">
-        <v>XLF 1.5, ICLN -1, IWM 1.5, FEZ -1</v>
+        <v>SHY 1, BSV 1</v>
       </c>
       <c r="G75" t="str">
         <v>composite</v>
       </c>
       <c r="H75" t="str">
-        <v>ELECTION</v>
+        <v>FED</v>
       </c>
       <c r="I75" t="str">
         <v>lognormal</v>
@@ -20041,7 +19977,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
-        <v>FED</v>
+        <v>AI</v>
       </c>
       <c r="B76" t="str">
         <v>Theme</v>
@@ -20056,13 +19992,13 @@
         <v>1</v>
       </c>
       <c r="F76" t="str">
-        <v>SHY 1, BSV 1</v>
+        <v>AIQ 1, QQQ 0.25, IWM -0.25</v>
       </c>
       <c r="G76" t="str">
         <v>composite</v>
       </c>
       <c r="H76" t="str">
-        <v>FED</v>
+        <v>AI</v>
       </c>
       <c r="I76" t="str">
         <v>lognormal</v>
@@ -20073,7 +20009,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
-        <v>AI</v>
+        <v>GEOPOLITICS</v>
       </c>
       <c r="B77" t="str">
         <v>Theme</v>
@@ -20088,13 +20024,13 @@
         <v>1</v>
       </c>
       <c r="F77" t="str">
-        <v>AIQ 1, QQQ 0.25, IWM -0.25</v>
+        <v>GLD 0.65, USO 0.3, ^VIX3M -0.15, FEZ -0.05</v>
       </c>
       <c r="G77" t="str">
         <v>composite</v>
       </c>
       <c r="H77" t="str">
-        <v>AI</v>
+        <v>GEOPOLITICS</v>
       </c>
       <c r="I77" t="str">
         <v>lognormal</v>
@@ -20105,7 +20041,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
-        <v>GEOPOLITICS</v>
+        <v>TRADEWAR</v>
       </c>
       <c r="B78" t="str">
         <v>Theme</v>
@@ -20120,13 +20056,13 @@
         <v>1</v>
       </c>
       <c r="F78" t="str">
-        <v>GLD 0.65, USO 0.3, ^VIX3M -0.15, FEZ -0.05</v>
+        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
       </c>
       <c r="G78" t="str">
         <v>composite</v>
       </c>
       <c r="H78" t="str">
-        <v>GEOPOLITICS</v>
+        <v>TRADEWAR</v>
       </c>
       <c r="I78" t="str">
         <v>lognormal</v>
@@ -20137,7 +20073,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
-        <v>TRADEWAR</v>
+        <v>IRAN</v>
       </c>
       <c r="B79" t="str">
         <v>Theme</v>
@@ -20152,13 +20088,13 @@
         <v>1</v>
       </c>
       <c r="F79" t="str">
-        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
+        <v>USO 1</v>
       </c>
       <c r="G79" t="str">
         <v>composite</v>
       </c>
       <c r="H79" t="str">
-        <v>TRADEWAR</v>
+        <v>IRAN</v>
       </c>
       <c r="I79" t="str">
         <v>lognormal</v>
@@ -20169,7 +20105,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
-        <v>IRAN</v>
+        <v>SEMI-SOFT</v>
       </c>
       <c r="B80" t="str">
         <v>Theme</v>
@@ -20184,13 +20120,13 @@
         <v>1</v>
       </c>
       <c r="F80" t="str">
-        <v>USD 1</v>
+        <v>SMH 1, IGV -1</v>
       </c>
       <c r="G80" t="str">
         <v>composite</v>
       </c>
       <c r="H80" t="str">
-        <v>IRAN</v>
+        <v>SEMI-SOFT</v>
       </c>
       <c r="I80" t="str">
         <v>lognormal</v>
@@ -20201,10 +20137,10 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
-        <v>SEMI-SOFT</v>
+        <v>2s10s</v>
       </c>
       <c r="B81" t="str">
-        <v>Theme</v>
+        <v>Rates</v>
       </c>
       <c r="C81" t="str">
         <v>USD</v>
@@ -20216,13 +20152,13 @@
         <v>1</v>
       </c>
       <c r="F81" t="str">
-        <v>SMH 1, IGV -1</v>
+        <v>SHY -3.86, IEF 1</v>
       </c>
       <c r="G81" t="str">
         <v>composite</v>
       </c>
       <c r="H81" t="str">
-        <v>SEMI-SOFT</v>
+        <v>2s10s</v>
       </c>
       <c r="I81" t="str">
         <v>lognormal</v>
@@ -20233,10 +20169,10 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
-        <v>2s10s</v>
+        <v>XLPXLY</v>
       </c>
       <c r="B82" t="str">
-        <v>Rates</v>
+        <v>Equities</v>
       </c>
       <c r="C82" t="str">
         <v>USD</v>
@@ -20248,13 +20184,13 @@
         <v>1</v>
       </c>
       <c r="F82" t="str">
-        <v>SHY -3.86, IEF 1</v>
+        <v>Staples/Discretionary</v>
       </c>
       <c r="G82" t="str">
         <v>composite</v>
       </c>
       <c r="H82" t="str">
-        <v>2s10s</v>
+        <v>XLPXLY</v>
       </c>
       <c r="I82" t="str">
         <v>lognormal</v>
@@ -20265,42 +20201,42 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="str">
-        <v>XLPXLY</v>
+        <v>UNCERTAINTY</v>
       </c>
       <c r="B83" t="str">
-        <v>Equities</v>
+        <v>Econ</v>
       </c>
       <c r="C83" t="str">
         <v>USD</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="str">
-        <v>Staples/Discretionary</v>
+        <v>Economic Policy Uncertainty Index for United States</v>
       </c>
       <c r="G83" t="str">
-        <v>composite</v>
+        <v>fred</v>
       </c>
       <c r="H83" t="str">
-        <v>XLPXLY</v>
+        <v>USEPUINDXD</v>
       </c>
       <c r="I83" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J83">
-        <v>1E-4</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
-        <v>UNCERTAINTY</v>
+        <v>BTC</v>
       </c>
       <c r="B84" t="str">
-        <v>Econ</v>
+        <v>Currencies</v>
       </c>
       <c r="C84" t="str">
         <v>USD</v>
@@ -20312,27 +20248,27 @@
         <v>0</v>
       </c>
       <c r="F84" t="str">
-        <v>Economic Policy Uncertainty Index for United States</v>
+        <v>-</v>
       </c>
       <c r="G84" t="str">
-        <v>fred</v>
+        <v>lmxl</v>
       </c>
       <c r="H84" t="str">
-        <v>USEPUINDXD</v>
+        <v>BTC1_price</v>
       </c>
       <c r="I84" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J84">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
-        <v>BTC</v>
+        <v>BTC_vol</v>
       </c>
       <c r="B85" t="str">
-        <v>Currencies</v>
+        <v>Vol</v>
       </c>
       <c r="C85" t="str">
         <v>USD</v>
@@ -20350,44 +20286,12 @@
         <v>lmxl</v>
       </c>
       <c r="H85" t="str">
-        <v>BTC1_price</v>
+        <v>BTC1_atm</v>
       </c>
       <c r="I85" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J85">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" t="str">
-        <v>BTC_vol</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Vol</v>
-      </c>
-      <c r="C86" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D86">
-        <v>0</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86" t="str">
-        <v>-</v>
-      </c>
-      <c r="G86" t="str">
-        <v>lmxl</v>
-      </c>
-      <c r="H86" t="str">
-        <v>BTC1_atm</v>
-      </c>
-      <c r="I86" t="str">
-        <v>normal</v>
-      </c>
-      <c r="J86">
         <v>-0.01</v>
       </c>
     </row>
@@ -20605,7 +20509,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1A08F2F-299B-47F7-8064-36693758F4E3}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="44.28515625" bestFit="1" customWidth="1"/>
@@ -20630,11 +20534,11 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A77">_xlfn._xlws.FILTER(data[factor_name],data[Active]*NOT(data[composite]))</f>
+        <f t="array" ref="A2:A76">_xlfn._xlws.FILTER(data[factor_name],data[Active]*NOT(data[composite]))</f>
         <v>SPY</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:E77">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:E1,data[#Headers]))</f>
+        <f t="array" ref="B2:E76">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:E1,data[#Headers]))</f>
         <v>Equities</v>
       </c>
       <c r="C2" t="str">
@@ -21040,7 +20944,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
-        <v>GPZ</v>
+        <v>PFF</v>
       </c>
       <c r="B26" t="str">
         <v>Equities</v>
@@ -21052,131 +20956,131 @@
         <v>0</v>
       </c>
       <c r="E26" t="str">
-        <v>Private Alts</v>
+        <v>Preferred</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
-        <v>PFF</v>
+        <v>FEZ</v>
       </c>
       <c r="B27" t="str">
         <v>Equities</v>
       </c>
       <c r="C27" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27" t="str">
-        <v>Preferred</v>
+        <v>Eurostoxx 50</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <v>FEZ</v>
+        <v>EWU</v>
       </c>
       <c r="B28" t="str">
         <v>Equities</v>
       </c>
       <c r="C28" t="str">
-        <v>EUR</v>
+        <v>GBP</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28" t="str">
-        <v>Eurostoxx 50</v>
+        <v>FTSE 100</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <v>EWU</v>
+        <v>DAX</v>
       </c>
       <c r="B29" t="str">
         <v>Equities</v>
       </c>
       <c r="C29" t="str">
-        <v>GBP</v>
+        <v>EUR</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29" t="str">
-        <v>FTSE 100</v>
+        <v>DAX (Germany)</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <v>DAX</v>
+        <v>EWC</v>
       </c>
       <c r="B30" t="str">
         <v>Equities</v>
       </c>
       <c r="C30" t="str">
-        <v>EUR</v>
+        <v>CAD</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" t="str">
-        <v>DAX (Germany)</v>
+        <v>MSCI Canada</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
-        <v>EWC</v>
+        <v>EWI</v>
       </c>
       <c r="B31" t="str">
         <v>Equities</v>
       </c>
       <c r="C31" t="str">
-        <v>CAD</v>
+        <v>EUR</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31" t="str">
-        <v>MSCI Canada</v>
+        <v>MSCI Italy</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
-        <v>EWI</v>
+        <v>^N225</v>
       </c>
       <c r="B32" t="str">
         <v>Equities</v>
       </c>
       <c r="C32" t="str">
-        <v>EUR</v>
+        <v>JPY</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32" t="str">
-        <v>MSCI Italy</v>
+        <v>Nikkei 225</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
-        <v>^N225</v>
+        <v>FXI</v>
       </c>
       <c r="B33" t="str">
         <v>Equities</v>
       </c>
       <c r="C33" t="str">
-        <v>JPY</v>
+        <v>CNH</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33" t="str">
-        <v>Nikkei 225</v>
+        <v>China Large-Cap</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
-        <v>FXI</v>
+        <v>ASHR</v>
       </c>
       <c r="B34" t="str">
         <v>Equities</v>
@@ -21188,12 +21092,12 @@
         <v>0</v>
       </c>
       <c r="E34" t="str">
-        <v>China Large-Cap</v>
+        <v>CSI 300 (China)</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
-        <v>ASHR</v>
+        <v>KWEB</v>
       </c>
       <c r="B35" t="str">
         <v>Equities</v>
@@ -21205,46 +21109,46 @@
         <v>0</v>
       </c>
       <c r="E35" t="str">
-        <v>CSI 300 (China)</v>
+        <v>CSI China Internet</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
-        <v>KWEB</v>
+        <v>EEM</v>
       </c>
       <c r="B36" t="str">
         <v>Equities</v>
       </c>
       <c r="C36" t="str">
-        <v>CNH</v>
+        <v>EM</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36" t="str">
-        <v>CSI China Internet</v>
+        <v>MSCI EM</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
-        <v>EEM</v>
+        <v>LQD</v>
       </c>
       <c r="B37" t="str">
-        <v>Equities</v>
+        <v>Credit</v>
       </c>
       <c r="C37" t="str">
-        <v>EM</v>
+        <v>USD</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37" t="str">
-        <v>MSCI EM</v>
+        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
-        <v>LQD</v>
+        <v>BSV</v>
       </c>
       <c r="B38" t="str">
         <v>Credit</v>
@@ -21256,12 +21160,12 @@
         <v>0</v>
       </c>
       <c r="E38" t="str">
-        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
+        <v>Vanguard Short-Term Bond Index Fund ETF</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
-        <v>BSV</v>
+        <v>HYG</v>
       </c>
       <c r="B39" t="str">
         <v>Credit</v>
@@ -21273,12 +21177,12 @@
         <v>0</v>
       </c>
       <c r="E39" t="str">
-        <v>Vanguard Short-Term Bond Index Fund ETF</v>
+        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
-        <v>HYG</v>
+        <v>LQDH</v>
       </c>
       <c r="B40" t="str">
         <v>Credit</v>
@@ -21287,15 +21191,15 @@
         <v>USD</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="str">
-        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
+        <v>Hedged LQD</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
-        <v>LQDH</v>
+        <v>HYGH</v>
       </c>
       <c r="B41" t="str">
         <v>Credit</v>
@@ -21304,15 +21208,15 @@
         <v>USD</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="str">
-        <v>Hedged LQD</v>
+        <v>Hedged HYG</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
-        <v>HYGH</v>
+        <v>BKLN</v>
       </c>
       <c r="B42" t="str">
         <v>Credit</v>
@@ -21324,12 +21228,12 @@
         <v>0</v>
       </c>
       <c r="E42" t="str">
-        <v>Hedged HYG</v>
+        <v>Bank Loans</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
-        <v>BKLN</v>
+        <v>AGG</v>
       </c>
       <c r="B43" t="str">
         <v>Credit</v>
@@ -21341,15 +21245,15 @@
         <v>0</v>
       </c>
       <c r="E43" t="str">
-        <v>Bank Loans</v>
+        <v>US Agg</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
-        <v>AGG</v>
+        <v>^TNX</v>
       </c>
       <c r="B44" t="str">
-        <v>Credit</v>
+        <v>Rates</v>
       </c>
       <c r="C44" t="str">
         <v>USD</v>
@@ -21358,12 +21262,12 @@
         <v>0</v>
       </c>
       <c r="E44" t="str">
-        <v>US Agg</v>
+        <v>CBOE Interest Rate 10 Year</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
-        <v>^TNX</v>
+        <v>SHY</v>
       </c>
       <c r="B45" t="str">
         <v>Rates</v>
@@ -21375,12 +21279,12 @@
         <v>0</v>
       </c>
       <c r="E45" t="str">
-        <v>CBOE Interest Rate 10 Year</v>
+        <v>1-3 Year Treasury</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
-        <v>SHY</v>
+        <v>IEI</v>
       </c>
       <c r="B46" t="str">
         <v>Rates</v>
@@ -21392,12 +21296,12 @@
         <v>0</v>
       </c>
       <c r="E46" t="str">
-        <v>1-3 Year Treasury</v>
+        <v>3-7 Year Treasury</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
-        <v>IEI</v>
+        <v>IEF</v>
       </c>
       <c r="B47" t="str">
         <v>Rates</v>
@@ -21406,15 +21310,15 @@
         <v>USD</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="str">
-        <v>3-7 Year Treasury</v>
+        <v>7-10 Year Treasury</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
-        <v>IEF</v>
+        <v>TLT</v>
       </c>
       <c r="B48" t="str">
         <v>Rates</v>
@@ -21423,15 +21327,15 @@
         <v>USD</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="str">
-        <v>7-10 Year Treasury</v>
+        <v>20+ Year Treasury</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
-        <v>TLT</v>
+        <v>TIP</v>
       </c>
       <c r="B49" t="str">
         <v>Rates</v>
@@ -21443,12 +21347,12 @@
         <v>0</v>
       </c>
       <c r="E49" t="str">
-        <v>20+ Year Treasury</v>
+        <v>iShares TIPS Bond ETF</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
-        <v>TIP</v>
+        <v>VTIP</v>
       </c>
       <c r="B50" t="str">
         <v>Rates</v>
@@ -21460,12 +21364,12 @@
         <v>0</v>
       </c>
       <c r="E50" t="str">
-        <v>iShares TIPS Bond ETF</v>
+        <v>Short-Term Inflation-Protected Securities ETF</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
-        <v>VTIP</v>
+        <v>AGNC</v>
       </c>
       <c r="B51" t="str">
         <v>Rates</v>
@@ -21477,12 +21381,12 @@
         <v>0</v>
       </c>
       <c r="E51" t="str">
-        <v>Short-Term Inflation-Protected Securities ETF</v>
+        <v>AGNC Investment Corp.</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
-        <v>AGNC</v>
+        <v>VMBS</v>
       </c>
       <c r="B52" t="str">
         <v>Rates</v>
@@ -21494,12 +21398,12 @@
         <v>0</v>
       </c>
       <c r="E52" t="str">
-        <v>AGNC Investment Corp.</v>
+        <v>Mortgage-Backed Securities ETF</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
-        <v>VMBS</v>
+        <v>CMBS</v>
       </c>
       <c r="B53" t="str">
         <v>Rates</v>
@@ -21511,46 +21415,46 @@
         <v>0</v>
       </c>
       <c r="E53" t="str">
-        <v>Mortgage-Backed Securities ETF</v>
+        <v>iShares CMBS ETF</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
-        <v>CMBS</v>
+        <v>EMB</v>
       </c>
       <c r="B54" t="str">
         <v>Rates</v>
       </c>
       <c r="C54" t="str">
-        <v>USD</v>
+        <v>EM</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54" t="str">
-        <v>iShares CMBS ETF</v>
+        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
-        <v>EMB</v>
+        <v>GLD</v>
       </c>
       <c r="B55" t="str">
-        <v>Rates</v>
+        <v>Commodities</v>
       </c>
       <c r="C55" t="str">
-        <v>EM</v>
+        <v>USD</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55" t="str">
-        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
+        <v>SPDR Gold Shares</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
-        <v>GLD</v>
+        <v>SLV</v>
       </c>
       <c r="B56" t="str">
         <v>Commodities</v>
@@ -21562,12 +21466,12 @@
         <v>0</v>
       </c>
       <c r="E56" t="str">
-        <v>SPDR Gold Shares</v>
+        <v>iShares Silver Trust</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
-        <v>SLV</v>
+        <v>USO</v>
       </c>
       <c r="B57" t="str">
         <v>Commodities</v>
@@ -21579,15 +21483,15 @@
         <v>0</v>
       </c>
       <c r="E57" t="str">
-        <v>iShares Silver Trust</v>
+        <v>United States Oil Fund</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
-        <v>USO</v>
+        <v>UUP</v>
       </c>
       <c r="B58" t="str">
-        <v>Commodities</v>
+        <v>Currencies</v>
       </c>
       <c r="C58" t="str">
         <v>USD</v>
@@ -21596,12 +21500,12 @@
         <v>0</v>
       </c>
       <c r="E58" t="str">
-        <v>United States Oil Fund</v>
+        <v>Invesco DB US Dollar Index Bullish Fund</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
-        <v>UUP</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="B59" t="str">
         <v>Currencies</v>
@@ -21613,29 +21517,29 @@
         <v>0</v>
       </c>
       <c r="E59" t="str">
-        <v>Invesco DB US Dollar Index Bullish Fund</v>
+        <v>U.S. Dollar Index</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
-        <v>DX-Y.NYB</v>
+        <v>FXE</v>
       </c>
       <c r="B60" t="str">
         <v>Currencies</v>
       </c>
       <c r="C60" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60" t="str">
-        <v>U.S. Dollar Index</v>
+        <v>Invesco CurrencyShares Euro Trust</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
-        <v>FXE</v>
+        <v>FXF</v>
       </c>
       <c r="B61" t="str">
         <v>Currencies</v>
@@ -21647,97 +21551,97 @@
         <v>0</v>
       </c>
       <c r="E61" t="str">
-        <v>Invesco CurrencyShares Euro Trust</v>
+        <v>Invesco CurrencyShares Swiss Franc Trust</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
-        <v>FXF</v>
+        <v>FXA</v>
       </c>
       <c r="B62" t="str">
         <v>Currencies</v>
       </c>
       <c r="C62" t="str">
-        <v>EUR</v>
+        <v>Commod</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62" t="str">
-        <v>Invesco CurrencyShares Swiss Franc Trust</v>
+        <v>Invesco CurrencyShares Australian Dollar Trust</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
-        <v>FXA</v>
+        <v>FXB</v>
       </c>
       <c r="B63" t="str">
         <v>Currencies</v>
       </c>
       <c r="C63" t="str">
-        <v>Commod</v>
+        <v>GBP</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63" t="str">
-        <v>Invesco CurrencyShares Australian Dollar Trust</v>
+        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
-        <v>FXB</v>
+        <v>FXC</v>
       </c>
       <c r="B64" t="str">
         <v>Currencies</v>
       </c>
       <c r="C64" t="str">
-        <v>GBP</v>
+        <v>USD</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64" t="str">
-        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
+        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
-        <v>FXC</v>
+        <v>FXY</v>
       </c>
       <c r="B65" t="str">
         <v>Currencies</v>
       </c>
       <c r="C65" t="str">
-        <v>USD</v>
+        <v>JPY</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" t="str">
-        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
+        <v>Invesco CurrencyShares Japanese Yen Trust</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
-        <v>FXY</v>
+        <v>^VIX</v>
       </c>
       <c r="B66" t="str">
-        <v>Currencies</v>
+        <v>Vol</v>
       </c>
       <c r="C66" t="str">
-        <v>JPY</v>
+        <v>USD</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66" t="str">
-        <v>Invesco CurrencyShares Japanese Yen Trust</v>
+        <v>CBOE Volatility Index</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
-        <v>^VIX</v>
+        <v>VXX</v>
       </c>
       <c r="B67" t="str">
         <v>Vol</v>
@@ -21749,12 +21653,12 @@
         <v>0</v>
       </c>
       <c r="E67" t="str">
-        <v>CBOE Volatility Index</v>
+        <v>VIX Short-Term Futures ETN</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
-        <v>VXX</v>
+        <v>^VIX3M</v>
       </c>
       <c r="B68" t="str">
         <v>Vol</v>
@@ -21766,12 +21670,12 @@
         <v>0</v>
       </c>
       <c r="E68" t="str">
-        <v>VIX Short-Term Futures ETN</v>
+        <v>CBOE S&amp;P 500 3-Month Volatility</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
-        <v>^VIX3M</v>
+        <v>^MOVE</v>
       </c>
       <c r="B69" t="str">
         <v>Vol</v>
@@ -21783,12 +21687,12 @@
         <v>0</v>
       </c>
       <c r="E69" t="str">
-        <v>CBOE S&amp;P 500 3-Month Volatility</v>
+        <v>ICE BofAML MOVE Index</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
-        <v>^MOVE</v>
+        <v>^OVX</v>
       </c>
       <c r="B70" t="str">
         <v>Vol</v>
@@ -21800,12 +21704,12 @@
         <v>0</v>
       </c>
       <c r="E70" t="str">
-        <v>ICE BofAML MOVE Index</v>
+        <v>CBOE Crude Oil Volatility Index</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
-        <v>^OVX</v>
+        <v>^GVZ</v>
       </c>
       <c r="B71" t="str">
         <v>Vol</v>
@@ -21817,29 +21721,29 @@
         <v>0</v>
       </c>
       <c r="E71" t="str">
-        <v>CBOE Crude Oil Volatility Index</v>
+        <v>CBOE Gold Volatility Index</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
-        <v>^GVZ</v>
+        <v>MWTIX</v>
       </c>
       <c r="B72" t="str">
-        <v>Vol</v>
+        <v>Portfolio</v>
       </c>
       <c r="C72" t="str">
         <v>USD</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="str">
-        <v>CBOE Gold Volatility Index</v>
+        <v>TCW MetWest Total Return Bd I</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
-        <v>MWTIX</v>
+        <v>FCNTX</v>
       </c>
       <c r="B73" t="str">
         <v>Portfolio</v>
@@ -21848,18 +21752,18 @@
         <v>USD</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" t="str">
-        <v>TCW MetWest Total Return Bd I</v>
+        <v>Fidelity Contrafund</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
-        <v>FCNTX</v>
+        <v>UNCERTAINTY</v>
       </c>
       <c r="B74" t="str">
-        <v>Portfolio</v>
+        <v>Econ</v>
       </c>
       <c r="C74" t="str">
         <v>USD</v>
@@ -21868,15 +21772,15 @@
         <v>0</v>
       </c>
       <c r="E74" t="str">
-        <v>Fidelity Contrafund</v>
+        <v>Economic Policy Uncertainty Index for United States</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
-        <v>UNCERTAINTY</v>
+        <v>BTC</v>
       </c>
       <c r="B75" t="str">
-        <v>Econ</v>
+        <v>Currencies</v>
       </c>
       <c r="C75" t="str">
         <v>USD</v>
@@ -21885,15 +21789,15 @@
         <v>0</v>
       </c>
       <c r="E75" t="str">
-        <v>Economic Policy Uncertainty Index for United States</v>
+        <v>-</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
-        <v>BTC</v>
+        <v>BTC_vol</v>
       </c>
       <c r="B76" t="str">
-        <v>Currencies</v>
+        <v>Vol</v>
       </c>
       <c r="C76" t="str">
         <v>USD</v>
@@ -21902,23 +21806,6 @@
         <v>0</v>
       </c>
       <c r="E76" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="str">
-        <v>BTC_vol</v>
-      </c>
-      <c r="B77" t="str">
-        <v>Vol</v>
-      </c>
-      <c r="C77" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D77">
-        <v>0</v>
-      </c>
-      <c r="E77" t="str">
         <v>-</v>
       </c>
     </row>
@@ -27374,7 +27261,7 @@
         <v>IRAN</v>
       </c>
       <c r="B25" t="str">
-        <v>USD</v>
+        <v>USO</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -27704,7 +27591,7 @@
         <v>IRAN</v>
       </c>
       <c r="G9" t="str">
-        <v>USD 1</v>
+        <v>USO 1</v>
       </c>
       <c r="U9" t="b">
         <f ca="1"/>
@@ -28165,7 +28052,7 @@
         <v>722</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C25" s="8">
         <v>1</v>
@@ -28624,7 +28511,7 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <f ca="1">TODAY()-1</f>
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="B2">
         <v>0.20547945205479451</v>

--- a/factor_master.xlsx
+++ b/factor_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrai\Source\risk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BBBDC7-40CE-4F2B-ABE0-9F9DDC1790A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B54171-EAE9-4306-B460-2C14ECFCA98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="8" activeTab="10" xr2:uid="{C31FDC5B-A809-4BFD-99CB-DA02246721F7}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2589" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2592" uniqueCount="729">
   <si>
     <t>SPX</t>
   </si>
@@ -2287,6 +2287,9 @@
   </si>
   <si>
     <t>PRIVATES</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -2810,8 +2813,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B096ECD9-9D11-4532-B7BB-C59C7AF13EE1}" name="composities" displayName="composities" ref="A1:C27" totalsRowShown="0">
-  <autoFilter ref="A1:C27" xr:uid="{B096ECD9-9D11-4532-B7BB-C59C7AF13EE1}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B096ECD9-9D11-4532-B7BB-C59C7AF13EE1}" name="composities" displayName="composities" ref="A1:C28" totalsRowShown="0">
+  <autoFilter ref="A1:C28" xr:uid="{B096ECD9-9D11-4532-B7BB-C59C7AF13EE1}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{871951C6-7319-4AA1-8565-79E8F38A5ACE}" name="portfolio_name"/>
     <tableColumn id="2" xr3:uid="{FF366C7B-7C4B-413F-92EE-C488EBE75CC9}" name="factor_name"/>
@@ -4793,7 +4796,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75C34FC6-78FE-492E-BECF-2EB9A04778A9}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AJ40"/>
+  <dimension ref="A1:AJ41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -4833,11 +4836,11 @@
         <v>1</v>
       </c>
       <c r="E2" s="23" cm="1">
-        <f t="array" ref="E2:E27">_xlfn.XLOOKUP(composities[portfolio_name],data[factor_name],data[Active])</f>
+        <f t="array" ref="E2:E28">_xlfn.XLOOKUP(composities[portfolio_name],data[factor_name],data[Active])</f>
         <v>1</v>
       </c>
       <c r="H2" t="str" cm="1">
-        <f t="array" ref="H2:H27">TEXT(composities[weight],IF(INT(composities[weight]*100)/100=composities[weight],"General","0.00"))</f>
+        <f t="array" ref="H2:H28">TEXT(composities[weight],IF(INT(composities[weight]*100)/100=composities[weight],"General","0.00"))</f>
         <v>1</v>
       </c>
       <c r="I2" t="str" cm="1">
@@ -4849,7 +4852,7 @@
         <v>SHY 1, BSV 1</v>
       </c>
       <c r="X2" t="b" cm="1">
-        <f t="array" aca="1" ref="X2:X27" ca="1">composities[portfolio_name]&lt;&gt;OFFSET(composities[portfolio_name],-1,0)</f>
+        <f t="array" aca="1" ref="X2:X28" ca="1">composities[portfolio_name]&lt;&gt;OFFSET(composities[portfolio_name],-1,0)</f>
         <v>1</v>
       </c>
       <c r="AE2" t="s">
@@ -5113,7 +5116,7 @@
         <v>SEMI-SOFT</v>
       </c>
       <c r="J9" t="str">
-        <v>SMH 1, IGV -1</v>
+        <v>SMH 1, IGV -1, QQQ 1</v>
       </c>
       <c r="X9" t="b">
         <f ca="1"/>
@@ -5144,6 +5147,9 @@
       </c>
       <c r="E10" s="23">
         <v>1</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>728</v>
       </c>
       <c r="H10" t="str">
         <v>-0.05</v>
@@ -5603,23 +5609,23 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B24" t="s">
-        <v>724</v>
+        <v>7</v>
       </c>
       <c r="C24" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E24" s="23">
         <v>1</v>
       </c>
       <c r="H24" t="str">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X24" t="b">
         <f ca="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
@@ -5627,20 +5633,20 @@
         <v>727</v>
       </c>
       <c r="B25" t="s">
-        <v>175</v>
+        <v>724</v>
       </c>
       <c r="C25" s="8">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="23">
         <v>1</v>
       </c>
       <c r="H25" t="str">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="X25" t="b">
         <f ca="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
@@ -5648,16 +5654,16 @@
         <v>727</v>
       </c>
       <c r="B26" t="s">
-        <v>293</v>
+        <v>175</v>
       </c>
       <c r="C26" s="8">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="E26" s="23">
         <v>1</v>
       </c>
       <c r="H26" t="str">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="X26" t="b">
         <f ca="1"/>
@@ -5669,16 +5675,16 @@
         <v>727</v>
       </c>
       <c r="B27" t="s">
-        <v>347</v>
+        <v>293</v>
       </c>
       <c r="C27" s="8">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="E27" s="23">
         <v>1</v>
       </c>
       <c r="H27" t="str">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="X27" t="b">
         <f ca="1"/>
@@ -5686,7 +5692,25 @@
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C28" s="8"/>
+      <c r="A28" t="s">
+        <v>727</v>
+      </c>
+      <c r="B28" t="s">
+        <v>347</v>
+      </c>
+      <c r="C28" s="8">
+        <v>-0.5</v>
+      </c>
+      <c r="E28" s="23">
+        <v>1</v>
+      </c>
+      <c r="H28" t="str">
+        <v>-0.5</v>
+      </c>
+      <c r="X28" t="b">
+        <f ca="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C29" s="8"/>
@@ -5699,6 +5723,9 @@
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="C32" s="8"/>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="C33" s="8"/>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="Q34" t="e" vm="1">
@@ -5737,21 +5764,11 @@
         <v>#VALUE!</v>
       </c>
       <c r="W36" cm="1">
-        <f t="array" ref="W36:W39">C37:C40*N36:N39</f>
+        <f t="array" ref="W36:W39">C38:C41*N36:N39</f>
         <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>504</v>
-      </c>
-      <c r="B37" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="8">
-        <f>O36/N36</f>
-        <v>0.20547945205479454</v>
-      </c>
       <c r="D37" s="8"/>
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
@@ -5781,11 +5798,11 @@
         <v>504</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C38" s="8">
-        <f>O37/N37</f>
-        <v>0.29702970297029702</v>
+        <f>O36/N36</f>
+        <v>0.20547945205479454</v>
       </c>
       <c r="D38" s="8"/>
       <c r="G38" s="8"/>
@@ -5813,11 +5830,11 @@
         <v>504</v>
       </c>
       <c r="B39" t="s">
-        <v>497</v>
+        <v>72</v>
       </c>
       <c r="C39" s="8">
-        <f>O38/N38</f>
-        <v>0.36585365853658541</v>
+        <f>O37/N37</f>
+        <v>0.29702970297029702</v>
       </c>
       <c r="D39" s="8"/>
       <c r="G39" s="8"/>
@@ -5843,9 +5860,21 @@
         <v>504</v>
       </c>
       <c r="B40" t="s">
+        <v>497</v>
+      </c>
+      <c r="C40" s="8">
+        <f>O38/N38</f>
+        <v>0.36585365853658541</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>504</v>
+      </c>
+      <c r="B41" t="s">
         <v>495</v>
       </c>
-      <c r="C40" s="8">
+      <c r="C41" s="8">
         <f>O39/N39</f>
         <v>-0.1125</v>
       </c>
@@ -5856,22 +5885,22 @@
       <formula>$Q1048571</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11:C18">
+  <conditionalFormatting sqref="A11:C18 A25:C28">
     <cfRule type="expression" dxfId="4" priority="41">
       <formula>$T6</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19:C27">
+  <conditionalFormatting sqref="A19:C24">
     <cfRule type="expression" dxfId="3" priority="40">
       <formula>$T15</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A31:C32">
+  <conditionalFormatting sqref="A32:C33">
     <cfRule type="expression" dxfId="2" priority="42">
       <formula>$T19</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A28:C30">
+  <conditionalFormatting sqref="A29:C31">
     <cfRule type="expression" dxfId="1" priority="44">
       <formula>$T21</formula>
     </cfRule>
@@ -12197,7 +12226,7 @@
       <c r="I102" s="4"/>
       <c r="J102" s="4" t="str" cm="1">
         <f t="array" ref="J102">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$I$2),_xlfn.ANCHORARRAY(composites!$J$2))</f>
-        <v>SMH 1, IGV -1</v>
+        <v>SMH 1, IGV -1, QQQ 1</v>
       </c>
       <c r="K102" s="4">
         <v>1</v>
@@ -12217,7 +12246,7 @@
       </c>
       <c r="P102" s="4" t="str" cm="1">
         <f t="array" ref="P102">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>SMH 1, IGV -1</v>
+        <v>SMH 1, IGV -1, QQQ 1</v>
       </c>
       <c r="Q102" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
@@ -15309,7 +15338,7 @@
         <v>1</v>
       </c>
       <c r="F81" t="str">
-        <v>SMH 1, IGV -1</v>
+        <v>SMH 1, IGV -1, QQQ 1</v>
       </c>
       <c r="G81" t="str">
         <v>composite</v>
@@ -20460,7 +20489,7 @@
         <v>1</v>
       </c>
       <c r="F81" t="str">
-        <v>SMH 1, IGV -1</v>
+        <v>SMH 1, IGV -1, QQQ 1</v>
       </c>
       <c r="G81" t="str">
         <v>composite</v>
@@ -27344,7 +27373,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7A5BD3C-985E-4AF9-B99B-18E2DCAB8A90}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -27361,7 +27390,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:C27">composities[]</f>
+        <f t="array" ref="A2:C28">composities[]</f>
         <v>FED</v>
       </c>
       <c r="B2" t="str">
@@ -27604,13 +27633,13 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
-        <v>PRIVATES</v>
+        <v>SEMI-SOFT</v>
       </c>
       <c r="B24" t="str">
-        <v>PSP</v>
+        <v>QQQ</v>
       </c>
       <c r="C24">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -27618,10 +27647,10 @@
         <v>PRIVATES</v>
       </c>
       <c r="B25" t="str">
-        <v>XLF</v>
+        <v>PSP</v>
       </c>
       <c r="C25">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -27629,10 +27658,10 @@
         <v>PRIVATES</v>
       </c>
       <c r="B26" t="str">
-        <v>BKLN</v>
+        <v>XLF</v>
       </c>
       <c r="C26">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -27640,9 +27669,20 @@
         <v>PRIVATES</v>
       </c>
       <c r="B27" t="str">
+        <v>BKLN</v>
+      </c>
+      <c r="C27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="str">
+        <v>PRIVATES</v>
+      </c>
+      <c r="B28" t="str">
         <v>LQDH</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <v>-0.5</v>
       </c>
     </row>
@@ -27863,7 +27903,7 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <f ca="1">TODAY()-1</f>
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B2">
         <v>0.20547945205479451</v>

--- a/factor_master.xlsx
+++ b/factor_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30208"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrai\Source\risk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B54171-EAE9-4306-B460-2C14ECFCA98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8F7DF1-93C2-43EB-82ED-923B3F7BF83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="8" activeTab="10" xr2:uid="{C31FDC5B-A809-4BFD-99CB-DA02246721F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="11" activeTab="11" xr2:uid="{C31FDC5B-A809-4BFD-99CB-DA02246721F7}"/>
   </bookViews>
   <sheets>
     <sheet name="legacy" sheetId="5" r:id="rId1"/>
@@ -2434,7 +2434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2459,15 +2459,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2482,7 +2478,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2549,16 +2544,6 @@
         </top>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2680,6 +2665,16 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="0" tint="-0.24994659260841701"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border>
@@ -2825,58 +2820,58 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6DAD1482-C63D-400D-9F51-F22A8E35CAD8}" name="data" displayName="data" ref="A1:T107" totalsRowShown="0" headerRowDxfId="7" dataDxfId="40" headerRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6DAD1482-C63D-400D-9F51-F22A8E35CAD8}" name="data" displayName="data" ref="A1:T107" totalsRowShown="0" headerRowDxfId="40" dataDxfId="38" headerRowBorderDxfId="39">
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{740DC173-AAC9-4239-A44E-C43F8517304D}" name="asset_class" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{A3BC3BB8-0420-458E-AECD-FD567519FA40}" name="region" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{0E50B2E3-0362-41DB-ACC2-478CC6F618A4}" name="factor_name" dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{C400A641-F032-4829-A2CD-62831D657B37}" name="source" dataDxfId="36"/>
-    <tableColumn id="12" xr3:uid="{BC682952-ADA8-4869-A16F-B9E7BC86E430}" name="diffusion_type" dataDxfId="35"/>
-    <tableColumn id="16" xr3:uid="{A99CC35E-FB67-451C-BF9C-DA8D933B1B0C}" name="multiplier" dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{740DC173-AAC9-4239-A44E-C43F8517304D}" name="asset_class" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{A3BC3BB8-0420-458E-AECD-FD567519FA40}" name="region" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{0E50B2E3-0362-41DB-ACC2-478CC6F618A4}" name="factor_name" dataDxfId="35"/>
+    <tableColumn id="11" xr3:uid="{C400A641-F032-4829-A2CD-62831D657B37}" name="source" dataDxfId="34"/>
+    <tableColumn id="12" xr3:uid="{BC682952-ADA8-4869-A16F-B9E7BC86E430}" name="diffusion_type" dataDxfId="33"/>
+    <tableColumn id="16" xr3:uid="{A99CC35E-FB67-451C-BF9C-DA8D933B1B0C}" name="multiplier" dataDxfId="32">
       <calculatedColumnFormula array="1">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{02943B27-7FCB-4450-B8E0-CF0DB6CF5CCA}" name="factor_name_new" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{D181BF84-863F-4FD0-B518-14EA5B0FB18E}" name="description_override" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{1C40DF9B-2910-4DE6-A188-563938E39797}" name="Description_GPT" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{1806E074-6CB5-47AB-8FA3-EF0F6E429062}" name="Underlying" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{21539C17-C1CC-4FA9-A0E1-A2F8FF8AB52C}" name="Active" dataDxfId="29"/>
-    <tableColumn id="37" xr3:uid="{DE50B7AE-5F67-471C-BE48-8BFA5076EDB0}" name="hyper_factor" dataDxfId="28"/>
-    <tableColumn id="10" xr3:uid="{494805E4-EBB6-47FD-9BC2-8DAD9FB9D3FA}" name="composite" dataDxfId="27"/>
-    <tableColumn id="14" xr3:uid="{608FE572-4016-436E-8625-08926F3A2371}" name="client" dataDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{64EF0381-B0C5-4226-B34E-0F9752A4A840}" name="ticker" dataDxfId="25">
+    <tableColumn id="8" xr3:uid="{02943B27-7FCB-4450-B8E0-CF0DB6CF5CCA}" name="factor_name_new" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{D181BF84-863F-4FD0-B518-14EA5B0FB18E}" name="description_override" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{1C40DF9B-2910-4DE6-A188-563938E39797}" name="Description_GPT" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{1806E074-6CB5-47AB-8FA3-EF0F6E429062}" name="Underlying" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{21539C17-C1CC-4FA9-A0E1-A2F8FF8AB52C}" name="Active" dataDxfId="27"/>
+    <tableColumn id="37" xr3:uid="{DE50B7AE-5F67-471C-BE48-8BFA5076EDB0}" name="hyper_factor" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{494805E4-EBB6-47FD-9BC2-8DAD9FB9D3FA}" name="composite" dataDxfId="25"/>
+    <tableColumn id="14" xr3:uid="{608FE572-4016-436E-8625-08926F3A2371}" name="client" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{64EF0381-B0C5-4226-B34E-0F9752A4A840}" name="ticker" dataDxfId="23">
       <calculatedColumnFormula>data[[#This Row],[factor_name]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5A601067-D384-419C-A711-AD3034F77E28}" name="description" dataDxfId="24">
+    <tableColumn id="9" xr3:uid="{5A601067-D384-419C-A711-AD3034F77E28}" name="description" dataDxfId="22">
       <calculatedColumnFormula array="1">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{073BDADC-3AC0-4FF9-9654-A316B2345A90}" name="short_name_yf" dataDxfId="23">
+    <tableColumn id="18" xr3:uid="{073BDADC-3AC0-4FF9-9654-A316B2345A90}" name="short_name_yf" dataDxfId="21">
       <calculatedColumnFormula>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{3A563104-B6B0-465C-9D22-154F5FEA1B83}" name="long_name_yf" dataDxfId="22">
+    <tableColumn id="19" xr3:uid="{3A563104-B6B0-465C-9D22-154F5FEA1B83}" name="long_name_yf" dataDxfId="20">
       <calculatedColumnFormula>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{A3F200A1-E769-49BA-8121-88EAA1180E80}" name="summary_yf" dataDxfId="21">
+    <tableColumn id="17" xr3:uid="{A3F200A1-E769-49BA-8121-88EAA1180E80}" name="summary_yf" dataDxfId="19">
       <calculatedColumnFormula>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{D49341AB-DA48-473E-8CCB-3A3D04AED743}" name="note" dataDxfId="20"/>
+    <tableColumn id="15" xr3:uid="{D49341AB-DA48-473E-8CCB-3A3D04AED743}" name="note" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F918301C-859F-40B7-9C3E-90E8F0495E68}" name="data_old" displayName="data_old" ref="A1:I45" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F918301C-859F-40B7-9C3E-90E8F0495E68}" name="data_old" displayName="data_old" ref="A1:I45" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A1:I45" xr:uid="{6DAD1482-C63D-400D-9F51-F22A8E35CAD8}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{B19D2B17-9AC9-4F1B-B32E-D4F72AAE469F}" name="asset_class" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{2C7CF29D-8E72-4B0C-A212-31F2A25D75C9}" name="region" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{C7E89EEC-2B5D-4C94-9327-1AC8E33DE708}" name="factor_name" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{B3F9004A-8BEB-463E-A746-8189A2AC2B3E}" name="factor_name_new" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{51CD7FB3-58FE-4906-B73C-7726C0A9C471}" name="description_override" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{3CFF990B-3164-4533-821F-08CE7C6D82CA}" name="Description_GPT" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{DD86D53E-A9B4-4387-ABF9-F2625E77982D}" name="Underlying" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{D56FFF9A-72FF-42A4-B3D2-2F27AB16AF7A}" name="Active" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{8476DFDE-B4B1-4FD9-99B4-DF1F2ABBD7D5}" name="description" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{B19D2B17-9AC9-4F1B-B32E-D4F72AAE469F}" name="asset_class" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{2C7CF29D-8E72-4B0C-A212-31F2A25D75C9}" name="region" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{C7E89EEC-2B5D-4C94-9327-1AC8E33DE708}" name="factor_name" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{B3F9004A-8BEB-463E-A746-8189A2AC2B3E}" name="factor_name_new" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{51CD7FB3-58FE-4906-B73C-7726C0A9C471}" name="description_override" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{3CFF990B-3164-4533-821F-08CE7C6D82CA}" name="Description_GPT" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{DD86D53E-A9B4-4387-ABF9-F2625E77982D}" name="Underlying" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{D56FFF9A-72FF-42A4-B3D2-2F27AB16AF7A}" name="Active" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{8476DFDE-B4B1-4FD9-99B4-DF1F2ABBD7D5}" name="description" dataDxfId="7">
       <calculatedColumnFormula>IF(data_old[[#This Row],[description_override]]="",data_old[[#This Row],[Description_GPT]],data_old[[#This Row],[description_override]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4617,169 +4612,169 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="19" t="s">
         <v>316</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="19" t="s">
         <v>466</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="19" t="s">
         <v>464</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="19" t="s">
         <v>468</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="K6" s="21" t="s">
+      <c r="K6" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="L6" s="21" t="s">
+      <c r="L6" s="19" t="s">
         <v>428</v>
       </c>
-      <c r="M6" s="21" t="s">
+      <c r="M6" s="19" t="s">
         <v>445</v>
       </c>
-      <c r="N6" s="21" t="s">
+      <c r="N6" s="19" t="s">
         <v>486</v>
       </c>
-      <c r="O6" s="21" t="s">
+      <c r="O6" s="19" t="s">
         <v>465</v>
       </c>
-      <c r="P6" s="21" t="s">
+      <c r="P6" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="Q6" s="21" t="s">
+      <c r="Q6" s="19" t="s">
         <v>661</v>
       </c>
-      <c r="R6" s="21" t="s">
+      <c r="R6" s="19" t="s">
         <v>660</v>
       </c>
-      <c r="S6" s="21" t="s">
+      <c r="S6" s="19" t="s">
         <v>662</v>
       </c>
-      <c r="T6" s="22" t="s">
+      <c r="T6" s="20" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>444</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="F7" s="18" cm="1">
+      <c r="F7" s="4" cm="1">
         <f t="array" ref="F7">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18" t="e" cm="1">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4" t="e" cm="1">
         <f t="array" ref="J7">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$I$2),_xlfn.ANCHORARRAY(composites!$J$2))</f>
         <v>#N/A</v>
       </c>
-      <c r="K7" s="18">
-        <v>1</v>
-      </c>
-      <c r="L7" s="18">
-        <v>0</v>
-      </c>
-      <c r="M7" s="18">
-        <v>0</v>
-      </c>
-      <c r="N7" s="18">
-        <v>0</v>
-      </c>
-      <c r="O7" s="18" t="str">
+      <c r="K7" s="4">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
         <v>DIA</v>
       </c>
-      <c r="P7" s="18" t="str" cm="1">
+      <c r="P7" s="4" t="str" cm="1">
         <f t="array" ref="P7">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
         <v>Dow Jones 30</v>
       </c>
-      <c r="Q7" s="18" t="str">
+      <c r="Q7" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
         <v>SPDR Dow Jones Industrial Avera</v>
       </c>
-      <c r="R7" s="18" t="str">
+      <c r="R7" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
         <v>SPDR Dow Jones Industrial Average ETF Trust</v>
       </c>
-      <c r="S7" s="18" t="str">
+      <c r="S7" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
         <v>The Trust’s Portfolio consists of substantially all of the component common stocks that comprise the DJIA, which are weighted in accordance with the terms of the Trust Agreement.</v>
       </c>
-      <c r="T7" s="19"/>
+      <c r="T7" s="17"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>507</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="14">
         <v>1.5</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" t="s">
         <v>431</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="15">
         <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="15">
         <v>1.5</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="15">
         <v>-1</v>
       </c>
     </row>
@@ -4802,9 +4797,7 @@
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="6" width="12" style="23" customWidth="1"/>
-    <col min="7" max="13" width="12" customWidth="1"/>
+    <col min="4" max="13" width="12" customWidth="1"/>
     <col min="22" max="22" width="29.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4835,7 +4828,7 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="E2" s="23" cm="1">
+      <c r="E2" cm="1">
         <f t="array" ref="E2:E28">_xlfn.XLOOKUP(composities[portfolio_name],data[factor_name],data[Active])</f>
         <v>1</v>
       </c>
@@ -4878,7 +4871,7 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="E3" s="23">
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="H3" t="str">
@@ -4914,7 +4907,7 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4">
         <v>1</v>
       </c>
       <c r="H4" t="str">
@@ -4953,7 +4946,7 @@
       <c r="C5">
         <v>0.25</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5">
         <v>1</v>
       </c>
       <c r="H5" t="str">
@@ -4989,7 +4982,7 @@
       <c r="C6">
         <v>-0.25</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6">
         <v>1</v>
       </c>
       <c r="H6" t="str">
@@ -5025,7 +5018,7 @@
       <c r="C7">
         <v>0.65</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7">
         <v>1</v>
       </c>
       <c r="H7" t="str">
@@ -5064,7 +5057,7 @@
       <c r="C8">
         <v>0.3</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8">
         <v>1</v>
       </c>
       <c r="H8" t="str">
@@ -5106,7 +5099,7 @@
       <c r="C9">
         <v>-0.15</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9">
         <v>1</v>
       </c>
       <c r="H9" t="str">
@@ -5145,10 +5138,10 @@
       <c r="C10">
         <v>-0.05</v>
       </c>
-      <c r="E10" s="23">
-        <v>1</v>
-      </c>
-      <c r="F10" s="23" t="s">
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
         <v>728</v>
       </c>
       <c r="H10" t="str">
@@ -5191,7 +5184,7 @@
         <f>-C12*Y15/Y13</f>
         <v>-3.8633879781420766</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11">
         <v>1</v>
       </c>
       <c r="H11" t="str">
@@ -5218,7 +5211,7 @@
       <c r="C12">
         <v>1</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12">
         <v>1</v>
       </c>
       <c r="H12" t="str">
@@ -5245,7 +5238,7 @@
       <c r="C13" s="8">
         <v>1</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13">
         <v>1</v>
       </c>
       <c r="H13" t="str">
@@ -5272,7 +5265,7 @@
       <c r="C14" s="8">
         <v>-1</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14">
         <v>1</v>
       </c>
       <c r="H14" t="str">
@@ -5294,7 +5287,7 @@
         <f t="array" ref="C15">O18/N18*$P$18/SUM(ABS(($O$18:$O$22)))</f>
         <v>0.20547945205479451</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15">
         <v>1</v>
       </c>
       <c r="H15" t="str">
@@ -5327,7 +5320,7 @@
         <v>0.29702970297029702</v>
       </c>
       <c r="D16" s="8"/>
-      <c r="E16" s="23">
+      <c r="E16">
         <v>1</v>
       </c>
       <c r="G16" s="8"/>
@@ -5365,7 +5358,7 @@
         <v>0.36585365853658536</v>
       </c>
       <c r="D17" s="8"/>
-      <c r="E17" s="23">
+      <c r="E17">
         <v>1</v>
       </c>
       <c r="G17" s="8"/>
@@ -5397,7 +5390,7 @@
         <v>-3.7499999999999999E-2</v>
       </c>
       <c r="D18" s="8"/>
-      <c r="E18" s="23">
+      <c r="E18">
         <v>1</v>
       </c>
       <c r="G18" s="8"/>
@@ -5440,7 +5433,7 @@
         <v>0.15</v>
       </c>
       <c r="D19" s="8"/>
-      <c r="E19" s="23">
+      <c r="E19">
         <v>1</v>
       </c>
       <c r="G19" s="8"/>
@@ -5479,7 +5472,7 @@
         <v>-0.15</v>
       </c>
       <c r="D20" s="8"/>
-      <c r="E20" s="23">
+      <c r="E20">
         <v>1</v>
       </c>
       <c r="G20" s="8"/>
@@ -5519,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="8"/>
-      <c r="E21" s="23">
+      <c r="E21">
         <v>1</v>
       </c>
       <c r="G21" s="8"/>
@@ -5556,7 +5549,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="8"/>
-      <c r="E22" s="23">
+      <c r="E22">
         <v>1</v>
       </c>
       <c r="G22" s="8"/>
@@ -5590,7 +5583,7 @@
         <v>-1</v>
       </c>
       <c r="D23" s="8"/>
-      <c r="E23" s="23">
+      <c r="E23">
         <v>1</v>
       </c>
       <c r="G23" s="8"/>
@@ -5617,7 +5610,7 @@
       <c r="C24" s="8">
         <v>1</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24">
         <v>1</v>
       </c>
       <c r="H24" t="str">
@@ -5638,7 +5631,7 @@
       <c r="C25" s="8">
         <v>0.5</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25">
         <v>1</v>
       </c>
       <c r="H25" t="str">
@@ -5659,7 +5652,7 @@
       <c r="C26" s="8">
         <v>-0.5</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26">
         <v>1</v>
       </c>
       <c r="H26" t="str">
@@ -5680,7 +5673,7 @@
       <c r="C27" s="8">
         <v>0.5</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27">
         <v>1</v>
       </c>
       <c r="H27" t="str">
@@ -5701,7 +5694,7 @@
       <c r="C28" s="8">
         <v>-0.5</v>
       </c>
-      <c r="E28" s="23">
+      <c r="E28">
         <v>1</v>
       </c>
       <c r="H28" t="str">
@@ -5895,14 +5888,14 @@
       <formula>$T15</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A32:C33">
-    <cfRule type="expression" dxfId="2" priority="42">
-      <formula>$T19</formula>
+  <conditionalFormatting sqref="A29:C31">
+    <cfRule type="expression" dxfId="2" priority="44">
+      <formula>$T21</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A29:C31">
-    <cfRule type="expression" dxfId="1" priority="44">
-      <formula>$T21</formula>
+  <conditionalFormatting sqref="A32:C33">
+    <cfRule type="expression" dxfId="1" priority="42">
+      <formula>$T19</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5916,7 +5909,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C29859C-7358-4E2F-B5CC-7696F1DAC449}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:Y113"/>
+  <dimension ref="A1:Y107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -5931,64 +5924,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="19" t="s">
         <v>316</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="19" t="s">
         <v>466</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="19" t="s">
         <v>464</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="19" t="s">
         <v>468</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="19" t="s">
         <v>428</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="M1" s="19" t="s">
         <v>445</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="N1" s="19" t="s">
         <v>486</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="O1" s="19" t="s">
         <v>465</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="P1" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="21" t="s">
+      <c r="Q1" s="19" t="s">
         <v>661</v>
       </c>
-      <c r="R1" s="21" t="s">
+      <c r="R1" s="19" t="s">
         <v>660</v>
       </c>
-      <c r="S1" s="21" t="s">
+      <c r="S1" s="19" t="s">
         <v>662</v>
       </c>
-      <c r="T1" s="22" t="s">
+      <c r="T1" s="20" t="s">
         <v>490</v>
       </c>
     </row>
@@ -12412,7 +12405,7 @@
         <v>530</v>
       </c>
       <c r="K105" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="4">
         <v>0</v>
@@ -12557,18 +12550,6 @@
         <v>-</v>
       </c>
       <c r="T107" s="4"/>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E110" s="12"/>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E111" s="12"/>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E112" s="12"/>
-    </row>
-    <row r="113" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E113" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -12753,7 +12734,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5A64DEF-E706-4B9C-B282-71F34F86B3DF}">
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
@@ -12793,11 +12774,11 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A86">_xlfn._xlws.FILTER(data[factor_name],data[Active])</f>
+        <f t="array" ref="A2:A85">_xlfn._xlws.FILTER(data[factor_name],data[Active])</f>
         <v>SPY</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:J86">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
+        <f t="array" ref="B2:J85">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
         <v>Equities</v>
       </c>
       <c r="C2" t="str">
@@ -15419,10 +15400,10 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
-        <v>UNCERTAINTY</v>
+        <v>BTC</v>
       </c>
       <c r="B84" t="str">
-        <v>Econ</v>
+        <v>Currencies</v>
       </c>
       <c r="C84" t="str">
         <v>USD</v>
@@ -15434,27 +15415,27 @@
         <v>0</v>
       </c>
       <c r="F84" t="str">
-        <v>Economic Policy Uncertainty Index for United States</v>
+        <v>-</v>
       </c>
       <c r="G84" t="str">
-        <v>fred</v>
+        <v>lmxl</v>
       </c>
       <c r="H84" t="str">
-        <v>USEPUINDXD</v>
+        <v>BTC1_price</v>
       </c>
       <c r="I84" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J84">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
-        <v>BTC</v>
+        <v>BTC_vol</v>
       </c>
       <c r="B85" t="str">
-        <v>Currencies</v>
+        <v>Vol</v>
       </c>
       <c r="C85" t="str">
         <v>USD</v>
@@ -15472,44 +15453,12 @@
         <v>lmxl</v>
       </c>
       <c r="H85" t="str">
-        <v>BTC1_price</v>
+        <v>BTC1_atm</v>
       </c>
       <c r="I85" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J85">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" t="str">
-        <v>BTC_vol</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Vol</v>
-      </c>
-      <c r="C86" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D86">
-        <v>0</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86" t="str">
-        <v>-</v>
-      </c>
-      <c r="G86" t="str">
-        <v>lmxl</v>
-      </c>
-      <c r="H86" t="str">
-        <v>BTC1_atm</v>
-      </c>
-      <c r="I86" t="str">
-        <v>normal</v>
-      </c>
-      <c r="J86">
         <v>-0.01</v>
       </c>
     </row>
@@ -17904,7 +17853,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2977BD7F-9323-4F6D-98BF-C1B39119DCDE}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
@@ -17944,11 +17893,11 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A86">_xlfn._xlws.FILTER(data[factor_name],data[Active]*(data[client]=0))</f>
+        <f t="array" ref="A2:A85">_xlfn._xlws.FILTER(data[factor_name],data[Active]*(data[client]=0))</f>
         <v>SPY</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:J86">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
+        <f t="array" ref="B2:J85">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
         <v>Equities</v>
       </c>
       <c r="C2" t="str">
@@ -20570,10 +20519,10 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
-        <v>UNCERTAINTY</v>
+        <v>BTC</v>
       </c>
       <c r="B84" t="str">
-        <v>Econ</v>
+        <v>Currencies</v>
       </c>
       <c r="C84" t="str">
         <v>USD</v>
@@ -20585,27 +20534,27 @@
         <v>0</v>
       </c>
       <c r="F84" t="str">
-        <v>Economic Policy Uncertainty Index for United States</v>
+        <v>-</v>
       </c>
       <c r="G84" t="str">
-        <v>fred</v>
+        <v>lmxl</v>
       </c>
       <c r="H84" t="str">
-        <v>USEPUINDXD</v>
+        <v>BTC1_price</v>
       </c>
       <c r="I84" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J84">
-        <v>0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
-        <v>BTC</v>
+        <v>BTC_vol</v>
       </c>
       <c r="B85" t="str">
-        <v>Currencies</v>
+        <v>Vol</v>
       </c>
       <c r="C85" t="str">
         <v>USD</v>
@@ -20623,44 +20572,12 @@
         <v>lmxl</v>
       </c>
       <c r="H85" t="str">
-        <v>BTC1_price</v>
+        <v>BTC1_atm</v>
       </c>
       <c r="I85" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J85">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" t="str">
-        <v>BTC_vol</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Vol</v>
-      </c>
-      <c r="C86" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D86">
-        <v>0</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86" t="str">
-        <v>-</v>
-      </c>
-      <c r="G86" t="str">
-        <v>lmxl</v>
-      </c>
-      <c r="H86" t="str">
-        <v>BTC1_atm</v>
-      </c>
-      <c r="I86" t="str">
-        <v>normal</v>
-      </c>
-      <c r="J86">
         <v>-0.01</v>
       </c>
     </row>
@@ -20878,7 +20795,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1A08F2F-299B-47F7-8064-36693758F4E3}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="44.28515625" bestFit="1" customWidth="1"/>
@@ -20903,11 +20820,11 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A77">_xlfn._xlws.FILTER(data[factor_name],data[Active]*NOT(data[composite]))</f>
+        <f t="array" ref="A2:A76">_xlfn._xlws.FILTER(data[factor_name],data[Active]*NOT(data[composite]))</f>
         <v>SPY</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:E77">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:E1,data[#Headers]))</f>
+        <f t="array" ref="B2:E76">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:E1,data[#Headers]))</f>
         <v>Equities</v>
       </c>
       <c r="C2" t="str">
@@ -22146,10 +22063,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
-        <v>UNCERTAINTY</v>
+        <v>BTC</v>
       </c>
       <c r="B75" t="str">
-        <v>Econ</v>
+        <v>Currencies</v>
       </c>
       <c r="C75" t="str">
         <v>USD</v>
@@ -22158,15 +22075,15 @@
         <v>0</v>
       </c>
       <c r="E75" t="str">
-        <v>Economic Policy Uncertainty Index for United States</v>
+        <v>-</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
-        <v>BTC</v>
+        <v>BTC_vol</v>
       </c>
       <c r="B76" t="str">
-        <v>Currencies</v>
+        <v>Vol</v>
       </c>
       <c r="C76" t="str">
         <v>USD</v>
@@ -22175,23 +22092,6 @@
         <v>0</v>
       </c>
       <c r="E76" t="str">
-        <v>-</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="str">
-        <v>BTC_vol</v>
-      </c>
-      <c r="B77" t="str">
-        <v>Vol</v>
-      </c>
-      <c r="C77" t="str">
-        <v>USD</v>
-      </c>
-      <c r="D77">
-        <v>0</v>
-      </c>
-      <c r="E77" t="str">
         <v>-</v>
       </c>
     </row>
@@ -27903,7 +27803,7 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <f ca="1">TODAY()-1</f>
-        <v>46131</v>
+        <v>46186</v>
       </c>
       <c r="B2">
         <v>0.20547945205479451</v>

--- a/factor_master.xlsx
+++ b/factor_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrai\Source\risk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8F7DF1-93C2-43EB-82ED-923B3F7BF83C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3EA20C8-F633-4FE5-AFF4-B6F6041E4058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="11" activeTab="11" xr2:uid="{C31FDC5B-A809-4BFD-99CB-DA02246721F7}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2592" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="738">
   <si>
     <t>SPX</t>
   </si>
@@ -2290,6 +2290,33 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>IWO</t>
+  </si>
+  <si>
+    <t>IWN</t>
+  </si>
+  <si>
+    <t>MTUM</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>iShares Russell 2000 Value ETF</t>
+  </si>
+  <si>
+    <t>iShares Russell 2000 Growth ETF</t>
+  </si>
+  <si>
+    <t>Growth</t>
+  </si>
+  <si>
+    <t>iShares MSCI USA Momentum Factor ETF</t>
+  </si>
+  <si>
+    <t>Momentum</t>
   </si>
 </sst>
 </file>
@@ -2820,7 +2847,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6DAD1482-C63D-400D-9F51-F22A8E35CAD8}" name="data" displayName="data" ref="A1:T107" totalsRowShown="0" headerRowDxfId="40" dataDxfId="38" headerRowBorderDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6DAD1482-C63D-400D-9F51-F22A8E35CAD8}" name="data" displayName="data" ref="A1:T110" totalsRowShown="0" headerRowDxfId="40" dataDxfId="38" headerRowBorderDxfId="39">
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{740DC173-AAC9-4239-A44E-C43F8517304D}" name="asset_class" dataDxfId="37"/>
     <tableColumn id="2" xr3:uid="{A3BC3BB8-0420-458E-AECD-FD567519FA40}" name="region" dataDxfId="36"/>
@@ -5909,12 +5936,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C29859C-7358-4E2F-B5CC-7696F1DAC449}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:Y107"/>
+  <dimension ref="A1:Y110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="44.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="59.140625" bestFit="1" customWidth="1"/>
@@ -7681,10 +7709,10 @@
         <v>39</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>13</v>
+        <v>730</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>455</v>
@@ -7696,49 +7724,37 @@
         <f t="array" ref="F29">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>150</v>
+        <v>732</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K29" s="4">
-        <v>1</v>
-      </c>
-      <c r="L29" s="4">
-        <v>0</v>
-      </c>
-      <c r="M29" s="4">
-        <v>0</v>
-      </c>
-      <c r="N29" s="4">
-        <v>0</v>
-      </c>
+        <v>733</v>
+      </c>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
       <c r="O29" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>FEZ</v>
+        <v>IWN</v>
       </c>
       <c r="P29" s="4" t="str" cm="1">
         <f t="array" ref="P29">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Eurostoxx 50</v>
+        <v>Value</v>
       </c>
       <c r="Q29" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>SPDR DJ Euro STOXX 50 Etf</v>
+        <v>-</v>
       </c>
       <c r="R29" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>SPDR EURO STOXX 50 ETF</v>
+        <v>-</v>
       </c>
       <c r="S29" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund employs a sampling strategy, which means that the fund is not required to purchase all of the securities represented in the index. It generally invests substantially all, but at least 80%, of its total assets in the securities comprising the index. The index is a market capitalization weighted index designed to represent the performance of some of the largest companies across components of the 20 EURO STOXX Supersector Indexes. The EURO STOXX Supersector Indexes are subsets of the EURO STOXX Index.</v>
+        <v>-</v>
       </c>
       <c r="T29" s="4"/>
     </row>
@@ -7747,10 +7763,10 @@
         <v>39</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>156</v>
+        <v>729</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>455</v>
@@ -7762,33 +7778,25 @@
         <f t="array" ref="F30">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>156</v>
-      </c>
+      <c r="G30" s="4"/>
       <c r="H30" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="I30" s="4"/>
+        <v>735</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>734</v>
+      </c>
       <c r="J30" s="4"/>
-      <c r="K30" s="4">
-        <v>0</v>
-      </c>
-      <c r="L30" s="4">
-        <v>0</v>
-      </c>
-      <c r="M30" s="4">
-        <v>0</v>
-      </c>
-      <c r="N30" s="4">
-        <v>0</v>
-      </c>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
       <c r="O30" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>SX7E</v>
+        <v>IWO</v>
       </c>
       <c r="P30" s="4" t="str" cm="1">
         <f t="array" ref="P30">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Eurostoxx Banks</v>
+        <v>Growth</v>
       </c>
       <c r="Q30" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
@@ -7809,10 +7817,10 @@
         <v>39</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>220</v>
+        <v>40</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>86</v>
+        <v>731</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>455</v>
@@ -7826,45 +7834,35 @@
       </c>
       <c r="G31" s="4"/>
       <c r="H31" s="4" t="s">
-        <v>509</v>
+        <v>737</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="K31" s="4">
-        <v>1</v>
-      </c>
-      <c r="L31" s="4">
-        <v>0</v>
-      </c>
-      <c r="M31" s="4">
-        <v>0</v>
-      </c>
-      <c r="N31" s="4">
-        <v>0</v>
-      </c>
+        <v>736</v>
+      </c>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
       <c r="O31" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>EWU</v>
+        <v>MTUM</v>
       </c>
       <c r="P31" s="4" t="str" cm="1">
         <f t="array" ref="P31">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>FTSE 100</v>
+        <v>Momentum</v>
       </c>
       <c r="Q31" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares MSCI</v>
+        <v>-</v>
       </c>
       <c r="R31" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares MSCI United Kingdom ETF</v>
+        <v>-</v>
       </c>
       <c r="S31" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund generally will invest at least 80% of its assets in the component securities of its underlying index and in investments that have economic characteristics that are substantially identical to the component securities of its underlying index. The underlying index is designed to measure the performance of the large- and mid-capitalization segments of the UK market. The fund is non-diversified.</v>
+        <v>-</v>
       </c>
       <c r="T31" s="4"/>
     </row>
@@ -7873,10 +7871,10 @@
         <v>39</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>455</v>
@@ -7889,16 +7887,16 @@
         <v>1E-4</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>85</v>
+        <v>149</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="K32" s="4">
         <v>1</v>
@@ -7914,23 +7912,23 @@
       </c>
       <c r="O32" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>DAX</v>
+        <v>FEZ</v>
       </c>
       <c r="P32" s="4" t="str" cm="1">
         <f t="array" ref="P32">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>DAX (Germany)</v>
+        <v>Eurostoxx 50</v>
       </c>
       <c r="Q32" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>Global X DAX Germany ETF</v>
+        <v>SPDR DJ Euro STOXX 50 Etf</v>
       </c>
       <c r="R32" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>Global X DAX Germany ETF</v>
+        <v>SPDR EURO STOXX 50 ETF</v>
       </c>
       <c r="S32" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund invests at least 80% of its total assets in the securities of the underlying index and in American Depositary Receipts ("ADRs") and Global Depositary Receipts ("GDRs") based on the securities in the underlying index. The index tracks the segment of the largest and most actively traded companies - known as blue chips - on the German equities market. The fund is non-diversified.</v>
+        <v>The fund employs a sampling strategy, which means that the fund is not required to purchase all of the securities represented in the index. It generally invests substantially all, but at least 80%, of its total assets in the securities comprising the index. The index is a market capitalization weighted index designed to represent the performance of some of the largest companies across components of the 20 EURO STOXX Supersector Indexes. The EURO STOXX Supersector Indexes are subsets of the EURO STOXX Index.</v>
       </c>
       <c r="T32" s="4"/>
     </row>
@@ -7939,10 +7937,10 @@
         <v>39</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>455</v>
@@ -7954,18 +7952,16 @@
         <f t="array" ref="F33">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G33" s="4"/>
+      <c r="G33" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="H33" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>120</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
       <c r="K33" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="4">
         <v>0</v>
@@ -7978,23 +7974,23 @@
       </c>
       <c r="O33" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>EWC</v>
+        <v>SX7E</v>
       </c>
       <c r="P33" s="4" t="str" cm="1">
         <f t="array" ref="P33">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>MSCI Canada</v>
+        <v>Eurostoxx Banks</v>
       </c>
       <c r="Q33" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares MSCI Canada Index Fund</v>
+        <v>-</v>
       </c>
       <c r="R33" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares MSCI Canada ETF</v>
+        <v>-</v>
       </c>
       <c r="S33" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund generally will invest at least 80% of its assets in the component securities of its underlying index and in investments that have economic characteristics that are substantially identical to the component securities of its underlying index. The underlying index is designed to measure broad-based equity performance in Canada. The underlying index includes large- and mid-capitalization companies and may change over time.</v>
+        <v>-</v>
       </c>
       <c r="T33" s="4"/>
     </row>
@@ -8003,10 +7999,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>68</v>
+        <v>220</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>327</v>
+        <v>86</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>455</v>
@@ -8018,16 +8014,18 @@
         <f t="array" ref="F34">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>328</v>
-      </c>
+      <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+        <v>509</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="K34" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="4">
         <v>0</v>
@@ -8040,23 +8038,23 @@
       </c>
       <c r="O34" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>FTSEMIB.MI</v>
+        <v>EWU</v>
       </c>
       <c r="P34" s="4" t="str" cm="1">
         <f t="array" ref="P34">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>FTSE MIB (Italy)</v>
+        <v>FTSE 100</v>
       </c>
       <c r="Q34" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>FTSE MIB Index</v>
+        <v>iShares MSCI</v>
       </c>
       <c r="R34" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>FTSE MIB Index</v>
-      </c>
-      <c r="S34" s="4">
+        <v>iShares MSCI United Kingdom ETF</v>
+      </c>
+      <c r="S34" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>0</v>
+        <v>The fund generally will invest at least 80% of its assets in the component securities of its underlying index and in investments that have economic characteristics that are substantially identical to the component securities of its underlying index. The underlying index is designed to measure the performance of the large- and mid-capitalization segments of the UK market. The fund is non-diversified.</v>
       </c>
       <c r="T34" s="4"/>
     </row>
@@ -8068,7 +8066,7 @@
         <v>68</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>455</v>
@@ -8081,19 +8079,19 @@
         <v>1E-4</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="K35" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="4">
         <v>0</v>
@@ -8106,23 +8104,23 @@
       </c>
       <c r="O35" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>CAC</v>
+        <v>DAX</v>
       </c>
       <c r="P35" s="4" t="str" cm="1">
         <f t="array" ref="P35">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>CAC 40 (France)</v>
+        <v>DAX (Germany)</v>
       </c>
       <c r="Q35" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>Camden National Corporation</v>
+        <v>Global X DAX Germany ETF</v>
       </c>
       <c r="R35" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>Camden National Corporation</v>
+        <v>Global X DAX Germany ETF</v>
       </c>
       <c r="S35" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>Camden National Corporation operates as the bank holding company for Camden National Bank that provides various commercial and consumer banking products and services for consumer, institutional, municipal, non-profit, and commercial customers in the United States. The company accepts checking, savings, time, and brokered deposits, as well as deposits with the certificate of deposit account registry system. Its loan products include non-owner-occupied commercial real estate loans; owner-occupied commercial real estate loans; commercial loans; residential real estate loans, including one- to four-family residences; and consumer and home equity loans. In addition, the company provides brokerage and insurance services through its financial offerings consisting of college, retirement, estate planning, mutual funds, strategic asset management accounts, and variable and fixed annuities. Further, it offers a range of fiduciary and asset management, wealth management, investment management and advisory, financial planning, and trustee services. Camden National Corporation was founded in 1875 and is headquartered in Camden, Maine.</v>
+        <v>The fund invests at least 80% of its total assets in the securities of the underlying index and in American Depositary Receipts ("ADRs") and Global Depositary Receipts ("GDRs") based on the securities in the underlying index. The index tracks the segment of the largest and most actively traded companies - known as blue chips - on the German equities market. The fund is non-diversified.</v>
       </c>
       <c r="T35" s="4"/>
     </row>
@@ -8131,10 +8129,10 @@
         <v>39</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>455</v>
@@ -8148,13 +8146,13 @@
       </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K36" s="4">
         <v>1</v>
@@ -8170,23 +8168,23 @@
       </c>
       <c r="O36" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>EWI</v>
+        <v>EWC</v>
       </c>
       <c r="P36" s="4" t="str" cm="1">
         <f t="array" ref="P36">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>MSCI Italy</v>
+        <v>MSCI Canada</v>
       </c>
       <c r="Q36" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v xml:space="preserve">iShares Inc iShares MSCI Italy </v>
+        <v>iShares MSCI Canada Index Fund</v>
       </c>
       <c r="R36" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares MSCI Italy ETF</v>
+        <v>iShares MSCI Canada ETF</v>
       </c>
       <c r="S36" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund generally will invest at least 80% of its assets in the component securities of its underlying index and in investments that have economic characteristics that are substantially identical to the component securities of its underlying index. The underlying index is a free float-adjusted market capitalization-weighted index that is designed to measure the performance of the large- and mid-capitalization segments of the equity market in Italy. The fund is non-diversified.</v>
+        <v>The fund generally will invest at least 80% of its assets in the component securities of its underlying index and in investments that have economic characteristics that are substantially identical to the component securities of its underlying index. The underlying index is designed to measure broad-based equity performance in Canada. The underlying index includes large- and mid-capitalization companies and may change over time.</v>
       </c>
       <c r="T36" s="4"/>
     </row>
@@ -8198,7 +8196,7 @@
         <v>68</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>455</v>
@@ -8211,15 +8209,13 @@
         <v>1E-4</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I37" s="4"/>
-      <c r="J37" s="4" t="s">
-        <v>121</v>
-      </c>
+      <c r="J37" s="4"/>
       <c r="K37" s="4">
         <v>0</v>
       </c>
@@ -8234,19 +8230,19 @@
       </c>
       <c r="O37" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>^IBEX</v>
+        <v>FTSEMIB.MI</v>
       </c>
       <c r="P37" s="4" t="str" cm="1">
         <f t="array" ref="P37">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>IBEX 35 (Spain)</v>
+        <v>FTSE MIB (Italy)</v>
       </c>
       <c r="Q37" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>IBEX 35...</v>
+        <v>FTSE MIB Index</v>
       </c>
       <c r="R37" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>IBEX 35...</v>
+        <v>FTSE MIB Index</v>
       </c>
       <c r="S37" s="4">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
@@ -8262,7 +8258,7 @@
         <v>68</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>455</v>
@@ -8274,15 +8270,17 @@
         <f t="array" ref="F38">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G38" s="4"/>
+      <c r="G38" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="H38" s="4" t="s">
-        <v>512</v>
+        <v>158</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K38" s="4">
         <v>0</v>
@@ -8298,23 +8296,23 @@
       </c>
       <c r="O38" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>EWP</v>
+        <v>CAC</v>
       </c>
       <c r="P38" s="4" t="str" cm="1">
         <f t="array" ref="P38">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>MSCI Spain</v>
+        <v>CAC 40 (France)</v>
       </c>
       <c r="Q38" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v xml:space="preserve">iShares Inc iShares MSCI Spain </v>
+        <v>Camden National Corporation</v>
       </c>
       <c r="R38" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares MSCI Spain ETF</v>
+        <v>Camden National Corporation</v>
       </c>
       <c r="S38" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund generally will invest at least 80% of its assets in the component securities of its underlying index and in investments that have economic characteristics that are substantially identical to the component securities of its underlying index. The index is a free float-adjusted market capitalization-weighted index that is designed to measure the performance of the large- and mid-capitalization segments of the equity market in Spain. The fund is non-diversified.</v>
+        <v>Camden National Corporation operates as the bank holding company for Camden National Bank that provides various commercial and consumer banking products and services for consumer, institutional, municipal, non-profit, and commercial customers in the United States. The company accepts checking, savings, time, and brokered deposits, as well as deposits with the certificate of deposit account registry system. Its loan products include non-owner-occupied commercial real estate loans; owner-occupied commercial real estate loans; commercial loans; residential real estate loans, including one- to four-family residences; and consumer and home equity loans. In addition, the company provides brokerage and insurance services through its financial offerings consisting of college, retirement, estate planning, mutual funds, strategic asset management accounts, and variable and fixed annuities. Further, it offers a range of fiduciary and asset management, wealth management, investment management and advisory, financial planning, and trustee services. Camden National Corporation was founded in 1875 and is headquartered in Camden, Maine.</v>
       </c>
       <c r="T38" s="4"/>
     </row>
@@ -8323,10 +8321,10 @@
         <v>39</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>324</v>
+        <v>93</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>455</v>
@@ -8338,17 +8336,15 @@
         <f t="array" ref="F39">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G39" s="4" t="s">
-        <v>77</v>
-      </c>
+      <c r="G39" s="4"/>
       <c r="H39" s="4" t="s">
-        <v>141</v>
+        <v>511</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="K39" s="4">
         <v>1</v>
@@ -8364,23 +8360,23 @@
       </c>
       <c r="O39" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>^N225</v>
+        <v>EWI</v>
       </c>
       <c r="P39" s="4" t="str" cm="1">
         <f t="array" ref="P39">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Nikkei 225</v>
+        <v>MSCI Italy</v>
       </c>
       <c r="Q39" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>Nikkei 225</v>
+        <v xml:space="preserve">iShares Inc iShares MSCI Italy </v>
       </c>
       <c r="R39" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>Nikkei 225</v>
-      </c>
-      <c r="S39" s="4">
+        <v>iShares MSCI Italy ETF</v>
+      </c>
+      <c r="S39" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>0</v>
+        <v>The fund generally will invest at least 80% of its assets in the component securities of its underlying index and in investments that have economic characteristics that are substantially identical to the component securities of its underlying index. The underlying index is a free float-adjusted market capitalization-weighted index that is designed to measure the performance of the large- and mid-capitalization segments of the equity market in Italy. The fund is non-diversified.</v>
       </c>
       <c r="T39" s="4"/>
     </row>
@@ -8389,10 +8385,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>142</v>
+        <v>330</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>455</v>
@@ -8405,16 +8401,14 @@
         <v>1E-4</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>142</v>
+        <v>329</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="I40" s="4"/>
       <c r="J40" s="4" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="K40" s="4">
         <v>0</v>
@@ -8430,37 +8424,35 @@
       </c>
       <c r="O40" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>TPX</v>
+        <v>^IBEX</v>
       </c>
       <c r="P40" s="4" t="str" cm="1">
         <f t="array" ref="P40">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>TOPIX</v>
+        <v>IBEX 35 (Spain)</v>
       </c>
       <c r="Q40" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>-</v>
+        <v>IBEX 35...</v>
       </c>
       <c r="R40" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>-</v>
-      </c>
-      <c r="S40" s="4" t="str">
+        <v>IBEX 35...</v>
+      </c>
+      <c r="S40" s="4">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>-</v>
-      </c>
-      <c r="T40" s="4" t="s">
-        <v>489</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T40" s="4"/>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>455</v>
@@ -8472,20 +8464,18 @@
         <f t="array" ref="F41">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G41" s="4" t="s">
-        <v>80</v>
-      </c>
+      <c r="G41" s="4"/>
       <c r="H41" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K41" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="4">
         <v>0</v>
@@ -8498,23 +8488,23 @@
       </c>
       <c r="O41" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>FXI</v>
+        <v>EWP</v>
       </c>
       <c r="P41" s="4" t="str" cm="1">
         <f t="array" ref="P41">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>China Large-Cap</v>
+        <v>MSCI Spain</v>
       </c>
       <c r="Q41" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares China Large-Cap ETF</v>
+        <v xml:space="preserve">iShares Inc iShares MSCI Spain </v>
       </c>
       <c r="R41" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares China Large-Cap ETF</v>
+        <v>iShares MSCI Spain ETF</v>
       </c>
       <c r="S41" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund generally will invest at least 80% of its assets in the component securities of its underlying index and in investments that have economic characteristics that are substantially identical to the component securities of its underlying index. The index designed to measure the performance of the largest companies in the Chinese equity market that trade on the Stock Exchange of Hong Kong and are available to international investors. The fund is non-diversified.</v>
+        <v>The fund generally will invest at least 80% of its assets in the component securities of its underlying index and in investments that have economic characteristics that are substantially identical to the component securities of its underlying index. The index is a free float-adjusted market capitalization-weighted index that is designed to measure the performance of the large- and mid-capitalization segments of the equity market in Spain. The fund is non-diversified.</v>
       </c>
       <c r="T41" s="4"/>
     </row>
@@ -8523,10 +8513,10 @@
         <v>39</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>82</v>
+        <v>324</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>455</v>
@@ -8539,16 +8529,16 @@
         <v>1E-4</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K42" s="4">
         <v>1</v>
@@ -8564,23 +8554,23 @@
       </c>
       <c r="O42" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>ASHR</v>
+        <v>^N225</v>
       </c>
       <c r="P42" s="4" t="str" cm="1">
         <f t="array" ref="P42">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>CSI 300 (China)</v>
+        <v>Nikkei 225</v>
       </c>
       <c r="Q42" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>Xtrackers Harvest CSI 300 China</v>
+        <v>Nikkei 225</v>
       </c>
       <c r="R42" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>Xtrackers Harvest CSI 300 China A-Shares ETF</v>
-      </c>
-      <c r="S42" s="4" t="str">
+        <v>Nikkei 225</v>
+      </c>
+      <c r="S42" s="4">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund will normally invest at least 80% of its total assets in securities of issuers that comprise the underlying index. The underlying index is designed to reflect the price fluctuation and performance of the China A-Share market and is composed of the 300 largest and most liquid stocks in the China A-Share market. The underlying index includes small-cap, mid-cap, and large-cap stocks. It is non-diversified.</v>
+        <v>0</v>
       </c>
       <c r="T42" s="4"/>
     </row>
@@ -8589,10 +8579,10 @@
         <v>39</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>400</v>
+        <v>142</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>455</v>
@@ -8605,17 +8595,19 @@
         <v>1E-4</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>400</v>
+        <v>142</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>514</v>
+        <v>145</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="J43" s="4"/>
+        <v>143</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="K43" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="4">
         <v>0</v>
@@ -8628,35 +8620,37 @@
       </c>
       <c r="O43" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>KWEB</v>
+        <v>TPX</v>
       </c>
       <c r="P43" s="4" t="str" cm="1">
         <f t="array" ref="P43">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>CSI China Internet</v>
+        <v>TOPIX</v>
       </c>
       <c r="Q43" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>KraneShares Trust KraneShares C</v>
+        <v>-</v>
       </c>
       <c r="R43" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>KraneShares CSI China Internet ETF</v>
+        <v>-</v>
       </c>
       <c r="S43" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund will invest at least 80% of its net assets in instruments in its underlying index or in instruments that have economic characteristics similar to those in the underlying index. The index is designed to measure the equity market performance of investable publicly traded "China-based companies" whose primary business or businesses are in the Internet and Internet-related sectors, and are listed outside of Mainland China, as determined by the index provider. The fund is non-diversified.</v>
-      </c>
-      <c r="T43" s="4"/>
+        <v>-</v>
+      </c>
+      <c r="T43" s="4" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>199</v>
+        <v>80</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>455</v>
@@ -8668,13 +8662,17 @@
         <f t="array" ref="F44">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G44" s="4"/>
+      <c r="G44" s="4" t="s">
+        <v>80</v>
+      </c>
       <c r="H44" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="I44" s="4"/>
+        <v>513</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="J44" s="4" t="s">
-        <v>515</v>
+        <v>116</v>
       </c>
       <c r="K44" s="4">
         <v>1</v>
@@ -8690,35 +8688,35 @@
       </c>
       <c r="O44" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>EEM</v>
+        <v>FXI</v>
       </c>
       <c r="P44" s="4" t="str" cm="1">
         <f t="array" ref="P44">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>MSCI EM</v>
+        <v>China Large-Cap</v>
       </c>
       <c r="Q44" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares MSCI Emerging Index Fun</v>
+        <v>iShares China Large-Cap ETF</v>
       </c>
       <c r="R44" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares MSCI Emerging Markets ETF</v>
+        <v>iShares China Large-Cap ETF</v>
       </c>
       <c r="S44" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund generally will invest at least 80% of its assets in the component securities of its underlying index and in investments that have economic characteristics that are substantially identical to the component securities of its underlying index. The index is designed to measure equity market performance in the global emerging markets. The underlying index includes large- and mid-capitalization companies and may change over time.</v>
+        <v>The fund generally will invest at least 80% of its assets in the component securities of its underlying index and in investments that have economic characteristics that are substantially identical to the component securities of its underlying index. The index designed to measure the performance of the largest companies in the Chinese equity market that trade on the Stock Exchange of Hong Kong and are available to international investors. The fund is non-diversified.</v>
       </c>
       <c r="T44" s="4"/>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>455</v>
@@ -8731,14 +8729,16 @@
         <v>1E-4</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="H45" s="4"/>
+        <v>82</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>192</v>
+      </c>
       <c r="I45" s="4" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="K45" s="4">
         <v>1</v>
@@ -8754,35 +8754,35 @@
       </c>
       <c r="O45" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>LQD</v>
+        <v>ASHR</v>
       </c>
       <c r="P45" s="4" t="str" cm="1">
         <f t="array" ref="P45">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
+        <v>CSI 300 (China)</v>
       </c>
       <c r="Q45" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares iBoxx $ Investment Grad</v>
+        <v>Xtrackers Harvest CSI 300 China</v>
       </c>
       <c r="R45" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
+        <v>Xtrackers Harvest CSI 300 China A-Shares ETF</v>
       </c>
       <c r="S45" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund will invest at least 80% of its assets in the component securities of the underlying index, and it will invest at least 90% of its assets in fixed income securities of the types included in the underlying index that the advisor believes will help the fund track the underlying index. The underlying index is designed to provide a broad representation of the U.S. dollar-denominated liquid investment-grade corporate bond market.</v>
+        <v>The fund will normally invest at least 80% of its total assets in securities of issuers that comprise the underlying index. The underlying index is designed to reflect the price fluctuation and performance of the China A-Share market and is composed of the 300 largest and most liquid stocks in the China A-Share market. The underlying index includes small-cap, mid-cap, and large-cap stocks. It is non-diversified.</v>
       </c>
       <c r="T45" s="4"/>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>455</v>
@@ -8794,14 +8794,16 @@
         <f t="array" ref="F46">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
+      <c r="G46" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>514</v>
+      </c>
       <c r="I46" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>488</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="J46" s="4"/>
       <c r="K46" s="4">
         <v>1</v>
       </c>
@@ -8816,35 +8818,35 @@
       </c>
       <c r="O46" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>BSV</v>
+        <v>KWEB</v>
       </c>
       <c r="P46" s="4" t="str" cm="1">
         <f t="array" ref="P46">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Vanguard Short-Term Bond Index Fund ETF</v>
+        <v>CSI China Internet</v>
       </c>
       <c r="Q46" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>Vanguard Short-Term Bond ETF</v>
+        <v>KraneShares Trust KraneShares C</v>
       </c>
       <c r="R46" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>Vanguard Short-Term Bond Index Fund ETF Shares</v>
+        <v>KraneShares CSI China Internet ETF</v>
       </c>
       <c r="S46" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>This index includes all medium and larger issues of U.S. government, investment-grade corporate, and investment-grade international dollar-denominated bonds that have maturities between 1 and 5 years and are publicly issued. All of the fund's investments will be selected through the sampling process, and at least 80% of its assets will be invested in bonds held in the index.</v>
+        <v>The fund will invest at least 80% of its net assets in instruments in its underlying index or in instruments that have economic characteristics similar to those in the underlying index. The index is designed to measure the equity market performance of investable publicly traded "China-based companies" whose primary business or businesses are in the Internet and Internet-related sectors, and are listed outside of Mainland China, as determined by the index provider. The fund is non-diversified.</v>
       </c>
       <c r="T46" s="4"/>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>12</v>
+        <v>199</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>455</v>
@@ -8856,15 +8858,13 @@
         <f t="array" ref="F47">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G47" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4" t="s">
-        <v>48</v>
-      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I47" s="4"/>
       <c r="J47" s="4" t="s">
-        <v>104</v>
+        <v>515</v>
       </c>
       <c r="K47" s="4">
         <v>1</v>
@@ -8880,23 +8880,23 @@
       </c>
       <c r="O47" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>HYG</v>
+        <v>EEM</v>
       </c>
       <c r="P47" s="4" t="str" cm="1">
         <f t="array" ref="P47">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
+        <v>MSCI EM</v>
       </c>
       <c r="Q47" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares iBoxx $ High Yield Corp</v>
+        <v>iShares MSCI Emerging Index Fun</v>
       </c>
       <c r="R47" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
+        <v>iShares MSCI Emerging Markets ETF</v>
       </c>
       <c r="S47" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The underlying index is a rules-based index consisting of U.S. dollar-denominated, high yield corporate bonds for sale in the U.S. The fund will invest at least 80% of its assets in the component securities of the underlying index, and the fund will invest at least 90% of its assets in fixed income securities of the types included in the underlying index that the advisor believes will help the fund track the underlying index.</v>
+        <v>The fund generally will invest at least 80% of its assets in the component securities of its underlying index and in investments that have economic characteristics that are substantially identical to the component securities of its underlying index. The index is designed to measure equity market performance in the global emerging markets. The underlying index includes large- and mid-capitalization companies and may change over time.</v>
       </c>
       <c r="T47" s="4"/>
     </row>
@@ -8908,7 +8908,7 @@
         <v>40</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>347</v>
+        <v>10</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>455</v>
@@ -8921,20 +8921,20 @@
         <v>1E-4</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="I48" s="4"/>
+        <v>426</v>
+      </c>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="J48" s="4" t="s">
-        <v>406</v>
+        <v>103</v>
       </c>
       <c r="K48" s="4">
         <v>1</v>
       </c>
       <c r="L48" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="4">
         <v>0</v>
@@ -8944,23 +8944,23 @@
       </c>
       <c r="O48" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>LQDH</v>
+        <v>LQD</v>
       </c>
       <c r="P48" s="4" t="str" cm="1">
         <f t="array" ref="P48">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Hedged LQD</v>
+        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
       </c>
       <c r="Q48" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares Interest Rate Hedged Co</v>
+        <v>iShares iBoxx $ Investment Grad</v>
       </c>
       <c r="R48" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares Interest Rate Hedged Corporate Bond ETF</v>
+        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
       </c>
       <c r="S48" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The index is designed to minimize the interest-rate risk exposure of a portfolio composed of U.S. dollar-denominated, investment grade bonds, represented in the index by the underlying fund, by including a series of up to 10 interest rate swap contracts with different maturities. The fund invests, under normal circumstances, at least 80% of its net assets, plus the amount of any borrowings for investment purposes, in component securities and instruments in the index and/or bonds included in the underlying index of the underlying fund.</v>
+        <v>The fund will invest at least 80% of its assets in the component securities of the underlying index, and it will invest at least 90% of its assets in fixed income securities of the types included in the underlying index that the advisor believes will help the fund track the underlying index. The underlying index is designed to provide a broad representation of the U.S. dollar-denominated liquid investment-grade corporate bond market.</v>
       </c>
       <c r="T48" s="4"/>
     </row>
@@ -8972,7 +8972,7 @@
         <v>40</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>348</v>
+        <v>447</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>455</v>
@@ -8984,15 +8984,13 @@
         <f t="array" ref="F49">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G49" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>525</v>
-      </c>
-      <c r="I49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4" t="s">
+        <v>487</v>
+      </c>
       <c r="J49" s="4" t="s">
-        <v>408</v>
+        <v>488</v>
       </c>
       <c r="K49" s="4">
         <v>1</v>
@@ -9008,23 +9006,23 @@
       </c>
       <c r="O49" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>HYGH</v>
+        <v>BSV</v>
       </c>
       <c r="P49" s="4" t="str" cm="1">
         <f t="array" ref="P49">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Hedged HYG</v>
+        <v>Vanguard Short-Term Bond Index Fund ETF</v>
       </c>
       <c r="Q49" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares Interest Rate Hedged Hi</v>
+        <v>Vanguard Short-Term Bond ETF</v>
       </c>
       <c r="R49" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares Interest Rate Hedged High Yield Bond ETF</v>
+        <v>Vanguard Short-Term Bond Index Fund ETF Shares</v>
       </c>
       <c r="S49" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund seeks to track the investment results of the underlying index, which is designed to minimize the interest-rate risk of a portfolio composed of U.S. dollar-denominated, high yield corporate bonds, represented in the underlying index by the underlying fund. It invests at least 80% of its net assets in component securities and instruments in the fund’s underlying index.</v>
+        <v>This index includes all medium and larger issues of U.S. government, investment-grade corporate, and investment-grade international dollar-denominated bonds that have maturities between 1 and 5 years and are publicly issued. All of the fund's investments will be selected through the sampling process, and at least 80% of its assets will be invested in bonds held in the index.</v>
       </c>
       <c r="T49" s="4"/>
     </row>
@@ -9036,7 +9034,7 @@
         <v>40</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>293</v>
+        <v>12</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>455</v>
@@ -9049,13 +9047,15 @@
         <v>1E-4</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
+        <v>427</v>
+      </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>104</v>
+      </c>
       <c r="K50" s="4">
         <v>1</v>
       </c>
@@ -9070,23 +9070,23 @@
       </c>
       <c r="O50" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>BKLN</v>
+        <v>HYG</v>
       </c>
       <c r="P50" s="4" t="str" cm="1">
         <f t="array" ref="P50">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Bank Loans</v>
+        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
       </c>
       <c r="Q50" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>-</v>
+        <v>iShares iBoxx $ High Yield Corp</v>
       </c>
       <c r="R50" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>-</v>
+        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
       </c>
       <c r="S50" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>-</v>
+        <v>The underlying index is a rules-based index consisting of U.S. dollar-denominated, high yield corporate bonds for sale in the U.S. The fund will invest at least 80% of its assets in the component securities of the underlying index, and the fund will invest at least 90% of its assets in fixed income securities of the types included in the underlying index that the advisor believes will help the fund track the underlying index.</v>
       </c>
       <c r="T50" s="4"/>
     </row>
@@ -9098,7 +9098,7 @@
         <v>40</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>218</v>
+        <v>347</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>455</v>
@@ -9110,19 +9110,21 @@
         <f t="array" ref="F51">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G51" s="4"/>
+      <c r="G51" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="H51" s="4" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="I51" s="4"/>
       <c r="J51" s="4" t="s">
-        <v>516</v>
+        <v>406</v>
       </c>
       <c r="K51" s="4">
         <v>1</v>
       </c>
       <c r="L51" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="4">
         <v>0</v>
@@ -9132,51 +9134,55 @@
       </c>
       <c r="O51" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>AGG</v>
+        <v>LQDH</v>
       </c>
       <c r="P51" s="4" t="str" cm="1">
         <f t="array" ref="P51">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>US Agg</v>
+        <v>Hedged LQD</v>
       </c>
       <c r="Q51" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares Core U.S. Aggregate Bon</v>
+        <v>iShares Interest Rate Hedged Co</v>
       </c>
       <c r="R51" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares Core U.S. Aggregate Bond ETF</v>
+        <v>iShares Interest Rate Hedged Corporate Bond ETF</v>
       </c>
       <c r="S51" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The index measures the performance of the total U.S. investment-grade bond market. The fund will invest at least 80% of its assets in the component securities of the underlying index and TBAs that have economic characteristics that are substantially identical to the economic characteristics of the component securities of the underlying index, and the fund will invest at least 90% of its assets in fixed income securities of the types included in the underlying index that the advisor believes will help the fund track the underlying index.</v>
+        <v>The index is designed to minimize the interest-rate risk exposure of a portfolio composed of U.S. dollar-denominated, investment grade bonds, represented in the index by the underlying fund, by including a series of up to 10 interest rate swap contracts with different maturities. The fund invests, under normal circumstances, at least 80% of its net assets, plus the amount of any borrowings for investment purposes, in component securities and instruments in the index and/or bonds included in the underlying index of the underlying fund.</v>
       </c>
       <c r="T51" s="4"/>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>458</v>
+        <v>348</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>455</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="F52" s="4" cm="1">
         <f t="array" ref="F52">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
-        <v>-0.01</v>
-      </c>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
+        <v>1E-4</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>525</v>
+      </c>
       <c r="I52" s="4"/>
       <c r="J52" s="4" t="s">
-        <v>518</v>
+        <v>408</v>
       </c>
       <c r="K52" s="4">
         <v>1</v>
@@ -9192,35 +9198,35 @@
       </c>
       <c r="O52" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>^TNX</v>
+        <v>HYGH</v>
       </c>
       <c r="P52" s="4" t="str" cm="1">
         <f t="array" ref="P52">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>CBOE Interest Rate 10 Year</v>
+        <v>Hedged HYG</v>
       </c>
       <c r="Q52" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>CBOE Interest Rate 10 Year T No</v>
+        <v>iShares Interest Rate Hedged Hi</v>
       </c>
       <c r="R52" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>CBOE Interest Rate 10 Year T No</v>
-      </c>
-      <c r="S52" s="4">
+        <v>iShares Interest Rate Hedged High Yield Bond ETF</v>
+      </c>
+      <c r="S52" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>0</v>
+        <v>The fund seeks to track the investment results of the underlying index, which is designed to minimize the interest-rate risk of a portfolio composed of U.S. dollar-denominated, high yield corporate bonds, represented in the underlying index by the underlying fund. It invests at least 80% of its net assets in component securities and instruments in the fund’s underlying index.</v>
       </c>
       <c r="T52" s="4"/>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>51</v>
+        <v>293</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>455</v>
@@ -9233,18 +9239,13 @@
         <v>1E-4</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="H53" s="4" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(data[[#This Row],[Description_GPT]],"iShares ")," Bond")</f>
-        <v>1-3 Year Treasury</v>
-      </c>
-      <c r="I53" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>129</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
       <c r="K53" s="4">
         <v>1</v>
       </c>
@@ -9259,35 +9260,35 @@
       </c>
       <c r="O53" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>SHY</v>
+        <v>BKLN</v>
       </c>
       <c r="P53" s="4" t="str" cm="1">
         <f t="array" ref="P53">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>1-3 Year Treasury</v>
+        <v>Bank Loans</v>
       </c>
       <c r="Q53" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v xml:space="preserve">iShares 1-3 Year Treasury Bond </v>
+        <v>-</v>
       </c>
       <c r="R53" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares 1-3 Year Treasury Bond ETF</v>
+        <v>-</v>
       </c>
       <c r="S53" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund will invest at least 80% of its assets in the component securities of the underlying index and it will invest at least 90% of its assets in U.S. Treasury securities that BFA believes will help the fund track the underlying index. The underlying index measures the performance of public obligations of the U.S. Treasury that have a remaining maturity of greater than or equal to one year and less than three years.</v>
+        <v>-</v>
       </c>
       <c r="T53" s="4"/>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>126</v>
+        <v>218</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>455</v>
@@ -9299,18 +9300,13 @@
         <f t="array" ref="F54">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G54" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="H54" s="4" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(data[[#This Row],[Description_GPT]],"iShares ")," Bond")</f>
-        <v>3-7 Year Treasury</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>127</v>
-      </c>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="I54" s="4"/>
       <c r="J54" s="4" t="s">
-        <v>130</v>
+        <v>516</v>
       </c>
       <c r="K54" s="4">
         <v>1</v>
@@ -9326,23 +9322,23 @@
       </c>
       <c r="O54" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>IEI</v>
+        <v>AGG</v>
       </c>
       <c r="P54" s="4" t="str" cm="1">
         <f t="array" ref="P54">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>3-7 Year Treasury</v>
+        <v>US Agg</v>
       </c>
       <c r="Q54" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v xml:space="preserve">iShares 3-7 Year Treasury Bond </v>
+        <v>iShares Core U.S. Aggregate Bon</v>
       </c>
       <c r="R54" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares 3-7 Year Treasury Bond ETF</v>
+        <v>iShares Core U.S. Aggregate Bond ETF</v>
       </c>
       <c r="S54" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The index measures the performance of public obligations of the U.S. Treasury that have a remaining maturity of greater than or equal to three years and less than seven years. The fund will invest at least 80% of its assets in the component securities of the index, and the fund will invest at least 90% of its assets in U.S. Treasury securities that BFA believes will help the fund track the index.</v>
+        <v>The index measures the performance of the total U.S. investment-grade bond market. The fund will invest at least 80% of its assets in the component securities of the underlying index and TBAs that have economic characteristics that are substantially identical to the economic characteristics of the component securities of the underlying index, and the fund will invest at least 90% of its assets in fixed income securities of the types included in the underlying index that the advisor believes will help the fund track the underlying index.</v>
       </c>
       <c r="T54" s="4"/>
     </row>
@@ -9354,36 +9350,29 @@
         <v>40</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>131</v>
+        <v>458</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>455</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="F55" s="4" cm="1">
         <f t="array" ref="F55">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
-        <v>1E-4</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="H55" s="4" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(data[[#This Row],[Description_GPT]],"iShares ")," Bond")</f>
-        <v>7-10 Year Treasury</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>132</v>
-      </c>
+        <v>-0.01</v>
+      </c>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
       <c r="J55" s="4" t="s">
-        <v>133</v>
+        <v>518</v>
       </c>
       <c r="K55" s="4">
         <v>1</v>
       </c>
       <c r="L55" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="4">
         <v>0</v>
@@ -9393,23 +9382,23 @@
       </c>
       <c r="O55" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>IEF</v>
+        <v>^TNX</v>
       </c>
       <c r="P55" s="4" t="str" cm="1">
         <f t="array" ref="P55">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>7-10 Year Treasury</v>
+        <v>CBOE Interest Rate 10 Year</v>
       </c>
       <c r="Q55" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares 7-10 Year Treasury Bond</v>
+        <v>CBOE Interest Rate 10 Year T No</v>
       </c>
       <c r="R55" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares 7-10 Year Treasury Bond ETF</v>
-      </c>
-      <c r="S55" s="4" t="str">
+        <v>CBOE Interest Rate 10 Year T No</v>
+      </c>
+      <c r="S55" s="4">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The underlying index measures the performance of public obligations of the U.S. Treasury that have a remaining maturity of greater than or equal to seven years and less than ten years. The fund will invest at least 80% of its assets in the component securities of the underlying index, and the fund will invest at least 90% of its assets in U.S. Treasury securities that the advisor believes will help the fund track the underlying index.</v>
+        <v>0</v>
       </c>
       <c r="T55" s="4"/>
     </row>
@@ -9421,7 +9410,7 @@
         <v>40</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>455</v>
@@ -9434,17 +9423,17 @@
         <v>1E-4</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H56" s="4" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(data[[#This Row],[Description_GPT]],"iShares ")," Bond")</f>
-        <v>20+ Year Treasury</v>
+        <v>1-3 Year Treasury</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K56" s="4">
         <v>1</v>
@@ -9460,23 +9449,23 @@
       </c>
       <c r="O56" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>TLT</v>
+        <v>SHY</v>
       </c>
       <c r="P56" s="4" t="str" cm="1">
         <f t="array" ref="P56">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>20+ Year Treasury</v>
+        <v>1-3 Year Treasury</v>
       </c>
       <c r="Q56" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v xml:space="preserve">iShares 20+ Year Treasury Bond </v>
+        <v xml:space="preserve">iShares 1-3 Year Treasury Bond </v>
       </c>
       <c r="R56" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares 20+ Year Treasury Bond ETF</v>
+        <v>iShares 1-3 Year Treasury Bond ETF</v>
       </c>
       <c r="S56" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund will invest at least 80% of its assets in the component securities of the underlying index, and it will invest at least 90% of its assets in U.S. Treasury securities that the advisor believes will help the fund track the underlying index. The underlying index measures the performance of public obligations of the U.S. Treasury that have a remaining maturity greater than or equal to twenty years.</v>
+        <v>The fund will invest at least 80% of its assets in the component securities of the underlying index and it will invest at least 90% of its assets in U.S. Treasury securities that BFA believes will help the fund track the underlying index. The underlying index measures the performance of public obligations of the U.S. Treasury that have a remaining maturity of greater than or equal to one year and less than three years.</v>
       </c>
       <c r="T56" s="4"/>
     </row>
@@ -9488,7 +9477,7 @@
         <v>40</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>455</v>
@@ -9500,13 +9489,18 @@
         <f t="array" ref="F57">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
+      <c r="G57" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="H57" s="4" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(data[[#This Row],[Description_GPT]],"iShares ")," Bond")</f>
+        <v>3-7 Year Treasury</v>
+      </c>
       <c r="I57" s="4" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="K57" s="4">
         <v>1</v>
@@ -9522,23 +9516,23 @@
       </c>
       <c r="O57" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>TIP</v>
+        <v>IEI</v>
       </c>
       <c r="P57" s="4" t="str" cm="1">
         <f t="array" ref="P57">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>iShares TIPS Bond ETF</v>
+        <v>3-7 Year Treasury</v>
       </c>
       <c r="Q57" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares TIPS Bond ETF</v>
+        <v xml:space="preserve">iShares 3-7 Year Treasury Bond </v>
       </c>
       <c r="R57" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares TIPS Bond ETF</v>
+        <v>iShares 3-7 Year Treasury Bond ETF</v>
       </c>
       <c r="S57" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The index tracks the performance of inflation-protected public obligations of the U.S. Treasury, commonly known as “TIPS,” that have a remaining maturity of more than one year. The fund will invest at least 80% of its assets in the component securities of the index, and it will invest at least 90% of its assets in U.S. Treasury securities that BFA believes will help the fund track the index.</v>
+        <v>The index measures the performance of public obligations of the U.S. Treasury that have a remaining maturity of greater than or equal to three years and less than seven years. The fund will invest at least 80% of its assets in the component securities of the index, and the fund will invest at least 90% of its assets in U.S. Treasury securities that BFA believes will help the fund track the index.</v>
       </c>
       <c r="T57" s="4"/>
     </row>
@@ -9550,7 +9544,7 @@
         <v>40</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>344</v>
+        <v>131</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>455</v>
@@ -9562,17 +9556,24 @@
         <f t="array" ref="F58">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
+      <c r="G58" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="H58" s="4" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(data[[#This Row],[Description_GPT]],"iShares ")," Bond")</f>
+        <v>7-10 Year Treasury</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="J58" s="4" t="s">
-        <v>519</v>
+        <v>133</v>
       </c>
       <c r="K58" s="4">
         <v>1</v>
       </c>
       <c r="L58" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="4">
         <v>0</v>
@@ -9582,23 +9583,23 @@
       </c>
       <c r="O58" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>VTIP</v>
+        <v>IEF</v>
       </c>
       <c r="P58" s="4" t="str" cm="1">
         <f t="array" ref="P58">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Short-Term Inflation-Protected Securities ETF</v>
+        <v>7-10 Year Treasury</v>
       </c>
       <c r="Q58" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>Vanguard Short-Term Inflation-P</v>
+        <v>iShares 7-10 Year Treasury Bond</v>
       </c>
       <c r="R58" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>Vanguard Short-Term Inflation-Protected Securities Index Fund ETF Shares</v>
+        <v>iShares 7-10 Year Treasury Bond ETF</v>
       </c>
       <c r="S58" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The index is a market-capitalization-weighted index that includes all inflation-protected public obligations issued by the U.S. Treasury with remaining maturities of less than 5 years.</v>
+        <v>The underlying index measures the performance of public obligations of the U.S. Treasury that have a remaining maturity of greater than or equal to seven years and less than ten years. The fund will invest at least 80% of its assets in the component securities of the underlying index, and the fund will invest at least 90% of its assets in U.S. Treasury securities that the advisor believes will help the fund track the underlying index.</v>
       </c>
       <c r="T58" s="4"/>
     </row>
@@ -9610,7 +9611,7 @@
         <v>40</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>455</v>
@@ -9622,16 +9623,21 @@
         <f t="array" ref="F59">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
+      <c r="G59" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="H59" s="4" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(data[[#This Row],[Description_GPT]],"iShares ")," Bond")</f>
+        <v>20+ Year Treasury</v>
+      </c>
       <c r="I59" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="K59" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="4">
         <v>0</v>
@@ -9644,23 +9650,23 @@
       </c>
       <c r="O59" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>MBB</v>
+        <v>TLT</v>
       </c>
       <c r="P59" s="4" t="str" cm="1">
         <f t="array" ref="P59">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>iShares MBS ETF</v>
+        <v>20+ Year Treasury</v>
       </c>
       <c r="Q59" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares MBS ETF</v>
+        <v xml:space="preserve">iShares 20+ Year Treasury Bond </v>
       </c>
       <c r="R59" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares MBS ETF</v>
+        <v>iShares 20+ Year Treasury Bond ETF</v>
       </c>
       <c r="S59" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund will invest at least 80% of its assets in the component securities of the underlying index and TBAs that have economic characteristics that are substantially identical to the economic characteristics of the component securities of the index, and the fund will invest at least 90% of its assets in fixed income securities of the types included in the underlying index that BFA believes will help the fund track the index.</v>
+        <v>The fund will invest at least 80% of its assets in the component securities of the underlying index, and it will invest at least 90% of its assets in U.S. Treasury securities that the advisor believes will help the fund track the underlying index. The underlying index measures the performance of public obligations of the U.S. Treasury that have a remaining maturity greater than or equal to twenty years.</v>
       </c>
       <c r="T59" s="4"/>
     </row>
@@ -9672,7 +9678,7 @@
         <v>40</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>455</v>
@@ -9686,14 +9692,14 @@
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
-      <c r="I60" t="s">
-        <v>152</v>
+      <c r="I60" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="K60" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="4">
         <v>0</v>
@@ -9706,23 +9712,23 @@
       </c>
       <c r="O60" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>MBTA</v>
+        <v>TIP</v>
       </c>
       <c r="P60" s="4" t="str" cm="1">
         <f t="array" ref="P60">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Simplify Mortgage Backed Securities ETF</v>
+        <v>iShares TIPS Bond ETF</v>
       </c>
       <c r="Q60" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>-</v>
+        <v>iShares TIPS Bond ETF</v>
       </c>
       <c r="R60" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>-</v>
+        <v>iShares TIPS Bond ETF</v>
       </c>
       <c r="S60" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>-</v>
+        <v>The index tracks the performance of inflation-protected public obligations of the U.S. Treasury, commonly known as “TIPS,” that have a remaining maturity of more than one year. The fund will invest at least 80% of its assets in the component securities of the index, and it will invest at least 90% of its assets in U.S. Treasury securities that BFA believes will help the fund track the index.</v>
       </c>
       <c r="T60" s="4"/>
     </row>
@@ -9734,7 +9740,7 @@
         <v>40</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>15</v>
+        <v>344</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>455</v>
@@ -9748,11 +9754,9 @@
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
-      <c r="I61" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="I61" s="4"/>
       <c r="J61" s="4" t="s">
-        <v>106</v>
+        <v>519</v>
       </c>
       <c r="K61" s="4">
         <v>1</v>
@@ -9768,23 +9772,23 @@
       </c>
       <c r="O61" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>AGNC</v>
+        <v>VTIP</v>
       </c>
       <c r="P61" s="4" t="str" cm="1">
         <f t="array" ref="P61">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>AGNC Investment Corp.</v>
+        <v>Short-Term Inflation-Protected Securities ETF</v>
       </c>
       <c r="Q61" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>AGNC Investment Corp.</v>
+        <v>Vanguard Short-Term Inflation-P</v>
       </c>
       <c r="R61" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>AGNC Investment Corp.</v>
+        <v>Vanguard Short-Term Inflation-Protected Securities Index Fund ETF Shares</v>
       </c>
       <c r="S61" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>AGNC Investment Corp. provides private capital to housing market in the United States. The company invests in residential mortgage pass-through securities and collateralized mortgage obligations for which the principal and interest payments are guaranteed by the United States government-sponsored enterprise or by the United States government agency. It qualifies as a real estate investment trust for federal income tax purposes. The company generally would not be subject to federal or state corporate income taxes if it distributes at least 90% of its taxable income to its stockholders. The company was formerly known as American Capital Agency Corp. and changed its name to AGNC Investment Corp. in September 2016. AGNC Investment Corp. was incorporated in 2008 and is headquartered in Bethesda, Maryland.</v>
+        <v>The index is a market-capitalization-weighted index that includes all inflation-protected public obligations issued by the U.S. Treasury with remaining maturities of less than 5 years.</v>
       </c>
       <c r="T61" s="4"/>
     </row>
@@ -9796,7 +9800,7 @@
         <v>40</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>346</v>
+        <v>53</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>455</v>
@@ -9810,12 +9814,14 @@
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
+      <c r="I62" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="J62" s="4" t="s">
-        <v>520</v>
+        <v>105</v>
       </c>
       <c r="K62" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="4">
         <v>0</v>
@@ -9828,23 +9834,23 @@
       </c>
       <c r="O62" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>VMBS</v>
+        <v>MBB</v>
       </c>
       <c r="P62" s="4" t="str" cm="1">
         <f t="array" ref="P62">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Mortgage-Backed Securities ETF</v>
+        <v>iShares MBS ETF</v>
       </c>
       <c r="Q62" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>Vanguard Mortgage-Backed Securi</v>
+        <v>iShares MBS ETF</v>
       </c>
       <c r="R62" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>Vanguard Mortgage-Backed Securities Index Fund ETF Shares</v>
+        <v>iShares MBS ETF</v>
       </c>
       <c r="S62" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund employs an indexing investment approach designed to track the performance of the Bloomberg U.S. MBS Float Adjusted Index. This index covers U.S. agency mortgage-backed pass-through securities issued by the GNMA, the FNMA, and the FHLMC. To be included in the index, pool aggregates must have at least $1 billion currently outstanding and a weighted average maturity of at least 1 year. All of the fund's investments will be selected through the sampling process, and at least 80% of the fund's assets will be invested in bonds included in the index.</v>
+        <v>The fund will invest at least 80% of its assets in the component securities of the underlying index and TBAs that have economic characteristics that are substantially identical to the economic characteristics of the component securities of the index, and the fund will invest at least 90% of its assets in fixed income securities of the types included in the underlying index that BFA believes will help the fund track the index.</v>
       </c>
       <c r="T62" s="4"/>
     </row>
@@ -9856,7 +9862,7 @@
         <v>40</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>345</v>
+        <v>14</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>455</v>
@@ -9870,12 +9876,14 @@
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
+      <c r="I63" t="s">
+        <v>152</v>
+      </c>
       <c r="J63" s="4" t="s">
-        <v>417</v>
+        <v>153</v>
       </c>
       <c r="K63" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="4">
         <v>0</v>
@@ -9888,23 +9896,23 @@
       </c>
       <c r="O63" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>CMBS</v>
+        <v>MBTA</v>
       </c>
       <c r="P63" s="4" t="str" cm="1">
         <f t="array" ref="P63">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>iShares CMBS ETF</v>
+        <v>Simplify Mortgage Backed Securities ETF</v>
       </c>
       <c r="Q63" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares CMBS Bond ETF</v>
+        <v>-</v>
       </c>
       <c r="R63" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares CMBS ETF</v>
+        <v>-</v>
       </c>
       <c r="S63" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The index measures the performance of investment-grade commercial mortgage-backed securities ("CMBS"), which are classes of securities (known as "certificates") that represent interests in "pools" of commercial mortgages. The fund will invest at least 80% of its assets in the component securities of the underlying index, and it will invest at least 90% of its assets in fixed income securities of the types included in the underlying index that BFA believes will help the fund track the underlying index.</v>
+        <v>-</v>
       </c>
       <c r="T63" s="4"/>
     </row>
@@ -9913,10 +9921,10 @@
         <v>128</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>455</v>
@@ -9931,10 +9939,10 @@
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="K64" s="4">
         <v>1</v>
@@ -9950,23 +9958,23 @@
       </c>
       <c r="O64" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>EMB</v>
+        <v>AGNC</v>
       </c>
       <c r="P64" s="4" t="str" cm="1">
         <f t="array" ref="P64">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
+        <v>AGNC Investment Corp.</v>
       </c>
       <c r="Q64" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares J.P. Morgan USD Emergin</v>
+        <v>AGNC Investment Corp.</v>
       </c>
       <c r="R64" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
+        <v>AGNC Investment Corp.</v>
       </c>
       <c r="S64" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund will invest at least 80% of its assets in the component securities of the underlying index and will invest at least 90% of its assets in fixed income securities of the types included in the underlying index. The index is a broad, diverse U.S. dollar-denominated emerging markets debt benchmark that tracks the total return of actively traded external debt instruments in emerging market countries.</v>
+        <v>AGNC Investment Corp. provides private capital to housing market in the United States. The company invests in residential mortgage pass-through securities and collateralized mortgage obligations for which the principal and interest payments are guaranteed by the United States government-sponsored enterprise or by the United States government agency. It qualifies as a real estate investment trust for federal income tax purposes. The company generally would not be subject to federal or state corporate income taxes if it distributes at least 90% of its taxable income to its stockholders. The company was formerly known as American Capital Agency Corp. and changed its name to AGNC Investment Corp. in September 2016. AGNC Investment Corp. was incorporated in 2008 and is headquartered in Bethesda, Maryland.</v>
       </c>
       <c r="T64" s="4"/>
     </row>
@@ -9975,10 +9983,10 @@
         <v>128</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>455</v>
@@ -9994,10 +10002,10 @@
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
       <c r="J65" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K65" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="4">
         <v>0</v>
@@ -10010,23 +10018,23 @@
       </c>
       <c r="O65" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>EMHY</v>
+        <v>VMBS</v>
       </c>
       <c r="P65" s="4" t="str" cm="1">
         <f t="array" ref="P65">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>iShares JP Morgan EM High Yield Bond ETF</v>
+        <v>Mortgage-Backed Securities ETF</v>
       </c>
       <c r="Q65" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares J.P. Morgan EM High Yie</v>
+        <v>Vanguard Mortgage-Backed Securi</v>
       </c>
       <c r="R65" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares J.P. Morgan EM High Yield Bond ETF</v>
+        <v>Vanguard Mortgage-Backed Securities Index Fund ETF Shares</v>
       </c>
       <c r="S65" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund will invest at least 80% of its assets in the component securities of the underlying index, and the fund will invest at least 90% of its assets in fixed income securities of the types included in the underlying index that BFA believes will help the fund track the underlying index. The index tracks the performance of below investment-grade U.S. dollar-denominated, emerging market fixed and floating-rate debt securities issued by corporate, sovereign, and quasi-sovereign entities.</v>
+        <v>The fund employs an indexing investment approach designed to track the performance of the Bloomberg U.S. MBS Float Adjusted Index. This index covers U.S. agency mortgage-backed pass-through securities issued by the GNMA, the FNMA, and the FHLMC. To be included in the index, pool aggregates must have at least $1 billion currently outstanding and a weighted average maturity of at least 1 year. All of the fund's investments will be selected through the sampling process, and at least 80% of the fund's assets will be invested in bonds included in the index.</v>
       </c>
       <c r="T65" s="4"/>
     </row>
@@ -10034,11 +10042,11 @@
       <c r="A66" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B66" t="s">
-        <v>74</v>
-      </c>
-      <c r="C66" t="s">
-        <v>75</v>
+      <c r="B66" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>345</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>455</v>
@@ -10050,14 +10058,14 @@
         <f t="array" ref="F66">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="I66" t="s">
-        <v>76</v>
-      </c>
-      <c r="J66" t="s">
-        <v>114</v>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4" t="s">
+        <v>417</v>
       </c>
       <c r="K66" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="4">
         <v>0</v>
@@ -10070,23 +10078,23 @@
       </c>
       <c r="O66" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>CEW</v>
+        <v>CMBS</v>
       </c>
       <c r="P66" s="4" t="str" cm="1">
         <f t="array" ref="P66">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>WisdomTree Emerging Markets Local Debt Fund</v>
+        <v>iShares CMBS ETF</v>
       </c>
       <c r="Q66" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>WisdomTree Emerging Currency St</v>
+        <v>iShares CMBS Bond ETF</v>
       </c>
       <c r="R66" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>WisdomTree Emerging Currency Strategy Fund</v>
+        <v>iShares CMBS ETF</v>
       </c>
       <c r="S66" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund will invest, under normal circumstances, at least 80% of its net assets, plus the amount of any borrowings for investment purposes, in investments whose combined performance is tied economically to selected emerging market countries. It generally will maintain a weighted average portfolio maturity of 90 days or less with respect to the money market securities in its portfolio. The fund is non-diversified.</v>
+        <v>The index measures the performance of investment-grade commercial mortgage-backed securities ("CMBS"), which are classes of securities (known as "certificates") that represent interests in "pools" of commercial mortgages. The fund will invest at least 80% of its assets in the component securities of the underlying index, and it will invest at least 90% of its assets in fixed income securities of the types included in the underlying index that BFA believes will help the fund track the underlying index.</v>
       </c>
       <c r="T66" s="4"/>
     </row>
@@ -10098,7 +10106,7 @@
         <v>74</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>455</v>
@@ -10113,13 +10121,13 @@
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K67" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="4">
         <v>0</v>
@@ -10132,35 +10140,35 @@
       </c>
       <c r="O67" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>IGOV</v>
+        <v>EMB</v>
       </c>
       <c r="P67" s="4" t="str" cm="1">
         <f t="array" ref="P67">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>iShares International Government Bonds ETF</v>
+        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
       </c>
       <c r="Q67" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v xml:space="preserve">iShares International Treasury </v>
+        <v>iShares J.P. Morgan USD Emergin</v>
       </c>
       <c r="R67" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares International Treasury Bond ETF</v>
+        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
       </c>
       <c r="S67" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund will invest at least 80% of its assets in the component securities of the underlying index and will invest at least 90% of its assets in fixed income securities of the types included in the underlying index. The underlying index measures the performance of fixed-rate, local currency, investment-grade, sovereign bonds from certain developed markets. The fund is non-diversified.</v>
+        <v>The fund will invest at least 80% of its assets in the component securities of the underlying index and will invest at least 90% of its assets in fixed income securities of the types included in the underlying index. The index is a broad, diverse U.S. dollar-denominated emerging markets debt benchmark that tracks the total return of actively traded external debt instruments in emerging market countries.</v>
       </c>
       <c r="T67" s="4"/>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>57</v>
+        <v>349</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>455</v>
@@ -10172,18 +10180,14 @@
         <f t="array" ref="F68">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G68" s="4" t="s">
-        <v>263</v>
-      </c>
+      <c r="G68" s="4"/>
       <c r="H68" s="4"/>
-      <c r="I68" s="4" t="s">
-        <v>58</v>
-      </c>
+      <c r="I68" s="4"/>
       <c r="J68" s="4" t="s">
-        <v>107</v>
+        <v>521</v>
       </c>
       <c r="K68" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="4">
         <v>0</v>
@@ -10196,35 +10200,35 @@
       </c>
       <c r="O68" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>GLD</v>
+        <v>EMHY</v>
       </c>
       <c r="P68" s="4" t="str" cm="1">
         <f t="array" ref="P68">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>SPDR Gold Shares</v>
+        <v>iShares JP Morgan EM High Yield Bond ETF</v>
       </c>
       <c r="Q68" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>SPDR Gold Trust</v>
+        <v>iShares J.P. Morgan EM High Yie</v>
       </c>
       <c r="R68" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>SPDR Gold Shares</v>
+        <v>iShares J.P. Morgan EM High Yield Bond ETF</v>
       </c>
       <c r="S68" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The Trust holds gold bars and from time to time, issues Baskets in exchange for deposits of gold and distributes gold in connection with redemptions of Baskets. The investment objective of the Trust is for the Shares to reflect the performance of the price of gold bullion, less the Trust’s expenses. The Sponsor believes that, for many investors, the Shares represent a cost-effective investment in gold.</v>
+        <v>The fund will invest at least 80% of its assets in the component securities of the underlying index, and the fund will invest at least 90% of its assets in fixed income securities of the types included in the underlying index that BFA believes will help the fund track the underlying index. The index tracks the performance of below investment-grade U.S. dollar-denominated, emerging market fixed and floating-rate debt securities issued by corporate, sovereign, and quasi-sovereign entities.</v>
       </c>
       <c r="T68" s="4"/>
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>59</v>
+        <v>128</v>
+      </c>
+      <c r="B69" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" t="s">
+        <v>75</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>455</v>
@@ -10236,18 +10240,14 @@
         <f t="array" ref="F69">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G69" s="4" t="s">
-        <v>703</v>
-      </c>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>108</v>
+      <c r="I69" t="s">
+        <v>76</v>
+      </c>
+      <c r="J69" t="s">
+        <v>114</v>
       </c>
       <c r="K69" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="4">
         <v>0</v>
@@ -10260,35 +10260,35 @@
       </c>
       <c r="O69" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>SLV</v>
+        <v>CEW</v>
       </c>
       <c r="P69" s="4" t="str" cm="1">
         <f t="array" ref="P69">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>iShares Silver Trust</v>
+        <v>WisdomTree Emerging Markets Local Debt Fund</v>
       </c>
       <c r="Q69" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iShares Silver Trust</v>
+        <v>WisdomTree Emerging Currency St</v>
       </c>
       <c r="R69" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iShares Silver Trust</v>
+        <v>WisdomTree Emerging Currency Strategy Fund</v>
       </c>
       <c r="S69" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The Trust seeks to reflect such performance before payment of the Trust's expenses and liabilities. It is not actively managed. The Trust does not engage in any activities designed to obtain a profit from, or to ameliorate losses caused by, changes in the price of silver.</v>
+        <v>The fund will invest, under normal circumstances, at least 80% of its net assets, plus the amount of any borrowings for investment purposes, in investments whose combined performance is tied economically to selected emerging market countries. It generally will maintain a weighted average portfolio maturity of 90 days or less with respect to the money market securities in its portfolio. The fund is non-diversified.</v>
       </c>
       <c r="T69" s="4"/>
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>455</v>
@@ -10300,18 +10300,16 @@
         <f t="array" ref="F70">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G70" s="4" t="s">
-        <v>704</v>
-      </c>
+      <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="K70" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="4">
         <v>0</v>
@@ -10324,23 +10322,23 @@
       </c>
       <c r="O70" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>USO</v>
+        <v>IGOV</v>
       </c>
       <c r="P70" s="4" t="str" cm="1">
         <f t="array" ref="P70">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>United States Oil Fund</v>
+        <v>iShares International Government Bonds ETF</v>
       </c>
       <c r="Q70" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>United States Oil Fund</v>
+        <v xml:space="preserve">iShares International Treasury </v>
       </c>
       <c r="R70" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>United States Oil Fund, LP</v>
+        <v>iShares International Treasury Bond ETF</v>
       </c>
       <c r="S70" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>USO invests primarily in futures contracts for light, sweet crude oil, other types of crude oil, diesel-heating oil, gasoline, natural gas, and other petroleum-based fuels.</v>
+        <v>The fund will invest at least 80% of its assets in the component securities of the underlying index and will invest at least 90% of its assets in fixed income securities of the types included in the underlying index. The underlying index measures the performance of fixed-rate, local currency, investment-grade, sovereign bonds from certain developed markets. The fund is non-diversified.</v>
       </c>
       <c r="T70" s="4"/>
     </row>
@@ -10352,7 +10350,7 @@
         <v>40</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>698</v>
+        <v>57</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>455</v>
@@ -10365,34 +10363,46 @@
         <v>1E-4</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>705</v>
+        <v>263</v>
       </c>
       <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4"/>
+      <c r="I71" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="K71" s="4">
+        <v>1</v>
+      </c>
+      <c r="L71" s="4">
+        <v>0</v>
+      </c>
+      <c r="M71" s="4">
+        <v>0</v>
+      </c>
+      <c r="N71" s="4">
+        <v>0</v>
+      </c>
       <c r="O71" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>DBA</v>
+        <v>GLD</v>
       </c>
       <c r="P71" s="4" t="str" cm="1">
         <f t="array" ref="P71">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>-</v>
+        <v>SPDR Gold Shares</v>
       </c>
       <c r="Q71" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>-</v>
+        <v>SPDR Gold Trust</v>
       </c>
       <c r="R71" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>-</v>
+        <v>SPDR Gold Shares</v>
       </c>
       <c r="S71" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>-</v>
+        <v>The Trust holds gold bars and from time to time, issues Baskets in exchange for deposits of gold and distributes gold in connection with redemptions of Baskets. The investment objective of the Trust is for the Shares to reflect the performance of the price of gold bullion, less the Trust’s expenses. The Sponsor believes that, for many investors, the Shares represent a cost-effective investment in gold.</v>
       </c>
       <c r="T71" s="4"/>
     </row>
@@ -10404,7 +10414,7 @@
         <v>40</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>699</v>
+        <v>59</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>455</v>
@@ -10417,34 +10427,46 @@
         <v>1E-4</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
-      <c r="N72" s="4"/>
+      <c r="I72" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K72" s="4">
+        <v>1</v>
+      </c>
+      <c r="L72" s="4">
+        <v>0</v>
+      </c>
+      <c r="M72" s="4">
+        <v>0</v>
+      </c>
+      <c r="N72" s="4">
+        <v>0</v>
+      </c>
       <c r="O72" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>DBB</v>
+        <v>SLV</v>
       </c>
       <c r="P72" s="4" t="str" cm="1">
         <f t="array" ref="P72">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>-</v>
+        <v>iShares Silver Trust</v>
       </c>
       <c r="Q72" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>-</v>
+        <v>iShares Silver Trust</v>
       </c>
       <c r="R72" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>-</v>
+        <v>iShares Silver Trust</v>
       </c>
       <c r="S72" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>-</v>
+        <v>The Trust seeks to reflect such performance before payment of the Trust's expenses and liabilities. It is not actively managed. The Trust does not engage in any activities designed to obtain a profit from, or to ameliorate losses caused by, changes in the price of silver.</v>
       </c>
       <c r="T72" s="4"/>
     </row>
@@ -10456,7 +10478,7 @@
         <v>40</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>455</v>
@@ -10469,17 +10491,17 @@
         <v>1E-4</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K73" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="4">
         <v>0</v>
@@ -10492,23 +10514,23 @@
       </c>
       <c r="O73" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>DBC</v>
+        <v>USO</v>
       </c>
       <c r="P73" s="4" t="str" cm="1">
         <f t="array" ref="P73">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Invesco DB Commodity Index Tracking Fund</v>
+        <v>United States Oil Fund</v>
       </c>
       <c r="Q73" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>Invesco DB Commodity Index Trac</v>
+        <v>United States Oil Fund</v>
       </c>
       <c r="R73" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>Invesco DB Commodity Index Tracking Fund</v>
+        <v>United States Oil Fund, LP</v>
       </c>
       <c r="S73" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund pursues its investment objective by investing in a portfolio of exchange-traded futures on Light Sweet Crude Oil (WTI), Heating Oil, RBOB Gasoline, Natural Gas, Brent Crude, Gold, Silver, Aluminum, Zinc, Copper Grade A, Corn, Wheat, Soybeans, and Sugar. The index is composed of notional amounts of each of these commodities.</v>
+        <v>USO invests primarily in futures contracts for light, sweet crude oil, other types of crude oil, diesel-heating oil, gasoline, natural gas, and other petroleum-based fuels.</v>
       </c>
       <c r="T73" s="4"/>
     </row>
@@ -10520,7 +10542,7 @@
         <v>40</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>455</v>
@@ -10533,7 +10555,7 @@
         <v>1E-4</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
@@ -10544,7 +10566,7 @@
       <c r="N74" s="4"/>
       <c r="O74" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>DBE</v>
+        <v>DBA</v>
       </c>
       <c r="P74" s="4" t="str" cm="1">
         <f t="array" ref="P74">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
@@ -10572,7 +10594,7 @@
         <v>40</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>455</v>
@@ -10585,7 +10607,7 @@
         <v>1E-4</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
@@ -10596,7 +10618,7 @@
       <c r="N75" s="4"/>
       <c r="O75" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>DBO</v>
+        <v>DBB</v>
       </c>
       <c r="P75" s="4" t="str" cm="1">
         <f t="array" ref="P75">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
@@ -10624,7 +10646,7 @@
         <v>40</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>702</v>
+        <v>63</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>455</v>
@@ -10637,46 +10659,58 @@
         <v>1E-4</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4"/>
-      <c r="M76" s="4"/>
-      <c r="N76" s="4"/>
+      <c r="I76" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="K76" s="4">
+        <v>0</v>
+      </c>
+      <c r="L76" s="4">
+        <v>0</v>
+      </c>
+      <c r="M76" s="4">
+        <v>0</v>
+      </c>
+      <c r="N76" s="4">
+        <v>0</v>
+      </c>
       <c r="O76" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>DBP</v>
+        <v>DBC</v>
       </c>
       <c r="P76" s="4" t="str" cm="1">
         <f t="array" ref="P76">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>-</v>
+        <v>Invesco DB Commodity Index Tracking Fund</v>
       </c>
       <c r="Q76" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>-</v>
+        <v>Invesco DB Commodity Index Trac</v>
       </c>
       <c r="R76" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>-</v>
+        <v>Invesco DB Commodity Index Tracking Fund</v>
       </c>
       <c r="S76" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>-</v>
+        <v>The fund pursues its investment objective by investing in a portfolio of exchange-traded futures on Light Sweet Crude Oil (WTI), Heating Oil, RBOB Gasoline, Natural Gas, Brent Crude, Gold, Silver, Aluminum, Zinc, Copper Grade A, Corn, Wheat, Soybeans, and Sugar. The index is composed of notional amounts of each of these commodities.</v>
       </c>
       <c r="T76" s="4"/>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>66</v>
+        <v>700</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>455</v>
@@ -10688,57 +10722,47 @@
         <f t="array" ref="F77">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G77" s="4"/>
+      <c r="G77" s="4" t="s">
+        <v>707</v>
+      </c>
       <c r="H77" s="4"/>
-      <c r="I77" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="K77" s="4">
-        <v>1</v>
-      </c>
-      <c r="L77" s="4">
-        <v>0</v>
-      </c>
-      <c r="M77" s="4">
-        <v>0</v>
-      </c>
-      <c r="N77" s="4">
-        <v>0</v>
-      </c>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
       <c r="O77" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>UUP</v>
+        <v>DBE</v>
       </c>
       <c r="P77" s="4" t="str" cm="1">
         <f t="array" ref="P77">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Invesco DB US Dollar Index Bullish Fund</v>
+        <v>-</v>
       </c>
       <c r="Q77" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>Invesco DB USD Index Bullish Fu</v>
+        <v>-</v>
       </c>
       <c r="R77" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>Invesco DB US Dollar Index Bullish Fund</v>
+        <v>-</v>
       </c>
       <c r="S77" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund invests in futures contracts in an attempt to track its index. The index is calculated to reflect the changes in market value over time, whether positive or negative, of long positions in DX Contracts.</v>
+        <v>-</v>
       </c>
       <c r="T77" s="4"/>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>491</v>
+        <v>701</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>455</v>
@@ -10751,56 +10775,46 @@
         <v>1E-4</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>492</v>
+        <v>704</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
-      <c r="J78" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="K78" s="4">
-        <v>1</v>
-      </c>
-      <c r="L78" s="4">
-        <v>0</v>
-      </c>
-      <c r="M78" s="4">
-        <v>0</v>
-      </c>
-      <c r="N78" s="4">
-        <v>0</v>
-      </c>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
       <c r="O78" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>DX-Y.NYB</v>
+        <v>DBO</v>
       </c>
       <c r="P78" s="4" t="str" cm="1">
         <f t="array" ref="P78">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>U.S. Dollar Index</v>
+        <v>-</v>
       </c>
       <c r="Q78" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>ICE US Dollar Index - Index - C</v>
+        <v>-</v>
       </c>
       <c r="R78" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>US Dollar Index</v>
-      </c>
-      <c r="S78" s="4">
+        <v>-</v>
+      </c>
+      <c r="S78" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="T78" s="4"/>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>69</v>
+        <v>702</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>455</v>
@@ -10813,58 +10827,46 @@
         <v>1E-4</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>297</v>
+        <v>708</v>
       </c>
       <c r="H79" s="4"/>
-      <c r="I79" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J79" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="K79" s="4">
-        <v>1</v>
-      </c>
-      <c r="L79" s="4">
-        <v>0</v>
-      </c>
-      <c r="M79" s="4">
-        <v>0</v>
-      </c>
-      <c r="N79" s="4">
-        <v>0</v>
-      </c>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
       <c r="O79" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>FXE</v>
+        <v>DBP</v>
       </c>
       <c r="P79" s="4" t="str" cm="1">
         <f t="array" ref="P79">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Invesco CurrencyShares Euro Trust</v>
+        <v>-</v>
       </c>
       <c r="Q79" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>Invesco CurrencyShares Euro Cur</v>
+        <v>-</v>
       </c>
       <c r="R79" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>Invesco CurrencyShares Euro Currency Trust</v>
-      </c>
-      <c r="S79" s="4">
+        <v>-</v>
+      </c>
+      <c r="S79" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="T79" s="4"/>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="A80" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B80" t="s">
-        <v>68</v>
-      </c>
-      <c r="C80" t="s">
-        <v>497</v>
+      <c r="B80" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>455</v>
@@ -10876,14 +10878,13 @@
         <f t="array" ref="F80">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G80" t="s">
-        <v>524</v>
-      </c>
-      <c r="I80" t="s">
-        <v>498</v>
-      </c>
-      <c r="J80" t="s">
-        <v>499</v>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="K80" s="4">
         <v>1</v>
@@ -10899,35 +10900,35 @@
       </c>
       <c r="O80" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>FXF</v>
+        <v>UUP</v>
       </c>
       <c r="P80" s="4" t="str" cm="1">
         <f t="array" ref="P80">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Invesco CurrencyShares Swiss Franc Trust</v>
+        <v>Invesco DB US Dollar Index Bullish Fund</v>
       </c>
       <c r="Q80" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>Invesco CurrencyShares Swiss Fr</v>
+        <v>Invesco DB USD Index Bullish Fu</v>
       </c>
       <c r="R80" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>Invesco CurrencyShares Swiss Franc Trust</v>
+        <v>Invesco DB US Dollar Index Bullish Fund</v>
       </c>
       <c r="S80" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund seeks to reflect the price of the Swiss Franc. The sponsor believes that, for many investors, the shares represent a cost-effective investment relative to traditional means of investing in the foreign exchange market.</v>
+        <v>The fund invests in futures contracts in an attempt to track its index. The index is calculated to reflect the changes in market value over time, whether positive or negative, of long positions in DX Contracts.</v>
       </c>
       <c r="T80" s="4"/>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="A81" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B81" t="s">
-        <v>690</v>
-      </c>
-      <c r="C81" t="s">
-        <v>691</v>
+      <c r="B81" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>491</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>455</v>
@@ -10939,11 +10940,13 @@
         <f t="array" ref="F81">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G81" t="s">
-        <v>300</v>
-      </c>
-      <c r="I81" t="s">
-        <v>694</v>
+      <c r="G81" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="K81" s="4">
         <v>1</v>
@@ -10959,35 +10962,35 @@
       </c>
       <c r="O81" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>FXA</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="P81" s="4" t="str" cm="1">
         <f t="array" ref="P81">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Invesco CurrencyShares Australian Dollar Trust</v>
+        <v>U.S. Dollar Index</v>
       </c>
       <c r="Q81" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>-</v>
+        <v>ICE US Dollar Index - Index - C</v>
       </c>
       <c r="R81" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>-</v>
-      </c>
-      <c r="S81" s="4" t="str">
+        <v>US Dollar Index</v>
+      </c>
+      <c r="S81" s="4">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="T81" s="4"/>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="A82" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B82" t="s">
-        <v>220</v>
-      </c>
-      <c r="C82" t="s">
-        <v>689</v>
+      <c r="B82" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>455</v>
@@ -10999,11 +11002,15 @@
         <f t="array" ref="F82">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
         <v>1E-4</v>
       </c>
-      <c r="G82" t="s">
-        <v>299</v>
-      </c>
-      <c r="I82" t="s">
-        <v>695</v>
+      <c r="G82" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="K82" s="4">
         <v>1</v>
@@ -11019,23 +11026,23 @@
       </c>
       <c r="O82" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>FXB</v>
+        <v>FXE</v>
       </c>
       <c r="P82" s="4" t="str" cm="1">
         <f t="array" ref="P82">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
+        <v>Invesco CurrencyShares Euro Trust</v>
       </c>
       <c r="Q82" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>-</v>
+        <v>Invesco CurrencyShares Euro Cur</v>
       </c>
       <c r="R82" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>-</v>
-      </c>
-      <c r="S82" s="4" t="str">
+        <v>Invesco CurrencyShares Euro Currency Trust</v>
+      </c>
+      <c r="S82" s="4">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="T82" s="4"/>
     </row>
@@ -11044,10 +11051,10 @@
         <v>65</v>
       </c>
       <c r="B83" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="C83" t="s">
-        <v>692</v>
+        <v>497</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>455</v>
@@ -11060,10 +11067,13 @@
         <v>1E-4</v>
       </c>
       <c r="G83" t="s">
-        <v>693</v>
+        <v>524</v>
       </c>
       <c r="I83" t="s">
-        <v>696</v>
+        <v>498</v>
+      </c>
+      <c r="J83" t="s">
+        <v>499</v>
       </c>
       <c r="K83" s="4">
         <v>1</v>
@@ -11079,23 +11089,23 @@
       </c>
       <c r="O83" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>FXC</v>
+        <v>FXF</v>
       </c>
       <c r="P83" s="4" t="str" cm="1">
         <f t="array" ref="P83">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
+        <v>Invesco CurrencyShares Swiss Franc Trust</v>
       </c>
       <c r="Q83" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>-</v>
+        <v>Invesco CurrencyShares Swiss Fr</v>
       </c>
       <c r="R83" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>-</v>
+        <v>Invesco CurrencyShares Swiss Franc Trust</v>
       </c>
       <c r="S83" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>-</v>
+        <v>The fund seeks to reflect the price of the Swiss Franc. The sponsor believes that, for many investors, the shares represent a cost-effective investment relative to traditional means of investing in the foreign exchange market.</v>
       </c>
       <c r="T83" s="4"/>
     </row>
@@ -11104,10 +11114,10 @@
         <v>65</v>
       </c>
       <c r="B84" t="s">
-        <v>71</v>
+        <v>690</v>
       </c>
       <c r="C84" t="s">
-        <v>72</v>
+        <v>691</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>455</v>
@@ -11120,13 +11130,10 @@
         <v>1E-4</v>
       </c>
       <c r="G84" t="s">
-        <v>523</v>
+        <v>300</v>
       </c>
       <c r="I84" t="s">
-        <v>73</v>
-      </c>
-      <c r="J84" t="s">
-        <v>113</v>
+        <v>694</v>
       </c>
       <c r="K84" s="4">
         <v>1</v>
@@ -11142,52 +11149,52 @@
       </c>
       <c r="O84" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>FXY</v>
+        <v>FXA</v>
       </c>
       <c r="P84" s="4" t="str" cm="1">
         <f t="array" ref="P84">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Invesco CurrencyShares Japanese Yen Trust</v>
+        <v>Invesco CurrencyShares Australian Dollar Trust</v>
       </c>
       <c r="Q84" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>Invesco CurrencyShares Japanese</v>
+        <v>-</v>
       </c>
       <c r="R84" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>Invesco CurrencyShares Japanese Yen Trust</v>
+        <v>-</v>
       </c>
       <c r="S84" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The fund seeks to reflect the price in USD of the Japanese Yen. The sponsor believes that, for many investors, the shares represent a cost-effective investment relative to traditional means of investing in the foreign exchange market.</v>
+        <v>-</v>
       </c>
       <c r="T84" s="4"/>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>471</v>
+      <c r="A85" t="s">
+        <v>65</v>
+      </c>
+      <c r="B85" t="s">
+        <v>220</v>
+      </c>
+      <c r="C85" t="s">
+        <v>689</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>455</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="F85" s="4" cm="1">
         <f t="array" ref="F85">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
-        <v>-0.01</v>
-      </c>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="J85" s="4"/>
+        <v>1E-4</v>
+      </c>
+      <c r="G85" t="s">
+        <v>299</v>
+      </c>
+      <c r="I85" t="s">
+        <v>695</v>
+      </c>
       <c r="K85" s="4">
         <v>1</v>
       </c>
@@ -11202,52 +11209,52 @@
       </c>
       <c r="O85" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>^VIX</v>
+        <v>FXB</v>
       </c>
       <c r="P85" s="4" t="str" cm="1">
         <f t="array" ref="P85">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>CBOE Volatility Index</v>
+        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
       </c>
       <c r="Q85" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>CBOE Volatility Index</v>
+        <v>-</v>
       </c>
       <c r="R85" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>CBOE Volatility Index</v>
-      </c>
-      <c r="S85" s="4">
+        <v>-</v>
+      </c>
+      <c r="S85" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>0</v>
+        <v>-</v>
       </c>
       <c r="T85" s="4"/>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="B86" s="4" t="s">
+      <c r="A86" t="s">
+        <v>65</v>
+      </c>
+      <c r="B86" t="s">
         <v>40</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>493</v>
+      <c r="C86" t="s">
+        <v>692</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>455</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="F86" s="4" cm="1">
         <f t="array" ref="F86">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
-        <v>-0.01</v>
-      </c>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="J86" s="4"/>
+        <v>1E-4</v>
+      </c>
+      <c r="G86" t="s">
+        <v>693</v>
+      </c>
+      <c r="I86" t="s">
+        <v>696</v>
+      </c>
       <c r="K86" s="4">
         <v>1</v>
       </c>
@@ -11262,52 +11269,55 @@
       </c>
       <c r="O86" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>VXX</v>
+        <v>FXC</v>
       </c>
       <c r="P86" s="4" t="str" cm="1">
         <f t="array" ref="P86">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>VIX Short-Term Futures ETN</v>
+        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
       </c>
       <c r="Q86" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>iPath Series B S&amp;P 500 VIX Shor</v>
+        <v>-</v>
       </c>
       <c r="R86" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>iPath Series B S&amp;P 500 VIX Short-Term Futures ETN</v>
+        <v>-</v>
       </c>
       <c r="S86" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>The ETN offers exposure to futures contracts of specified maturities on the VIX index and not direct exposure to the VIX index or its spot level. The index is designed to provide investors with exposure to one or more maturities of futures contracts on the CBOE Volatility Index®.</v>
+        <v>-</v>
       </c>
       <c r="T86" s="4"/>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>495</v>
+      <c r="A87" t="s">
+        <v>65</v>
+      </c>
+      <c r="B87" t="s">
+        <v>71</v>
+      </c>
+      <c r="C87" t="s">
+        <v>72</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>455</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="F87" s="4" cm="1">
         <f t="array" ref="F87">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
-        <v>-0.01</v>
-      </c>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="J87" s="4"/>
+        <v>1E-4</v>
+      </c>
+      <c r="G87" t="s">
+        <v>523</v>
+      </c>
+      <c r="I87" t="s">
+        <v>73</v>
+      </c>
+      <c r="J87" t="s">
+        <v>113</v>
+      </c>
       <c r="K87" s="4">
         <v>1</v>
       </c>
@@ -11322,23 +11332,23 @@
       </c>
       <c r="O87" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>^VIX3M</v>
+        <v>FXY</v>
       </c>
       <c r="P87" s="4" t="str" cm="1">
         <f t="array" ref="P87">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>CBOE S&amp;P 500 3-Month Volatility</v>
+        <v>Invesco CurrencyShares Japanese Yen Trust</v>
       </c>
       <c r="Q87" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>CBOE S&amp;P 500 3-Month Volatility</v>
+        <v>Invesco CurrencyShares Japanese</v>
       </c>
       <c r="R87" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>CBOE S&amp;P 500 3-Month Volatility</v>
-      </c>
-      <c r="S87" s="4">
+        <v>Invesco CurrencyShares Japanese Yen Trust</v>
+      </c>
+      <c r="S87" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>0</v>
+        <v>The fund seeks to reflect the price in USD of the Japanese Yen. The sponsor believes that, for many investors, the shares represent a cost-effective investment relative to traditional means of investing in the foreign exchange market.</v>
       </c>
       <c r="T87" s="4"/>
     </row>
@@ -11350,7 +11360,7 @@
         <v>40</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>455</v>
@@ -11365,11 +11375,11 @@
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J88" s="4"/>
       <c r="K88" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="4">
         <v>0</v>
@@ -11382,19 +11392,19 @@
       </c>
       <c r="O88" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>^VVIX</v>
+        <v>^VIX</v>
       </c>
       <c r="P88" s="4" t="str" cm="1">
         <f t="array" ref="P88">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>CBOE VIX VOLATILITY INDEX</v>
+        <v>CBOE Volatility Index</v>
       </c>
       <c r="Q88" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>CBOE VIX VOLATILITY INDEX</v>
+        <v>CBOE Volatility Index</v>
       </c>
       <c r="R88" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>^VVIX</v>
+        <v>CBOE Volatility Index</v>
       </c>
       <c r="S88" s="4">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
@@ -11411,7 +11421,7 @@
         <v>40</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>455</v>
@@ -11426,7 +11436,7 @@
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
       <c r="I89" s="4" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="J89" s="4"/>
       <c r="K89" s="4">
@@ -11443,23 +11453,23 @@
       </c>
       <c r="O89" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>^MOVE</v>
+        <v>VXX</v>
       </c>
       <c r="P89" s="4" t="str" cm="1">
         <f t="array" ref="P89">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>ICE BofAML MOVE Index</v>
+        <v>VIX Short-Term Futures ETN</v>
       </c>
       <c r="Q89" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>ICE BofAML MOVE Index</v>
+        <v>iPath Series B S&amp;P 500 VIX Shor</v>
       </c>
       <c r="R89" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>ICE BofAML MOVE Index</v>
-      </c>
-      <c r="S89" s="4">
+        <v>iPath Series B S&amp;P 500 VIX Short-Term Futures ETN</v>
+      </c>
+      <c r="S89" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>0</v>
+        <v>The ETN offers exposure to futures contracts of specified maturities on the VIX index and not direct exposure to the VIX index or its spot level. The index is designed to provide investors with exposure to one or more maturities of futures contracts on the CBOE Volatility Index®.</v>
       </c>
       <c r="T89" s="4"/>
       <c r="U89" s="2"/>
@@ -11472,7 +11482,7 @@
         <v>40</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>455</v>
@@ -11487,7 +11497,7 @@
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="J90" s="4"/>
       <c r="K90" s="4">
@@ -11504,19 +11514,19 @@
       </c>
       <c r="O90" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>^OVX</v>
+        <v>^VIX3M</v>
       </c>
       <c r="P90" s="4" t="str" cm="1">
         <f t="array" ref="P90">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>CBOE Crude Oil Volatility Index</v>
+        <v>CBOE S&amp;P 500 3-Month Volatility</v>
       </c>
       <c r="Q90" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>CBOE Crude Oil Volatility Index</v>
+        <v>CBOE S&amp;P 500 3-Month Volatility</v>
       </c>
       <c r="R90" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>^OVX</v>
+        <v>CBOE S&amp;P 500 3-Month Volatility</v>
       </c>
       <c r="S90" s="4">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
@@ -11536,7 +11546,7 @@
         <v>40</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>455</v>
@@ -11551,7 +11561,7 @@
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4">
@@ -11568,19 +11578,19 @@
       </c>
       <c r="O91" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>^EVZ</v>
+        <v>^VVIX</v>
       </c>
       <c r="P91" s="4" t="str" cm="1">
         <f t="array" ref="P91">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>CBOE Euro currency Volatility I</v>
+        <v>CBOE VIX VOLATILITY INDEX</v>
       </c>
       <c r="Q91" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>^EVZ,92169,0</v>
+        <v>CBOE VIX VOLATILITY INDEX</v>
       </c>
       <c r="R91" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>^EVZ,92169,0</v>
+        <v>^VVIX</v>
       </c>
       <c r="S91" s="4">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
@@ -11596,7 +11606,7 @@
         <v>40</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>455</v>
@@ -11611,7 +11621,7 @@
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="J92" s="4"/>
       <c r="K92" s="4">
@@ -11628,19 +11638,19 @@
       </c>
       <c r="O92" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>^GVZ</v>
+        <v>^MOVE</v>
       </c>
       <c r="P92" s="4" t="str" cm="1">
         <f t="array" ref="P92">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>CBOE Gold Volatility Index</v>
+        <v>ICE BofAML MOVE Index</v>
       </c>
       <c r="Q92" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>CBOE Gold Volatility Index</v>
+        <v>ICE BofAML MOVE Index</v>
       </c>
       <c r="R92" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>^GVZ</v>
+        <v>ICE BofAML MOVE Index</v>
       </c>
       <c r="S92" s="4">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
@@ -11656,7 +11666,7 @@
         <v>40</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>455</v>
@@ -11671,11 +11681,11 @@
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="J93" s="4"/>
       <c r="K93" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="4">
         <v>0</v>
@@ -11688,19 +11698,19 @@
       </c>
       <c r="O93" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>^COR3M</v>
+        <v>^OVX</v>
       </c>
       <c r="P93" s="4" t="str" cm="1">
         <f t="array" ref="P93">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Cboe Implied Correlation Index</v>
+        <v>CBOE Crude Oil Volatility Index</v>
       </c>
       <c r="Q93" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>Cboe Implied Correlation Index</v>
+        <v>CBOE Crude Oil Volatility Index</v>
       </c>
       <c r="R93" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>Cboe Implied Correlation Index</v>
+        <v>^OVX</v>
       </c>
       <c r="S93" s="4">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
@@ -11710,35 +11720,35 @@
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>446</v>
+        <v>475</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>429</v>
+        <v>479</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>455</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="F94" s="4" cm="1">
         <f t="array" ref="F94">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4" t="s">
-        <v>522</v>
-      </c>
+      <c r="I94" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="J94" s="4"/>
       <c r="K94" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="4">
         <v>0</v>
@@ -11748,52 +11758,52 @@
       </c>
       <c r="O94" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>MWTIX</v>
+        <v>^EVZ</v>
       </c>
       <c r="P94" s="4" t="str" cm="1">
         <f t="array" ref="P94">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>TCW MetWest Total Return Bd I</v>
+        <v>CBOE Euro currency Volatility I</v>
       </c>
       <c r="Q94" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>-</v>
+        <v>^EVZ,92169,0</v>
       </c>
       <c r="R94" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>-</v>
-      </c>
-      <c r="S94" s="4" t="str">
+        <v>^EVZ,92169,0</v>
+      </c>
+      <c r="S94" s="4">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="T94" s="4"/>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>446</v>
+        <v>475</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>687</v>
+        <v>481</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>455</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="F95" s="4" cm="1">
         <f t="array" ref="F95">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4" t="s">
-        <v>688</v>
-      </c>
+      <c r="I95" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="J95" s="4"/>
       <c r="K95" s="4">
         <v>1</v>
       </c>
@@ -11808,99 +11818,98 @@
       </c>
       <c r="O95" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>FCNTX</v>
+        <v>^GVZ</v>
       </c>
       <c r="P95" s="4" t="str" cm="1">
         <f t="array" ref="P95">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Fidelity Contrafund</v>
+        <v>CBOE Gold Volatility Index</v>
       </c>
       <c r="Q95" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>-</v>
+        <v>CBOE Gold Volatility Index</v>
       </c>
       <c r="R95" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>-</v>
-      </c>
-      <c r="S95" s="4" t="str">
+        <v>^GVZ</v>
+      </c>
+      <c r="S95" s="4">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="T95" s="4"/>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>444</v>
+        <v>475</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>727</v>
+        <v>484</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="F96" s="4" cm="1">
         <f t="array" ref="F96">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-      <c r="J96" s="4" t="str" cm="1">
-        <f t="array" ref="J96">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$I$2),_xlfn.ANCHORARRAY(composites!$J$2))</f>
-        <v>PSP 0.5, XLF -0.5, BKLN 0.5, LQDH -0.5</v>
-      </c>
+      <c r="I96" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="J96" s="4"/>
       <c r="K96" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N96" s="4">
         <v>0</v>
       </c>
       <c r="O96" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>PRIVATES</v>
+        <v>^COR3M</v>
       </c>
       <c r="P96" s="4" t="str" cm="1">
         <f t="array" ref="P96">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>PSP 0.5, XLF -0.5, BKLN 0.5, LQDH -0.5</v>
+        <v>Cboe Implied Correlation Index</v>
       </c>
       <c r="Q96" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
-        <v>-</v>
+        <v>Cboe Implied Correlation Index</v>
       </c>
       <c r="R96" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
-        <v>-</v>
-      </c>
-      <c r="S96" s="4" t="str">
+        <v>Cboe Implied Correlation Index</v>
+      </c>
+      <c r="S96" s="4">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
-        <v>-</v>
+        <v>0</v>
       </c>
       <c r="T96" s="4"/>
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>454</v>
@@ -11912,9 +11921,8 @@
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
-      <c r="J97" s="4" t="str" cm="1">
-        <f t="array" ref="J97">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$I$2),_xlfn.ANCHORARRAY(composites!$J$2))</f>
-        <v>SHY 1, BSV 1</v>
+      <c r="J97" s="4" t="s">
+        <v>522</v>
       </c>
       <c r="K97" s="4">
         <v>1</v>
@@ -11923,18 +11931,18 @@
         <v>1</v>
       </c>
       <c r="M97" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N97" s="4">
         <v>0</v>
       </c>
       <c r="O97" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>FED</v>
+        <v>MWTIX</v>
       </c>
       <c r="P97" s="4" t="str" cm="1">
         <f t="array" ref="P97">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>SHY 1, BSV 1</v>
+        <v>TCW MetWest Total Return Bd I</v>
       </c>
       <c r="Q97" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
@@ -11952,16 +11960,16 @@
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>421</v>
+        <v>687</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>454</v>
@@ -11973,29 +11981,28 @@
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
-      <c r="J98" s="4" t="str" cm="1">
-        <f t="array" ref="J98">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$I$2),_xlfn.ANCHORARRAY(composites!$J$2))</f>
-        <v>AIQ 1, QQQ 0.25, IWM -0.25</v>
+      <c r="J98" s="4" t="s">
+        <v>688</v>
       </c>
       <c r="K98" s="4">
         <v>1</v>
       </c>
       <c r="L98" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N98" s="4">
         <v>0</v>
       </c>
       <c r="O98" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>AI</v>
+        <v>FCNTX</v>
       </c>
       <c r="P98" s="4" t="str" cm="1">
         <f t="array" ref="P98">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>AIQ 1, QQQ 0.25, IWM -0.25</v>
+        <v>Fidelity Contrafund</v>
       </c>
       <c r="Q98" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
@@ -12019,7 +12026,7 @@
         <v>40</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>450</v>
+        <v>727</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>445</v>
@@ -12036,7 +12043,7 @@
       <c r="I99" s="4"/>
       <c r="J99" s="4" t="str" cm="1">
         <f t="array" ref="J99">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$I$2),_xlfn.ANCHORARRAY(composites!$J$2))</f>
-        <v>GLD 0.65, USO 0.3, ^VIX3M -0.15, FEZ -0.05</v>
+        <v>PSP 0.5, XLF -0.5, BKLN 0.5, LQDH -0.5</v>
       </c>
       <c r="K99" s="4">
         <v>1</v>
@@ -12052,11 +12059,11 @@
       </c>
       <c r="O99" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>GEOPOLITICS</v>
+        <v>PRIVATES</v>
       </c>
       <c r="P99" s="4" t="str" cm="1">
         <f t="array" ref="P99">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>GLD 0.65, USO 0.3, ^VIX3M -0.15, FEZ -0.05</v>
+        <v>PSP 0.5, XLF -0.5, BKLN 0.5, LQDH -0.5</v>
       </c>
       <c r="Q99" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
@@ -12080,7 +12087,7 @@
         <v>40</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>500</v>
+        <v>439</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>445</v>
@@ -12097,7 +12104,7 @@
       <c r="I100" s="4"/>
       <c r="J100" s="4" t="str" cm="1">
         <f t="array" ref="J100">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$I$2),_xlfn.ANCHORARRAY(composites!$J$2))</f>
-        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
+        <v>SHY 1, BSV 1</v>
       </c>
       <c r="K100" s="4">
         <v>1</v>
@@ -12113,11 +12120,11 @@
       </c>
       <c r="O100" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>TRADEWAR</v>
+        <v>FED</v>
       </c>
       <c r="P100" s="4" t="str" cm="1">
         <f t="array" ref="P100">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
+        <v>SHY 1, BSV 1</v>
       </c>
       <c r="Q100" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
@@ -12141,7 +12148,7 @@
         <v>40</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>722</v>
+        <v>421</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>445</v>
@@ -12158,7 +12165,7 @@
       <c r="I101" s="4"/>
       <c r="J101" s="4" t="str" cm="1">
         <f t="array" ref="J101">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$I$2),_xlfn.ANCHORARRAY(composites!$J$2))</f>
-        <v>USO 1</v>
+        <v>AIQ 1, QQQ 0.25, IWM -0.25</v>
       </c>
       <c r="K101" s="4">
         <v>1</v>
@@ -12174,11 +12181,11 @@
       </c>
       <c r="O101" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>IRAN</v>
+        <v>AI</v>
       </c>
       <c r="P101" s="4" t="str" cm="1">
         <f t="array" ref="P101">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>USO 1</v>
+        <v>AIQ 1, QQQ 0.25, IWM -0.25</v>
       </c>
       <c r="Q101" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
@@ -12202,7 +12209,7 @@
         <v>40</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>723</v>
+        <v>450</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>445</v>
@@ -12219,7 +12226,7 @@
       <c r="I102" s="4"/>
       <c r="J102" s="4" t="str" cm="1">
         <f t="array" ref="J102">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$I$2),_xlfn.ANCHORARRAY(composites!$J$2))</f>
-        <v>SMH 1, IGV -1, QQQ 1</v>
+        <v>GLD 0.65, USO 0.3, ^VIX3M -0.15, FEZ -0.05</v>
       </c>
       <c r="K102" s="4">
         <v>1</v>
@@ -12235,11 +12242,11 @@
       </c>
       <c r="O102" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>SEMI-SOFT</v>
+        <v>GEOPOLITICS</v>
       </c>
       <c r="P102" s="4" t="str" cm="1">
         <f t="array" ref="P102">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>SMH 1, IGV -1, QQQ 1</v>
+        <v>GLD 0.65, USO 0.3, ^VIX3M -0.15, FEZ -0.05</v>
       </c>
       <c r="Q102" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
@@ -12257,13 +12264,13 @@
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>128</v>
+        <v>444</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>451</v>
+        <v>500</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>445</v>
@@ -12280,7 +12287,7 @@
       <c r="I103" s="4"/>
       <c r="J103" s="4" t="str" cm="1">
         <f t="array" ref="J103">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$I$2),_xlfn.ANCHORARRAY(composites!$J$2))</f>
-        <v>SHY -3.86, IEF 1</v>
+        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
       </c>
       <c r="K103" s="4">
         <v>1</v>
@@ -12296,11 +12303,11 @@
       </c>
       <c r="O103" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>2s10s</v>
+        <v>TRADEWAR</v>
       </c>
       <c r="P103" s="4" t="str" cm="1">
         <f t="array" ref="P103">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>SHY -3.86, IEF 1</v>
+        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
       </c>
       <c r="Q103" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
@@ -12318,13 +12325,13 @@
     </row>
     <row r="104" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>39</v>
+        <v>444</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>503</v>
+        <v>722</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>445</v>
@@ -12337,13 +12344,11 @@
         <v>1E-4</v>
       </c>
       <c r="G104" s="4"/>
-      <c r="H104" s="4" t="s">
-        <v>505</v>
-      </c>
+      <c r="H104" s="4"/>
       <c r="I104" s="4"/>
       <c r="J104" s="4" t="str" cm="1">
         <f t="array" ref="J104">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$I$2),_xlfn.ANCHORARRAY(composites!$J$2))</f>
-        <v>XLP 1, XLY -1</v>
+        <v>USO 1</v>
       </c>
       <c r="K104" s="4">
         <v>1</v>
@@ -12359,11 +12364,11 @@
       </c>
       <c r="O104" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
-        <v>XLPXLY</v>
+        <v>IRAN</v>
       </c>
       <c r="P104" s="4" t="str" cm="1">
         <f t="array" ref="P104">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Staples/Discretionary</v>
+        <v>USO 1</v>
       </c>
       <c r="Q104" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
@@ -12381,57 +12386,60 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>527</v>
+        <v>444</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>528</v>
+        <v>723</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>529</v>
+        <v>445</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="F105" s="4">
-        <v>0.01</v>
+        <v>454</v>
+      </c>
+      <c r="F105" s="4" cm="1">
+        <f t="array" ref="F105">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
+        <v>1E-4</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
-      <c r="J105" s="4" t="s">
-        <v>530</v>
+      <c r="J105" s="4" t="str" cm="1">
+        <f t="array" ref="J105">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$I$2),_xlfn.ANCHORARRAY(composites!$J$2))</f>
+        <v>SMH 1, IGV -1, QQQ 1</v>
       </c>
       <c r="K105" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N105" s="4">
         <v>0</v>
       </c>
-      <c r="O105" s="11" t="s">
-        <v>531</v>
+      <c r="O105" s="4" t="str">
+        <f>data[[#This Row],[factor_name]]</f>
+        <v>SEMI-SOFT</v>
       </c>
       <c r="P105" s="4" t="str" cm="1">
         <f t="array" ref="P105">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>Economic Policy Uncertainty Index for United States</v>
-      </c>
-      <c r="Q105" s="11" t="str">
+        <v>SMH 1, IGV -1, QQQ 1</v>
+      </c>
+      <c r="Q105" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
         <v>-</v>
       </c>
-      <c r="R105" s="11" t="str">
+      <c r="R105" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
         <v>-</v>
       </c>
-      <c r="S105" s="11" t="str">
+      <c r="S105" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
         <v>-</v>
       </c>
@@ -12439,16 +12447,16 @@
     </row>
     <row r="106" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>682</v>
+        <v>451</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>686</v>
+        <v>445</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>454</v>
@@ -12460,25 +12468,29 @@
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
+      <c r="J106" s="4" t="str" cm="1">
+        <f t="array" ref="J106">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$I$2),_xlfn.ANCHORARRAY(composites!$J$2))</f>
+        <v>SHY -3.86, IEF 1</v>
+      </c>
       <c r="K106" s="4">
         <v>1</v>
       </c>
       <c r="L106" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N106" s="4">
         <v>0</v>
       </c>
-      <c r="O106" s="4" t="s">
-        <v>684</v>
+      <c r="O106" s="4" t="str">
+        <f>data[[#This Row],[factor_name]]</f>
+        <v>2s10s</v>
       </c>
       <c r="P106" s="4" t="str" cm="1">
         <f t="array" ref="P106">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>-</v>
+        <v>SHY -3.86, IEF 1</v>
       </c>
       <c r="Q106" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
@@ -12496,46 +12508,52 @@
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>475</v>
+        <v>39</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>683</v>
+        <v>503</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>686</v>
+        <v>445</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="F107" s="4" cm="1">
         <f t="array" ref="F107">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
       <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
+      <c r="H107" s="4" t="s">
+        <v>505</v>
+      </c>
       <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
+      <c r="J107" s="4" t="str" cm="1">
+        <f t="array" ref="J107">_xlfn.XLOOKUP(data[[#This Row],[factor_name]],_xlfn.ANCHORARRAY(composites!$I$2),_xlfn.ANCHORARRAY(composites!$J$2))</f>
+        <v>XLP 1, XLY -1</v>
+      </c>
       <c r="K107" s="4">
         <v>1</v>
       </c>
       <c r="L107" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N107" s="4">
         <v>0</v>
       </c>
-      <c r="O107" s="4" t="s">
-        <v>685</v>
+      <c r="O107" s="4" t="str">
+        <f>data[[#This Row],[factor_name]]</f>
+        <v>XLPXLY</v>
       </c>
       <c r="P107" s="4" t="str" cm="1">
         <f t="array" ref="P107">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
-        <v>-</v>
+        <v>Staples/Discretionary</v>
       </c>
       <c r="Q107" s="4" t="str">
         <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
@@ -12551,11 +12569,183 @@
       </c>
       <c r="T107" s="4"/>
     </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F108" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="K108" s="4">
+        <v>0</v>
+      </c>
+      <c r="L108" s="4">
+        <v>0</v>
+      </c>
+      <c r="M108" s="4">
+        <v>0</v>
+      </c>
+      <c r="N108" s="4">
+        <v>0</v>
+      </c>
+      <c r="O108" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="P108" s="4" t="str" cm="1">
+        <f t="array" ref="P108">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
+        <v>Economic Policy Uncertainty Index for United States</v>
+      </c>
+      <c r="Q108" s="11" t="str">
+        <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
+        <v>-</v>
+      </c>
+      <c r="R108" s="11" t="str">
+        <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
+        <v>-</v>
+      </c>
+      <c r="S108" s="11" t="str">
+        <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T108" s="4"/>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="F109" s="4" cm="1">
+        <f t="array" ref="F109">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
+        <v>1E-4</v>
+      </c>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4">
+        <v>1</v>
+      </c>
+      <c r="L109" s="4">
+        <v>0</v>
+      </c>
+      <c r="M109" s="4">
+        <v>0</v>
+      </c>
+      <c r="N109" s="4">
+        <v>0</v>
+      </c>
+      <c r="O109" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="P109" s="4" t="str" cm="1">
+        <f t="array" ref="P109">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Q109" s="4" t="str">
+        <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
+        <v>-</v>
+      </c>
+      <c r="R109" s="4" t="str">
+        <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
+        <v>-</v>
+      </c>
+      <c r="S109" s="4" t="str">
+        <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T109" s="4"/>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F110" s="4" cm="1">
+        <f t="array" ref="F110">_xlfn.SWITCH(data[[#This Row],[diffusion_type]],"lognormal",0.0001,"normal",-0.01)*IF(data[[#This Row],[asset_class]]="Vol",1,1)</f>
+        <v>-0.01</v>
+      </c>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4">
+        <v>1</v>
+      </c>
+      <c r="L110" s="4">
+        <v>0</v>
+      </c>
+      <c r="M110" s="4">
+        <v>0</v>
+      </c>
+      <c r="N110" s="4">
+        <v>0</v>
+      </c>
+      <c r="O110" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="P110" s="4" t="str" cm="1">
+        <f t="array" ref="P110">_xlfn.IFS(data[[#This Row],[description_override]]&lt;&gt;"",data[[#This Row],[description_override]],data[[#This Row],[Description_GPT]]&lt;&gt;"",data[[#This Row],[Description_GPT]],data[[#This Row],[Underlying]]&lt;&gt;"",data[[#This Row],[Underlying]],TRUE,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Q110" s="4" t="str">
+        <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[shortName],"-")</f>
+        <v>-</v>
+      </c>
+      <c r="R110" s="4" t="str">
+        <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longName],"-")</f>
+        <v>-</v>
+      </c>
+      <c r="S110" s="4" t="str">
+        <f>_xlfn.XLOOKUP(data[[#This Row],[ticker]],yf_desc[ticker],yf_desc[longBusinessSummary],"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T110" s="4"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="E110:E113">
+  <conditionalFormatting sqref="E113:E116">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$Q106</formula>
+      <formula>$Q109</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13614,7 +13804,7 @@
         <v>Equities</v>
       </c>
       <c r="C28" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -16349,7 +16539,7 @@
         <v>Equities</v>
       </c>
       <c r="C28" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -18733,7 +18923,7 @@
         <v>Equities</v>
       </c>
       <c r="C28" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -21270,7 +21460,7 @@
         <v>Equities</v>
       </c>
       <c r="C28" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -25887,7 +26077,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
@@ -25914,7 +26104,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
         <v>156</v>
@@ -25941,7 +26131,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
         <v>86</v>
@@ -25968,7 +26158,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
         <v>84</v>
@@ -25995,7 +26185,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
         <v>89</v>
@@ -26022,7 +26212,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
         <v>327</v>
@@ -26049,7 +26239,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
         <v>95</v>
@@ -26076,7 +26266,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
         <v>93</v>
@@ -26103,7 +26293,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
         <v>330</v>
@@ -26130,7 +26320,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
         <v>91</v>
@@ -26157,7 +26347,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
         <v>324</v>
@@ -26184,7 +26374,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C36" t="s">
         <v>142</v>
@@ -26211,7 +26401,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
         <v>80</v>
@@ -26238,7 +26428,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
         <v>82</v>
@@ -26265,7 +26455,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C39" t="s">
         <v>400</v>
@@ -26292,7 +26482,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
         <v>10</v>
@@ -26319,7 +26509,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
@@ -26346,7 +26536,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
         <v>347</v>
@@ -26373,7 +26563,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
         <v>348</v>
@@ -26400,7 +26590,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C44" t="s">
         <v>51</v>
@@ -26427,7 +26617,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C45" t="s">
         <v>126</v>
@@ -26454,7 +26644,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C46" t="s">
         <v>131</v>
@@ -26481,7 +26671,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C47" t="s">
         <v>49</v>
@@ -26508,7 +26698,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C48" t="s">
         <v>135</v>
@@ -26535,7 +26725,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C49" t="s">
         <v>344</v>
@@ -26562,7 +26752,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C50" t="s">
         <v>53</v>
@@ -26589,7 +26779,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
@@ -26616,7 +26806,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C52" t="s">
         <v>15</v>
@@ -26643,7 +26833,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C53" t="s">
         <v>346</v>
@@ -26670,7 +26860,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C54" t="s">
         <v>345</v>
@@ -26699,7 +26889,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s">
         <v>97</v>
@@ -26726,7 +26916,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C56" t="s">
         <v>349</v>
@@ -26753,7 +26943,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C57" t="s">
         <v>75</v>
@@ -26780,7 +26970,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C58" t="s">
         <v>99</v>
@@ -26807,7 +26997,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C59" t="s">
         <v>57</v>
@@ -26834,7 +27024,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C60" t="s">
         <v>59</v>
@@ -26861,7 +27051,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C61" t="s">
         <v>61</v>
@@ -26888,7 +27078,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C62" t="s">
         <v>63</v>
@@ -26915,7 +27105,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C63" t="s">
         <v>66</v>
@@ -26942,7 +27132,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C64" t="s">
         <v>69</v>
@@ -26969,7 +27159,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C65" t="s">
         <v>72</v>
@@ -27011,7 +27201,7 @@
       </c>
       <c r="B1" cm="1">
         <f t="array" ref="B1:B9">_xlfn.XMATCH(A1:A9,data[factor_name])</f>
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" cm="1">
         <f t="array" ref="D1:D32">_xlfn.XLOOKUP(_xlfn._TRO_ALL(A:A),data[factor_name],data[Active])</f>
@@ -27023,7 +27213,7 @@
         <v>334</v>
       </c>
       <c r="B2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -27034,7 +27224,7 @@
         <v>335</v>
       </c>
       <c r="B3">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -27045,7 +27235,7 @@
         <v>336</v>
       </c>
       <c r="B4">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -27056,7 +27246,7 @@
         <v>337</v>
       </c>
       <c r="B5">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -27067,7 +27257,7 @@
         <v>338</v>
       </c>
       <c r="B6">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -27078,7 +27268,7 @@
         <v>339</v>
       </c>
       <c r="B7">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -27089,7 +27279,7 @@
         <v>340</v>
       </c>
       <c r="B8">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -27100,7 +27290,7 @@
         <v>341</v>
       </c>
       <c r="B9">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D9">
         <v>1</v>

--- a/factor_master.xlsx
+++ b/factor_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrai\Source\risk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3EA20C8-F633-4FE5-AFF4-B6F6041E4058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218A1016-A3C6-4B52-9D86-674CA51357C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="11" activeTab="11" xr2:uid="{C31FDC5B-A809-4BFD-99CB-DA02246721F7}"/>
   </bookViews>
@@ -7732,10 +7732,18 @@
         <v>733</v>
       </c>
       <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
+      <c r="K29" s="4">
+        <v>1</v>
+      </c>
+      <c r="L29" s="4">
+        <v>0</v>
+      </c>
+      <c r="M29" s="4">
+        <v>0</v>
+      </c>
+      <c r="N29" s="4">
+        <v>0</v>
+      </c>
       <c r="O29" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
         <v>IWN</v>
@@ -7786,10 +7794,18 @@
         <v>734</v>
       </c>
       <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
+      <c r="K30" s="4">
+        <v>1</v>
+      </c>
+      <c r="L30" s="4">
+        <v>0</v>
+      </c>
+      <c r="M30" s="4">
+        <v>0</v>
+      </c>
+      <c r="N30" s="4">
+        <v>0</v>
+      </c>
       <c r="O30" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
         <v>IWO</v>
@@ -7840,10 +7856,18 @@
         <v>736</v>
       </c>
       <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
+      <c r="K31" s="4">
+        <v>1</v>
+      </c>
+      <c r="L31" s="4">
+        <v>0</v>
+      </c>
+      <c r="M31" s="4">
+        <v>0</v>
+      </c>
+      <c r="N31" s="4">
+        <v>0</v>
+      </c>
       <c r="O31" s="4" t="str">
         <f>data[[#This Row],[factor_name]]</f>
         <v>MTUM</v>
@@ -12924,7 +12948,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5A64DEF-E706-4B9C-B282-71F34F86B3DF}">
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
@@ -12964,11 +12988,11 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A85">_xlfn._xlws.FILTER(data[factor_name],data[Active])</f>
+        <f t="array" ref="A2:A88">_xlfn._xlws.FILTER(data[factor_name],data[Active])</f>
         <v>SPY</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:J85">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
+        <f t="array" ref="B2:J88">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
         <v>Equities</v>
       </c>
       <c r="C2" t="str">
@@ -13798,7 +13822,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <v>FEZ</v>
+        <v>IWN</v>
       </c>
       <c r="B28" t="str">
         <v>Equities</v>
@@ -13813,13 +13837,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="str">
-        <v>Eurostoxx 50</v>
+        <v>Value</v>
       </c>
       <c r="G28" t="str">
         <v>yfinance</v>
       </c>
       <c r="H28" t="str">
-        <v>FEZ</v>
+        <v>IWN</v>
       </c>
       <c r="I28" t="str">
         <v>lognormal</v>
@@ -13830,13 +13854,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <v>EWU</v>
+        <v>IWO</v>
       </c>
       <c r="B29" t="str">
         <v>Equities</v>
       </c>
       <c r="C29" t="str">
-        <v>GBP</v>
+        <v>USD</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -13845,13 +13869,13 @@
         <v>0</v>
       </c>
       <c r="F29" t="str">
-        <v>FTSE 100</v>
+        <v>Growth</v>
       </c>
       <c r="G29" t="str">
         <v>yfinance</v>
       </c>
       <c r="H29" t="str">
-        <v>EWU</v>
+        <v>IWO</v>
       </c>
       <c r="I29" t="str">
         <v>lognormal</v>
@@ -13862,13 +13886,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <v>DAX</v>
+        <v>MTUM</v>
       </c>
       <c r="B30" t="str">
         <v>Equities</v>
       </c>
       <c r="C30" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -13877,13 +13901,13 @@
         <v>0</v>
       </c>
       <c r="F30" t="str">
-        <v>DAX (Germany)</v>
+        <v>Momentum</v>
       </c>
       <c r="G30" t="str">
         <v>yfinance</v>
       </c>
       <c r="H30" t="str">
-        <v>DAX</v>
+        <v>MTUM</v>
       </c>
       <c r="I30" t="str">
         <v>lognormal</v>
@@ -13894,13 +13918,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
-        <v>EWC</v>
+        <v>FEZ</v>
       </c>
       <c r="B31" t="str">
         <v>Equities</v>
       </c>
       <c r="C31" t="str">
-        <v>CAD</v>
+        <v>USD</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -13909,13 +13933,13 @@
         <v>0</v>
       </c>
       <c r="F31" t="str">
-        <v>MSCI Canada</v>
+        <v>Eurostoxx 50</v>
       </c>
       <c r="G31" t="str">
         <v>yfinance</v>
       </c>
       <c r="H31" t="str">
-        <v>EWC</v>
+        <v>FEZ</v>
       </c>
       <c r="I31" t="str">
         <v>lognormal</v>
@@ -13926,13 +13950,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
-        <v>EWI</v>
+        <v>EWU</v>
       </c>
       <c r="B32" t="str">
         <v>Equities</v>
       </c>
       <c r="C32" t="str">
-        <v>EUR</v>
+        <v>GBP</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -13941,13 +13965,13 @@
         <v>0</v>
       </c>
       <c r="F32" t="str">
-        <v>MSCI Italy</v>
+        <v>FTSE 100</v>
       </c>
       <c r="G32" t="str">
         <v>yfinance</v>
       </c>
       <c r="H32" t="str">
-        <v>EWI</v>
+        <v>EWU</v>
       </c>
       <c r="I32" t="str">
         <v>lognormal</v>
@@ -13958,13 +13982,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
-        <v>^N225</v>
+        <v>DAX</v>
       </c>
       <c r="B33" t="str">
         <v>Equities</v>
       </c>
       <c r="C33" t="str">
-        <v>JPY</v>
+        <v>EUR</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -13973,13 +13997,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="str">
-        <v>Nikkei 225</v>
+        <v>DAX (Germany)</v>
       </c>
       <c r="G33" t="str">
         <v>yfinance</v>
       </c>
       <c r="H33" t="str">
-        <v>^N225</v>
+        <v>DAX</v>
       </c>
       <c r="I33" t="str">
         <v>lognormal</v>
@@ -13990,13 +14014,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
-        <v>FXI</v>
+        <v>EWC</v>
       </c>
       <c r="B34" t="str">
         <v>Equities</v>
       </c>
       <c r="C34" t="str">
-        <v>CNH</v>
+        <v>CAD</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -14005,13 +14029,13 @@
         <v>0</v>
       </c>
       <c r="F34" t="str">
-        <v>China Large-Cap</v>
+        <v>MSCI Canada</v>
       </c>
       <c r="G34" t="str">
         <v>yfinance</v>
       </c>
       <c r="H34" t="str">
-        <v>FXI</v>
+        <v>EWC</v>
       </c>
       <c r="I34" t="str">
         <v>lognormal</v>
@@ -14022,13 +14046,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
-        <v>ASHR</v>
+        <v>EWI</v>
       </c>
       <c r="B35" t="str">
         <v>Equities</v>
       </c>
       <c r="C35" t="str">
-        <v>CNH</v>
+        <v>EUR</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -14037,13 +14061,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="str">
-        <v>CSI 300 (China)</v>
+        <v>MSCI Italy</v>
       </c>
       <c r="G35" t="str">
         <v>yfinance</v>
       </c>
       <c r="H35" t="str">
-        <v>ASHR</v>
+        <v>EWI</v>
       </c>
       <c r="I35" t="str">
         <v>lognormal</v>
@@ -14054,13 +14078,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
-        <v>KWEB</v>
+        <v>^N225</v>
       </c>
       <c r="B36" t="str">
         <v>Equities</v>
       </c>
       <c r="C36" t="str">
-        <v>CNH</v>
+        <v>JPY</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -14069,13 +14093,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="str">
-        <v>CSI China Internet</v>
+        <v>Nikkei 225</v>
       </c>
       <c r="G36" t="str">
         <v>yfinance</v>
       </c>
       <c r="H36" t="str">
-        <v>KWEB</v>
+        <v>^N225</v>
       </c>
       <c r="I36" t="str">
         <v>lognormal</v>
@@ -14086,13 +14110,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
-        <v>EEM</v>
+        <v>FXI</v>
       </c>
       <c r="B37" t="str">
         <v>Equities</v>
       </c>
       <c r="C37" t="str">
-        <v>EM</v>
+        <v>CNH</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -14101,13 +14125,13 @@
         <v>0</v>
       </c>
       <c r="F37" t="str">
-        <v>MSCI EM</v>
+        <v>China Large-Cap</v>
       </c>
       <c r="G37" t="str">
         <v>yfinance</v>
       </c>
       <c r="H37" t="str">
-        <v>EEM</v>
+        <v>FXI</v>
       </c>
       <c r="I37" t="str">
         <v>lognormal</v>
@@ -14118,13 +14142,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
-        <v>LQD</v>
+        <v>ASHR</v>
       </c>
       <c r="B38" t="str">
-        <v>Credit</v>
+        <v>Equities</v>
       </c>
       <c r="C38" t="str">
-        <v>USD</v>
+        <v>CNH</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -14133,13 +14157,13 @@
         <v>0</v>
       </c>
       <c r="F38" t="str">
-        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
+        <v>CSI 300 (China)</v>
       </c>
       <c r="G38" t="str">
         <v>yfinance</v>
       </c>
       <c r="H38" t="str">
-        <v>LQD</v>
+        <v>ASHR</v>
       </c>
       <c r="I38" t="str">
         <v>lognormal</v>
@@ -14150,13 +14174,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
-        <v>BSV</v>
+        <v>KWEB</v>
       </c>
       <c r="B39" t="str">
-        <v>Credit</v>
+        <v>Equities</v>
       </c>
       <c r="C39" t="str">
-        <v>USD</v>
+        <v>CNH</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -14165,13 +14189,13 @@
         <v>0</v>
       </c>
       <c r="F39" t="str">
-        <v>Vanguard Short-Term Bond Index Fund ETF</v>
+        <v>CSI China Internet</v>
       </c>
       <c r="G39" t="str">
         <v>yfinance</v>
       </c>
       <c r="H39" t="str">
-        <v>BSV</v>
+        <v>KWEB</v>
       </c>
       <c r="I39" t="str">
         <v>lognormal</v>
@@ -14182,13 +14206,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
-        <v>HYG</v>
+        <v>EEM</v>
       </c>
       <c r="B40" t="str">
-        <v>Credit</v>
+        <v>Equities</v>
       </c>
       <c r="C40" t="str">
-        <v>USD</v>
+        <v>EM</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -14197,13 +14221,13 @@
         <v>0</v>
       </c>
       <c r="F40" t="str">
-        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
+        <v>MSCI EM</v>
       </c>
       <c r="G40" t="str">
         <v>yfinance</v>
       </c>
       <c r="H40" t="str">
-        <v>HYG</v>
+        <v>EEM</v>
       </c>
       <c r="I40" t="str">
         <v>lognormal</v>
@@ -14214,7 +14238,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
-        <v>LQDH</v>
+        <v>LQD</v>
       </c>
       <c r="B41" t="str">
         <v>Credit</v>
@@ -14223,19 +14247,19 @@
         <v>USD</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41" t="str">
-        <v>Hedged LQD</v>
+        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
       </c>
       <c r="G41" t="str">
         <v>yfinance</v>
       </c>
       <c r="H41" t="str">
-        <v>LQDH</v>
+        <v>LQD</v>
       </c>
       <c r="I41" t="str">
         <v>lognormal</v>
@@ -14246,7 +14270,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
-        <v>HYGH</v>
+        <v>BSV</v>
       </c>
       <c r="B42" t="str">
         <v>Credit</v>
@@ -14261,13 +14285,13 @@
         <v>0</v>
       </c>
       <c r="F42" t="str">
-        <v>Hedged HYG</v>
+        <v>Vanguard Short-Term Bond Index Fund ETF</v>
       </c>
       <c r="G42" t="str">
         <v>yfinance</v>
       </c>
       <c r="H42" t="str">
-        <v>HYGH</v>
+        <v>BSV</v>
       </c>
       <c r="I42" t="str">
         <v>lognormal</v>
@@ -14278,7 +14302,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
-        <v>BKLN</v>
+        <v>HYG</v>
       </c>
       <c r="B43" t="str">
         <v>Credit</v>
@@ -14293,13 +14317,13 @@
         <v>0</v>
       </c>
       <c r="F43" t="str">
-        <v>Bank Loans</v>
+        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
       </c>
       <c r="G43" t="str">
         <v>yfinance</v>
       </c>
       <c r="H43" t="str">
-        <v>BKLN</v>
+        <v>HYG</v>
       </c>
       <c r="I43" t="str">
         <v>lognormal</v>
@@ -14310,7 +14334,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
-        <v>AGG</v>
+        <v>LQDH</v>
       </c>
       <c r="B44" t="str">
         <v>Credit</v>
@@ -14319,19 +14343,19 @@
         <v>USD</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44" t="str">
-        <v>US Agg</v>
+        <v>Hedged LQD</v>
       </c>
       <c r="G44" t="str">
         <v>yfinance</v>
       </c>
       <c r="H44" t="str">
-        <v>AGG</v>
+        <v>LQDH</v>
       </c>
       <c r="I44" t="str">
         <v>lognormal</v>
@@ -14342,10 +14366,10 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
-        <v>^TNX</v>
+        <v>HYGH</v>
       </c>
       <c r="B45" t="str">
-        <v>Rates</v>
+        <v>Credit</v>
       </c>
       <c r="C45" t="str">
         <v>USD</v>
@@ -14357,27 +14381,27 @@
         <v>0</v>
       </c>
       <c r="F45" t="str">
-        <v>CBOE Interest Rate 10 Year</v>
+        <v>Hedged HYG</v>
       </c>
       <c r="G45" t="str">
         <v>yfinance</v>
       </c>
       <c r="H45" t="str">
-        <v>^TNX</v>
+        <v>HYGH</v>
       </c>
       <c r="I45" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J45">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
-        <v>SHY</v>
+        <v>BKLN</v>
       </c>
       <c r="B46" t="str">
-        <v>Rates</v>
+        <v>Credit</v>
       </c>
       <c r="C46" t="str">
         <v>USD</v>
@@ -14389,13 +14413,13 @@
         <v>0</v>
       </c>
       <c r="F46" t="str">
-        <v>1-3 Year Treasury</v>
+        <v>Bank Loans</v>
       </c>
       <c r="G46" t="str">
         <v>yfinance</v>
       </c>
       <c r="H46" t="str">
-        <v>SHY</v>
+        <v>BKLN</v>
       </c>
       <c r="I46" t="str">
         <v>lognormal</v>
@@ -14406,10 +14430,10 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
-        <v>IEI</v>
+        <v>AGG</v>
       </c>
       <c r="B47" t="str">
-        <v>Rates</v>
+        <v>Credit</v>
       </c>
       <c r="C47" t="str">
         <v>USD</v>
@@ -14421,13 +14445,13 @@
         <v>0</v>
       </c>
       <c r="F47" t="str">
-        <v>3-7 Year Treasury</v>
+        <v>US Agg</v>
       </c>
       <c r="G47" t="str">
         <v>yfinance</v>
       </c>
       <c r="H47" t="str">
-        <v>IEI</v>
+        <v>AGG</v>
       </c>
       <c r="I47" t="str">
         <v>lognormal</v>
@@ -14438,7 +14462,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
-        <v>IEF</v>
+        <v>^TNX</v>
       </c>
       <c r="B48" t="str">
         <v>Rates</v>
@@ -14447,30 +14471,30 @@
         <v>USD</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="str">
-        <v>7-10 Year Treasury</v>
+        <v>CBOE Interest Rate 10 Year</v>
       </c>
       <c r="G48" t="str">
         <v>yfinance</v>
       </c>
       <c r="H48" t="str">
-        <v>IEF</v>
+        <v>^TNX</v>
       </c>
       <c r="I48" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J48">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
-        <v>TLT</v>
+        <v>SHY</v>
       </c>
       <c r="B49" t="str">
         <v>Rates</v>
@@ -14485,13 +14509,13 @@
         <v>0</v>
       </c>
       <c r="F49" t="str">
-        <v>20+ Year Treasury</v>
+        <v>1-3 Year Treasury</v>
       </c>
       <c r="G49" t="str">
         <v>yfinance</v>
       </c>
       <c r="H49" t="str">
-        <v>TLT</v>
+        <v>SHY</v>
       </c>
       <c r="I49" t="str">
         <v>lognormal</v>
@@ -14502,7 +14526,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
-        <v>TIP</v>
+        <v>IEI</v>
       </c>
       <c r="B50" t="str">
         <v>Rates</v>
@@ -14517,13 +14541,13 @@
         <v>0</v>
       </c>
       <c r="F50" t="str">
-        <v>iShares TIPS Bond ETF</v>
+        <v>3-7 Year Treasury</v>
       </c>
       <c r="G50" t="str">
         <v>yfinance</v>
       </c>
       <c r="H50" t="str">
-        <v>TIP</v>
+        <v>IEI</v>
       </c>
       <c r="I50" t="str">
         <v>lognormal</v>
@@ -14534,7 +14558,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
-        <v>VTIP</v>
+        <v>IEF</v>
       </c>
       <c r="B51" t="str">
         <v>Rates</v>
@@ -14543,19 +14567,19 @@
         <v>USD</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51" t="str">
-        <v>Short-Term Inflation-Protected Securities ETF</v>
+        <v>7-10 Year Treasury</v>
       </c>
       <c r="G51" t="str">
         <v>yfinance</v>
       </c>
       <c r="H51" t="str">
-        <v>VTIP</v>
+        <v>IEF</v>
       </c>
       <c r="I51" t="str">
         <v>lognormal</v>
@@ -14566,7 +14590,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
-        <v>AGNC</v>
+        <v>TLT</v>
       </c>
       <c r="B52" t="str">
         <v>Rates</v>
@@ -14581,13 +14605,13 @@
         <v>0</v>
       </c>
       <c r="F52" t="str">
-        <v>AGNC Investment Corp.</v>
+        <v>20+ Year Treasury</v>
       </c>
       <c r="G52" t="str">
         <v>yfinance</v>
       </c>
       <c r="H52" t="str">
-        <v>AGNC</v>
+        <v>TLT</v>
       </c>
       <c r="I52" t="str">
         <v>lognormal</v>
@@ -14598,7 +14622,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
-        <v>VMBS</v>
+        <v>TIP</v>
       </c>
       <c r="B53" t="str">
         <v>Rates</v>
@@ -14613,13 +14637,13 @@
         <v>0</v>
       </c>
       <c r="F53" t="str">
-        <v>Mortgage-Backed Securities ETF</v>
+        <v>iShares TIPS Bond ETF</v>
       </c>
       <c r="G53" t="str">
         <v>yfinance</v>
       </c>
       <c r="H53" t="str">
-        <v>VMBS</v>
+        <v>TIP</v>
       </c>
       <c r="I53" t="str">
         <v>lognormal</v>
@@ -14630,7 +14654,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
-        <v>CMBS</v>
+        <v>VTIP</v>
       </c>
       <c r="B54" t="str">
         <v>Rates</v>
@@ -14645,13 +14669,13 @@
         <v>0</v>
       </c>
       <c r="F54" t="str">
-        <v>iShares CMBS ETF</v>
+        <v>Short-Term Inflation-Protected Securities ETF</v>
       </c>
       <c r="G54" t="str">
         <v>yfinance</v>
       </c>
       <c r="H54" t="str">
-        <v>CMBS</v>
+        <v>VTIP</v>
       </c>
       <c r="I54" t="str">
         <v>lognormal</v>
@@ -14662,13 +14686,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
-        <v>EMB</v>
+        <v>AGNC</v>
       </c>
       <c r="B55" t="str">
         <v>Rates</v>
       </c>
       <c r="C55" t="str">
-        <v>EM</v>
+        <v>USD</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -14677,13 +14701,13 @@
         <v>0</v>
       </c>
       <c r="F55" t="str">
-        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
+        <v>AGNC Investment Corp.</v>
       </c>
       <c r="G55" t="str">
         <v>yfinance</v>
       </c>
       <c r="H55" t="str">
-        <v>EMB</v>
+        <v>AGNC</v>
       </c>
       <c r="I55" t="str">
         <v>lognormal</v>
@@ -14694,10 +14718,10 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
-        <v>GLD</v>
+        <v>VMBS</v>
       </c>
       <c r="B56" t="str">
-        <v>Commodities</v>
+        <v>Rates</v>
       </c>
       <c r="C56" t="str">
         <v>USD</v>
@@ -14709,13 +14733,13 @@
         <v>0</v>
       </c>
       <c r="F56" t="str">
-        <v>SPDR Gold Shares</v>
+        <v>Mortgage-Backed Securities ETF</v>
       </c>
       <c r="G56" t="str">
         <v>yfinance</v>
       </c>
       <c r="H56" t="str">
-        <v>GLD</v>
+        <v>VMBS</v>
       </c>
       <c r="I56" t="str">
         <v>lognormal</v>
@@ -14726,10 +14750,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
-        <v>SLV</v>
+        <v>CMBS</v>
       </c>
       <c r="B57" t="str">
-        <v>Commodities</v>
+        <v>Rates</v>
       </c>
       <c r="C57" t="str">
         <v>USD</v>
@@ -14741,13 +14765,13 @@
         <v>0</v>
       </c>
       <c r="F57" t="str">
-        <v>iShares Silver Trust</v>
+        <v>iShares CMBS ETF</v>
       </c>
       <c r="G57" t="str">
         <v>yfinance</v>
       </c>
       <c r="H57" t="str">
-        <v>SLV</v>
+        <v>CMBS</v>
       </c>
       <c r="I57" t="str">
         <v>lognormal</v>
@@ -14758,13 +14782,13 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
-        <v>USO</v>
+        <v>EMB</v>
       </c>
       <c r="B58" t="str">
-        <v>Commodities</v>
+        <v>Rates</v>
       </c>
       <c r="C58" t="str">
-        <v>USD</v>
+        <v>EM</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -14773,13 +14797,13 @@
         <v>0</v>
       </c>
       <c r="F58" t="str">
-        <v>United States Oil Fund</v>
+        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
       </c>
       <c r="G58" t="str">
         <v>yfinance</v>
       </c>
       <c r="H58" t="str">
-        <v>USO</v>
+        <v>EMB</v>
       </c>
       <c r="I58" t="str">
         <v>lognormal</v>
@@ -14790,10 +14814,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
-        <v>UUP</v>
+        <v>GLD</v>
       </c>
       <c r="B59" t="str">
-        <v>Currencies</v>
+        <v>Commodities</v>
       </c>
       <c r="C59" t="str">
         <v>USD</v>
@@ -14805,13 +14829,13 @@
         <v>0</v>
       </c>
       <c r="F59" t="str">
-        <v>Invesco DB US Dollar Index Bullish Fund</v>
+        <v>SPDR Gold Shares</v>
       </c>
       <c r="G59" t="str">
         <v>yfinance</v>
       </c>
       <c r="H59" t="str">
-        <v>UUP</v>
+        <v>GLD</v>
       </c>
       <c r="I59" t="str">
         <v>lognormal</v>
@@ -14822,10 +14846,10 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
-        <v>DX-Y.NYB</v>
+        <v>SLV</v>
       </c>
       <c r="B60" t="str">
-        <v>Currencies</v>
+        <v>Commodities</v>
       </c>
       <c r="C60" t="str">
         <v>USD</v>
@@ -14837,13 +14861,13 @@
         <v>0</v>
       </c>
       <c r="F60" t="str">
-        <v>U.S. Dollar Index</v>
+        <v>iShares Silver Trust</v>
       </c>
       <c r="G60" t="str">
         <v>yfinance</v>
       </c>
       <c r="H60" t="str">
-        <v>DX-Y.NYB</v>
+        <v>SLV</v>
       </c>
       <c r="I60" t="str">
         <v>lognormal</v>
@@ -14854,13 +14878,13 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
-        <v>FXE</v>
+        <v>USO</v>
       </c>
       <c r="B61" t="str">
-        <v>Currencies</v>
+        <v>Commodities</v>
       </c>
       <c r="C61" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -14869,13 +14893,13 @@
         <v>0</v>
       </c>
       <c r="F61" t="str">
-        <v>Invesco CurrencyShares Euro Trust</v>
+        <v>United States Oil Fund</v>
       </c>
       <c r="G61" t="str">
         <v>yfinance</v>
       </c>
       <c r="H61" t="str">
-        <v>FXE</v>
+        <v>USO</v>
       </c>
       <c r="I61" t="str">
         <v>lognormal</v>
@@ -14886,13 +14910,13 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
-        <v>FXF</v>
+        <v>UUP</v>
       </c>
       <c r="B62" t="str">
         <v>Currencies</v>
       </c>
       <c r="C62" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -14901,13 +14925,13 @@
         <v>0</v>
       </c>
       <c r="F62" t="str">
-        <v>Invesco CurrencyShares Swiss Franc Trust</v>
+        <v>Invesco DB US Dollar Index Bullish Fund</v>
       </c>
       <c r="G62" t="str">
         <v>yfinance</v>
       </c>
       <c r="H62" t="str">
-        <v>FXF</v>
+        <v>UUP</v>
       </c>
       <c r="I62" t="str">
         <v>lognormal</v>
@@ -14918,13 +14942,13 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
-        <v>FXA</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="B63" t="str">
         <v>Currencies</v>
       </c>
       <c r="C63" t="str">
-        <v>Commod</v>
+        <v>USD</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -14933,13 +14957,13 @@
         <v>0</v>
       </c>
       <c r="F63" t="str">
-        <v>Invesco CurrencyShares Australian Dollar Trust</v>
+        <v>U.S. Dollar Index</v>
       </c>
       <c r="G63" t="str">
         <v>yfinance</v>
       </c>
       <c r="H63" t="str">
-        <v>FXA</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="I63" t="str">
         <v>lognormal</v>
@@ -14950,13 +14974,13 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
-        <v>FXB</v>
+        <v>FXE</v>
       </c>
       <c r="B64" t="str">
         <v>Currencies</v>
       </c>
       <c r="C64" t="str">
-        <v>GBP</v>
+        <v>EUR</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -14965,13 +14989,13 @@
         <v>0</v>
       </c>
       <c r="F64" t="str">
-        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
+        <v>Invesco CurrencyShares Euro Trust</v>
       </c>
       <c r="G64" t="str">
         <v>yfinance</v>
       </c>
       <c r="H64" t="str">
-        <v>FXB</v>
+        <v>FXE</v>
       </c>
       <c r="I64" t="str">
         <v>lognormal</v>
@@ -14982,13 +15006,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
-        <v>FXC</v>
+        <v>FXF</v>
       </c>
       <c r="B65" t="str">
         <v>Currencies</v>
       </c>
       <c r="C65" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -14997,13 +15021,13 @@
         <v>0</v>
       </c>
       <c r="F65" t="str">
-        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
+        <v>Invesco CurrencyShares Swiss Franc Trust</v>
       </c>
       <c r="G65" t="str">
         <v>yfinance</v>
       </c>
       <c r="H65" t="str">
-        <v>FXC</v>
+        <v>FXF</v>
       </c>
       <c r="I65" t="str">
         <v>lognormal</v>
@@ -15014,13 +15038,13 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
-        <v>FXY</v>
+        <v>FXA</v>
       </c>
       <c r="B66" t="str">
         <v>Currencies</v>
       </c>
       <c r="C66" t="str">
-        <v>JPY</v>
+        <v>Commod</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -15029,13 +15053,13 @@
         <v>0</v>
       </c>
       <c r="F66" t="str">
-        <v>Invesco CurrencyShares Japanese Yen Trust</v>
+        <v>Invesco CurrencyShares Australian Dollar Trust</v>
       </c>
       <c r="G66" t="str">
         <v>yfinance</v>
       </c>
       <c r="H66" t="str">
-        <v>FXY</v>
+        <v>FXA</v>
       </c>
       <c r="I66" t="str">
         <v>lognormal</v>
@@ -15046,13 +15070,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
-        <v>^VIX</v>
+        <v>FXB</v>
       </c>
       <c r="B67" t="str">
-        <v>Vol</v>
+        <v>Currencies</v>
       </c>
       <c r="C67" t="str">
-        <v>USD</v>
+        <v>GBP</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -15061,27 +15085,27 @@
         <v>0</v>
       </c>
       <c r="F67" t="str">
-        <v>CBOE Volatility Index</v>
+        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
       </c>
       <c r="G67" t="str">
         <v>yfinance</v>
       </c>
       <c r="H67" t="str">
-        <v>^VIX</v>
+        <v>FXB</v>
       </c>
       <c r="I67" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J67">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
-        <v>VXX</v>
+        <v>FXC</v>
       </c>
       <c r="B68" t="str">
-        <v>Vol</v>
+        <v>Currencies</v>
       </c>
       <c r="C68" t="str">
         <v>USD</v>
@@ -15093,30 +15117,30 @@
         <v>0</v>
       </c>
       <c r="F68" t="str">
-        <v>VIX Short-Term Futures ETN</v>
+        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
       </c>
       <c r="G68" t="str">
         <v>yfinance</v>
       </c>
       <c r="H68" t="str">
-        <v>VXX</v>
+        <v>FXC</v>
       </c>
       <c r="I68" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J68">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
-        <v>^VIX3M</v>
+        <v>FXY</v>
       </c>
       <c r="B69" t="str">
-        <v>Vol</v>
+        <v>Currencies</v>
       </c>
       <c r="C69" t="str">
-        <v>USD</v>
+        <v>JPY</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -15125,24 +15149,24 @@
         <v>0</v>
       </c>
       <c r="F69" t="str">
-        <v>CBOE S&amp;P 500 3-Month Volatility</v>
+        <v>Invesco CurrencyShares Japanese Yen Trust</v>
       </c>
       <c r="G69" t="str">
         <v>yfinance</v>
       </c>
       <c r="H69" t="str">
-        <v>^VIX3M</v>
+        <v>FXY</v>
       </c>
       <c r="I69" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J69">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
-        <v>^MOVE</v>
+        <v>^VIX</v>
       </c>
       <c r="B70" t="str">
         <v>Vol</v>
@@ -15157,13 +15181,13 @@
         <v>0</v>
       </c>
       <c r="F70" t="str">
-        <v>ICE BofAML MOVE Index</v>
+        <v>CBOE Volatility Index</v>
       </c>
       <c r="G70" t="str">
         <v>yfinance</v>
       </c>
       <c r="H70" t="str">
-        <v>^MOVE</v>
+        <v>^VIX</v>
       </c>
       <c r="I70" t="str">
         <v>normal</v>
@@ -15174,7 +15198,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
-        <v>^OVX</v>
+        <v>VXX</v>
       </c>
       <c r="B71" t="str">
         <v>Vol</v>
@@ -15189,13 +15213,13 @@
         <v>0</v>
       </c>
       <c r="F71" t="str">
-        <v>CBOE Crude Oil Volatility Index</v>
+        <v>VIX Short-Term Futures ETN</v>
       </c>
       <c r="G71" t="str">
         <v>yfinance</v>
       </c>
       <c r="H71" t="str">
-        <v>^OVX</v>
+        <v>VXX</v>
       </c>
       <c r="I71" t="str">
         <v>normal</v>
@@ -15206,7 +15230,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
-        <v>^GVZ</v>
+        <v>^VIX3M</v>
       </c>
       <c r="B72" t="str">
         <v>Vol</v>
@@ -15221,13 +15245,13 @@
         <v>0</v>
       </c>
       <c r="F72" t="str">
-        <v>CBOE Gold Volatility Index</v>
+        <v>CBOE S&amp;P 500 3-Month Volatility</v>
       </c>
       <c r="G72" t="str">
         <v>yfinance</v>
       </c>
       <c r="H72" t="str">
-        <v>^GVZ</v>
+        <v>^VIX3M</v>
       </c>
       <c r="I72" t="str">
         <v>normal</v>
@@ -15238,42 +15262,42 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
-        <v>MWTIX</v>
+        <v>^MOVE</v>
       </c>
       <c r="B73" t="str">
-        <v>Portfolio</v>
+        <v>Vol</v>
       </c>
       <c r="C73" t="str">
         <v>USD</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73" t="str">
-        <v>TCW MetWest Total Return Bd I</v>
+        <v>ICE BofAML MOVE Index</v>
       </c>
       <c r="G73" t="str">
         <v>yfinance</v>
       </c>
       <c r="H73" t="str">
-        <v>MWTIX</v>
+        <v>^MOVE</v>
       </c>
       <c r="I73" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J73">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
-        <v>FCNTX</v>
+        <v>^OVX</v>
       </c>
       <c r="B74" t="str">
-        <v>Portfolio</v>
+        <v>Vol</v>
       </c>
       <c r="C74" t="str">
         <v>USD</v>
@@ -15285,59 +15309,59 @@
         <v>0</v>
       </c>
       <c r="F74" t="str">
-        <v>Fidelity Contrafund</v>
+        <v>CBOE Crude Oil Volatility Index</v>
       </c>
       <c r="G74" t="str">
         <v>yfinance</v>
       </c>
       <c r="H74" t="str">
-        <v>FCNTX</v>
+        <v>^OVX</v>
       </c>
       <c r="I74" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J74">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
-        <v>PRIVATES</v>
+        <v>^GVZ</v>
       </c>
       <c r="B75" t="str">
-        <v>Theme</v>
+        <v>Vol</v>
       </c>
       <c r="C75" t="str">
         <v>USD</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="str">
-        <v>PSP 0.5, XLF -0.5, BKLN 0.5, LQDH -0.5</v>
+        <v>CBOE Gold Volatility Index</v>
       </c>
       <c r="G75" t="str">
-        <v>composite</v>
+        <v>yfinance</v>
       </c>
       <c r="H75" t="str">
-        <v>PRIVATES</v>
+        <v>^GVZ</v>
       </c>
       <c r="I75" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J75">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
-        <v>FED</v>
+        <v>MWTIX</v>
       </c>
       <c r="B76" t="str">
-        <v>Theme</v>
+        <v>Portfolio</v>
       </c>
       <c r="C76" t="str">
         <v>USD</v>
@@ -15346,16 +15370,16 @@
         <v>1</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" t="str">
-        <v>SHY 1, BSV 1</v>
+        <v>TCW MetWest Total Return Bd I</v>
       </c>
       <c r="G76" t="str">
-        <v>composite</v>
+        <v>yfinance</v>
       </c>
       <c r="H76" t="str">
-        <v>FED</v>
+        <v>MWTIX</v>
       </c>
       <c r="I76" t="str">
         <v>lognormal</v>
@@ -15366,28 +15390,28 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
-        <v>AI</v>
+        <v>FCNTX</v>
       </c>
       <c r="B77" t="str">
-        <v>Theme</v>
+        <v>Portfolio</v>
       </c>
       <c r="C77" t="str">
         <v>USD</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" t="str">
-        <v>AIQ 1, QQQ 0.25, IWM -0.25</v>
+        <v>Fidelity Contrafund</v>
       </c>
       <c r="G77" t="str">
-        <v>composite</v>
+        <v>yfinance</v>
       </c>
       <c r="H77" t="str">
-        <v>AI</v>
+        <v>FCNTX</v>
       </c>
       <c r="I77" t="str">
         <v>lognormal</v>
@@ -15398,7 +15422,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
-        <v>GEOPOLITICS</v>
+        <v>PRIVATES</v>
       </c>
       <c r="B78" t="str">
         <v>Theme</v>
@@ -15413,13 +15437,13 @@
         <v>1</v>
       </c>
       <c r="F78" t="str">
-        <v>GLD 0.65, USO 0.3, ^VIX3M -0.15, FEZ -0.05</v>
+        <v>PSP 0.5, XLF -0.5, BKLN 0.5, LQDH -0.5</v>
       </c>
       <c r="G78" t="str">
         <v>composite</v>
       </c>
       <c r="H78" t="str">
-        <v>GEOPOLITICS</v>
+        <v>PRIVATES</v>
       </c>
       <c r="I78" t="str">
         <v>lognormal</v>
@@ -15430,7 +15454,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
-        <v>TRADEWAR</v>
+        <v>FED</v>
       </c>
       <c r="B79" t="str">
         <v>Theme</v>
@@ -15445,13 +15469,13 @@
         <v>1</v>
       </c>
       <c r="F79" t="str">
-        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
+        <v>SHY 1, BSV 1</v>
       </c>
       <c r="G79" t="str">
         <v>composite</v>
       </c>
       <c r="H79" t="str">
-        <v>TRADEWAR</v>
+        <v>FED</v>
       </c>
       <c r="I79" t="str">
         <v>lognormal</v>
@@ -15462,7 +15486,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
-        <v>IRAN</v>
+        <v>AI</v>
       </c>
       <c r="B80" t="str">
         <v>Theme</v>
@@ -15477,13 +15501,13 @@
         <v>1</v>
       </c>
       <c r="F80" t="str">
-        <v>USO 1</v>
+        <v>AIQ 1, QQQ 0.25, IWM -0.25</v>
       </c>
       <c r="G80" t="str">
         <v>composite</v>
       </c>
       <c r="H80" t="str">
-        <v>IRAN</v>
+        <v>AI</v>
       </c>
       <c r="I80" t="str">
         <v>lognormal</v>
@@ -15494,7 +15518,7 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
-        <v>SEMI-SOFT</v>
+        <v>GEOPOLITICS</v>
       </c>
       <c r="B81" t="str">
         <v>Theme</v>
@@ -15509,13 +15533,13 @@
         <v>1</v>
       </c>
       <c r="F81" t="str">
-        <v>SMH 1, IGV -1, QQQ 1</v>
+        <v>GLD 0.65, USO 0.3, ^VIX3M -0.15, FEZ -0.05</v>
       </c>
       <c r="G81" t="str">
         <v>composite</v>
       </c>
       <c r="H81" t="str">
-        <v>SEMI-SOFT</v>
+        <v>GEOPOLITICS</v>
       </c>
       <c r="I81" t="str">
         <v>lognormal</v>
@@ -15526,10 +15550,10 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
-        <v>2s10s</v>
+        <v>TRADEWAR</v>
       </c>
       <c r="B82" t="str">
-        <v>Rates</v>
+        <v>Theme</v>
       </c>
       <c r="C82" t="str">
         <v>USD</v>
@@ -15541,13 +15565,13 @@
         <v>1</v>
       </c>
       <c r="F82" t="str">
-        <v>SHY -3.86, IEF 1</v>
+        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
       </c>
       <c r="G82" t="str">
         <v>composite</v>
       </c>
       <c r="H82" t="str">
-        <v>2s10s</v>
+        <v>TRADEWAR</v>
       </c>
       <c r="I82" t="str">
         <v>lognormal</v>
@@ -15558,10 +15582,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="str">
-        <v>XLPXLY</v>
+        <v>IRAN</v>
       </c>
       <c r="B83" t="str">
-        <v>Equities</v>
+        <v>Theme</v>
       </c>
       <c r="C83" t="str">
         <v>USD</v>
@@ -15573,13 +15597,13 @@
         <v>1</v>
       </c>
       <c r="F83" t="str">
-        <v>Staples/Discretionary</v>
+        <v>USO 1</v>
       </c>
       <c r="G83" t="str">
         <v>composite</v>
       </c>
       <c r="H83" t="str">
-        <v>XLPXLY</v>
+        <v>IRAN</v>
       </c>
       <c r="I83" t="str">
         <v>lognormal</v>
@@ -15590,28 +15614,28 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
-        <v>BTC</v>
+        <v>SEMI-SOFT</v>
       </c>
       <c r="B84" t="str">
-        <v>Currencies</v>
+        <v>Theme</v>
       </c>
       <c r="C84" t="str">
         <v>USD</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="str">
-        <v>-</v>
+        <v>SMH 1, IGV -1, QQQ 1</v>
       </c>
       <c r="G84" t="str">
-        <v>lmxl</v>
+        <v>composite</v>
       </c>
       <c r="H84" t="str">
-        <v>BTC1_price</v>
+        <v>SEMI-SOFT</v>
       </c>
       <c r="I84" t="str">
         <v>lognormal</v>
@@ -15622,33 +15646,129 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
-        <v>BTC_vol</v>
+        <v>2s10s</v>
       </c>
       <c r="B85" t="str">
-        <v>Vol</v>
+        <v>Rates</v>
       </c>
       <c r="C85" t="str">
         <v>USD</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="str">
+        <v>SHY -3.86, IEF 1</v>
+      </c>
+      <c r="G85" t="str">
+        <v>composite</v>
+      </c>
+      <c r="H85" t="str">
+        <v>2s10s</v>
+      </c>
+      <c r="I85" t="str">
+        <v>lognormal</v>
+      </c>
+      <c r="J85">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="str">
+        <v>XLPXLY</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Equities</v>
+      </c>
+      <c r="C86" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Staples/Discretionary</v>
+      </c>
+      <c r="G86" t="str">
+        <v>composite</v>
+      </c>
+      <c r="H86" t="str">
+        <v>XLPXLY</v>
+      </c>
+      <c r="I86" t="str">
+        <v>lognormal</v>
+      </c>
+      <c r="J86">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="str">
+        <v>BTC</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Currencies</v>
+      </c>
+      <c r="C87" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87" t="str">
         <v>-</v>
       </c>
-      <c r="G85" t="str">
+      <c r="G87" t="str">
         <v>lmxl</v>
       </c>
-      <c r="H85" t="str">
+      <c r="H87" t="str">
+        <v>BTC1_price</v>
+      </c>
+      <c r="I87" t="str">
+        <v>lognormal</v>
+      </c>
+      <c r="J87">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="str">
+        <v>BTC_vol</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Vol</v>
+      </c>
+      <c r="C88" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88" t="str">
+        <v>-</v>
+      </c>
+      <c r="G88" t="str">
+        <v>lmxl</v>
+      </c>
+      <c r="H88" t="str">
         <v>BTC1_atm</v>
       </c>
-      <c r="I85" t="str">
+      <c r="I88" t="str">
         <v>normal</v>
       </c>
-      <c r="J85">
+      <c r="J88">
         <v>-0.01</v>
       </c>
     </row>
@@ -15659,7 +15779,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9123E77-EA56-403E-A728-B01259D22573}">
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
@@ -15699,11 +15819,11 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A74">_xlfn._xlws.FILTER(data[factor_name],(data[Active])*(data[source]="yfinance"))</f>
+        <f t="array" ref="A2:A77">_xlfn._xlws.FILTER(data[factor_name],(data[Active])*(data[source]="yfinance"))</f>
         <v>SPY</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:J74">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
+        <f t="array" ref="B2:J77">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
         <v>Equities</v>
       </c>
       <c r="C2" t="str">
@@ -16533,7 +16653,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <v>FEZ</v>
+        <v>IWN</v>
       </c>
       <c r="B28" t="str">
         <v>Equities</v>
@@ -16548,13 +16668,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="str">
-        <v>Eurostoxx 50</v>
+        <v>Value</v>
       </c>
       <c r="G28" t="str">
         <v>yfinance</v>
       </c>
       <c r="H28" t="str">
-        <v>FEZ</v>
+        <v>IWN</v>
       </c>
       <c r="I28" t="str">
         <v>lognormal</v>
@@ -16565,13 +16685,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <v>EWU</v>
+        <v>IWO</v>
       </c>
       <c r="B29" t="str">
         <v>Equities</v>
       </c>
       <c r="C29" t="str">
-        <v>GBP</v>
+        <v>USD</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -16580,13 +16700,13 @@
         <v>0</v>
       </c>
       <c r="F29" t="str">
-        <v>FTSE 100</v>
+        <v>Growth</v>
       </c>
       <c r="G29" t="str">
         <v>yfinance</v>
       </c>
       <c r="H29" t="str">
-        <v>EWU</v>
+        <v>IWO</v>
       </c>
       <c r="I29" t="str">
         <v>lognormal</v>
@@ -16597,13 +16717,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <v>DAX</v>
+        <v>MTUM</v>
       </c>
       <c r="B30" t="str">
         <v>Equities</v>
       </c>
       <c r="C30" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -16612,13 +16732,13 @@
         <v>0</v>
       </c>
       <c r="F30" t="str">
-        <v>DAX (Germany)</v>
+        <v>Momentum</v>
       </c>
       <c r="G30" t="str">
         <v>yfinance</v>
       </c>
       <c r="H30" t="str">
-        <v>DAX</v>
+        <v>MTUM</v>
       </c>
       <c r="I30" t="str">
         <v>lognormal</v>
@@ -16629,13 +16749,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
-        <v>EWC</v>
+        <v>FEZ</v>
       </c>
       <c r="B31" t="str">
         <v>Equities</v>
       </c>
       <c r="C31" t="str">
-        <v>CAD</v>
+        <v>USD</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -16644,13 +16764,13 @@
         <v>0</v>
       </c>
       <c r="F31" t="str">
-        <v>MSCI Canada</v>
+        <v>Eurostoxx 50</v>
       </c>
       <c r="G31" t="str">
         <v>yfinance</v>
       </c>
       <c r="H31" t="str">
-        <v>EWC</v>
+        <v>FEZ</v>
       </c>
       <c r="I31" t="str">
         <v>lognormal</v>
@@ -16661,13 +16781,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
-        <v>EWI</v>
+        <v>EWU</v>
       </c>
       <c r="B32" t="str">
         <v>Equities</v>
       </c>
       <c r="C32" t="str">
-        <v>EUR</v>
+        <v>GBP</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -16676,13 +16796,13 @@
         <v>0</v>
       </c>
       <c r="F32" t="str">
-        <v>MSCI Italy</v>
+        <v>FTSE 100</v>
       </c>
       <c r="G32" t="str">
         <v>yfinance</v>
       </c>
       <c r="H32" t="str">
-        <v>EWI</v>
+        <v>EWU</v>
       </c>
       <c r="I32" t="str">
         <v>lognormal</v>
@@ -16693,13 +16813,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
-        <v>^N225</v>
+        <v>DAX</v>
       </c>
       <c r="B33" t="str">
         <v>Equities</v>
       </c>
       <c r="C33" t="str">
-        <v>JPY</v>
+        <v>EUR</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -16708,13 +16828,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="str">
-        <v>Nikkei 225</v>
+        <v>DAX (Germany)</v>
       </c>
       <c r="G33" t="str">
         <v>yfinance</v>
       </c>
       <c r="H33" t="str">
-        <v>^N225</v>
+        <v>DAX</v>
       </c>
       <c r="I33" t="str">
         <v>lognormal</v>
@@ -16725,13 +16845,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
-        <v>FXI</v>
+        <v>EWC</v>
       </c>
       <c r="B34" t="str">
         <v>Equities</v>
       </c>
       <c r="C34" t="str">
-        <v>CNH</v>
+        <v>CAD</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -16740,13 +16860,13 @@
         <v>0</v>
       </c>
       <c r="F34" t="str">
-        <v>China Large-Cap</v>
+        <v>MSCI Canada</v>
       </c>
       <c r="G34" t="str">
         <v>yfinance</v>
       </c>
       <c r="H34" t="str">
-        <v>FXI</v>
+        <v>EWC</v>
       </c>
       <c r="I34" t="str">
         <v>lognormal</v>
@@ -16757,13 +16877,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
-        <v>ASHR</v>
+        <v>EWI</v>
       </c>
       <c r="B35" t="str">
         <v>Equities</v>
       </c>
       <c r="C35" t="str">
-        <v>CNH</v>
+        <v>EUR</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -16772,13 +16892,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="str">
-        <v>CSI 300 (China)</v>
+        <v>MSCI Italy</v>
       </c>
       <c r="G35" t="str">
         <v>yfinance</v>
       </c>
       <c r="H35" t="str">
-        <v>ASHR</v>
+        <v>EWI</v>
       </c>
       <c r="I35" t="str">
         <v>lognormal</v>
@@ -16789,13 +16909,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
-        <v>KWEB</v>
+        <v>^N225</v>
       </c>
       <c r="B36" t="str">
         <v>Equities</v>
       </c>
       <c r="C36" t="str">
-        <v>CNH</v>
+        <v>JPY</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -16804,13 +16924,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="str">
-        <v>CSI China Internet</v>
+        <v>Nikkei 225</v>
       </c>
       <c r="G36" t="str">
         <v>yfinance</v>
       </c>
       <c r="H36" t="str">
-        <v>KWEB</v>
+        <v>^N225</v>
       </c>
       <c r="I36" t="str">
         <v>lognormal</v>
@@ -16821,13 +16941,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
-        <v>EEM</v>
+        <v>FXI</v>
       </c>
       <c r="B37" t="str">
         <v>Equities</v>
       </c>
       <c r="C37" t="str">
-        <v>EM</v>
+        <v>CNH</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -16836,13 +16956,13 @@
         <v>0</v>
       </c>
       <c r="F37" t="str">
-        <v>MSCI EM</v>
+        <v>China Large-Cap</v>
       </c>
       <c r="G37" t="str">
         <v>yfinance</v>
       </c>
       <c r="H37" t="str">
-        <v>EEM</v>
+        <v>FXI</v>
       </c>
       <c r="I37" t="str">
         <v>lognormal</v>
@@ -16853,13 +16973,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
-        <v>LQD</v>
+        <v>ASHR</v>
       </c>
       <c r="B38" t="str">
-        <v>Credit</v>
+        <v>Equities</v>
       </c>
       <c r="C38" t="str">
-        <v>USD</v>
+        <v>CNH</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -16868,13 +16988,13 @@
         <v>0</v>
       </c>
       <c r="F38" t="str">
-        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
+        <v>CSI 300 (China)</v>
       </c>
       <c r="G38" t="str">
         <v>yfinance</v>
       </c>
       <c r="H38" t="str">
-        <v>LQD</v>
+        <v>ASHR</v>
       </c>
       <c r="I38" t="str">
         <v>lognormal</v>
@@ -16885,13 +17005,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
-        <v>BSV</v>
+        <v>KWEB</v>
       </c>
       <c r="B39" t="str">
-        <v>Credit</v>
+        <v>Equities</v>
       </c>
       <c r="C39" t="str">
-        <v>USD</v>
+        <v>CNH</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -16900,13 +17020,13 @@
         <v>0</v>
       </c>
       <c r="F39" t="str">
-        <v>Vanguard Short-Term Bond Index Fund ETF</v>
+        <v>CSI China Internet</v>
       </c>
       <c r="G39" t="str">
         <v>yfinance</v>
       </c>
       <c r="H39" t="str">
-        <v>BSV</v>
+        <v>KWEB</v>
       </c>
       <c r="I39" t="str">
         <v>lognormal</v>
@@ -16917,13 +17037,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
-        <v>HYG</v>
+        <v>EEM</v>
       </c>
       <c r="B40" t="str">
-        <v>Credit</v>
+        <v>Equities</v>
       </c>
       <c r="C40" t="str">
-        <v>USD</v>
+        <v>EM</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -16932,13 +17052,13 @@
         <v>0</v>
       </c>
       <c r="F40" t="str">
-        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
+        <v>MSCI EM</v>
       </c>
       <c r="G40" t="str">
         <v>yfinance</v>
       </c>
       <c r="H40" t="str">
-        <v>HYG</v>
+        <v>EEM</v>
       </c>
       <c r="I40" t="str">
         <v>lognormal</v>
@@ -16949,7 +17069,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
-        <v>LQDH</v>
+        <v>LQD</v>
       </c>
       <c r="B41" t="str">
         <v>Credit</v>
@@ -16958,19 +17078,19 @@
         <v>USD</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41" t="str">
-        <v>Hedged LQD</v>
+        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
       </c>
       <c r="G41" t="str">
         <v>yfinance</v>
       </c>
       <c r="H41" t="str">
-        <v>LQDH</v>
+        <v>LQD</v>
       </c>
       <c r="I41" t="str">
         <v>lognormal</v>
@@ -16981,7 +17101,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
-        <v>HYGH</v>
+        <v>BSV</v>
       </c>
       <c r="B42" t="str">
         <v>Credit</v>
@@ -16996,13 +17116,13 @@
         <v>0</v>
       </c>
       <c r="F42" t="str">
-        <v>Hedged HYG</v>
+        <v>Vanguard Short-Term Bond Index Fund ETF</v>
       </c>
       <c r="G42" t="str">
         <v>yfinance</v>
       </c>
       <c r="H42" t="str">
-        <v>HYGH</v>
+        <v>BSV</v>
       </c>
       <c r="I42" t="str">
         <v>lognormal</v>
@@ -17013,7 +17133,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
-        <v>BKLN</v>
+        <v>HYG</v>
       </c>
       <c r="B43" t="str">
         <v>Credit</v>
@@ -17028,13 +17148,13 @@
         <v>0</v>
       </c>
       <c r="F43" t="str">
-        <v>Bank Loans</v>
+        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
       </c>
       <c r="G43" t="str">
         <v>yfinance</v>
       </c>
       <c r="H43" t="str">
-        <v>BKLN</v>
+        <v>HYG</v>
       </c>
       <c r="I43" t="str">
         <v>lognormal</v>
@@ -17045,7 +17165,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
-        <v>AGG</v>
+        <v>LQDH</v>
       </c>
       <c r="B44" t="str">
         <v>Credit</v>
@@ -17054,19 +17174,19 @@
         <v>USD</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44" t="str">
-        <v>US Agg</v>
+        <v>Hedged LQD</v>
       </c>
       <c r="G44" t="str">
         <v>yfinance</v>
       </c>
       <c r="H44" t="str">
-        <v>AGG</v>
+        <v>LQDH</v>
       </c>
       <c r="I44" t="str">
         <v>lognormal</v>
@@ -17077,10 +17197,10 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
-        <v>^TNX</v>
+        <v>HYGH</v>
       </c>
       <c r="B45" t="str">
-        <v>Rates</v>
+        <v>Credit</v>
       </c>
       <c r="C45" t="str">
         <v>USD</v>
@@ -17092,27 +17212,27 @@
         <v>0</v>
       </c>
       <c r="F45" t="str">
-        <v>CBOE Interest Rate 10 Year</v>
+        <v>Hedged HYG</v>
       </c>
       <c r="G45" t="str">
         <v>yfinance</v>
       </c>
       <c r="H45" t="str">
-        <v>^TNX</v>
+        <v>HYGH</v>
       </c>
       <c r="I45" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J45">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
-        <v>SHY</v>
+        <v>BKLN</v>
       </c>
       <c r="B46" t="str">
-        <v>Rates</v>
+        <v>Credit</v>
       </c>
       <c r="C46" t="str">
         <v>USD</v>
@@ -17124,13 +17244,13 @@
         <v>0</v>
       </c>
       <c r="F46" t="str">
-        <v>1-3 Year Treasury</v>
+        <v>Bank Loans</v>
       </c>
       <c r="G46" t="str">
         <v>yfinance</v>
       </c>
       <c r="H46" t="str">
-        <v>SHY</v>
+        <v>BKLN</v>
       </c>
       <c r="I46" t="str">
         <v>lognormal</v>
@@ -17141,10 +17261,10 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
-        <v>IEI</v>
+        <v>AGG</v>
       </c>
       <c r="B47" t="str">
-        <v>Rates</v>
+        <v>Credit</v>
       </c>
       <c r="C47" t="str">
         <v>USD</v>
@@ -17156,13 +17276,13 @@
         <v>0</v>
       </c>
       <c r="F47" t="str">
-        <v>3-7 Year Treasury</v>
+        <v>US Agg</v>
       </c>
       <c r="G47" t="str">
         <v>yfinance</v>
       </c>
       <c r="H47" t="str">
-        <v>IEI</v>
+        <v>AGG</v>
       </c>
       <c r="I47" t="str">
         <v>lognormal</v>
@@ -17173,7 +17293,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
-        <v>IEF</v>
+        <v>^TNX</v>
       </c>
       <c r="B48" t="str">
         <v>Rates</v>
@@ -17182,30 +17302,30 @@
         <v>USD</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="str">
-        <v>7-10 Year Treasury</v>
+        <v>CBOE Interest Rate 10 Year</v>
       </c>
       <c r="G48" t="str">
         <v>yfinance</v>
       </c>
       <c r="H48" t="str">
-        <v>IEF</v>
+        <v>^TNX</v>
       </c>
       <c r="I48" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J48">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
-        <v>TLT</v>
+        <v>SHY</v>
       </c>
       <c r="B49" t="str">
         <v>Rates</v>
@@ -17220,13 +17340,13 @@
         <v>0</v>
       </c>
       <c r="F49" t="str">
-        <v>20+ Year Treasury</v>
+        <v>1-3 Year Treasury</v>
       </c>
       <c r="G49" t="str">
         <v>yfinance</v>
       </c>
       <c r="H49" t="str">
-        <v>TLT</v>
+        <v>SHY</v>
       </c>
       <c r="I49" t="str">
         <v>lognormal</v>
@@ -17237,7 +17357,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
-        <v>TIP</v>
+        <v>IEI</v>
       </c>
       <c r="B50" t="str">
         <v>Rates</v>
@@ -17252,13 +17372,13 @@
         <v>0</v>
       </c>
       <c r="F50" t="str">
-        <v>iShares TIPS Bond ETF</v>
+        <v>3-7 Year Treasury</v>
       </c>
       <c r="G50" t="str">
         <v>yfinance</v>
       </c>
       <c r="H50" t="str">
-        <v>TIP</v>
+        <v>IEI</v>
       </c>
       <c r="I50" t="str">
         <v>lognormal</v>
@@ -17269,7 +17389,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
-        <v>VTIP</v>
+        <v>IEF</v>
       </c>
       <c r="B51" t="str">
         <v>Rates</v>
@@ -17278,19 +17398,19 @@
         <v>USD</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51" t="str">
-        <v>Short-Term Inflation-Protected Securities ETF</v>
+        <v>7-10 Year Treasury</v>
       </c>
       <c r="G51" t="str">
         <v>yfinance</v>
       </c>
       <c r="H51" t="str">
-        <v>VTIP</v>
+        <v>IEF</v>
       </c>
       <c r="I51" t="str">
         <v>lognormal</v>
@@ -17301,7 +17421,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
-        <v>AGNC</v>
+        <v>TLT</v>
       </c>
       <c r="B52" t="str">
         <v>Rates</v>
@@ -17316,13 +17436,13 @@
         <v>0</v>
       </c>
       <c r="F52" t="str">
-        <v>AGNC Investment Corp.</v>
+        <v>20+ Year Treasury</v>
       </c>
       <c r="G52" t="str">
         <v>yfinance</v>
       </c>
       <c r="H52" t="str">
-        <v>AGNC</v>
+        <v>TLT</v>
       </c>
       <c r="I52" t="str">
         <v>lognormal</v>
@@ -17333,7 +17453,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
-        <v>VMBS</v>
+        <v>TIP</v>
       </c>
       <c r="B53" t="str">
         <v>Rates</v>
@@ -17348,13 +17468,13 @@
         <v>0</v>
       </c>
       <c r="F53" t="str">
-        <v>Mortgage-Backed Securities ETF</v>
+        <v>iShares TIPS Bond ETF</v>
       </c>
       <c r="G53" t="str">
         <v>yfinance</v>
       </c>
       <c r="H53" t="str">
-        <v>VMBS</v>
+        <v>TIP</v>
       </c>
       <c r="I53" t="str">
         <v>lognormal</v>
@@ -17365,7 +17485,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
-        <v>CMBS</v>
+        <v>VTIP</v>
       </c>
       <c r="B54" t="str">
         <v>Rates</v>
@@ -17380,13 +17500,13 @@
         <v>0</v>
       </c>
       <c r="F54" t="str">
-        <v>iShares CMBS ETF</v>
+        <v>Short-Term Inflation-Protected Securities ETF</v>
       </c>
       <c r="G54" t="str">
         <v>yfinance</v>
       </c>
       <c r="H54" t="str">
-        <v>CMBS</v>
+        <v>VTIP</v>
       </c>
       <c r="I54" t="str">
         <v>lognormal</v>
@@ -17397,13 +17517,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
-        <v>EMB</v>
+        <v>AGNC</v>
       </c>
       <c r="B55" t="str">
         <v>Rates</v>
       </c>
       <c r="C55" t="str">
-        <v>EM</v>
+        <v>USD</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -17412,13 +17532,13 @@
         <v>0</v>
       </c>
       <c r="F55" t="str">
-        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
+        <v>AGNC Investment Corp.</v>
       </c>
       <c r="G55" t="str">
         <v>yfinance</v>
       </c>
       <c r="H55" t="str">
-        <v>EMB</v>
+        <v>AGNC</v>
       </c>
       <c r="I55" t="str">
         <v>lognormal</v>
@@ -17429,10 +17549,10 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
-        <v>GLD</v>
+        <v>VMBS</v>
       </c>
       <c r="B56" t="str">
-        <v>Commodities</v>
+        <v>Rates</v>
       </c>
       <c r="C56" t="str">
         <v>USD</v>
@@ -17444,13 +17564,13 @@
         <v>0</v>
       </c>
       <c r="F56" t="str">
-        <v>SPDR Gold Shares</v>
+        <v>Mortgage-Backed Securities ETF</v>
       </c>
       <c r="G56" t="str">
         <v>yfinance</v>
       </c>
       <c r="H56" t="str">
-        <v>GLD</v>
+        <v>VMBS</v>
       </c>
       <c r="I56" t="str">
         <v>lognormal</v>
@@ -17461,10 +17581,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
-        <v>SLV</v>
+        <v>CMBS</v>
       </c>
       <c r="B57" t="str">
-        <v>Commodities</v>
+        <v>Rates</v>
       </c>
       <c r="C57" t="str">
         <v>USD</v>
@@ -17476,13 +17596,13 @@
         <v>0</v>
       </c>
       <c r="F57" t="str">
-        <v>iShares Silver Trust</v>
+        <v>iShares CMBS ETF</v>
       </c>
       <c r="G57" t="str">
         <v>yfinance</v>
       </c>
       <c r="H57" t="str">
-        <v>SLV</v>
+        <v>CMBS</v>
       </c>
       <c r="I57" t="str">
         <v>lognormal</v>
@@ -17493,13 +17613,13 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
-        <v>USO</v>
+        <v>EMB</v>
       </c>
       <c r="B58" t="str">
-        <v>Commodities</v>
+        <v>Rates</v>
       </c>
       <c r="C58" t="str">
-        <v>USD</v>
+        <v>EM</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -17508,13 +17628,13 @@
         <v>0</v>
       </c>
       <c r="F58" t="str">
-        <v>United States Oil Fund</v>
+        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
       </c>
       <c r="G58" t="str">
         <v>yfinance</v>
       </c>
       <c r="H58" t="str">
-        <v>USO</v>
+        <v>EMB</v>
       </c>
       <c r="I58" t="str">
         <v>lognormal</v>
@@ -17525,10 +17645,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
-        <v>UUP</v>
+        <v>GLD</v>
       </c>
       <c r="B59" t="str">
-        <v>Currencies</v>
+        <v>Commodities</v>
       </c>
       <c r="C59" t="str">
         <v>USD</v>
@@ -17540,13 +17660,13 @@
         <v>0</v>
       </c>
       <c r="F59" t="str">
-        <v>Invesco DB US Dollar Index Bullish Fund</v>
+        <v>SPDR Gold Shares</v>
       </c>
       <c r="G59" t="str">
         <v>yfinance</v>
       </c>
       <c r="H59" t="str">
-        <v>UUP</v>
+        <v>GLD</v>
       </c>
       <c r="I59" t="str">
         <v>lognormal</v>
@@ -17557,10 +17677,10 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
-        <v>DX-Y.NYB</v>
+        <v>SLV</v>
       </c>
       <c r="B60" t="str">
-        <v>Currencies</v>
+        <v>Commodities</v>
       </c>
       <c r="C60" t="str">
         <v>USD</v>
@@ -17572,13 +17692,13 @@
         <v>0</v>
       </c>
       <c r="F60" t="str">
-        <v>U.S. Dollar Index</v>
+        <v>iShares Silver Trust</v>
       </c>
       <c r="G60" t="str">
         <v>yfinance</v>
       </c>
       <c r="H60" t="str">
-        <v>DX-Y.NYB</v>
+        <v>SLV</v>
       </c>
       <c r="I60" t="str">
         <v>lognormal</v>
@@ -17589,13 +17709,13 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
-        <v>FXE</v>
+        <v>USO</v>
       </c>
       <c r="B61" t="str">
-        <v>Currencies</v>
+        <v>Commodities</v>
       </c>
       <c r="C61" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -17604,13 +17724,13 @@
         <v>0</v>
       </c>
       <c r="F61" t="str">
-        <v>Invesco CurrencyShares Euro Trust</v>
+        <v>United States Oil Fund</v>
       </c>
       <c r="G61" t="str">
         <v>yfinance</v>
       </c>
       <c r="H61" t="str">
-        <v>FXE</v>
+        <v>USO</v>
       </c>
       <c r="I61" t="str">
         <v>lognormal</v>
@@ -17621,13 +17741,13 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
-        <v>FXF</v>
+        <v>UUP</v>
       </c>
       <c r="B62" t="str">
         <v>Currencies</v>
       </c>
       <c r="C62" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -17636,13 +17756,13 @@
         <v>0</v>
       </c>
       <c r="F62" t="str">
-        <v>Invesco CurrencyShares Swiss Franc Trust</v>
+        <v>Invesco DB US Dollar Index Bullish Fund</v>
       </c>
       <c r="G62" t="str">
         <v>yfinance</v>
       </c>
       <c r="H62" t="str">
-        <v>FXF</v>
+        <v>UUP</v>
       </c>
       <c r="I62" t="str">
         <v>lognormal</v>
@@ -17653,13 +17773,13 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
-        <v>FXA</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="B63" t="str">
         <v>Currencies</v>
       </c>
       <c r="C63" t="str">
-        <v>Commod</v>
+        <v>USD</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -17668,13 +17788,13 @@
         <v>0</v>
       </c>
       <c r="F63" t="str">
-        <v>Invesco CurrencyShares Australian Dollar Trust</v>
+        <v>U.S. Dollar Index</v>
       </c>
       <c r="G63" t="str">
         <v>yfinance</v>
       </c>
       <c r="H63" t="str">
-        <v>FXA</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="I63" t="str">
         <v>lognormal</v>
@@ -17685,13 +17805,13 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
-        <v>FXB</v>
+        <v>FXE</v>
       </c>
       <c r="B64" t="str">
         <v>Currencies</v>
       </c>
       <c r="C64" t="str">
-        <v>GBP</v>
+        <v>EUR</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -17700,13 +17820,13 @@
         <v>0</v>
       </c>
       <c r="F64" t="str">
-        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
+        <v>Invesco CurrencyShares Euro Trust</v>
       </c>
       <c r="G64" t="str">
         <v>yfinance</v>
       </c>
       <c r="H64" t="str">
-        <v>FXB</v>
+        <v>FXE</v>
       </c>
       <c r="I64" t="str">
         <v>lognormal</v>
@@ -17717,13 +17837,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
-        <v>FXC</v>
+        <v>FXF</v>
       </c>
       <c r="B65" t="str">
         <v>Currencies</v>
       </c>
       <c r="C65" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -17732,13 +17852,13 @@
         <v>0</v>
       </c>
       <c r="F65" t="str">
-        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
+        <v>Invesco CurrencyShares Swiss Franc Trust</v>
       </c>
       <c r="G65" t="str">
         <v>yfinance</v>
       </c>
       <c r="H65" t="str">
-        <v>FXC</v>
+        <v>FXF</v>
       </c>
       <c r="I65" t="str">
         <v>lognormal</v>
@@ -17749,13 +17869,13 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
-        <v>FXY</v>
+        <v>FXA</v>
       </c>
       <c r="B66" t="str">
         <v>Currencies</v>
       </c>
       <c r="C66" t="str">
-        <v>JPY</v>
+        <v>Commod</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -17764,13 +17884,13 @@
         <v>0</v>
       </c>
       <c r="F66" t="str">
-        <v>Invesco CurrencyShares Japanese Yen Trust</v>
+        <v>Invesco CurrencyShares Australian Dollar Trust</v>
       </c>
       <c r="G66" t="str">
         <v>yfinance</v>
       </c>
       <c r="H66" t="str">
-        <v>FXY</v>
+        <v>FXA</v>
       </c>
       <c r="I66" t="str">
         <v>lognormal</v>
@@ -17781,13 +17901,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
-        <v>^VIX</v>
+        <v>FXB</v>
       </c>
       <c r="B67" t="str">
-        <v>Vol</v>
+        <v>Currencies</v>
       </c>
       <c r="C67" t="str">
-        <v>USD</v>
+        <v>GBP</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -17796,27 +17916,27 @@
         <v>0</v>
       </c>
       <c r="F67" t="str">
-        <v>CBOE Volatility Index</v>
+        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
       </c>
       <c r="G67" t="str">
         <v>yfinance</v>
       </c>
       <c r="H67" t="str">
-        <v>^VIX</v>
+        <v>FXB</v>
       </c>
       <c r="I67" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J67">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
-        <v>VXX</v>
+        <v>FXC</v>
       </c>
       <c r="B68" t="str">
-        <v>Vol</v>
+        <v>Currencies</v>
       </c>
       <c r="C68" t="str">
         <v>USD</v>
@@ -17828,30 +17948,30 @@
         <v>0</v>
       </c>
       <c r="F68" t="str">
-        <v>VIX Short-Term Futures ETN</v>
+        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
       </c>
       <c r="G68" t="str">
         <v>yfinance</v>
       </c>
       <c r="H68" t="str">
-        <v>VXX</v>
+        <v>FXC</v>
       </c>
       <c r="I68" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J68">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
-        <v>^VIX3M</v>
+        <v>FXY</v>
       </c>
       <c r="B69" t="str">
-        <v>Vol</v>
+        <v>Currencies</v>
       </c>
       <c r="C69" t="str">
-        <v>USD</v>
+        <v>JPY</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -17860,24 +17980,24 @@
         <v>0</v>
       </c>
       <c r="F69" t="str">
-        <v>CBOE S&amp;P 500 3-Month Volatility</v>
+        <v>Invesco CurrencyShares Japanese Yen Trust</v>
       </c>
       <c r="G69" t="str">
         <v>yfinance</v>
       </c>
       <c r="H69" t="str">
-        <v>^VIX3M</v>
+        <v>FXY</v>
       </c>
       <c r="I69" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J69">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
-        <v>^MOVE</v>
+        <v>^VIX</v>
       </c>
       <c r="B70" t="str">
         <v>Vol</v>
@@ -17892,13 +18012,13 @@
         <v>0</v>
       </c>
       <c r="F70" t="str">
-        <v>ICE BofAML MOVE Index</v>
+        <v>CBOE Volatility Index</v>
       </c>
       <c r="G70" t="str">
         <v>yfinance</v>
       </c>
       <c r="H70" t="str">
-        <v>^MOVE</v>
+        <v>^VIX</v>
       </c>
       <c r="I70" t="str">
         <v>normal</v>
@@ -17909,7 +18029,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
-        <v>^OVX</v>
+        <v>VXX</v>
       </c>
       <c r="B71" t="str">
         <v>Vol</v>
@@ -17924,13 +18044,13 @@
         <v>0</v>
       </c>
       <c r="F71" t="str">
-        <v>CBOE Crude Oil Volatility Index</v>
+        <v>VIX Short-Term Futures ETN</v>
       </c>
       <c r="G71" t="str">
         <v>yfinance</v>
       </c>
       <c r="H71" t="str">
-        <v>^OVX</v>
+        <v>VXX</v>
       </c>
       <c r="I71" t="str">
         <v>normal</v>
@@ -17941,7 +18061,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
-        <v>^GVZ</v>
+        <v>^VIX3M</v>
       </c>
       <c r="B72" t="str">
         <v>Vol</v>
@@ -17956,13 +18076,13 @@
         <v>0</v>
       </c>
       <c r="F72" t="str">
-        <v>CBOE Gold Volatility Index</v>
+        <v>CBOE S&amp;P 500 3-Month Volatility</v>
       </c>
       <c r="G72" t="str">
         <v>yfinance</v>
       </c>
       <c r="H72" t="str">
-        <v>^GVZ</v>
+        <v>^VIX3M</v>
       </c>
       <c r="I72" t="str">
         <v>normal</v>
@@ -17973,42 +18093,42 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
-        <v>MWTIX</v>
+        <v>^MOVE</v>
       </c>
       <c r="B73" t="str">
-        <v>Portfolio</v>
+        <v>Vol</v>
       </c>
       <c r="C73" t="str">
         <v>USD</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73" t="str">
-        <v>TCW MetWest Total Return Bd I</v>
+        <v>ICE BofAML MOVE Index</v>
       </c>
       <c r="G73" t="str">
         <v>yfinance</v>
       </c>
       <c r="H73" t="str">
-        <v>MWTIX</v>
+        <v>^MOVE</v>
       </c>
       <c r="I73" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J73">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
-        <v>FCNTX</v>
+        <v>^OVX</v>
       </c>
       <c r="B74" t="str">
-        <v>Portfolio</v>
+        <v>Vol</v>
       </c>
       <c r="C74" t="str">
         <v>USD</v>
@@ -18020,18 +18140,114 @@
         <v>0</v>
       </c>
       <c r="F74" t="str">
-        <v>Fidelity Contrafund</v>
+        <v>CBOE Crude Oil Volatility Index</v>
       </c>
       <c r="G74" t="str">
         <v>yfinance</v>
       </c>
       <c r="H74" t="str">
+        <v>^OVX</v>
+      </c>
+      <c r="I74" t="str">
+        <v>normal</v>
+      </c>
+      <c r="J74">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="str">
+        <v>^GVZ</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Vol</v>
+      </c>
+      <c r="C75" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75" t="str">
+        <v>CBOE Gold Volatility Index</v>
+      </c>
+      <c r="G75" t="str">
+        <v>yfinance</v>
+      </c>
+      <c r="H75" t="str">
+        <v>^GVZ</v>
+      </c>
+      <c r="I75" t="str">
+        <v>normal</v>
+      </c>
+      <c r="J75">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="str">
+        <v>MWTIX</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Portfolio</v>
+      </c>
+      <c r="C76" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76" t="str">
+        <v>TCW MetWest Total Return Bd I</v>
+      </c>
+      <c r="G76" t="str">
+        <v>yfinance</v>
+      </c>
+      <c r="H76" t="str">
+        <v>MWTIX</v>
+      </c>
+      <c r="I76" t="str">
+        <v>lognormal</v>
+      </c>
+      <c r="J76">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="str">
         <v>FCNTX</v>
       </c>
-      <c r="I74" t="str">
+      <c r="B77" t="str">
+        <v>Portfolio</v>
+      </c>
+      <c r="C77" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Fidelity Contrafund</v>
+      </c>
+      <c r="G77" t="str">
+        <v>yfinance</v>
+      </c>
+      <c r="H77" t="str">
+        <v>FCNTX</v>
+      </c>
+      <c r="I77" t="str">
         <v>lognormal</v>
       </c>
-      <c r="J74">
+      <c r="J77">
         <v>1E-4</v>
       </c>
     </row>
@@ -18043,7 +18259,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2977BD7F-9323-4F6D-98BF-C1B39119DCDE}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
@@ -18083,11 +18299,11 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A85">_xlfn._xlws.FILTER(data[factor_name],data[Active]*(data[client]=0))</f>
+        <f t="array" ref="A2:A88">_xlfn._xlws.FILTER(data[factor_name],data[Active]*(data[client]=0))</f>
         <v>SPY</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:J85">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
+        <f t="array" ref="B2:J88">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:J1,data[#Headers]))</f>
         <v>Equities</v>
       </c>
       <c r="C2" t="str">
@@ -18917,7 +19133,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <v>FEZ</v>
+        <v>IWN</v>
       </c>
       <c r="B28" t="str">
         <v>Equities</v>
@@ -18932,13 +19148,13 @@
         <v>0</v>
       </c>
       <c r="F28" t="str">
-        <v>Eurostoxx 50</v>
+        <v>Value</v>
       </c>
       <c r="G28" t="str">
         <v>yfinance</v>
       </c>
       <c r="H28" t="str">
-        <v>FEZ</v>
+        <v>IWN</v>
       </c>
       <c r="I28" t="str">
         <v>lognormal</v>
@@ -18949,13 +19165,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <v>EWU</v>
+        <v>IWO</v>
       </c>
       <c r="B29" t="str">
         <v>Equities</v>
       </c>
       <c r="C29" t="str">
-        <v>GBP</v>
+        <v>USD</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -18964,13 +19180,13 @@
         <v>0</v>
       </c>
       <c r="F29" t="str">
-        <v>FTSE 100</v>
+        <v>Growth</v>
       </c>
       <c r="G29" t="str">
         <v>yfinance</v>
       </c>
       <c r="H29" t="str">
-        <v>EWU</v>
+        <v>IWO</v>
       </c>
       <c r="I29" t="str">
         <v>lognormal</v>
@@ -18981,13 +19197,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <v>DAX</v>
+        <v>MTUM</v>
       </c>
       <c r="B30" t="str">
         <v>Equities</v>
       </c>
       <c r="C30" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -18996,13 +19212,13 @@
         <v>0</v>
       </c>
       <c r="F30" t="str">
-        <v>DAX (Germany)</v>
+        <v>Momentum</v>
       </c>
       <c r="G30" t="str">
         <v>yfinance</v>
       </c>
       <c r="H30" t="str">
-        <v>DAX</v>
+        <v>MTUM</v>
       </c>
       <c r="I30" t="str">
         <v>lognormal</v>
@@ -19013,13 +19229,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
-        <v>EWC</v>
+        <v>FEZ</v>
       </c>
       <c r="B31" t="str">
         <v>Equities</v>
       </c>
       <c r="C31" t="str">
-        <v>CAD</v>
+        <v>USD</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -19028,13 +19244,13 @@
         <v>0</v>
       </c>
       <c r="F31" t="str">
-        <v>MSCI Canada</v>
+        <v>Eurostoxx 50</v>
       </c>
       <c r="G31" t="str">
         <v>yfinance</v>
       </c>
       <c r="H31" t="str">
-        <v>EWC</v>
+        <v>FEZ</v>
       </c>
       <c r="I31" t="str">
         <v>lognormal</v>
@@ -19045,13 +19261,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
-        <v>EWI</v>
+        <v>EWU</v>
       </c>
       <c r="B32" t="str">
         <v>Equities</v>
       </c>
       <c r="C32" t="str">
-        <v>EUR</v>
+        <v>GBP</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -19060,13 +19276,13 @@
         <v>0</v>
       </c>
       <c r="F32" t="str">
-        <v>MSCI Italy</v>
+        <v>FTSE 100</v>
       </c>
       <c r="G32" t="str">
         <v>yfinance</v>
       </c>
       <c r="H32" t="str">
-        <v>EWI</v>
+        <v>EWU</v>
       </c>
       <c r="I32" t="str">
         <v>lognormal</v>
@@ -19077,13 +19293,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
-        <v>^N225</v>
+        <v>DAX</v>
       </c>
       <c r="B33" t="str">
         <v>Equities</v>
       </c>
       <c r="C33" t="str">
-        <v>JPY</v>
+        <v>EUR</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -19092,13 +19308,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="str">
-        <v>Nikkei 225</v>
+        <v>DAX (Germany)</v>
       </c>
       <c r="G33" t="str">
         <v>yfinance</v>
       </c>
       <c r="H33" t="str">
-        <v>^N225</v>
+        <v>DAX</v>
       </c>
       <c r="I33" t="str">
         <v>lognormal</v>
@@ -19109,13 +19325,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
-        <v>FXI</v>
+        <v>EWC</v>
       </c>
       <c r="B34" t="str">
         <v>Equities</v>
       </c>
       <c r="C34" t="str">
-        <v>CNH</v>
+        <v>CAD</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -19124,13 +19340,13 @@
         <v>0</v>
       </c>
       <c r="F34" t="str">
-        <v>China Large-Cap</v>
+        <v>MSCI Canada</v>
       </c>
       <c r="G34" t="str">
         <v>yfinance</v>
       </c>
       <c r="H34" t="str">
-        <v>FXI</v>
+        <v>EWC</v>
       </c>
       <c r="I34" t="str">
         <v>lognormal</v>
@@ -19141,13 +19357,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
-        <v>ASHR</v>
+        <v>EWI</v>
       </c>
       <c r="B35" t="str">
         <v>Equities</v>
       </c>
       <c r="C35" t="str">
-        <v>CNH</v>
+        <v>EUR</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -19156,13 +19372,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="str">
-        <v>CSI 300 (China)</v>
+        <v>MSCI Italy</v>
       </c>
       <c r="G35" t="str">
         <v>yfinance</v>
       </c>
       <c r="H35" t="str">
-        <v>ASHR</v>
+        <v>EWI</v>
       </c>
       <c r="I35" t="str">
         <v>lognormal</v>
@@ -19173,13 +19389,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
-        <v>KWEB</v>
+        <v>^N225</v>
       </c>
       <c r="B36" t="str">
         <v>Equities</v>
       </c>
       <c r="C36" t="str">
-        <v>CNH</v>
+        <v>JPY</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -19188,13 +19404,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="str">
-        <v>CSI China Internet</v>
+        <v>Nikkei 225</v>
       </c>
       <c r="G36" t="str">
         <v>yfinance</v>
       </c>
       <c r="H36" t="str">
-        <v>KWEB</v>
+        <v>^N225</v>
       </c>
       <c r="I36" t="str">
         <v>lognormal</v>
@@ -19205,13 +19421,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
-        <v>EEM</v>
+        <v>FXI</v>
       </c>
       <c r="B37" t="str">
         <v>Equities</v>
       </c>
       <c r="C37" t="str">
-        <v>EM</v>
+        <v>CNH</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -19220,13 +19436,13 @@
         <v>0</v>
       </c>
       <c r="F37" t="str">
-        <v>MSCI EM</v>
+        <v>China Large-Cap</v>
       </c>
       <c r="G37" t="str">
         <v>yfinance</v>
       </c>
       <c r="H37" t="str">
-        <v>EEM</v>
+        <v>FXI</v>
       </c>
       <c r="I37" t="str">
         <v>lognormal</v>
@@ -19237,13 +19453,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
-        <v>LQD</v>
+        <v>ASHR</v>
       </c>
       <c r="B38" t="str">
-        <v>Credit</v>
+        <v>Equities</v>
       </c>
       <c r="C38" t="str">
-        <v>USD</v>
+        <v>CNH</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -19252,13 +19468,13 @@
         <v>0</v>
       </c>
       <c r="F38" t="str">
-        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
+        <v>CSI 300 (China)</v>
       </c>
       <c r="G38" t="str">
         <v>yfinance</v>
       </c>
       <c r="H38" t="str">
-        <v>LQD</v>
+        <v>ASHR</v>
       </c>
       <c r="I38" t="str">
         <v>lognormal</v>
@@ -19269,13 +19485,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
-        <v>BSV</v>
+        <v>KWEB</v>
       </c>
       <c r="B39" t="str">
-        <v>Credit</v>
+        <v>Equities</v>
       </c>
       <c r="C39" t="str">
-        <v>USD</v>
+        <v>CNH</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -19284,13 +19500,13 @@
         <v>0</v>
       </c>
       <c r="F39" t="str">
-        <v>Vanguard Short-Term Bond Index Fund ETF</v>
+        <v>CSI China Internet</v>
       </c>
       <c r="G39" t="str">
         <v>yfinance</v>
       </c>
       <c r="H39" t="str">
-        <v>BSV</v>
+        <v>KWEB</v>
       </c>
       <c r="I39" t="str">
         <v>lognormal</v>
@@ -19301,13 +19517,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
-        <v>HYG</v>
+        <v>EEM</v>
       </c>
       <c r="B40" t="str">
-        <v>Credit</v>
+        <v>Equities</v>
       </c>
       <c r="C40" t="str">
-        <v>USD</v>
+        <v>EM</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -19316,13 +19532,13 @@
         <v>0</v>
       </c>
       <c r="F40" t="str">
-        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
+        <v>MSCI EM</v>
       </c>
       <c r="G40" t="str">
         <v>yfinance</v>
       </c>
       <c r="H40" t="str">
-        <v>HYG</v>
+        <v>EEM</v>
       </c>
       <c r="I40" t="str">
         <v>lognormal</v>
@@ -19333,7 +19549,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
-        <v>LQDH</v>
+        <v>LQD</v>
       </c>
       <c r="B41" t="str">
         <v>Credit</v>
@@ -19342,19 +19558,19 @@
         <v>USD</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
       <c r="F41" t="str">
-        <v>Hedged LQD</v>
+        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
       </c>
       <c r="G41" t="str">
         <v>yfinance</v>
       </c>
       <c r="H41" t="str">
-        <v>LQDH</v>
+        <v>LQD</v>
       </c>
       <c r="I41" t="str">
         <v>lognormal</v>
@@ -19365,7 +19581,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
-        <v>HYGH</v>
+        <v>BSV</v>
       </c>
       <c r="B42" t="str">
         <v>Credit</v>
@@ -19380,13 +19596,13 @@
         <v>0</v>
       </c>
       <c r="F42" t="str">
-        <v>Hedged HYG</v>
+        <v>Vanguard Short-Term Bond Index Fund ETF</v>
       </c>
       <c r="G42" t="str">
         <v>yfinance</v>
       </c>
       <c r="H42" t="str">
-        <v>HYGH</v>
+        <v>BSV</v>
       </c>
       <c r="I42" t="str">
         <v>lognormal</v>
@@ -19397,7 +19613,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
-        <v>BKLN</v>
+        <v>HYG</v>
       </c>
       <c r="B43" t="str">
         <v>Credit</v>
@@ -19412,13 +19628,13 @@
         <v>0</v>
       </c>
       <c r="F43" t="str">
-        <v>Bank Loans</v>
+        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
       </c>
       <c r="G43" t="str">
         <v>yfinance</v>
       </c>
       <c r="H43" t="str">
-        <v>BKLN</v>
+        <v>HYG</v>
       </c>
       <c r="I43" t="str">
         <v>lognormal</v>
@@ -19429,7 +19645,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
-        <v>AGG</v>
+        <v>LQDH</v>
       </c>
       <c r="B44" t="str">
         <v>Credit</v>
@@ -19438,19 +19654,19 @@
         <v>USD</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44" t="str">
-        <v>US Agg</v>
+        <v>Hedged LQD</v>
       </c>
       <c r="G44" t="str">
         <v>yfinance</v>
       </c>
       <c r="H44" t="str">
-        <v>AGG</v>
+        <v>LQDH</v>
       </c>
       <c r="I44" t="str">
         <v>lognormal</v>
@@ -19461,10 +19677,10 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
-        <v>^TNX</v>
+        <v>HYGH</v>
       </c>
       <c r="B45" t="str">
-        <v>Rates</v>
+        <v>Credit</v>
       </c>
       <c r="C45" t="str">
         <v>USD</v>
@@ -19476,27 +19692,27 @@
         <v>0</v>
       </c>
       <c r="F45" t="str">
-        <v>CBOE Interest Rate 10 Year</v>
+        <v>Hedged HYG</v>
       </c>
       <c r="G45" t="str">
         <v>yfinance</v>
       </c>
       <c r="H45" t="str">
-        <v>^TNX</v>
+        <v>HYGH</v>
       </c>
       <c r="I45" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J45">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
-        <v>SHY</v>
+        <v>BKLN</v>
       </c>
       <c r="B46" t="str">
-        <v>Rates</v>
+        <v>Credit</v>
       </c>
       <c r="C46" t="str">
         <v>USD</v>
@@ -19508,13 +19724,13 @@
         <v>0</v>
       </c>
       <c r="F46" t="str">
-        <v>1-3 Year Treasury</v>
+        <v>Bank Loans</v>
       </c>
       <c r="G46" t="str">
         <v>yfinance</v>
       </c>
       <c r="H46" t="str">
-        <v>SHY</v>
+        <v>BKLN</v>
       </c>
       <c r="I46" t="str">
         <v>lognormal</v>
@@ -19525,10 +19741,10 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
-        <v>IEI</v>
+        <v>AGG</v>
       </c>
       <c r="B47" t="str">
-        <v>Rates</v>
+        <v>Credit</v>
       </c>
       <c r="C47" t="str">
         <v>USD</v>
@@ -19540,13 +19756,13 @@
         <v>0</v>
       </c>
       <c r="F47" t="str">
-        <v>3-7 Year Treasury</v>
+        <v>US Agg</v>
       </c>
       <c r="G47" t="str">
         <v>yfinance</v>
       </c>
       <c r="H47" t="str">
-        <v>IEI</v>
+        <v>AGG</v>
       </c>
       <c r="I47" t="str">
         <v>lognormal</v>
@@ -19557,7 +19773,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
-        <v>IEF</v>
+        <v>^TNX</v>
       </c>
       <c r="B48" t="str">
         <v>Rates</v>
@@ -19566,30 +19782,30 @@
         <v>USD</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="str">
-        <v>7-10 Year Treasury</v>
+        <v>CBOE Interest Rate 10 Year</v>
       </c>
       <c r="G48" t="str">
         <v>yfinance</v>
       </c>
       <c r="H48" t="str">
-        <v>IEF</v>
+        <v>^TNX</v>
       </c>
       <c r="I48" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J48">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
-        <v>TLT</v>
+        <v>SHY</v>
       </c>
       <c r="B49" t="str">
         <v>Rates</v>
@@ -19604,13 +19820,13 @@
         <v>0</v>
       </c>
       <c r="F49" t="str">
-        <v>20+ Year Treasury</v>
+        <v>1-3 Year Treasury</v>
       </c>
       <c r="G49" t="str">
         <v>yfinance</v>
       </c>
       <c r="H49" t="str">
-        <v>TLT</v>
+        <v>SHY</v>
       </c>
       <c r="I49" t="str">
         <v>lognormal</v>
@@ -19621,7 +19837,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
-        <v>TIP</v>
+        <v>IEI</v>
       </c>
       <c r="B50" t="str">
         <v>Rates</v>
@@ -19636,13 +19852,13 @@
         <v>0</v>
       </c>
       <c r="F50" t="str">
-        <v>iShares TIPS Bond ETF</v>
+        <v>3-7 Year Treasury</v>
       </c>
       <c r="G50" t="str">
         <v>yfinance</v>
       </c>
       <c r="H50" t="str">
-        <v>TIP</v>
+        <v>IEI</v>
       </c>
       <c r="I50" t="str">
         <v>lognormal</v>
@@ -19653,7 +19869,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
-        <v>VTIP</v>
+        <v>IEF</v>
       </c>
       <c r="B51" t="str">
         <v>Rates</v>
@@ -19662,19 +19878,19 @@
         <v>USD</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51" t="str">
-        <v>Short-Term Inflation-Protected Securities ETF</v>
+        <v>7-10 Year Treasury</v>
       </c>
       <c r="G51" t="str">
         <v>yfinance</v>
       </c>
       <c r="H51" t="str">
-        <v>VTIP</v>
+        <v>IEF</v>
       </c>
       <c r="I51" t="str">
         <v>lognormal</v>
@@ -19685,7 +19901,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
-        <v>AGNC</v>
+        <v>TLT</v>
       </c>
       <c r="B52" t="str">
         <v>Rates</v>
@@ -19700,13 +19916,13 @@
         <v>0</v>
       </c>
       <c r="F52" t="str">
-        <v>AGNC Investment Corp.</v>
+        <v>20+ Year Treasury</v>
       </c>
       <c r="G52" t="str">
         <v>yfinance</v>
       </c>
       <c r="H52" t="str">
-        <v>AGNC</v>
+        <v>TLT</v>
       </c>
       <c r="I52" t="str">
         <v>lognormal</v>
@@ -19717,7 +19933,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
-        <v>VMBS</v>
+        <v>TIP</v>
       </c>
       <c r="B53" t="str">
         <v>Rates</v>
@@ -19732,13 +19948,13 @@
         <v>0</v>
       </c>
       <c r="F53" t="str">
-        <v>Mortgage-Backed Securities ETF</v>
+        <v>iShares TIPS Bond ETF</v>
       </c>
       <c r="G53" t="str">
         <v>yfinance</v>
       </c>
       <c r="H53" t="str">
-        <v>VMBS</v>
+        <v>TIP</v>
       </c>
       <c r="I53" t="str">
         <v>lognormal</v>
@@ -19749,7 +19965,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
-        <v>CMBS</v>
+        <v>VTIP</v>
       </c>
       <c r="B54" t="str">
         <v>Rates</v>
@@ -19764,13 +19980,13 @@
         <v>0</v>
       </c>
       <c r="F54" t="str">
-        <v>iShares CMBS ETF</v>
+        <v>Short-Term Inflation-Protected Securities ETF</v>
       </c>
       <c r="G54" t="str">
         <v>yfinance</v>
       </c>
       <c r="H54" t="str">
-        <v>CMBS</v>
+        <v>VTIP</v>
       </c>
       <c r="I54" t="str">
         <v>lognormal</v>
@@ -19781,13 +19997,13 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
-        <v>EMB</v>
+        <v>AGNC</v>
       </c>
       <c r="B55" t="str">
         <v>Rates</v>
       </c>
       <c r="C55" t="str">
-        <v>EM</v>
+        <v>USD</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -19796,13 +20012,13 @@
         <v>0</v>
       </c>
       <c r="F55" t="str">
-        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
+        <v>AGNC Investment Corp.</v>
       </c>
       <c r="G55" t="str">
         <v>yfinance</v>
       </c>
       <c r="H55" t="str">
-        <v>EMB</v>
+        <v>AGNC</v>
       </c>
       <c r="I55" t="str">
         <v>lognormal</v>
@@ -19813,10 +20029,10 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
-        <v>GLD</v>
+        <v>VMBS</v>
       </c>
       <c r="B56" t="str">
-        <v>Commodities</v>
+        <v>Rates</v>
       </c>
       <c r="C56" t="str">
         <v>USD</v>
@@ -19828,13 +20044,13 @@
         <v>0</v>
       </c>
       <c r="F56" t="str">
-        <v>SPDR Gold Shares</v>
+        <v>Mortgage-Backed Securities ETF</v>
       </c>
       <c r="G56" t="str">
         <v>yfinance</v>
       </c>
       <c r="H56" t="str">
-        <v>GLD</v>
+        <v>VMBS</v>
       </c>
       <c r="I56" t="str">
         <v>lognormal</v>
@@ -19845,10 +20061,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
-        <v>SLV</v>
+        <v>CMBS</v>
       </c>
       <c r="B57" t="str">
-        <v>Commodities</v>
+        <v>Rates</v>
       </c>
       <c r="C57" t="str">
         <v>USD</v>
@@ -19860,13 +20076,13 @@
         <v>0</v>
       </c>
       <c r="F57" t="str">
-        <v>iShares Silver Trust</v>
+        <v>iShares CMBS ETF</v>
       </c>
       <c r="G57" t="str">
         <v>yfinance</v>
       </c>
       <c r="H57" t="str">
-        <v>SLV</v>
+        <v>CMBS</v>
       </c>
       <c r="I57" t="str">
         <v>lognormal</v>
@@ -19877,13 +20093,13 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
-        <v>USO</v>
+        <v>EMB</v>
       </c>
       <c r="B58" t="str">
-        <v>Commodities</v>
+        <v>Rates</v>
       </c>
       <c r="C58" t="str">
-        <v>USD</v>
+        <v>EM</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -19892,13 +20108,13 @@
         <v>0</v>
       </c>
       <c r="F58" t="str">
-        <v>United States Oil Fund</v>
+        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
       </c>
       <c r="G58" t="str">
         <v>yfinance</v>
       </c>
       <c r="H58" t="str">
-        <v>USO</v>
+        <v>EMB</v>
       </c>
       <c r="I58" t="str">
         <v>lognormal</v>
@@ -19909,10 +20125,10 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
-        <v>UUP</v>
+        <v>GLD</v>
       </c>
       <c r="B59" t="str">
-        <v>Currencies</v>
+        <v>Commodities</v>
       </c>
       <c r="C59" t="str">
         <v>USD</v>
@@ -19924,13 +20140,13 @@
         <v>0</v>
       </c>
       <c r="F59" t="str">
-        <v>Invesco DB US Dollar Index Bullish Fund</v>
+        <v>SPDR Gold Shares</v>
       </c>
       <c r="G59" t="str">
         <v>yfinance</v>
       </c>
       <c r="H59" t="str">
-        <v>UUP</v>
+        <v>GLD</v>
       </c>
       <c r="I59" t="str">
         <v>lognormal</v>
@@ -19941,10 +20157,10 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
-        <v>DX-Y.NYB</v>
+        <v>SLV</v>
       </c>
       <c r="B60" t="str">
-        <v>Currencies</v>
+        <v>Commodities</v>
       </c>
       <c r="C60" t="str">
         <v>USD</v>
@@ -19956,13 +20172,13 @@
         <v>0</v>
       </c>
       <c r="F60" t="str">
-        <v>U.S. Dollar Index</v>
+        <v>iShares Silver Trust</v>
       </c>
       <c r="G60" t="str">
         <v>yfinance</v>
       </c>
       <c r="H60" t="str">
-        <v>DX-Y.NYB</v>
+        <v>SLV</v>
       </c>
       <c r="I60" t="str">
         <v>lognormal</v>
@@ -19973,13 +20189,13 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
-        <v>FXE</v>
+        <v>USO</v>
       </c>
       <c r="B61" t="str">
-        <v>Currencies</v>
+        <v>Commodities</v>
       </c>
       <c r="C61" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -19988,13 +20204,13 @@
         <v>0</v>
       </c>
       <c r="F61" t="str">
-        <v>Invesco CurrencyShares Euro Trust</v>
+        <v>United States Oil Fund</v>
       </c>
       <c r="G61" t="str">
         <v>yfinance</v>
       </c>
       <c r="H61" t="str">
-        <v>FXE</v>
+        <v>USO</v>
       </c>
       <c r="I61" t="str">
         <v>lognormal</v>
@@ -20005,13 +20221,13 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
-        <v>FXF</v>
+        <v>UUP</v>
       </c>
       <c r="B62" t="str">
         <v>Currencies</v>
       </c>
       <c r="C62" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -20020,13 +20236,13 @@
         <v>0</v>
       </c>
       <c r="F62" t="str">
-        <v>Invesco CurrencyShares Swiss Franc Trust</v>
+        <v>Invesco DB US Dollar Index Bullish Fund</v>
       </c>
       <c r="G62" t="str">
         <v>yfinance</v>
       </c>
       <c r="H62" t="str">
-        <v>FXF</v>
+        <v>UUP</v>
       </c>
       <c r="I62" t="str">
         <v>lognormal</v>
@@ -20037,13 +20253,13 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
-        <v>FXA</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="B63" t="str">
         <v>Currencies</v>
       </c>
       <c r="C63" t="str">
-        <v>Commod</v>
+        <v>USD</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -20052,13 +20268,13 @@
         <v>0</v>
       </c>
       <c r="F63" t="str">
-        <v>Invesco CurrencyShares Australian Dollar Trust</v>
+        <v>U.S. Dollar Index</v>
       </c>
       <c r="G63" t="str">
         <v>yfinance</v>
       </c>
       <c r="H63" t="str">
-        <v>FXA</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="I63" t="str">
         <v>lognormal</v>
@@ -20069,13 +20285,13 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
-        <v>FXB</v>
+        <v>FXE</v>
       </c>
       <c r="B64" t="str">
         <v>Currencies</v>
       </c>
       <c r="C64" t="str">
-        <v>GBP</v>
+        <v>EUR</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -20084,13 +20300,13 @@
         <v>0</v>
       </c>
       <c r="F64" t="str">
-        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
+        <v>Invesco CurrencyShares Euro Trust</v>
       </c>
       <c r="G64" t="str">
         <v>yfinance</v>
       </c>
       <c r="H64" t="str">
-        <v>FXB</v>
+        <v>FXE</v>
       </c>
       <c r="I64" t="str">
         <v>lognormal</v>
@@ -20101,13 +20317,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
-        <v>FXC</v>
+        <v>FXF</v>
       </c>
       <c r="B65" t="str">
         <v>Currencies</v>
       </c>
       <c r="C65" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -20116,13 +20332,13 @@
         <v>0</v>
       </c>
       <c r="F65" t="str">
-        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
+        <v>Invesco CurrencyShares Swiss Franc Trust</v>
       </c>
       <c r="G65" t="str">
         <v>yfinance</v>
       </c>
       <c r="H65" t="str">
-        <v>FXC</v>
+        <v>FXF</v>
       </c>
       <c r="I65" t="str">
         <v>lognormal</v>
@@ -20133,13 +20349,13 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
-        <v>FXY</v>
+        <v>FXA</v>
       </c>
       <c r="B66" t="str">
         <v>Currencies</v>
       </c>
       <c r="C66" t="str">
-        <v>JPY</v>
+        <v>Commod</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -20148,13 +20364,13 @@
         <v>0</v>
       </c>
       <c r="F66" t="str">
-        <v>Invesco CurrencyShares Japanese Yen Trust</v>
+        <v>Invesco CurrencyShares Australian Dollar Trust</v>
       </c>
       <c r="G66" t="str">
         <v>yfinance</v>
       </c>
       <c r="H66" t="str">
-        <v>FXY</v>
+        <v>FXA</v>
       </c>
       <c r="I66" t="str">
         <v>lognormal</v>
@@ -20165,13 +20381,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
-        <v>^VIX</v>
+        <v>FXB</v>
       </c>
       <c r="B67" t="str">
-        <v>Vol</v>
+        <v>Currencies</v>
       </c>
       <c r="C67" t="str">
-        <v>USD</v>
+        <v>GBP</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -20180,27 +20396,27 @@
         <v>0</v>
       </c>
       <c r="F67" t="str">
-        <v>CBOE Volatility Index</v>
+        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
       </c>
       <c r="G67" t="str">
         <v>yfinance</v>
       </c>
       <c r="H67" t="str">
-        <v>^VIX</v>
+        <v>FXB</v>
       </c>
       <c r="I67" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J67">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
-        <v>VXX</v>
+        <v>FXC</v>
       </c>
       <c r="B68" t="str">
-        <v>Vol</v>
+        <v>Currencies</v>
       </c>
       <c r="C68" t="str">
         <v>USD</v>
@@ -20212,30 +20428,30 @@
         <v>0</v>
       </c>
       <c r="F68" t="str">
-        <v>VIX Short-Term Futures ETN</v>
+        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
       </c>
       <c r="G68" t="str">
         <v>yfinance</v>
       </c>
       <c r="H68" t="str">
-        <v>VXX</v>
+        <v>FXC</v>
       </c>
       <c r="I68" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J68">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
-        <v>^VIX3M</v>
+        <v>FXY</v>
       </c>
       <c r="B69" t="str">
-        <v>Vol</v>
+        <v>Currencies</v>
       </c>
       <c r="C69" t="str">
-        <v>USD</v>
+        <v>JPY</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -20244,24 +20460,24 @@
         <v>0</v>
       </c>
       <c r="F69" t="str">
-        <v>CBOE S&amp;P 500 3-Month Volatility</v>
+        <v>Invesco CurrencyShares Japanese Yen Trust</v>
       </c>
       <c r="G69" t="str">
         <v>yfinance</v>
       </c>
       <c r="H69" t="str">
-        <v>^VIX3M</v>
+        <v>FXY</v>
       </c>
       <c r="I69" t="str">
-        <v>normal</v>
+        <v>lognormal</v>
       </c>
       <c r="J69">
-        <v>-0.01</v>
+        <v>1E-4</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
-        <v>^MOVE</v>
+        <v>^VIX</v>
       </c>
       <c r="B70" t="str">
         <v>Vol</v>
@@ -20276,13 +20492,13 @@
         <v>0</v>
       </c>
       <c r="F70" t="str">
-        <v>ICE BofAML MOVE Index</v>
+        <v>CBOE Volatility Index</v>
       </c>
       <c r="G70" t="str">
         <v>yfinance</v>
       </c>
       <c r="H70" t="str">
-        <v>^MOVE</v>
+        <v>^VIX</v>
       </c>
       <c r="I70" t="str">
         <v>normal</v>
@@ -20293,7 +20509,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
-        <v>^OVX</v>
+        <v>VXX</v>
       </c>
       <c r="B71" t="str">
         <v>Vol</v>
@@ -20308,13 +20524,13 @@
         <v>0</v>
       </c>
       <c r="F71" t="str">
-        <v>CBOE Crude Oil Volatility Index</v>
+        <v>VIX Short-Term Futures ETN</v>
       </c>
       <c r="G71" t="str">
         <v>yfinance</v>
       </c>
       <c r="H71" t="str">
-        <v>^OVX</v>
+        <v>VXX</v>
       </c>
       <c r="I71" t="str">
         <v>normal</v>
@@ -20325,7 +20541,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
-        <v>^GVZ</v>
+        <v>^VIX3M</v>
       </c>
       <c r="B72" t="str">
         <v>Vol</v>
@@ -20340,13 +20556,13 @@
         <v>0</v>
       </c>
       <c r="F72" t="str">
-        <v>CBOE Gold Volatility Index</v>
+        <v>CBOE S&amp;P 500 3-Month Volatility</v>
       </c>
       <c r="G72" t="str">
         <v>yfinance</v>
       </c>
       <c r="H72" t="str">
-        <v>^GVZ</v>
+        <v>^VIX3M</v>
       </c>
       <c r="I72" t="str">
         <v>normal</v>
@@ -20357,42 +20573,42 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
-        <v>MWTIX</v>
+        <v>^MOVE</v>
       </c>
       <c r="B73" t="str">
-        <v>Portfolio</v>
+        <v>Vol</v>
       </c>
       <c r="C73" t="str">
         <v>USD</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73" t="str">
-        <v>TCW MetWest Total Return Bd I</v>
+        <v>ICE BofAML MOVE Index</v>
       </c>
       <c r="G73" t="str">
         <v>yfinance</v>
       </c>
       <c r="H73" t="str">
-        <v>MWTIX</v>
+        <v>^MOVE</v>
       </c>
       <c r="I73" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J73">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
-        <v>FCNTX</v>
+        <v>^OVX</v>
       </c>
       <c r="B74" t="str">
-        <v>Portfolio</v>
+        <v>Vol</v>
       </c>
       <c r="C74" t="str">
         <v>USD</v>
@@ -20404,59 +20620,59 @@
         <v>0</v>
       </c>
       <c r="F74" t="str">
-        <v>Fidelity Contrafund</v>
+        <v>CBOE Crude Oil Volatility Index</v>
       </c>
       <c r="G74" t="str">
         <v>yfinance</v>
       </c>
       <c r="H74" t="str">
-        <v>FCNTX</v>
+        <v>^OVX</v>
       </c>
       <c r="I74" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J74">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
-        <v>PRIVATES</v>
+        <v>^GVZ</v>
       </c>
       <c r="B75" t="str">
-        <v>Theme</v>
+        <v>Vol</v>
       </c>
       <c r="C75" t="str">
         <v>USD</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="str">
-        <v>PSP 0.5, XLF -0.5, BKLN 0.5, LQDH -0.5</v>
+        <v>CBOE Gold Volatility Index</v>
       </c>
       <c r="G75" t="str">
-        <v>composite</v>
+        <v>yfinance</v>
       </c>
       <c r="H75" t="str">
-        <v>PRIVATES</v>
+        <v>^GVZ</v>
       </c>
       <c r="I75" t="str">
-        <v>lognormal</v>
+        <v>normal</v>
       </c>
       <c r="J75">
-        <v>1E-4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
-        <v>FED</v>
+        <v>MWTIX</v>
       </c>
       <c r="B76" t="str">
-        <v>Theme</v>
+        <v>Portfolio</v>
       </c>
       <c r="C76" t="str">
         <v>USD</v>
@@ -20465,16 +20681,16 @@
         <v>1</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" t="str">
-        <v>SHY 1, BSV 1</v>
+        <v>TCW MetWest Total Return Bd I</v>
       </c>
       <c r="G76" t="str">
-        <v>composite</v>
+        <v>yfinance</v>
       </c>
       <c r="H76" t="str">
-        <v>FED</v>
+        <v>MWTIX</v>
       </c>
       <c r="I76" t="str">
         <v>lognormal</v>
@@ -20485,28 +20701,28 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
-        <v>AI</v>
+        <v>FCNTX</v>
       </c>
       <c r="B77" t="str">
-        <v>Theme</v>
+        <v>Portfolio</v>
       </c>
       <c r="C77" t="str">
         <v>USD</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" t="str">
-        <v>AIQ 1, QQQ 0.25, IWM -0.25</v>
+        <v>Fidelity Contrafund</v>
       </c>
       <c r="G77" t="str">
-        <v>composite</v>
+        <v>yfinance</v>
       </c>
       <c r="H77" t="str">
-        <v>AI</v>
+        <v>FCNTX</v>
       </c>
       <c r="I77" t="str">
         <v>lognormal</v>
@@ -20517,7 +20733,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
-        <v>GEOPOLITICS</v>
+        <v>PRIVATES</v>
       </c>
       <c r="B78" t="str">
         <v>Theme</v>
@@ -20532,13 +20748,13 @@
         <v>1</v>
       </c>
       <c r="F78" t="str">
-        <v>GLD 0.65, USO 0.3, ^VIX3M -0.15, FEZ -0.05</v>
+        <v>PSP 0.5, XLF -0.5, BKLN 0.5, LQDH -0.5</v>
       </c>
       <c r="G78" t="str">
         <v>composite</v>
       </c>
       <c r="H78" t="str">
-        <v>GEOPOLITICS</v>
+        <v>PRIVATES</v>
       </c>
       <c r="I78" t="str">
         <v>lognormal</v>
@@ -20549,7 +20765,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
-        <v>TRADEWAR</v>
+        <v>FED</v>
       </c>
       <c r="B79" t="str">
         <v>Theme</v>
@@ -20564,13 +20780,13 @@
         <v>1</v>
       </c>
       <c r="F79" t="str">
-        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
+        <v>SHY 1, BSV 1</v>
       </c>
       <c r="G79" t="str">
         <v>composite</v>
       </c>
       <c r="H79" t="str">
-        <v>TRADEWAR</v>
+        <v>FED</v>
       </c>
       <c r="I79" t="str">
         <v>lognormal</v>
@@ -20581,7 +20797,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
-        <v>IRAN</v>
+        <v>AI</v>
       </c>
       <c r="B80" t="str">
         <v>Theme</v>
@@ -20596,13 +20812,13 @@
         <v>1</v>
       </c>
       <c r="F80" t="str">
-        <v>USO 1</v>
+        <v>AIQ 1, QQQ 0.25, IWM -0.25</v>
       </c>
       <c r="G80" t="str">
         <v>composite</v>
       </c>
       <c r="H80" t="str">
-        <v>IRAN</v>
+        <v>AI</v>
       </c>
       <c r="I80" t="str">
         <v>lognormal</v>
@@ -20613,7 +20829,7 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
-        <v>SEMI-SOFT</v>
+        <v>GEOPOLITICS</v>
       </c>
       <c r="B81" t="str">
         <v>Theme</v>
@@ -20628,13 +20844,13 @@
         <v>1</v>
       </c>
       <c r="F81" t="str">
-        <v>SMH 1, IGV -1, QQQ 1</v>
+        <v>GLD 0.65, USO 0.3, ^VIX3M -0.15, FEZ -0.05</v>
       </c>
       <c r="G81" t="str">
         <v>composite</v>
       </c>
       <c r="H81" t="str">
-        <v>SEMI-SOFT</v>
+        <v>GEOPOLITICS</v>
       </c>
       <c r="I81" t="str">
         <v>lognormal</v>
@@ -20645,10 +20861,10 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
-        <v>2s10s</v>
+        <v>TRADEWAR</v>
       </c>
       <c r="B82" t="str">
-        <v>Rates</v>
+        <v>Theme</v>
       </c>
       <c r="C82" t="str">
         <v>USD</v>
@@ -20660,13 +20876,13 @@
         <v>1</v>
       </c>
       <c r="F82" t="str">
-        <v>SHY -3.86, IEF 1</v>
+        <v>GLD 0.21, FXY 0.30, FXF 0.37, ^VIX3M -0.04, XLP 0.15, XLY -0.15</v>
       </c>
       <c r="G82" t="str">
         <v>composite</v>
       </c>
       <c r="H82" t="str">
-        <v>2s10s</v>
+        <v>TRADEWAR</v>
       </c>
       <c r="I82" t="str">
         <v>lognormal</v>
@@ -20677,10 +20893,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="str">
-        <v>XLPXLY</v>
+        <v>IRAN</v>
       </c>
       <c r="B83" t="str">
-        <v>Equities</v>
+        <v>Theme</v>
       </c>
       <c r="C83" t="str">
         <v>USD</v>
@@ -20692,13 +20908,13 @@
         <v>1</v>
       </c>
       <c r="F83" t="str">
-        <v>Staples/Discretionary</v>
+        <v>USO 1</v>
       </c>
       <c r="G83" t="str">
         <v>composite</v>
       </c>
       <c r="H83" t="str">
-        <v>XLPXLY</v>
+        <v>IRAN</v>
       </c>
       <c r="I83" t="str">
         <v>lognormal</v>
@@ -20709,28 +20925,28 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="str">
-        <v>BTC</v>
+        <v>SEMI-SOFT</v>
       </c>
       <c r="B84" t="str">
-        <v>Currencies</v>
+        <v>Theme</v>
       </c>
       <c r="C84" t="str">
         <v>USD</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="str">
-        <v>-</v>
+        <v>SMH 1, IGV -1, QQQ 1</v>
       </c>
       <c r="G84" t="str">
-        <v>lmxl</v>
+        <v>composite</v>
       </c>
       <c r="H84" t="str">
-        <v>BTC1_price</v>
+        <v>SEMI-SOFT</v>
       </c>
       <c r="I84" t="str">
         <v>lognormal</v>
@@ -20741,33 +20957,129 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="str">
-        <v>BTC_vol</v>
+        <v>2s10s</v>
       </c>
       <c r="B85" t="str">
-        <v>Vol</v>
+        <v>Rates</v>
       </c>
       <c r="C85" t="str">
         <v>USD</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="str">
+        <v>SHY -3.86, IEF 1</v>
+      </c>
+      <c r="G85" t="str">
+        <v>composite</v>
+      </c>
+      <c r="H85" t="str">
+        <v>2s10s</v>
+      </c>
+      <c r="I85" t="str">
+        <v>lognormal</v>
+      </c>
+      <c r="J85">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="str">
+        <v>XLPXLY</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Equities</v>
+      </c>
+      <c r="C86" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Staples/Discretionary</v>
+      </c>
+      <c r="G86" t="str">
+        <v>composite</v>
+      </c>
+      <c r="H86" t="str">
+        <v>XLPXLY</v>
+      </c>
+      <c r="I86" t="str">
+        <v>lognormal</v>
+      </c>
+      <c r="J86">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="str">
+        <v>BTC</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Currencies</v>
+      </c>
+      <c r="C87" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87" t="str">
         <v>-</v>
       </c>
-      <c r="G85" t="str">
+      <c r="G87" t="str">
         <v>lmxl</v>
       </c>
-      <c r="H85" t="str">
+      <c r="H87" t="str">
+        <v>BTC1_price</v>
+      </c>
+      <c r="I87" t="str">
+        <v>lognormal</v>
+      </c>
+      <c r="J87">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="str">
+        <v>BTC_vol</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Vol</v>
+      </c>
+      <c r="C88" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88" t="str">
+        <v>-</v>
+      </c>
+      <c r="G88" t="str">
+        <v>lmxl</v>
+      </c>
+      <c r="H88" t="str">
         <v>BTC1_atm</v>
       </c>
-      <c r="I85" t="str">
+      <c r="I88" t="str">
         <v>normal</v>
       </c>
-      <c r="J85">
+      <c r="J88">
         <v>-0.01</v>
       </c>
     </row>
@@ -20985,7 +21297,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1A08F2F-299B-47F7-8064-36693758F4E3}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="44.28515625" bestFit="1" customWidth="1"/>
@@ -21010,11 +21322,11 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A76">_xlfn._xlws.FILTER(data[factor_name],data[Active]*NOT(data[composite]))</f>
+        <f t="array" ref="A2:A79">_xlfn._xlws.FILTER(data[factor_name],data[Active]*NOT(data[composite]))</f>
         <v>SPY</v>
       </c>
       <c r="B2" t="str" cm="1">
-        <f t="array" ref="B2:E76">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:E1,data[#Headers]))</f>
+        <f t="array" ref="B2:E79">INDEX(data[],_xlfn.XMATCH(_xlfn.ANCHORARRAY(A2),data[factor_name]),_xlfn.XMATCH(B1:E1,data[#Headers]))</f>
         <v>Equities</v>
       </c>
       <c r="C2" t="str">
@@ -21454,7 +21766,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <v>FEZ</v>
+        <v>IWN</v>
       </c>
       <c r="B28" t="str">
         <v>Equities</v>
@@ -21466,216 +21778,216 @@
         <v>0</v>
       </c>
       <c r="E28" t="str">
-        <v>Eurostoxx 50</v>
+        <v>Value</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <v>EWU</v>
+        <v>IWO</v>
       </c>
       <c r="B29" t="str">
         <v>Equities</v>
       </c>
       <c r="C29" t="str">
-        <v>GBP</v>
+        <v>USD</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29" t="str">
-        <v>FTSE 100</v>
+        <v>Growth</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <v>DAX</v>
+        <v>MTUM</v>
       </c>
       <c r="B30" t="str">
         <v>Equities</v>
       </c>
       <c r="C30" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30" t="str">
-        <v>DAX (Germany)</v>
+        <v>Momentum</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
-        <v>EWC</v>
+        <v>FEZ</v>
       </c>
       <c r="B31" t="str">
         <v>Equities</v>
       </c>
       <c r="C31" t="str">
-        <v>CAD</v>
+        <v>USD</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31" t="str">
-        <v>MSCI Canada</v>
+        <v>Eurostoxx 50</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
-        <v>EWI</v>
+        <v>EWU</v>
       </c>
       <c r="B32" t="str">
         <v>Equities</v>
       </c>
       <c r="C32" t="str">
-        <v>EUR</v>
+        <v>GBP</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32" t="str">
-        <v>MSCI Italy</v>
+        <v>FTSE 100</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
-        <v>^N225</v>
+        <v>DAX</v>
       </c>
       <c r="B33" t="str">
         <v>Equities</v>
       </c>
       <c r="C33" t="str">
-        <v>JPY</v>
+        <v>EUR</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33" t="str">
-        <v>Nikkei 225</v>
+        <v>DAX (Germany)</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
-        <v>FXI</v>
+        <v>EWC</v>
       </c>
       <c r="B34" t="str">
         <v>Equities</v>
       </c>
       <c r="C34" t="str">
-        <v>CNH</v>
+        <v>CAD</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34" t="str">
-        <v>China Large-Cap</v>
+        <v>MSCI Canada</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
-        <v>ASHR</v>
+        <v>EWI</v>
       </c>
       <c r="B35" t="str">
         <v>Equities</v>
       </c>
       <c r="C35" t="str">
-        <v>CNH</v>
+        <v>EUR</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35" t="str">
-        <v>CSI 300 (China)</v>
+        <v>MSCI Italy</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
-        <v>KWEB</v>
+        <v>^N225</v>
       </c>
       <c r="B36" t="str">
         <v>Equities</v>
       </c>
       <c r="C36" t="str">
-        <v>CNH</v>
+        <v>JPY</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36" t="str">
-        <v>CSI China Internet</v>
+        <v>Nikkei 225</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
-        <v>EEM</v>
+        <v>FXI</v>
       </c>
       <c r="B37" t="str">
         <v>Equities</v>
       </c>
       <c r="C37" t="str">
-        <v>EM</v>
+        <v>CNH</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37" t="str">
-        <v>MSCI EM</v>
+        <v>China Large-Cap</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
-        <v>LQD</v>
+        <v>ASHR</v>
       </c>
       <c r="B38" t="str">
-        <v>Credit</v>
+        <v>Equities</v>
       </c>
       <c r="C38" t="str">
-        <v>USD</v>
+        <v>CNH</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38" t="str">
-        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
+        <v>CSI 300 (China)</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
-        <v>BSV</v>
+        <v>KWEB</v>
       </c>
       <c r="B39" t="str">
-        <v>Credit</v>
+        <v>Equities</v>
       </c>
       <c r="C39" t="str">
-        <v>USD</v>
+        <v>CNH</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39" t="str">
-        <v>Vanguard Short-Term Bond Index Fund ETF</v>
+        <v>CSI China Internet</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
-        <v>HYG</v>
+        <v>EEM</v>
       </c>
       <c r="B40" t="str">
-        <v>Credit</v>
+        <v>Equities</v>
       </c>
       <c r="C40" t="str">
-        <v>USD</v>
+        <v>EM</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40" t="str">
-        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
+        <v>MSCI EM</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
-        <v>LQDH</v>
+        <v>LQD</v>
       </c>
       <c r="B41" t="str">
         <v>Credit</v>
@@ -21684,15 +21996,15 @@
         <v>USD</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="str">
-        <v>Hedged LQD</v>
+        <v>iShares iBoxx $ Investment Grade Corporate Bond ETF</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
-        <v>HYGH</v>
+        <v>BSV</v>
       </c>
       <c r="B42" t="str">
         <v>Credit</v>
@@ -21704,12 +22016,12 @@
         <v>0</v>
       </c>
       <c r="E42" t="str">
-        <v>Hedged HYG</v>
+        <v>Vanguard Short-Term Bond Index Fund ETF</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
-        <v>BKLN</v>
+        <v>HYG</v>
       </c>
       <c r="B43" t="str">
         <v>Credit</v>
@@ -21721,12 +22033,12 @@
         <v>0</v>
       </c>
       <c r="E43" t="str">
-        <v>Bank Loans</v>
+        <v>iShares iBoxx $ High Yield Corporate Bond ETF</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
-        <v>AGG</v>
+        <v>LQDH</v>
       </c>
       <c r="B44" t="str">
         <v>Credit</v>
@@ -21735,18 +22047,18 @@
         <v>USD</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="str">
-        <v>US Agg</v>
+        <v>Hedged LQD</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
-        <v>^TNX</v>
+        <v>HYGH</v>
       </c>
       <c r="B45" t="str">
-        <v>Rates</v>
+        <v>Credit</v>
       </c>
       <c r="C45" t="str">
         <v>USD</v>
@@ -21755,15 +22067,15 @@
         <v>0</v>
       </c>
       <c r="E45" t="str">
-        <v>CBOE Interest Rate 10 Year</v>
+        <v>Hedged HYG</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
-        <v>SHY</v>
+        <v>BKLN</v>
       </c>
       <c r="B46" t="str">
-        <v>Rates</v>
+        <v>Credit</v>
       </c>
       <c r="C46" t="str">
         <v>USD</v>
@@ -21772,15 +22084,15 @@
         <v>0</v>
       </c>
       <c r="E46" t="str">
-        <v>1-3 Year Treasury</v>
+        <v>Bank Loans</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
-        <v>IEI</v>
+        <v>AGG</v>
       </c>
       <c r="B47" t="str">
-        <v>Rates</v>
+        <v>Credit</v>
       </c>
       <c r="C47" t="str">
         <v>USD</v>
@@ -21789,12 +22101,12 @@
         <v>0</v>
       </c>
       <c r="E47" t="str">
-        <v>3-7 Year Treasury</v>
+        <v>US Agg</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
-        <v>IEF</v>
+        <v>^TNX</v>
       </c>
       <c r="B48" t="str">
         <v>Rates</v>
@@ -21803,15 +22115,15 @@
         <v>USD</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="str">
-        <v>7-10 Year Treasury</v>
+        <v>CBOE Interest Rate 10 Year</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
-        <v>TLT</v>
+        <v>SHY</v>
       </c>
       <c r="B49" t="str">
         <v>Rates</v>
@@ -21823,12 +22135,12 @@
         <v>0</v>
       </c>
       <c r="E49" t="str">
-        <v>20+ Year Treasury</v>
+        <v>1-3 Year Treasury</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
-        <v>TIP</v>
+        <v>IEI</v>
       </c>
       <c r="B50" t="str">
         <v>Rates</v>
@@ -21840,12 +22152,12 @@
         <v>0</v>
       </c>
       <c r="E50" t="str">
-        <v>iShares TIPS Bond ETF</v>
+        <v>3-7 Year Treasury</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
-        <v>VTIP</v>
+        <v>IEF</v>
       </c>
       <c r="B51" t="str">
         <v>Rates</v>
@@ -21854,15 +22166,15 @@
         <v>USD</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="str">
-        <v>Short-Term Inflation-Protected Securities ETF</v>
+        <v>7-10 Year Treasury</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
-        <v>AGNC</v>
+        <v>TLT</v>
       </c>
       <c r="B52" t="str">
         <v>Rates</v>
@@ -21874,12 +22186,12 @@
         <v>0</v>
       </c>
       <c r="E52" t="str">
-        <v>AGNC Investment Corp.</v>
+        <v>20+ Year Treasury</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
-        <v>VMBS</v>
+        <v>TIP</v>
       </c>
       <c r="B53" t="str">
         <v>Rates</v>
@@ -21891,12 +22203,12 @@
         <v>0</v>
       </c>
       <c r="E53" t="str">
-        <v>Mortgage-Backed Securities ETF</v>
+        <v>iShares TIPS Bond ETF</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
-        <v>CMBS</v>
+        <v>VTIP</v>
       </c>
       <c r="B54" t="str">
         <v>Rates</v>
@@ -21908,32 +22220,32 @@
         <v>0</v>
       </c>
       <c r="E54" t="str">
-        <v>iShares CMBS ETF</v>
+        <v>Short-Term Inflation-Protected Securities ETF</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
-        <v>EMB</v>
+        <v>AGNC</v>
       </c>
       <c r="B55" t="str">
         <v>Rates</v>
       </c>
       <c r="C55" t="str">
-        <v>EM</v>
+        <v>USD</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55" t="str">
-        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
+        <v>AGNC Investment Corp.</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
-        <v>GLD</v>
+        <v>VMBS</v>
       </c>
       <c r="B56" t="str">
-        <v>Commodities</v>
+        <v>Rates</v>
       </c>
       <c r="C56" t="str">
         <v>USD</v>
@@ -21942,15 +22254,15 @@
         <v>0</v>
       </c>
       <c r="E56" t="str">
-        <v>SPDR Gold Shares</v>
+        <v>Mortgage-Backed Securities ETF</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
-        <v>SLV</v>
+        <v>CMBS</v>
       </c>
       <c r="B57" t="str">
-        <v>Commodities</v>
+        <v>Rates</v>
       </c>
       <c r="C57" t="str">
         <v>USD</v>
@@ -21959,32 +22271,32 @@
         <v>0</v>
       </c>
       <c r="E57" t="str">
-        <v>iShares Silver Trust</v>
+        <v>iShares CMBS ETF</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
-        <v>USO</v>
+        <v>EMB</v>
       </c>
       <c r="B58" t="str">
-        <v>Commodities</v>
+        <v>Rates</v>
       </c>
       <c r="C58" t="str">
-        <v>USD</v>
+        <v>EM</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58" t="str">
-        <v>United States Oil Fund</v>
+        <v>iShares J.P. Morgan USD Emerging Markets Bond ETF</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
-        <v>UUP</v>
+        <v>GLD</v>
       </c>
       <c r="B59" t="str">
-        <v>Currencies</v>
+        <v>Commodities</v>
       </c>
       <c r="C59" t="str">
         <v>USD</v>
@@ -21993,15 +22305,15 @@
         <v>0</v>
       </c>
       <c r="E59" t="str">
-        <v>Invesco DB US Dollar Index Bullish Fund</v>
+        <v>SPDR Gold Shares</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
-        <v>DX-Y.NYB</v>
+        <v>SLV</v>
       </c>
       <c r="B60" t="str">
-        <v>Currencies</v>
+        <v>Commodities</v>
       </c>
       <c r="C60" t="str">
         <v>USD</v>
@@ -22010,134 +22322,134 @@
         <v>0</v>
       </c>
       <c r="E60" t="str">
-        <v>U.S. Dollar Index</v>
+        <v>iShares Silver Trust</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
-        <v>FXE</v>
+        <v>USO</v>
       </c>
       <c r="B61" t="str">
-        <v>Currencies</v>
+        <v>Commodities</v>
       </c>
       <c r="C61" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61" t="str">
-        <v>Invesco CurrencyShares Euro Trust</v>
+        <v>United States Oil Fund</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
-        <v>FXF</v>
+        <v>UUP</v>
       </c>
       <c r="B62" t="str">
         <v>Currencies</v>
       </c>
       <c r="C62" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62" t="str">
-        <v>Invesco CurrencyShares Swiss Franc Trust</v>
+        <v>Invesco DB US Dollar Index Bullish Fund</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
-        <v>FXA</v>
+        <v>DX-Y.NYB</v>
       </c>
       <c r="B63" t="str">
         <v>Currencies</v>
       </c>
       <c r="C63" t="str">
-        <v>Commod</v>
+        <v>USD</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63" t="str">
-        <v>Invesco CurrencyShares Australian Dollar Trust</v>
+        <v>U.S. Dollar Index</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
-        <v>FXB</v>
+        <v>FXE</v>
       </c>
       <c r="B64" t="str">
         <v>Currencies</v>
       </c>
       <c r="C64" t="str">
-        <v>GBP</v>
+        <v>EUR</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64" t="str">
-        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
+        <v>Invesco CurrencyShares Euro Trust</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
-        <v>FXC</v>
+        <v>FXF</v>
       </c>
       <c r="B65" t="str">
         <v>Currencies</v>
       </c>
       <c r="C65" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65" t="str">
-        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
+        <v>Invesco CurrencyShares Swiss Franc Trust</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
-        <v>FXY</v>
+        <v>FXA</v>
       </c>
       <c r="B66" t="str">
         <v>Currencies</v>
       </c>
       <c r="C66" t="str">
-        <v>JPY</v>
+        <v>Commod</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66" t="str">
-        <v>Invesco CurrencyShares Japanese Yen Trust</v>
+        <v>Invesco CurrencyShares Australian Dollar Trust</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
-        <v>^VIX</v>
+        <v>FXB</v>
       </c>
       <c r="B67" t="str">
-        <v>Vol</v>
+        <v>Currencies</v>
       </c>
       <c r="C67" t="str">
-        <v>USD</v>
+        <v>GBP</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67" t="str">
-        <v>CBOE Volatility Index</v>
+        <v>Invesco CurrencyShares British Pound Sterling Trust</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
-        <v>VXX</v>
+        <v>FXC</v>
       </c>
       <c r="B68" t="str">
-        <v>Vol</v>
+        <v>Currencies</v>
       </c>
       <c r="C68" t="str">
         <v>USD</v>
@@ -22146,29 +22458,29 @@
         <v>0</v>
       </c>
       <c r="E68" t="str">
-        <v>VIX Short-Term Futures ETN</v>
+        <v>Invesco CurrencyShares Canadian Dollar Trust</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
-        <v>^VIX3M</v>
+        <v>FXY</v>
       </c>
       <c r="B69" t="str">
-        <v>Vol</v>
+        <v>Currencies</v>
       </c>
       <c r="C69" t="str">
-        <v>USD</v>
+        <v>JPY</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69" t="str">
-        <v>CBOE S&amp;P 500 3-Month Volatility</v>
+        <v>Invesco CurrencyShares Japanese Yen Trust</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
-        <v>^MOVE</v>
+        <v>^VIX</v>
       </c>
       <c r="B70" t="str">
         <v>Vol</v>
@@ -22180,12 +22492,12 @@
         <v>0</v>
       </c>
       <c r="E70" t="str">
-        <v>ICE BofAML MOVE Index</v>
+        <v>CBOE Volatility Index</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
-        <v>^OVX</v>
+        <v>VXX</v>
       </c>
       <c r="B71" t="str">
         <v>Vol</v>
@@ -22197,12 +22509,12 @@
         <v>0</v>
       </c>
       <c r="E71" t="str">
-        <v>CBOE Crude Oil Volatility Index</v>
+        <v>VIX Short-Term Futures ETN</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
-        <v>^GVZ</v>
+        <v>^VIX3M</v>
       </c>
       <c r="B72" t="str">
         <v>Vol</v>
@@ -22214,32 +22526,32 @@
         <v>0</v>
       </c>
       <c r="E72" t="str">
-        <v>CBOE Gold Volatility Index</v>
+        <v>CBOE S&amp;P 500 3-Month Volatility</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
-        <v>MWTIX</v>
+        <v>^MOVE</v>
       </c>
       <c r="B73" t="str">
-        <v>Portfolio</v>
+        <v>Vol</v>
       </c>
       <c r="C73" t="str">
         <v>USD</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" t="str">
-        <v>TCW MetWest Total Return Bd I</v>
+        <v>ICE BofAML MOVE Index</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
-        <v>FCNTX</v>
+        <v>^OVX</v>
       </c>
       <c r="B74" t="str">
-        <v>Portfolio</v>
+        <v>Vol</v>
       </c>
       <c r="C74" t="str">
         <v>USD</v>
@@ -22248,15 +22560,15 @@
         <v>0</v>
       </c>
       <c r="E74" t="str">
-        <v>Fidelity Contrafund</v>
+        <v>CBOE Crude Oil Volatility Index</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
-        <v>BTC</v>
+        <v>^GVZ</v>
       </c>
       <c r="B75" t="str">
-        <v>Currencies</v>
+        <v>Vol</v>
       </c>
       <c r="C75" t="str">
         <v>USD</v>
@@ -22265,23 +22577,74 @@
         <v>0</v>
       </c>
       <c r="E75" t="str">
-        <v>-</v>
+        <v>CBOE Gold Volatility Index</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
-        <v>BTC_vol</v>
+        <v>MWTIX</v>
       </c>
       <c r="B76" t="str">
-        <v>Vol</v>
+        <v>Portfolio</v>
       </c>
       <c r="C76" t="str">
         <v>USD</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="str">
+        <v>TCW MetWest Total Return Bd I</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="str">
+        <v>FCNTX</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Portfolio</v>
+      </c>
+      <c r="C77" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Fidelity Contrafund</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="str">
+        <v>BTC</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Currencies</v>
+      </c>
+      <c r="C78" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78" t="str">
+        <v>-</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="str">
+        <v>BTC_vol</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Vol</v>
+      </c>
+      <c r="C79" t="str">
+        <v>USD</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79" t="str">
         <v>-</v>
       </c>
     </row>
@@ -27993,7 +28356,7 @@
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <f ca="1">TODAY()-1</f>
-        <v>46186</v>
+        <v>46204</v>
       </c>
       <c r="B2">
         <v>0.20547945205479451</v>
